--- a/research/traditional_assets/database/data/switzerland/switzerland_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_oil_gas_production_and_exploration.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nyse_rig" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,34 +590,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0126</v>
+        <v>0.0171</v>
       </c>
       <c r="G2">
-        <v>0.3129403040415276</v>
+        <v>0.2209477814669484</v>
       </c>
       <c r="H2">
-        <v>0.3129403040415276</v>
+        <v>0.2209477814669484</v>
       </c>
       <c r="I2">
-        <v>-0.02720756797648852</v>
+        <v>0.05786364534081854</v>
       </c>
       <c r="J2">
-        <v>-0.02720756797648852</v>
+        <v>0.05786364534081854</v>
       </c>
       <c r="K2">
-        <v>-1200</v>
+        <v>-623</v>
       </c>
       <c r="L2">
-        <v>-0.4449388209121246</v>
+        <v>-0.1880470872321159</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0001946547797481167</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.0008333333333333334</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +629,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>1</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>594</v>
+        <v>435</v>
       </c>
       <c r="V2">
-        <v>0.1156249391703813</v>
+        <v>0.1324483147093749</v>
       </c>
       <c r="W2">
-        <v>-0.1068566340160285</v>
+        <v>-0.06038577105747795</v>
       </c>
       <c r="X2">
-        <v>0.1380424614375926</v>
+        <v>0.164047143098262</v>
       </c>
       <c r="Y2">
-        <v>-0.2448990954536211</v>
+        <v>-0.2244329141557399</v>
       </c>
       <c r="Z2">
-        <v>0.1535099472787216</v>
+        <v>0.1924429828777939</v>
       </c>
       <c r="AA2">
-        <v>-0.004176632325652988</v>
+        <v>0.01113545250956988</v>
       </c>
       <c r="AB2">
-        <v>0.1106606583387638</v>
+        <v>0.112803408726836</v>
       </c>
       <c r="AC2">
-        <v>-0.1148372906644168</v>
+        <v>-0.1016679562172662</v>
       </c>
       <c r="AD2">
-        <v>7386</v>
+        <v>6960</v>
       </c>
       <c r="AE2">
-        <v>91.89405416294773</v>
+        <v>106.4887149293408</v>
       </c>
       <c r="AF2">
-        <v>7477.894054162948</v>
+        <v>7066.488714929341</v>
       </c>
       <c r="AG2">
-        <v>6883.894054162948</v>
+        <v>6631.488714929341</v>
       </c>
       <c r="AH2">
-        <v>0.5927688485850348</v>
+        <v>0.6827005081010949</v>
       </c>
       <c r="AI2">
-        <v>0.4202033363091225</v>
+        <v>0.4085977233214906</v>
       </c>
       <c r="AJ2">
-        <v>0.5726464461971688</v>
+        <v>0.6687807602177812</v>
       </c>
       <c r="AK2">
-        <v>0.4001823306484677</v>
+        <v>0.3933386609201887</v>
       </c>
       <c r="AL2">
-        <v>912</v>
+        <v>268</v>
       </c>
       <c r="AM2">
-        <v>858</v>
+        <v>218</v>
       </c>
       <c r="AN2">
-        <v>9.782781456953643</v>
+        <v>7.197518097207859</v>
       </c>
       <c r="AO2">
-        <v>-0.07456140350877193</v>
+        <v>0.7238805970149254</v>
       </c>
       <c r="AP2">
-        <v>9.117740469089998</v>
+        <v>6.857795982346785</v>
       </c>
       <c r="AQ2">
-        <v>-0.07925407925407925</v>
+        <v>0.8899082568807339</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +718,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0126</v>
+        <v>0.0171</v>
       </c>
       <c r="G3">
-        <v>0.3129403040415276</v>
+        <v>0.2209477814669484</v>
       </c>
       <c r="H3">
-        <v>0.3129403040415276</v>
+        <v>0.2209477814669484</v>
       </c>
       <c r="I3">
-        <v>-0.02720756797648852</v>
+        <v>0.05786364534081854</v>
       </c>
       <c r="J3">
-        <v>-0.02720756797648852</v>
+        <v>0.05786364534081854</v>
       </c>
       <c r="K3">
-        <v>-1200</v>
+        <v>-623</v>
       </c>
       <c r="L3">
-        <v>-0.4449388209121246</v>
+        <v>-0.1880470872321159</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.0001946547797481167</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.0008333333333333334</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +757,8848 @@
         <v>0</v>
       </c>
       <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>435</v>
+      </c>
+      <c r="V3">
+        <v>0.1324483147093749</v>
+      </c>
+      <c r="W3">
+        <v>-0.06038577105747795</v>
+      </c>
+      <c r="X3">
+        <v>0.164047143098262</v>
+      </c>
+      <c r="Y3">
+        <v>-0.2244329141557399</v>
+      </c>
+      <c r="Z3">
+        <v>0.1924429828777939</v>
+      </c>
+      <c r="AA3">
+        <v>0.01113545250956988</v>
+      </c>
+      <c r="AB3">
+        <v>0.112803408726836</v>
+      </c>
+      <c r="AC3">
+        <v>-0.1016679562172662</v>
+      </c>
+      <c r="AD3">
+        <v>6960</v>
+      </c>
+      <c r="AE3">
+        <v>106.4887149293408</v>
+      </c>
+      <c r="AF3">
+        <v>7066.488714929341</v>
+      </c>
+      <c r="AG3">
+        <v>6631.488714929341</v>
+      </c>
+      <c r="AH3">
+        <v>0.6827005081010949</v>
+      </c>
+      <c r="AI3">
+        <v>0.4085977233214906</v>
+      </c>
+      <c r="AJ3">
+        <v>0.6687807602177812</v>
+      </c>
+      <c r="AK3">
+        <v>0.3933386609201887</v>
+      </c>
+      <c r="AL3">
+        <v>268</v>
+      </c>
+      <c r="AM3">
+        <v>218</v>
+      </c>
+      <c r="AN3">
+        <v>7.197518097207859</v>
+      </c>
+      <c r="AO3">
+        <v>0.7238805970149254</v>
+      </c>
+      <c r="AP3">
+        <v>6.857795982346785</v>
+      </c>
+      <c r="AQ3">
+        <v>0.8899082568807339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Transocean Ltd. (NYSE:RIG)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NYSE:RIG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oil/Gas (Production and Exploration)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.835820895522388</v>
+      </c>
+      <c r="F2">
+        <v>9.934037791179881</v>
+      </c>
+      <c r="G2">
+        <v>7.30764086342228</v>
+      </c>
+      <c r="H2">
+        <v>1.71264342749606</v>
+      </c>
+      <c r="I2">
+        <v>0.6827005081010949</v>
+      </c>
+      <c r="J2">
+        <v>0.16</v>
+      </c>
+      <c r="K2">
+        <v>3284.3</v>
+      </c>
+      <c r="L2">
+        <v>15148.588217668</v>
+      </c>
+      <c r="M2">
+        <v>9915.78871492934</v>
+      </c>
+      <c r="N2">
+        <v>16369.7144120567</v>
+      </c>
+      <c r="O2">
+        <v>7066.48871492934</v>
+      </c>
+      <c r="P2">
+        <v>1656.12619438869</v>
+      </c>
+      <c r="Q2">
+        <v>0.112803408726836</v>
+      </c>
+      <c r="R2">
+        <v>0.08638663623514529</v>
+      </c>
+      <c r="S2">
+        <v>0.0889868</v>
+      </c>
+      <c r="T2">
+        <v>0.0450912</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.164047143098262</v>
+      </c>
+      <c r="X2">
+        <v>0.0942524336132682</v>
+      </c>
+      <c r="Y2">
+        <v>2.72912518934564</v>
+      </c>
+      <c r="Z2">
+        <v>1.11827443432763</v>
+      </c>
+      <c r="AA2">
+        <v>6960.000000000001</v>
+      </c>
+      <c r="AB2">
+        <v>0.1042</v>
+      </c>
+      <c r="AC2">
+        <v>0.835820895522388</v>
+      </c>
+      <c r="AD2">
+        <v>7066.488714929342</v>
+      </c>
+      <c r="AE2">
+        <v>268</v>
+      </c>
+      <c r="AF2">
+        <v>743</v>
+      </c>
+      <c r="AG2">
+        <v>967</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0458</v>
+      </c>
+      <c r="AJ2">
+        <v>3284.3</v>
+      </c>
+      <c r="AK2">
+        <v>0.043327855959079</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.146</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>444.9999999999999</v>
+      </c>
+      <c r="AR2">
+        <v>268</v>
+      </c>
+      <c r="AS2">
+        <v>6960</v>
+      </c>
+      <c r="AT2">
+        <v>435</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
         <v>1</v>
       </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08747353808480632</v>
+      </c>
+      <c r="C2">
+        <v>16377.77027218834</v>
+      </c>
+      <c r="D2">
+        <v>15942.77027218834</v>
+      </c>
+      <c r="E2">
+        <v>-7066.488714929342</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>435</v>
+      </c>
+      <c r="H2">
+        <v>3284.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K2">
+        <v>743</v>
+      </c>
+      <c r="L2">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="O2">
+        <v>126.8253333333333</v>
+      </c>
+      <c r="P2">
+        <v>741.8413333333334</v>
+      </c>
+      <c r="Q2">
+        <v>1484.841333333333</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08747353808480632</v>
+      </c>
+      <c r="T2">
+        <v>0.9618186075065632</v>
+      </c>
+      <c r="U2">
+        <v>0.0517</v>
+      </c>
+      <c r="V2">
+        <v>0.146</v>
+      </c>
+      <c r="W2">
+        <v>0.0441518</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08739621271920249</v>
+      </c>
+      <c r="C3">
+        <v>16303.89923078644</v>
+      </c>
+      <c r="D3">
+        <v>15972.40711793574</v>
+      </c>
+      <c r="E3">
+        <v>-6962.980827780048</v>
+      </c>
+      <c r="F3">
+        <v>103.5078871492934</v>
+      </c>
+      <c r="G3">
+        <v>435</v>
+      </c>
+      <c r="H3">
+        <v>3284.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K3">
+        <v>743</v>
+      </c>
+      <c r="L3">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M3">
+        <v>5.35135776561847</v>
+      </c>
+      <c r="N3">
+        <v>863.3153089010483</v>
+      </c>
+      <c r="O3">
+        <v>126.044035099553</v>
+      </c>
+      <c r="P3">
+        <v>737.2712738014952</v>
+      </c>
+      <c r="Q3">
+        <v>1480.271273801495</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08783302496889141</v>
+      </c>
       <c r="T3">
+        <v>0.970115507413741</v>
+      </c>
+      <c r="U3">
+        <v>0.0517</v>
+      </c>
+      <c r="V3">
+        <v>0.146</v>
+      </c>
+      <c r="W3">
+        <v>0.0441518</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>162.3264047580031</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08731888735359868</v>
+      </c>
+      <c r="C4">
+        <v>16230.13858154959</v>
+      </c>
+      <c r="D4">
+        <v>16002.15435584818</v>
+      </c>
+      <c r="E4">
+        <v>-6859.472940630755</v>
+      </c>
+      <c r="F4">
+        <v>207.0157742985868</v>
+      </c>
+      <c r="G4">
+        <v>435</v>
+      </c>
+      <c r="H4">
+        <v>3284.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K4">
+        <v>743</v>
+      </c>
+      <c r="L4">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M4">
+        <v>10.70271553123694</v>
+      </c>
+      <c r="N4">
+        <v>857.9639511354299</v>
+      </c>
+      <c r="O4">
+        <v>125.2627368657728</v>
+      </c>
+      <c r="P4">
+        <v>732.7012142696572</v>
+      </c>
+      <c r="Q4">
+        <v>1475.701214269657</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08819984831999865</v>
+      </c>
+      <c r="T4">
+        <v>0.9785817318088204</v>
+      </c>
+      <c r="U4">
+        <v>0.0517</v>
+      </c>
+      <c r="V4">
+        <v>0.146</v>
+      </c>
+      <c r="W4">
+        <v>0.0441518</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>81.16320237900155</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08724156198799485</v>
+      </c>
+      <c r="C5">
+        <v>16156.48894241646</v>
+      </c>
+      <c r="D5">
+        <v>16032.01260386434</v>
+      </c>
+      <c r="E5">
+        <v>-6755.965053481462</v>
+      </c>
+      <c r="F5">
+        <v>310.5236614478803</v>
+      </c>
+      <c r="G5">
+        <v>435</v>
+      </c>
+      <c r="H5">
+        <v>3284.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K5">
+        <v>743</v>
+      </c>
+      <c r="L5">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M5">
+        <v>16.05407329685541</v>
+      </c>
+      <c r="N5">
+        <v>852.6125933698113</v>
+      </c>
+      <c r="O5">
+        <v>124.4814386319924</v>
+      </c>
+      <c r="P5">
+        <v>728.1311547378189</v>
+      </c>
+      <c r="Q5">
+        <v>1471.131154737819</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08857423503916995</v>
+      </c>
+      <c r="T5">
+        <v>0.9872225175316334</v>
+      </c>
+      <c r="U5">
+        <v>0.0517</v>
+      </c>
+      <c r="V5">
+        <v>0.146</v>
+      </c>
+      <c r="W5">
+        <v>0.0441518</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>54.10880158600102</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08716423662239103</v>
+      </c>
+      <c r="C6">
+        <v>16082.95093594636</v>
+      </c>
+      <c r="D6">
+        <v>16061.98248454353</v>
+      </c>
+      <c r="E6">
+        <v>-6652.457166332168</v>
+      </c>
+      <c r="F6">
+        <v>414.0315485971737</v>
+      </c>
+      <c r="G6">
+        <v>435</v>
+      </c>
+      <c r="H6">
+        <v>3284.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K6">
+        <v>743</v>
+      </c>
+      <c r="L6">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M6">
+        <v>21.40543106247388</v>
+      </c>
+      <c r="N6">
+        <v>847.2612356041928</v>
+      </c>
+      <c r="O6">
+        <v>123.7001403982121</v>
+      </c>
+      <c r="P6">
+        <v>723.5610952059807</v>
+      </c>
+      <c r="Q6">
+        <v>1466.561095205981</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08895642148165733</v>
+      </c>
+      <c r="T6">
+        <v>0.9960433196236718</v>
+      </c>
+      <c r="U6">
+        <v>0.0517</v>
+      </c>
+      <c r="V6">
+        <v>0.146</v>
+      </c>
+      <c r="W6">
+        <v>0.0441518</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>40.58160118950077</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08708691125678722</v>
+      </c>
+      <c r="C7">
+        <v>16009.5251893625</v>
+      </c>
+      <c r="D7">
+        <v>16092.06462510897</v>
+      </c>
+      <c r="E7">
+        <v>-6548.949279182874</v>
+      </c>
+      <c r="F7">
+        <v>517.5394357464671</v>
+      </c>
+      <c r="G7">
+        <v>435</v>
+      </c>
+      <c r="H7">
+        <v>3284.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K7">
+        <v>743</v>
+      </c>
+      <c r="L7">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M7">
+        <v>26.75678882809235</v>
+      </c>
+      <c r="N7">
+        <v>841.9098778385744</v>
+      </c>
+      <c r="O7">
+        <v>122.9188421644319</v>
+      </c>
+      <c r="P7">
+        <v>718.9910356741425</v>
+      </c>
+      <c r="Q7">
+        <v>1461.991035674142</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08934665395451287</v>
+      </c>
+      <c r="T7">
+        <v>1.005049822812385</v>
+      </c>
+      <c r="U7">
+        <v>0.0517</v>
+      </c>
+      <c r="V7">
+        <v>0.146</v>
+      </c>
+      <c r="W7">
+        <v>0.0441518</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>32.46528095160062</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08700958589118341</v>
+      </c>
+      <c r="C8">
+        <v>15936.21233459578</v>
+      </c>
+      <c r="D8">
+        <v>16122.25965749154</v>
+      </c>
+      <c r="E8">
+        <v>-6445.441392033581</v>
+      </c>
+      <c r="F8">
+        <v>621.0473228957605</v>
+      </c>
+      <c r="G8">
+        <v>435</v>
+      </c>
+      <c r="H8">
+        <v>3284.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K8">
+        <v>743</v>
+      </c>
+      <c r="L8">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M8">
+        <v>32.10814659371082</v>
+      </c>
+      <c r="N8">
+        <v>836.558520072956</v>
+      </c>
+      <c r="O8">
+        <v>122.1375439306516</v>
+      </c>
+      <c r="P8">
+        <v>714.4209761423044</v>
+      </c>
+      <c r="Q8">
+        <v>1457.420976142304</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.0897451892459398</v>
+      </c>
+      <c r="T8">
+        <v>1.014247953728517</v>
+      </c>
+      <c r="U8">
+        <v>0.0517</v>
+      </c>
+      <c r="V8">
+        <v>0.146</v>
+      </c>
+      <c r="W8">
+        <v>0.0441518</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>27.05440079300051</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08693226052557959</v>
+      </c>
+      <c r="C9">
+        <v>15863.01300832901</v>
+      </c>
+      <c r="D9">
+        <v>16152.56821837406</v>
+      </c>
+      <c r="E9">
+        <v>-6341.933504884288</v>
+      </c>
+      <c r="F9">
+        <v>724.555210045054</v>
+      </c>
+      <c r="G9">
+        <v>435</v>
+      </c>
+      <c r="H9">
+        <v>3284.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K9">
+        <v>743</v>
+      </c>
+      <c r="L9">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M9">
+        <v>37.45950435932929</v>
+      </c>
+      <c r="N9">
+        <v>831.2071623073374</v>
+      </c>
+      <c r="O9">
+        <v>121.3562456968713</v>
+      </c>
+      <c r="P9">
+        <v>709.8509166104661</v>
+      </c>
+      <c r="Q9">
+        <v>1452.850916610466</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09015229518879526</v>
+      </c>
+      <c r="T9">
+        <v>1.023643893911663</v>
+      </c>
+      <c r="U9">
+        <v>0.0517</v>
+      </c>
+      <c r="V9">
+        <v>0.146</v>
+      </c>
+      <c r="W9">
+        <v>0.0441518</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>23.18948639400044</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08685493515997578</v>
+      </c>
+      <c r="C10">
+        <v>15789.92785204166</v>
+      </c>
+      <c r="D10">
+        <v>16182.990949236</v>
+      </c>
+      <c r="E10">
+        <v>-6238.425617734994</v>
+      </c>
+      <c r="F10">
+        <v>828.0630971943474</v>
+      </c>
+      <c r="G10">
+        <v>435</v>
+      </c>
+      <c r="H10">
+        <v>3284.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K10">
+        <v>743</v>
+      </c>
+      <c r="L10">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M10">
+        <v>42.81086212494776</v>
+      </c>
+      <c r="N10">
+        <v>825.855804541719</v>
+      </c>
+      <c r="O10">
+        <v>120.574947463091</v>
+      </c>
+      <c r="P10">
+        <v>705.2808570786279</v>
+      </c>
+      <c r="Q10">
+        <v>1448.280857078628</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09056825126084322</v>
+      </c>
+      <c r="T10">
+        <v>1.033244093664007</v>
+      </c>
+      <c r="U10">
+        <v>0.0517</v>
+      </c>
+      <c r="V10">
+        <v>0.146</v>
+      </c>
+      <c r="W10">
+        <v>0.0441518</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>20.29080059475038</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08677760979437195</v>
+      </c>
+      <c r="C11">
+        <v>15716.95751205513</v>
+      </c>
+      <c r="D11">
+        <v>16213.52849639877</v>
+      </c>
+      <c r="E11">
+        <v>-6134.917730585701</v>
+      </c>
+      <c r="F11">
+        <v>931.5709843436407</v>
+      </c>
+      <c r="G11">
+        <v>435</v>
+      </c>
+      <c r="H11">
+        <v>3284.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K11">
+        <v>743</v>
+      </c>
+      <c r="L11">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M11">
+        <v>48.16221989056623</v>
+      </c>
+      <c r="N11">
+        <v>820.5044467761005</v>
+      </c>
+      <c r="O11">
+        <v>119.7936492293107</v>
+      </c>
+      <c r="P11">
+        <v>700.7107975467899</v>
+      </c>
+      <c r="Q11">
+        <v>1443.71079754679</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09099334922458456</v>
+      </c>
+      <c r="T11">
+        <v>1.043055286817502</v>
+      </c>
+      <c r="U11">
+        <v>0.0517</v>
+      </c>
+      <c r="V11">
+        <v>0.146</v>
+      </c>
+      <c r="W11">
+        <v>0.0441518</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>18.03626719533368</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08670028442876813</v>
+      </c>
+      <c r="C12">
+        <v>15644.10263957852</v>
+      </c>
+      <c r="D12">
+        <v>16244.18151107145</v>
+      </c>
+      <c r="E12">
+        <v>-6031.409843436408</v>
+      </c>
+      <c r="F12">
+        <v>1035.078871492934</v>
+      </c>
+      <c r="G12">
+        <v>435</v>
+      </c>
+      <c r="H12">
+        <v>3284.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K12">
+        <v>743</v>
+      </c>
+      <c r="L12">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M12">
+        <v>53.5135776561847</v>
+      </c>
+      <c r="N12">
+        <v>815.1530890104821</v>
+      </c>
+      <c r="O12">
+        <v>119.0123509955304</v>
+      </c>
+      <c r="P12">
+        <v>696.1407380149517</v>
+      </c>
+      <c r="Q12">
+        <v>1439.140738014952</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09142789380974237</v>
+      </c>
+      <c r="T12">
+        <v>1.053084506485519</v>
+      </c>
+      <c r="U12">
+        <v>0.0517</v>
+      </c>
+      <c r="V12">
+        <v>0.146</v>
+      </c>
+      <c r="W12">
+        <v>0.0441518</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>16.23264047580031</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08662295906316433</v>
+      </c>
+      <c r="C13">
+        <v>15571.3638907549</v>
+      </c>
+      <c r="D13">
+        <v>16274.95064939713</v>
+      </c>
+      <c r="E13">
+        <v>-5927.901956287114</v>
+      </c>
+      <c r="F13">
+        <v>1138.586758642228</v>
+      </c>
+      <c r="G13">
+        <v>435</v>
+      </c>
+      <c r="H13">
+        <v>3284.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K13">
+        <v>743</v>
+      </c>
+      <c r="L13">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M13">
+        <v>58.86493542180317</v>
+      </c>
+      <c r="N13">
+        <v>809.8017312448636</v>
+      </c>
+      <c r="O13">
+        <v>118.2310527617501</v>
+      </c>
+      <c r="P13">
+        <v>691.5706784831135</v>
+      </c>
+      <c r="Q13">
+        <v>1434.570678483114</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09187220344175767</v>
+      </c>
+      <c r="T13">
+        <v>1.063339101876413</v>
+      </c>
+      <c r="U13">
+        <v>0.0517</v>
+      </c>
+      <c r="V13">
+        <v>0.146</v>
+      </c>
+      <c r="W13">
+        <v>0.0441518</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>14.75694588709119</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08654563369756051</v>
+      </c>
+      <c r="C14">
+        <v>15498.7419267082</v>
+      </c>
+      <c r="D14">
+        <v>16305.83657249972</v>
+      </c>
+      <c r="E14">
+        <v>-5824.394069137821</v>
+      </c>
+      <c r="F14">
+        <v>1242.094645791521</v>
+      </c>
+      <c r="G14">
+        <v>435</v>
+      </c>
+      <c r="H14">
+        <v>3284.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K14">
+        <v>743</v>
+      </c>
+      <c r="L14">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M14">
+        <v>64.21629318742164</v>
+      </c>
+      <c r="N14">
+        <v>804.4503734792451</v>
+      </c>
+      <c r="O14">
+        <v>117.4497545279698</v>
+      </c>
+      <c r="P14">
+        <v>687.0006189512753</v>
+      </c>
+      <c r="Q14">
+        <v>1430.000618951275</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09232661101995512</v>
+      </c>
+      <c r="T14">
+        <v>1.073826756253464</v>
+      </c>
+      <c r="U14">
+        <v>0.0517</v>
+      </c>
+      <c r="V14">
+        <v>0.146</v>
+      </c>
+      <c r="W14">
+        <v>0.0441518</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>13.52720039650026</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08659043033195669</v>
+      </c>
+      <c r="C15">
+        <v>15377.32673646065</v>
+      </c>
+      <c r="D15">
+        <v>16287.92926940147</v>
+      </c>
+      <c r="E15">
+        <v>-5720.886181988528</v>
+      </c>
+      <c r="F15">
+        <v>1345.602532940814</v>
+      </c>
+      <c r="G15">
+        <v>435</v>
+      </c>
+      <c r="H15">
+        <v>3284.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K15">
+        <v>743</v>
+      </c>
+      <c r="L15">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M15">
+        <v>71.047813739275</v>
+      </c>
+      <c r="N15">
+        <v>797.6188529273918</v>
+      </c>
+      <c r="O15">
+        <v>116.4523525273992</v>
+      </c>
+      <c r="P15">
+        <v>681.1665003999926</v>
+      </c>
+      <c r="Q15">
+        <v>1424.166500399993</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09279146474937551</v>
+      </c>
+      <c r="T15">
+        <v>1.084555506133435</v>
+      </c>
+      <c r="U15">
+        <v>0.0528</v>
+      </c>
+      <c r="V15">
+        <v>0.146</v>
+      </c>
+      <c r="W15">
+        <v>0.0450912</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>12.22650805068293</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08652249896635288</v>
+      </c>
+      <c r="C16">
+        <v>15300.98961009996</v>
+      </c>
+      <c r="D16">
+        <v>16315.10003019007</v>
+      </c>
+      <c r="E16">
+        <v>-5617.378294839234</v>
+      </c>
+      <c r="F16">
+        <v>1449.110420090108</v>
+      </c>
+      <c r="G16">
+        <v>435</v>
+      </c>
+      <c r="H16">
+        <v>3284.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K16">
+        <v>743</v>
+      </c>
+      <c r="L16">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M16">
+        <v>76.5130301807577</v>
+      </c>
+      <c r="N16">
+        <v>792.153636485909</v>
+      </c>
+      <c r="O16">
+        <v>115.6544309269427</v>
+      </c>
+      <c r="P16">
+        <v>676.4992055589663</v>
+      </c>
+      <c r="Q16">
+        <v>1419.499205558966</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09326712903064288</v>
+      </c>
+      <c r="T16">
+        <v>1.095533761824569</v>
+      </c>
+      <c r="U16">
+        <v>0.0528</v>
+      </c>
+      <c r="V16">
+        <v>0.146</v>
+      </c>
+      <c r="W16">
+        <v>0.0450912</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>11.35318604706272</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08645456760074906</v>
+      </c>
+      <c r="C17">
+        <v>15224.7432851913</v>
+      </c>
+      <c r="D17">
+        <v>16342.3615924307</v>
+      </c>
+      <c r="E17">
+        <v>-5513.87040768994</v>
+      </c>
+      <c r="F17">
+        <v>1552.618307239401</v>
+      </c>
+      <c r="G17">
+        <v>435</v>
+      </c>
+      <c r="H17">
+        <v>3284.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K17">
+        <v>743</v>
+      </c>
+      <c r="L17">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M17">
+        <v>81.97824662224039</v>
+      </c>
+      <c r="N17">
+        <v>786.6884200444264</v>
+      </c>
+      <c r="O17">
+        <v>114.8565093264862</v>
+      </c>
+      <c r="P17">
+        <v>671.8319107179401</v>
+      </c>
+      <c r="Q17">
+        <v>1414.83191071794</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09375398541264596</v>
+      </c>
+      <c r="T17">
+        <v>1.106770329414317</v>
+      </c>
+      <c r="U17">
+        <v>0.0528</v>
+      </c>
+      <c r="V17">
+        <v>0.146</v>
+      </c>
+      <c r="W17">
+        <v>0.0450912</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>10.59630697725854</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08638663623514525</v>
+      </c>
+      <c r="C18">
+        <v>15148.58821766798</v>
+      </c>
+      <c r="D18">
+        <v>16369.71441205667</v>
+      </c>
+      <c r="E18">
+        <v>-5410.362520540647</v>
+      </c>
+      <c r="F18">
+        <v>1656.126194388695</v>
+      </c>
+      <c r="G18">
+        <v>435</v>
+      </c>
+      <c r="H18">
+        <v>3284.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K18">
+        <v>743</v>
+      </c>
+      <c r="L18">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M18">
+        <v>87.44346306372309</v>
+      </c>
+      <c r="N18">
+        <v>781.2232036029436</v>
+      </c>
+      <c r="O18">
+        <v>114.0585877260298</v>
+      </c>
+      <c r="P18">
+        <v>667.1646158769139</v>
+      </c>
+      <c r="Q18">
+        <v>1410.164615876914</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09425243361326816</v>
+      </c>
+      <c r="T18">
+        <v>1.118274434327631</v>
+      </c>
+      <c r="U18">
+        <v>0.0528</v>
+      </c>
+      <c r="V18">
+        <v>0.146</v>
+      </c>
+      <c r="W18">
+        <v>0.0450912</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>9.934037791179875</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08663810086954141</v>
+      </c>
+      <c r="C19">
+        <v>14944.28219930913</v>
+      </c>
+      <c r="D19">
+        <v>16268.91628084712</v>
+      </c>
+      <c r="E19">
+        <v>-5306.854633391354</v>
+      </c>
+      <c r="F19">
+        <v>1759.634081537988</v>
+      </c>
+      <c r="G19">
+        <v>435</v>
+      </c>
+      <c r="H19">
+        <v>3284.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K19">
+        <v>743</v>
+      </c>
+      <c r="L19">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M19">
+        <v>96.77987448458936</v>
+      </c>
+      <c r="N19">
+        <v>771.8867921820774</v>
+      </c>
+      <c r="O19">
+        <v>112.6954716585833</v>
+      </c>
+      <c r="P19">
+        <v>659.1913205234941</v>
+      </c>
+      <c r="Q19">
+        <v>1402.191320523494</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09476289261390532</v>
+      </c>
+      <c r="T19">
+        <v>1.130055746588253</v>
+      </c>
+      <c r="U19">
+        <v>0.055</v>
+      </c>
+      <c r="V19">
+        <v>0.146</v>
+      </c>
+      <c r="W19">
+        <v>0.04697</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>8.975695321913111</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08658895750393761</v>
+      </c>
+      <c r="C20">
+        <v>14860.37543338707</v>
+      </c>
+      <c r="D20">
+        <v>16288.51740207435</v>
+      </c>
+      <c r="E20">
+        <v>-5203.34674624206</v>
+      </c>
+      <c r="F20">
+        <v>1863.141968687281</v>
+      </c>
+      <c r="G20">
+        <v>435</v>
+      </c>
+      <c r="H20">
+        <v>3284.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K20">
+        <v>743</v>
+      </c>
+      <c r="L20">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M20">
+        <v>102.4728082778005</v>
+      </c>
+      <c r="N20">
+        <v>766.1938583888663</v>
+      </c>
+      <c r="O20">
+        <v>111.8643033247745</v>
+      </c>
+      <c r="P20">
+        <v>654.3295550640918</v>
+      </c>
+      <c r="Q20">
+        <v>1397.329555064092</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09528580183407023</v>
+      </c>
+      <c r="T20">
+        <v>1.142124407928403</v>
+      </c>
+      <c r="U20">
+        <v>0.055</v>
+      </c>
+      <c r="V20">
+        <v>0.146</v>
+      </c>
+      <c r="W20">
+        <v>0.04697</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>8.477045581806827</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.0865398141383338</v>
+      </c>
+      <c r="C21">
+        <v>14776.51595609836</v>
+      </c>
+      <c r="D21">
+        <v>16308.16581193494</v>
+      </c>
+      <c r="E21">
+        <v>-5099.838859092767</v>
+      </c>
+      <c r="F21">
+        <v>1966.649855836575</v>
+      </c>
+      <c r="G21">
+        <v>435</v>
+      </c>
+      <c r="H21">
+        <v>3284.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K21">
+        <v>743</v>
+      </c>
+      <c r="L21">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M21">
+        <v>108.1657420710116</v>
+      </c>
+      <c r="N21">
+        <v>760.5009245956551</v>
+      </c>
+      <c r="O21">
+        <v>111.0331349909656</v>
+      </c>
+      <c r="P21">
+        <v>649.4677896046894</v>
+      </c>
+      <c r="Q21">
+        <v>1392.467789604689</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09582162239300468</v>
+      </c>
+      <c r="T21">
+        <v>1.154491060906582</v>
+      </c>
+      <c r="U21">
+        <v>0.055</v>
+      </c>
+      <c r="V21">
+        <v>0.146</v>
+      </c>
+      <c r="W21">
+        <v>0.04697</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>8.03088528802752</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08674687077272997</v>
+      </c>
+      <c r="C22">
+        <v>14590.5423307261</v>
+      </c>
+      <c r="D22">
+        <v>16225.70007371196</v>
+      </c>
+      <c r="E22">
+        <v>-4996.330971943473</v>
+      </c>
+      <c r="F22">
+        <v>2070.157742985868</v>
+      </c>
+      <c r="G22">
+        <v>435</v>
+      </c>
+      <c r="H22">
+        <v>3284.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K22">
+        <v>743</v>
+      </c>
+      <c r="L22">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M22">
+        <v>116.9639124787016</v>
+      </c>
+      <c r="N22">
+        <v>751.7027541879652</v>
+      </c>
+      <c r="O22">
+        <v>109.7486021114429</v>
+      </c>
+      <c r="P22">
+        <v>641.9541520765223</v>
+      </c>
+      <c r="Q22">
+        <v>1384.954152076522</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09637083846591246</v>
+      </c>
+      <c r="T22">
+        <v>1.167166880209215</v>
+      </c>
+      <c r="U22">
+        <v>0.0565</v>
+      </c>
+      <c r="V22">
+        <v>0.146</v>
+      </c>
+      <c r="W22">
+        <v>0.048251</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>7.426792146892707</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08671053740712616</v>
+      </c>
+      <c r="C23">
+        <v>14501.44477231654</v>
+      </c>
+      <c r="D23">
+        <v>16240.1104024517</v>
+      </c>
+      <c r="E23">
+        <v>-4892.82308479418</v>
+      </c>
+      <c r="F23">
+        <v>2173.665630135162</v>
+      </c>
+      <c r="G23">
+        <v>435</v>
+      </c>
+      <c r="H23">
+        <v>3284.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K23">
+        <v>743</v>
+      </c>
+      <c r="L23">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M23">
+        <v>122.8121081026366</v>
+      </c>
+      <c r="N23">
+        <v>745.8545585640301</v>
+      </c>
+      <c r="O23">
+        <v>108.8947655503484</v>
+      </c>
+      <c r="P23">
+        <v>636.9597930136817</v>
+      </c>
+      <c r="Q23">
+        <v>1379.959793013682</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09693395874319766</v>
+      </c>
+      <c r="T23">
+        <v>1.180163606329635</v>
+      </c>
+      <c r="U23">
+        <v>0.0565</v>
+      </c>
+      <c r="V23">
+        <v>0.146</v>
+      </c>
+      <c r="W23">
+        <v>0.048251</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>7.073135377993054</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08667420404152233</v>
+      </c>
+      <c r="C24">
+        <v>14412.37283279082</v>
+      </c>
+      <c r="D24">
+        <v>16254.54635007527</v>
+      </c>
+      <c r="E24">
+        <v>-4789.315197644886</v>
+      </c>
+      <c r="F24">
+        <v>2277.173517284455</v>
+      </c>
+      <c r="G24">
+        <v>435</v>
+      </c>
+      <c r="H24">
+        <v>3284.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K24">
+        <v>743</v>
+      </c>
+      <c r="L24">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M24">
+        <v>128.6603037265717</v>
+      </c>
+      <c r="N24">
+        <v>740.006362940095</v>
+      </c>
+      <c r="O24">
+        <v>108.0409289892539</v>
+      </c>
+      <c r="P24">
+        <v>631.9654339508411</v>
+      </c>
+      <c r="Q24">
+        <v>1374.965433950841</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09751151800195171</v>
+      </c>
+      <c r="T24">
+        <v>1.193493581837759</v>
+      </c>
+      <c r="U24">
+        <v>0.0565</v>
+      </c>
+      <c r="V24">
+        <v>0.146</v>
+      </c>
+      <c r="W24">
+        <v>0.048251</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>6.751629224447916</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08663787067591852</v>
+      </c>
+      <c r="C25">
+        <v>14323.32658052813</v>
+      </c>
+      <c r="D25">
+        <v>16269.00798496188</v>
+      </c>
+      <c r="E25">
+        <v>-4685.807310495593</v>
+      </c>
+      <c r="F25">
+        <v>2380.681404433749</v>
+      </c>
+      <c r="G25">
+        <v>435</v>
+      </c>
+      <c r="H25">
+        <v>3284.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K25">
+        <v>743</v>
+      </c>
+      <c r="L25">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M25">
+        <v>134.5084993505068</v>
+      </c>
+      <c r="N25">
+        <v>734.15816731616</v>
+      </c>
+      <c r="O25">
+        <v>107.1870924281593</v>
+      </c>
+      <c r="P25">
+        <v>626.9710748880007</v>
+      </c>
+      <c r="Q25">
+        <v>1369.971074888001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09810407879989418</v>
+      </c>
+      <c r="T25">
+        <v>1.207169790475965</v>
+      </c>
+      <c r="U25">
+        <v>0.0565</v>
+      </c>
+      <c r="V25">
+        <v>0.146</v>
+      </c>
+      <c r="W25">
+        <v>0.048251</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>6.458080127732789</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08660153731031471</v>
+      </c>
+      <c r="C26">
+        <v>14234.30608415123</v>
+      </c>
+      <c r="D26">
+        <v>16283.49537573427</v>
+      </c>
+      <c r="E26">
+        <v>-4582.2994233463</v>
+      </c>
+      <c r="F26">
+        <v>2484.189291583042</v>
+      </c>
+      <c r="G26">
+        <v>435</v>
+      </c>
+      <c r="H26">
+        <v>3284.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K26">
+        <v>743</v>
+      </c>
+      <c r="L26">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M26">
+        <v>140.3566949744419</v>
+      </c>
+      <c r="N26">
+        <v>728.3099716922248</v>
+      </c>
+      <c r="O26">
+        <v>106.3332558670648</v>
+      </c>
+      <c r="P26">
+        <v>621.97671582516</v>
+      </c>
+      <c r="Q26">
+        <v>1364.97671582516</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09871223330304565</v>
+      </c>
+      <c r="T26">
+        <v>1.221205899341491</v>
+      </c>
+      <c r="U26">
+        <v>0.0565</v>
+      </c>
+      <c r="V26">
+        <v>0.146</v>
+      </c>
+      <c r="W26">
+        <v>0.048251</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>6.188993455743923</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08686410394471089</v>
+      </c>
+      <c r="C27">
+        <v>14026.68043559239</v>
+      </c>
+      <c r="D27">
+        <v>16179.37761432472</v>
+      </c>
+      <c r="E27">
+        <v>-4478.791536197006</v>
+      </c>
+      <c r="F27">
+        <v>2587.697178732335</v>
+      </c>
+      <c r="G27">
+        <v>435</v>
+      </c>
+      <c r="H27">
+        <v>3284.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K27">
+        <v>743</v>
+      </c>
+      <c r="L27">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M27">
+        <v>149.8276666486022</v>
+      </c>
+      <c r="N27">
+        <v>718.8390000180646</v>
+      </c>
+      <c r="O27">
+        <v>104.9504940026374</v>
+      </c>
+      <c r="P27">
+        <v>613.8885060154271</v>
+      </c>
+      <c r="Q27">
+        <v>1356.888506015427</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09933660525961452</v>
+      </c>
+      <c r="T27">
+        <v>1.235616304443432</v>
+      </c>
+      <c r="U27">
+        <v>0.0579</v>
+      </c>
+      <c r="V27">
+        <v>0.146</v>
+      </c>
+      <c r="W27">
+        <v>0.0494466</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>5.797772107764255</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08683972657910706</v>
+      </c>
+      <c r="C28">
+        <v>13932.78300728927</v>
+      </c>
+      <c r="D28">
+        <v>16188.9880731709</v>
+      </c>
+      <c r="E28">
+        <v>-4375.283649047713</v>
+      </c>
+      <c r="F28">
+        <v>2691.205065881629</v>
+      </c>
+      <c r="G28">
+        <v>435</v>
+      </c>
+      <c r="H28">
+        <v>3284.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K28">
+        <v>743</v>
+      </c>
+      <c r="L28">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M28">
+        <v>155.8207733145463</v>
+      </c>
+      <c r="N28">
+        <v>712.8458933521205</v>
+      </c>
+      <c r="O28">
+        <v>104.0755004294096</v>
+      </c>
+      <c r="P28">
+        <v>608.7703929227109</v>
+      </c>
+      <c r="Q28">
+        <v>1351.770392922711</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09997785213392846</v>
+      </c>
+      <c r="T28">
+        <v>1.250416179953532</v>
+      </c>
+      <c r="U28">
+        <v>0.0579</v>
+      </c>
+      <c r="V28">
+        <v>0.146</v>
+      </c>
+      <c r="W28">
+        <v>0.0494466</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>5.574780872850246</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08681534921350326</v>
+      </c>
+      <c r="C29">
+        <v>13838.89700288834</v>
+      </c>
+      <c r="D29">
+        <v>16198.60995591926</v>
+      </c>
+      <c r="E29">
+        <v>-4271.77576189842</v>
+      </c>
+      <c r="F29">
+        <v>2794.712953030923</v>
+      </c>
+      <c r="G29">
+        <v>435</v>
+      </c>
+      <c r="H29">
+        <v>3284.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K29">
+        <v>743</v>
+      </c>
+      <c r="L29">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M29">
+        <v>161.8138799804904</v>
+      </c>
+      <c r="N29">
+        <v>706.8527866861764</v>
+      </c>
+      <c r="O29">
+        <v>103.2005068561817</v>
+      </c>
+      <c r="P29">
+        <v>603.6522798299947</v>
+      </c>
+      <c r="Q29">
+        <v>1346.652279829995</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1006366674157579</v>
+      </c>
+      <c r="T29">
+        <v>1.265621531505006</v>
+      </c>
+      <c r="U29">
+        <v>0.0579</v>
+      </c>
+      <c r="V29">
+        <v>0.146</v>
+      </c>
+      <c r="W29">
+        <v>0.0494466</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>5.368307507189125</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08679097184789943</v>
+      </c>
+      <c r="C30">
+        <v>13745.02244277102</v>
+      </c>
+      <c r="D30">
+        <v>16208.24328295123</v>
+      </c>
+      <c r="E30">
+        <v>-4168.267874749126</v>
+      </c>
+      <c r="F30">
+        <v>2898.220840180216</v>
+      </c>
+      <c r="G30">
+        <v>435</v>
+      </c>
+      <c r="H30">
+        <v>3284.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K30">
+        <v>743</v>
+      </c>
+      <c r="L30">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M30">
+        <v>167.8069866464345</v>
+      </c>
+      <c r="N30">
+        <v>700.8596800202322</v>
+      </c>
+      <c r="O30">
+        <v>102.3255132829539</v>
+      </c>
+      <c r="P30">
+        <v>598.5341667372783</v>
+      </c>
+      <c r="Q30">
+        <v>1341.534166737278</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1013137831220825</v>
+      </c>
+      <c r="T30">
+        <v>1.28124925393291</v>
+      </c>
+      <c r="U30">
+        <v>0.0579</v>
+      </c>
+      <c r="V30">
+        <v>0.146</v>
+      </c>
+      <c r="W30">
+        <v>0.0494466</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>5.176582239075228</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08676659448229561</v>
+      </c>
+      <c r="C31">
+        <v>13651.15934736722</v>
+      </c>
+      <c r="D31">
+        <v>16217.88807469673</v>
+      </c>
+      <c r="E31">
+        <v>-4064.759987599833</v>
+      </c>
+      <c r="F31">
+        <v>3001.728727329509</v>
+      </c>
+      <c r="G31">
+        <v>435</v>
+      </c>
+      <c r="H31">
+        <v>3284.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K31">
+        <v>743</v>
+      </c>
+      <c r="L31">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M31">
+        <v>173.8000933123786</v>
+      </c>
+      <c r="N31">
+        <v>694.8665733542882</v>
+      </c>
+      <c r="O31">
+        <v>101.4505197097261</v>
+      </c>
+      <c r="P31">
+        <v>593.4160536445621</v>
+      </c>
+      <c r="Q31">
+        <v>1336.416053644562</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1020099725102755</v>
+      </c>
+      <c r="T31">
+        <v>1.297317193893994</v>
+      </c>
+      <c r="U31">
+        <v>0.0579</v>
+      </c>
+      <c r="V31">
+        <v>0.146</v>
+      </c>
+      <c r="W31">
+        <v>0.0494466</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>4.998079403245049</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08674221711669179</v>
+      </c>
+      <c r="C32">
+        <v>13557.30773715554</v>
+      </c>
+      <c r="D32">
+        <v>16227.54435163434</v>
+      </c>
+      <c r="E32">
+        <v>-3961.252100450539</v>
+      </c>
+      <c r="F32">
+        <v>3105.236614478802</v>
+      </c>
+      <c r="G32">
+        <v>435</v>
+      </c>
+      <c r="H32">
+        <v>3284.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K32">
+        <v>743</v>
+      </c>
+      <c r="L32">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M32">
+        <v>179.7931999783227</v>
+      </c>
+      <c r="N32">
+        <v>688.873466688344</v>
+      </c>
+      <c r="O32">
+        <v>100.5755261364982</v>
+      </c>
+      <c r="P32">
+        <v>588.2979405518458</v>
+      </c>
+      <c r="Q32">
+        <v>1331.297940551846</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1027260530238454</v>
+      </c>
+      <c r="T32">
+        <v>1.313844217853966</v>
+      </c>
+      <c r="U32">
+        <v>0.0579</v>
+      </c>
+      <c r="V32">
+        <v>0.146</v>
+      </c>
+      <c r="W32">
+        <v>0.0494466</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>4.831476756470213</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08671783975108797</v>
+      </c>
+      <c r="C33">
+        <v>13463.46763266336</v>
+      </c>
+      <c r="D33">
+        <v>16237.21213429145</v>
+      </c>
+      <c r="E33">
+        <v>-3857.744213301246</v>
+      </c>
+      <c r="F33">
+        <v>3208.744501628096</v>
+      </c>
+      <c r="G33">
+        <v>435</v>
+      </c>
+      <c r="H33">
+        <v>3284.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K33">
+        <v>743</v>
+      </c>
+      <c r="L33">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M33">
+        <v>185.7863066442667</v>
+      </c>
+      <c r="N33">
+        <v>682.8803600224001</v>
+      </c>
+      <c r="O33">
+        <v>99.7005325632704</v>
+      </c>
+      <c r="P33">
+        <v>583.1798274591297</v>
+      </c>
+      <c r="Q33">
+        <v>1326.17982745913</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1034628894943304</v>
+      </c>
+      <c r="T33">
+        <v>1.33085028598669</v>
+      </c>
+      <c r="U33">
+        <v>0.0579</v>
+      </c>
+      <c r="V33">
+        <v>0.146</v>
+      </c>
+      <c r="W33">
+        <v>0.0494466</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>4.675622667551819</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.08669346238548414</v>
+      </c>
+      <c r="C34">
+        <v>13369.63905446701</v>
+      </c>
+      <c r="D34">
+        <v>16246.8914432444</v>
+      </c>
+      <c r="E34">
+        <v>-3754.236326151952</v>
+      </c>
+      <c r="F34">
+        <v>3312.25238877739</v>
+      </c>
+      <c r="G34">
+        <v>435</v>
+      </c>
+      <c r="H34">
+        <v>3284.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K34">
+        <v>743</v>
+      </c>
+      <c r="L34">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M34">
+        <v>191.7794133102109</v>
+      </c>
+      <c r="N34">
+        <v>676.8872533564559</v>
+      </c>
+      <c r="O34">
+        <v>98.82553899004255</v>
+      </c>
+      <c r="P34">
+        <v>578.0617143664133</v>
+      </c>
+      <c r="Q34">
+        <v>1321.061714366413</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.104221397625712</v>
+      </c>
+      <c r="T34">
+        <v>1.348356532593907</v>
+      </c>
+      <c r="U34">
+        <v>0.0579</v>
+      </c>
+      <c r="V34">
+        <v>0.146</v>
+      </c>
+      <c r="W34">
+        <v>0.0494466</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>4.529509459190824</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08740181701988034</v>
+      </c>
+      <c r="C35">
+        <v>12989.49515300963</v>
+      </c>
+      <c r="D35">
+        <v>15970.25542893631</v>
+      </c>
+      <c r="E35">
+        <v>-3650.728439002659</v>
+      </c>
+      <c r="F35">
+        <v>3415.760275926683</v>
+      </c>
+      <c r="G35">
+        <v>435</v>
+      </c>
+      <c r="H35">
+        <v>3284.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K35">
+        <v>743</v>
+      </c>
+      <c r="L35">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M35">
+        <v>206.6534966935643</v>
+      </c>
+      <c r="N35">
+        <v>662.0131699731024</v>
+      </c>
+      <c r="O35">
+        <v>96.65392281607295</v>
+      </c>
+      <c r="P35">
+        <v>565.3592471570295</v>
+      </c>
+      <c r="Q35">
+        <v>1308.35924715703</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1050025477908662</v>
+      </c>
+      <c r="T35">
+        <v>1.366385353726712</v>
+      </c>
+      <c r="U35">
+        <v>0.0605</v>
+      </c>
+      <c r="V35">
+        <v>0.146</v>
+      </c>
+      <c r="W35">
+        <v>0.051667</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>4.203493676929005</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08739964365427652</v>
+      </c>
+      <c r="C36">
+        <v>12886.82162886887</v>
+      </c>
+      <c r="D36">
+        <v>15971.08979194484</v>
+      </c>
+      <c r="E36">
+        <v>-3547.220551853365</v>
+      </c>
+      <c r="F36">
+        <v>3519.268163075977</v>
+      </c>
+      <c r="G36">
+        <v>435</v>
+      </c>
+      <c r="H36">
+        <v>3284.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K36">
+        <v>743</v>
+      </c>
+      <c r="L36">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M36">
+        <v>212.9157238660966</v>
+      </c>
+      <c r="N36">
+        <v>655.7509428005701</v>
+      </c>
+      <c r="O36">
+        <v>95.73963764888323</v>
+      </c>
+      <c r="P36">
+        <v>560.0113051516869</v>
+      </c>
+      <c r="Q36">
+        <v>1303.011305151687</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1058073691731463</v>
+      </c>
+      <c r="T36">
+        <v>1.384960502772633</v>
+      </c>
+      <c r="U36">
+        <v>0.0605</v>
+      </c>
+      <c r="V36">
+        <v>0.146</v>
+      </c>
+      <c r="W36">
+        <v>0.051667</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>4.079861509960505</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.0882045002886727</v>
+      </c>
+      <c r="C37">
+        <v>12480.17521891949</v>
+      </c>
+      <c r="D37">
+        <v>15667.95126914476</v>
+      </c>
+      <c r="E37">
+        <v>-3443.712664704072</v>
+      </c>
+      <c r="F37">
+        <v>3622.77605022527</v>
+      </c>
+      <c r="G37">
+        <v>435</v>
+      </c>
+      <c r="H37">
+        <v>3284.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K37">
+        <v>743</v>
+      </c>
+      <c r="L37">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M37">
+        <v>228.9594463742371</v>
+      </c>
+      <c r="N37">
+        <v>639.7072202924296</v>
+      </c>
+      <c r="O37">
+        <v>93.39725416269472</v>
+      </c>
+      <c r="P37">
+        <v>546.3099661297349</v>
+      </c>
+      <c r="Q37">
+        <v>1289.309966129735</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1066369542902657</v>
+      </c>
+      <c r="T37">
+        <v>1.40410719486612</v>
+      </c>
+      <c r="U37">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="V37">
+        <v>0.146</v>
+      </c>
+      <c r="W37">
+        <v>0.0539728</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>3.793976096739945</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.0882253849230689</v>
+      </c>
+      <c r="C38">
+        <v>12368.95450996347</v>
+      </c>
+      <c r="D38">
+        <v>15660.23844733803</v>
+      </c>
+      <c r="E38">
+        <v>-3340.204777554779</v>
+      </c>
+      <c r="F38">
+        <v>3726.283937374563</v>
+      </c>
+      <c r="G38">
+        <v>435</v>
+      </c>
+      <c r="H38">
+        <v>3284.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K38">
+        <v>743</v>
+      </c>
+      <c r="L38">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M38">
+        <v>235.5011448420724</v>
+      </c>
+      <c r="N38">
+        <v>633.1655218245944</v>
+      </c>
+      <c r="O38">
+        <v>92.44216618639078</v>
+      </c>
+      <c r="P38">
+        <v>540.7233556382037</v>
+      </c>
+      <c r="Q38">
+        <v>1283.723355638204</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1074924639422951</v>
+      </c>
+      <c r="T38">
+        <v>1.423852221087529</v>
+      </c>
+      <c r="U38">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="V38">
+        <v>0.146</v>
+      </c>
+      <c r="W38">
+        <v>0.0539728</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>3.688587871830503</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.08824626955746509</v>
+      </c>
+      <c r="C39">
+        <v>12257.74139081288</v>
+      </c>
+      <c r="D39">
+        <v>15652.53321533674</v>
+      </c>
+      <c r="E39">
+        <v>-3236.696890405485</v>
+      </c>
+      <c r="F39">
+        <v>3829.791824523857</v>
+      </c>
+      <c r="G39">
+        <v>435</v>
+      </c>
+      <c r="H39">
+        <v>3284.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K39">
+        <v>743</v>
+      </c>
+      <c r="L39">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M39">
+        <v>242.0428433099078</v>
+      </c>
+      <c r="N39">
+        <v>626.623823356759</v>
+      </c>
+      <c r="O39">
+        <v>91.48707821008681</v>
+      </c>
+      <c r="P39">
+        <v>535.1367451466722</v>
+      </c>
+      <c r="Q39">
+        <v>1278.136745146672</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.108375132630897</v>
+      </c>
+      <c r="T39">
+        <v>1.444224073538188</v>
+      </c>
+      <c r="U39">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="V39">
+        <v>0.146</v>
+      </c>
+      <c r="W39">
+        <v>0.0539728</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>3.588896307726975</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08979239819186127</v>
+      </c>
+      <c r="C40">
+        <v>11604.11960217715</v>
+      </c>
+      <c r="D40">
+        <v>15102.4193138503</v>
+      </c>
+      <c r="E40">
+        <v>-3133.189003256192</v>
+      </c>
+      <c r="F40">
+        <v>3933.29971167315</v>
+      </c>
+      <c r="G40">
+        <v>435</v>
+      </c>
+      <c r="H40">
+        <v>3284.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K40">
+        <v>743</v>
+      </c>
+      <c r="L40">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M40">
+        <v>267.0710504226069</v>
+      </c>
+      <c r="N40">
+        <v>601.5956162440598</v>
+      </c>
+      <c r="O40">
+        <v>87.83295997163272</v>
+      </c>
+      <c r="P40">
+        <v>513.7626562724271</v>
+      </c>
+      <c r="Q40">
+        <v>1256.762656272427</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.109286274503002</v>
+      </c>
+      <c r="T40">
+        <v>1.465253082519515</v>
+      </c>
+      <c r="U40">
+        <v>0.0679</v>
+      </c>
+      <c r="V40">
+        <v>0.146</v>
+      </c>
+      <c r="W40">
+        <v>0.0579866</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>3.252567679245314</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.08985342082625745</v>
+      </c>
+      <c r="C41">
+        <v>11479.69190006227</v>
+      </c>
+      <c r="D41">
+        <v>15081.49949888471</v>
+      </c>
+      <c r="E41">
+        <v>-3029.681116106898</v>
+      </c>
+      <c r="F41">
+        <v>4036.807598822444</v>
+      </c>
+      <c r="G41">
+        <v>435</v>
+      </c>
+      <c r="H41">
+        <v>3284.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K41">
+        <v>743</v>
+      </c>
+      <c r="L41">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M41">
+        <v>274.0992359600439</v>
+      </c>
+      <c r="N41">
+        <v>594.5674307066229</v>
+      </c>
+      <c r="O41">
+        <v>86.80684488316693</v>
+      </c>
+      <c r="P41">
+        <v>507.7605858234559</v>
+      </c>
+      <c r="Q41">
+        <v>1250.760585823456</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1102272898791106</v>
+      </c>
+      <c r="T41">
+        <v>1.486971567205147</v>
+      </c>
+      <c r="U41">
+        <v>0.0679</v>
+      </c>
+      <c r="V41">
+        <v>0.146</v>
+      </c>
+      <c r="W41">
+        <v>0.0579866</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>3.169168507982614</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.08991444346065364</v>
+      </c>
+      <c r="C42">
+        <v>11355.32207387735</v>
+      </c>
+      <c r="D42">
+        <v>15060.63755984908</v>
+      </c>
+      <c r="E42">
+        <v>-2926.173228957605</v>
+      </c>
+      <c r="F42">
+        <v>4140.315485971737</v>
+      </c>
+      <c r="G42">
+        <v>435</v>
+      </c>
+      <c r="H42">
+        <v>3284.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K42">
+        <v>743</v>
+      </c>
+      <c r="L42">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M42">
+        <v>281.127421497481</v>
+      </c>
+      <c r="N42">
+        <v>587.5392451691857</v>
+      </c>
+      <c r="O42">
+        <v>85.78072979470112</v>
+      </c>
+      <c r="P42">
+        <v>501.7585153744846</v>
+      </c>
+      <c r="Q42">
+        <v>1244.758515374485</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1111996724344227</v>
+      </c>
+      <c r="T42">
+        <v>1.5094140013803</v>
+      </c>
+      <c r="U42">
+        <v>0.0679</v>
+      </c>
+      <c r="V42">
+        <v>0.146</v>
+      </c>
+      <c r="W42">
+        <v>0.0579866</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>3.089939295283048</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.08997546609504981</v>
+      </c>
+      <c r="C43">
+        <v>11231.0098837783</v>
+      </c>
+      <c r="D43">
+        <v>15039.83325689933</v>
+      </c>
+      <c r="E43">
+        <v>-2822.665341808311</v>
+      </c>
+      <c r="F43">
+        <v>4243.82337312103</v>
+      </c>
+      <c r="G43">
+        <v>435</v>
+      </c>
+      <c r="H43">
+        <v>3284.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K43">
+        <v>743</v>
+      </c>
+      <c r="L43">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M43">
+        <v>288.155607034918</v>
+      </c>
+      <c r="N43">
+        <v>580.5110596317488</v>
+      </c>
+      <c r="O43">
+        <v>84.75461470623532</v>
+      </c>
+      <c r="P43">
+        <v>495.7564449255135</v>
+      </c>
+      <c r="Q43">
+        <v>1238.756444925514</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1122050171102539</v>
+      </c>
+      <c r="T43">
+        <v>1.532617196035967</v>
+      </c>
+      <c r="U43">
+        <v>0.0679</v>
+      </c>
+      <c r="V43">
+        <v>0.146</v>
+      </c>
+      <c r="W43">
+        <v>0.0579866</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>3.014574922227364</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.09337221272944599</v>
+      </c>
+      <c r="C44">
+        <v>10053.62924473931</v>
+      </c>
+      <c r="D44">
+        <v>13965.96050500963</v>
+      </c>
+      <c r="E44">
+        <v>-2719.157454659018</v>
+      </c>
+      <c r="F44">
+        <v>4347.331260270324</v>
+      </c>
+      <c r="G44">
+        <v>435</v>
+      </c>
+      <c r="H44">
+        <v>3284.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K44">
+        <v>743</v>
+      </c>
+      <c r="L44">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M44">
+        <v>335.6139732928689</v>
+      </c>
+      <c r="N44">
+        <v>533.0526933737979</v>
+      </c>
+      <c r="O44">
+        <v>77.82569323257448</v>
+      </c>
+      <c r="P44">
+        <v>455.2270001412234</v>
+      </c>
+      <c r="Q44">
+        <v>1198.227000141223</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1132450288438724</v>
+      </c>
+      <c r="T44">
+        <v>1.556620500852174</v>
+      </c>
+      <c r="U44">
+        <v>0.07719999999999999</v>
+      </c>
+      <c r="V44">
+        <v>0.146</v>
+      </c>
+      <c r="W44">
+        <v>0.0659288</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>2.588291119537614</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.09351265736384218</v>
+      </c>
+      <c r="C45">
+        <v>9909.01184230646</v>
+      </c>
+      <c r="D45">
+        <v>13924.85098972608</v>
+      </c>
+      <c r="E45">
+        <v>-2615.649567509725</v>
+      </c>
+      <c r="F45">
+        <v>4450.839147419617</v>
+      </c>
+      <c r="G45">
+        <v>435</v>
+      </c>
+      <c r="H45">
+        <v>3284.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K45">
+        <v>743</v>
+      </c>
+      <c r="L45">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M45">
+        <v>343.6047821807944</v>
+      </c>
+      <c r="N45">
+        <v>525.0618844858724</v>
+      </c>
+      <c r="O45">
+        <v>76.65903513493737</v>
+      </c>
+      <c r="P45">
+        <v>448.402849350935</v>
+      </c>
+      <c r="Q45">
+        <v>1191.402849350935</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.114321532217267</v>
+      </c>
+      <c r="T45">
+        <v>1.581466026890002</v>
+      </c>
+      <c r="U45">
+        <v>0.07719999999999999</v>
+      </c>
+      <c r="V45">
+        <v>0.146</v>
+      </c>
+      <c r="W45">
+        <v>0.0659288</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>2.528098302804182</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.09541917399823836</v>
+      </c>
+      <c r="C46">
+        <v>9270.4696548211</v>
+      </c>
+      <c r="D46">
+        <v>13389.81668939001</v>
+      </c>
+      <c r="E46">
+        <v>-2512.141680360432</v>
+      </c>
+      <c r="F46">
+        <v>4554.34703456891</v>
+      </c>
+      <c r="G46">
+        <v>435</v>
+      </c>
+      <c r="H46">
+        <v>3284.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K46">
+        <v>743</v>
+      </c>
+      <c r="L46">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M46">
+        <v>373.0010221311937</v>
+      </c>
+      <c r="N46">
+        <v>495.665644535473</v>
+      </c>
+      <c r="O46">
+        <v>72.36718410217905</v>
+      </c>
+      <c r="P46">
+        <v>423.2984604332939</v>
+      </c>
+      <c r="Q46">
+        <v>1166.298460433294</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1154364821397114</v>
+      </c>
+      <c r="T46">
+        <v>1.607198893143467</v>
+      </c>
+      <c r="U46">
+        <v>0.0819</v>
+      </c>
+      <c r="V46">
+        <v>0.146</v>
+      </c>
+      <c r="W46">
+        <v>0.06994259999999999</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>2.328858676320557</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.09559975663263454</v>
+      </c>
+      <c r="C47">
+        <v>9118.407948630302</v>
+      </c>
+      <c r="D47">
+        <v>13341.26287034851</v>
+      </c>
+      <c r="E47">
+        <v>-2408.633793211137</v>
+      </c>
+      <c r="F47">
+        <v>4657.854921718204</v>
+      </c>
+      <c r="G47">
+        <v>435</v>
+      </c>
+      <c r="H47">
+        <v>3284.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K47">
+        <v>743</v>
+      </c>
+      <c r="L47">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M47">
+        <v>381.4783180887209</v>
+      </c>
+      <c r="N47">
+        <v>487.1883485779458</v>
+      </c>
+      <c r="O47">
+        <v>71.12949889238008</v>
+      </c>
+      <c r="P47">
+        <v>416.0588496855657</v>
+      </c>
+      <c r="Q47">
+        <v>1159.058849685566</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1165919756956992</v>
+      </c>
+      <c r="T47">
+        <v>1.633867499987967</v>
+      </c>
+      <c r="U47">
+        <v>0.0819</v>
+      </c>
+      <c r="V47">
+        <v>0.146</v>
+      </c>
+      <c r="W47">
+        <v>0.06994259999999999</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>2.277106261291211</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.09578033926703074</v>
+      </c>
+      <c r="C48">
+        <v>8966.697099463723</v>
+      </c>
+      <c r="D48">
+        <v>13293.05990833122</v>
+      </c>
+      <c r="E48">
+        <v>-2305.125906061844</v>
+      </c>
+      <c r="F48">
+        <v>4761.362808867498</v>
+      </c>
+      <c r="G48">
+        <v>435</v>
+      </c>
+      <c r="H48">
+        <v>3284.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K48">
+        <v>743</v>
+      </c>
+      <c r="L48">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M48">
+        <v>389.9556140462481</v>
+      </c>
+      <c r="N48">
+        <v>478.7110526204187</v>
+      </c>
+      <c r="O48">
+        <v>69.89181368258113</v>
+      </c>
+      <c r="P48">
+        <v>408.8192389378376</v>
+      </c>
+      <c r="Q48">
+        <v>1151.819238937838</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1177902653093162</v>
+      </c>
+      <c r="T48">
+        <v>1.661523833011893</v>
+      </c>
+      <c r="U48">
+        <v>0.0819</v>
+      </c>
+      <c r="V48">
+        <v>0.146</v>
+      </c>
+      <c r="W48">
+        <v>0.06994259999999999</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>2.227603951263141</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.09596092190142691</v>
+      </c>
+      <c r="C49">
+        <v>8815.333317995941</v>
+      </c>
+      <c r="D49">
+        <v>13245.20401401273</v>
+      </c>
+      <c r="E49">
+        <v>-2201.618018912551</v>
+      </c>
+      <c r="F49">
+        <v>4864.870696016791</v>
+      </c>
+      <c r="G49">
+        <v>435</v>
+      </c>
+      <c r="H49">
+        <v>3284.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K49">
+        <v>743</v>
+      </c>
+      <c r="L49">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M49">
+        <v>398.4329100037752</v>
+      </c>
+      <c r="N49">
+        <v>470.2337566628916</v>
+      </c>
+      <c r="O49">
+        <v>68.65412847278216</v>
+      </c>
+      <c r="P49">
+        <v>401.5796281901094</v>
+      </c>
+      <c r="Q49">
+        <v>1144.579628190109</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1190337733989187</v>
+      </c>
+      <c r="T49">
+        <v>1.69022380124427</v>
+      </c>
+      <c r="U49">
+        <v>0.0819</v>
+      </c>
+      <c r="V49">
+        <v>0.146</v>
+      </c>
+      <c r="W49">
+        <v>0.06994259999999999</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>2.180208122512862</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.09614150453582307</v>
+      </c>
+      <c r="C50">
+        <v>8664.312869273066</v>
+      </c>
+      <c r="D50">
+        <v>13197.69145243915</v>
+      </c>
+      <c r="E50">
+        <v>-2098.110131763257</v>
+      </c>
+      <c r="F50">
+        <v>4968.378583166084</v>
+      </c>
+      <c r="G50">
+        <v>435</v>
+      </c>
+      <c r="H50">
+        <v>3284.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K50">
+        <v>743</v>
+      </c>
+      <c r="L50">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M50">
+        <v>406.9102059613023</v>
+      </c>
+      <c r="N50">
+        <v>461.7564607053644</v>
+      </c>
+      <c r="O50">
+        <v>67.41644326298321</v>
+      </c>
+      <c r="P50">
+        <v>394.3400174423812</v>
+      </c>
+      <c r="Q50">
+        <v>1137.340017442381</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1203251087227367</v>
+      </c>
+      <c r="T50">
+        <v>1.72002761440866</v>
+      </c>
+      <c r="U50">
+        <v>0.0819</v>
+      </c>
+      <c r="V50">
+        <v>0.146</v>
+      </c>
+      <c r="W50">
+        <v>0.06994259999999999</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>2.13478711996051</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.09632208717021926</v>
+      </c>
+      <c r="C51">
+        <v>8513.632071741038</v>
+      </c>
+      <c r="D51">
+        <v>13150.51854205642</v>
+      </c>
+      <c r="E51">
+        <v>-1994.602244613964</v>
+      </c>
+      <c r="F51">
+        <v>5071.886470315378</v>
+      </c>
+      <c r="G51">
+        <v>435</v>
+      </c>
+      <c r="H51">
+        <v>3284.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K51">
+        <v>743</v>
+      </c>
+      <c r="L51">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M51">
+        <v>415.3875019188295</v>
+      </c>
+      <c r="N51">
+        <v>453.2791647478373</v>
+      </c>
+      <c r="O51">
+        <v>66.17875805318424</v>
+      </c>
+      <c r="P51">
+        <v>387.100406694653</v>
+      </c>
+      <c r="Q51">
+        <v>1130.100406694653</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1216670846474888</v>
+      </c>
+      <c r="T51">
+        <v>1.75100020455989</v>
+      </c>
+      <c r="U51">
+        <v>0.0819</v>
+      </c>
+      <c r="V51">
+        <v>0.146</v>
+      </c>
+      <c r="W51">
+        <v>0.06994259999999999</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>2.091220035879684</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.09650266980461546</v>
+      </c>
+      <c r="C52">
+        <v>8363.2872962947</v>
+      </c>
+      <c r="D52">
+        <v>13103.68165375937</v>
+      </c>
+      <c r="E52">
+        <v>-1891.094357464671</v>
+      </c>
+      <c r="F52">
+        <v>5175.394357464671</v>
+      </c>
+      <c r="G52">
+        <v>435</v>
+      </c>
+      <c r="H52">
+        <v>3284.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K52">
+        <v>743</v>
+      </c>
+      <c r="L52">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M52">
+        <v>423.8647978763565</v>
+      </c>
+      <c r="N52">
+        <v>444.8018687903102</v>
+      </c>
+      <c r="O52">
+        <v>64.94107284338529</v>
+      </c>
+      <c r="P52">
+        <v>379.8607959469249</v>
+      </c>
+      <c r="Q52">
+        <v>1122.860795946925</v>
+      </c>
+      <c r="R52">
         <v>1</v>
       </c>
-      <c r="U3">
-        <v>594</v>
-      </c>
-      <c r="V3">
-        <v>0.1156249391703813</v>
-      </c>
-      <c r="W3">
-        <v>-0.1068566340160285</v>
-      </c>
-      <c r="X3">
-        <v>0.1380424614375926</v>
-      </c>
-      <c r="Y3">
-        <v>-0.2448990954536211</v>
-      </c>
-      <c r="Z3">
-        <v>0.1535099472787216</v>
-      </c>
-      <c r="AA3">
-        <v>-0.004176632325652988</v>
-      </c>
-      <c r="AB3">
-        <v>0.1106606583387638</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1148372906644168</v>
-      </c>
-      <c r="AD3">
-        <v>7386</v>
-      </c>
-      <c r="AE3">
-        <v>91.89405416294773</v>
-      </c>
-      <c r="AF3">
-        <v>7477.894054162948</v>
-      </c>
-      <c r="AG3">
-        <v>6883.894054162948</v>
-      </c>
-      <c r="AH3">
-        <v>0.5927688485850348</v>
-      </c>
-      <c r="AI3">
-        <v>0.4202033363091225</v>
-      </c>
-      <c r="AJ3">
-        <v>0.5726464461971688</v>
-      </c>
-      <c r="AK3">
-        <v>0.4001823306484677</v>
-      </c>
-      <c r="AL3">
-        <v>912</v>
-      </c>
-      <c r="AM3">
-        <v>858</v>
-      </c>
-      <c r="AN3">
-        <v>9.782781456953643</v>
-      </c>
-      <c r="AO3">
-        <v>-0.07456140350877193</v>
-      </c>
-      <c r="AP3">
-        <v>9.117740469089998</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.07925407925407925</v>
+      <c r="S52">
+        <v>0.1230627396092309</v>
+      </c>
+      <c r="T52">
+        <v>1.783211698317168</v>
+      </c>
+      <c r="U52">
+        <v>0.0819</v>
+      </c>
+      <c r="V52">
+        <v>0.146</v>
+      </c>
+      <c r="W52">
+        <v>0.06994259999999999</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>2.049395635162091</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.09668325243901163</v>
+      </c>
+      <c r="C53">
+        <v>8213.274965347109</v>
+      </c>
+      <c r="D53">
+        <v>13057.17720996107</v>
+      </c>
+      <c r="E53">
+        <v>-1787.586470315377</v>
+      </c>
+      <c r="F53">
+        <v>5278.902244613964</v>
+      </c>
+      <c r="G53">
+        <v>435</v>
+      </c>
+      <c r="H53">
+        <v>3284.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K53">
+        <v>743</v>
+      </c>
+      <c r="L53">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M53">
+        <v>432.3420938338837</v>
+      </c>
+      <c r="N53">
+        <v>436.3245728327831</v>
+      </c>
+      <c r="O53">
+        <v>63.70338763358632</v>
+      </c>
+      <c r="P53">
+        <v>372.6211851991968</v>
+      </c>
+      <c r="Q53">
+        <v>1115.621185199197</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1245153600796156</v>
+      </c>
+      <c r="T53">
+        <v>1.816737946921683</v>
+      </c>
+      <c r="U53">
+        <v>0.0819</v>
+      </c>
+      <c r="V53">
+        <v>0.146</v>
+      </c>
+      <c r="W53">
+        <v>0.06994259999999999</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>2.009211407021657</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1041023390734078</v>
+      </c>
+      <c r="C54">
+        <v>6448.215750053092</v>
+      </c>
+      <c r="D54">
+        <v>11395.62588181635</v>
+      </c>
+      <c r="E54">
+        <v>-1684.078583166084</v>
+      </c>
+      <c r="F54">
+        <v>5382.410131763258</v>
+      </c>
+      <c r="G54">
+        <v>435</v>
+      </c>
+      <c r="H54">
+        <v>3284.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K54">
+        <v>743</v>
+      </c>
+      <c r="L54">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M54">
+        <v>528.552674939152</v>
+      </c>
+      <c r="N54">
+        <v>340.1139917275148</v>
+      </c>
+      <c r="O54">
+        <v>49.65664279221715</v>
+      </c>
+      <c r="P54">
+        <v>290.4573489352976</v>
+      </c>
+      <c r="Q54">
+        <v>1033.457348935298</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1260285064029329</v>
+      </c>
+      <c r="T54">
+        <v>1.851661122551385</v>
+      </c>
+      <c r="U54">
+        <v>0.09820000000000001</v>
+      </c>
+      <c r="V54">
+        <v>0.146</v>
+      </c>
+      <c r="W54">
+        <v>0.0838628</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>1.643481733900352</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.104422123707804</v>
+      </c>
+      <c r="C55">
+        <v>6282.544539130403</v>
+      </c>
+      <c r="D55">
+        <v>11333.46255804295</v>
+      </c>
+      <c r="E55">
+        <v>-1580.57069601679</v>
+      </c>
+      <c r="F55">
+        <v>5485.918018912552</v>
+      </c>
+      <c r="G55">
+        <v>435</v>
+      </c>
+      <c r="H55">
+        <v>3284.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K55">
+        <v>743</v>
+      </c>
+      <c r="L55">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M55">
+        <v>538.7171494572126</v>
+      </c>
+      <c r="N55">
+        <v>329.9495172094541</v>
+      </c>
+      <c r="O55">
+        <v>48.1726295125803</v>
+      </c>
+      <c r="P55">
+        <v>281.7768876968738</v>
+      </c>
+      <c r="Q55">
+        <v>1024.776887696874</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1276060419314979</v>
+      </c>
+      <c r="T55">
+        <v>1.888070390761075</v>
+      </c>
+      <c r="U55">
+        <v>0.09820000000000001</v>
+      </c>
+      <c r="V55">
+        <v>0.146</v>
+      </c>
+      <c r="W55">
+        <v>0.0838628</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>1.612472644581478</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1047419083422002</v>
+      </c>
+      <c r="C56">
+        <v>6117.547852542771</v>
+      </c>
+      <c r="D56">
+        <v>11271.97375860462</v>
+      </c>
+      <c r="E56">
+        <v>-1477.062808867497</v>
+      </c>
+      <c r="F56">
+        <v>5589.425906061845</v>
+      </c>
+      <c r="G56">
+        <v>435</v>
+      </c>
+      <c r="H56">
+        <v>3284.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K56">
+        <v>743</v>
+      </c>
+      <c r="L56">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M56">
+        <v>548.8816239752732</v>
+      </c>
+      <c r="N56">
+        <v>319.7850426913935</v>
+      </c>
+      <c r="O56">
+        <v>46.68861623294345</v>
+      </c>
+      <c r="P56">
+        <v>273.0964264584501</v>
+      </c>
+      <c r="Q56">
+        <v>1016.09642645845</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1292521659613048</v>
+      </c>
+      <c r="T56">
+        <v>1.926062670632056</v>
+      </c>
+      <c r="U56">
+        <v>0.09820000000000001</v>
+      </c>
+      <c r="V56">
+        <v>0.146</v>
+      </c>
+      <c r="W56">
+        <v>0.0838628</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>1.582612040052191</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1050616929765964</v>
+      </c>
+      <c r="C57">
+        <v>5953.214770798676</v>
+      </c>
+      <c r="D57">
+        <v>11211.14856400981</v>
+      </c>
+      <c r="E57">
+        <v>-1373.554921718203</v>
+      </c>
+      <c r="F57">
+        <v>5692.933793211138</v>
+      </c>
+      <c r="G57">
+        <v>435</v>
+      </c>
+      <c r="H57">
+        <v>3284.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K57">
+        <v>743</v>
+      </c>
+      <c r="L57">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M57">
+        <v>559.0460984933338</v>
+      </c>
+      <c r="N57">
+        <v>309.6205681733329</v>
+      </c>
+      <c r="O57">
+        <v>45.2046029533066</v>
+      </c>
+      <c r="P57">
+        <v>264.4159652200263</v>
+      </c>
+      <c r="Q57">
+        <v>1007.415965220026</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.130971451059103</v>
+      </c>
+      <c r="T57">
+        <v>1.965743496275081</v>
+      </c>
+      <c r="U57">
+        <v>0.09820000000000001</v>
+      </c>
+      <c r="V57">
+        <v>0.146</v>
+      </c>
+      <c r="W57">
+        <v>0.0838628</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>1.553837275687606</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1053814776109926</v>
+      </c>
+      <c r="C58">
+        <v>5789.5346088342</v>
+      </c>
+      <c r="D58">
+        <v>11150.97628919463</v>
+      </c>
+      <c r="E58">
+        <v>-1270.04703456891</v>
+      </c>
+      <c r="F58">
+        <v>5796.441680360432</v>
+      </c>
+      <c r="G58">
+        <v>435</v>
+      </c>
+      <c r="H58">
+        <v>3284.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K58">
+        <v>743</v>
+      </c>
+      <c r="L58">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M58">
+        <v>569.2105730113944</v>
+      </c>
+      <c r="N58">
+        <v>299.4560936552723</v>
+      </c>
+      <c r="O58">
+        <v>43.72058967366975</v>
+      </c>
+      <c r="P58">
+        <v>255.7355039816026</v>
+      </c>
+      <c r="Q58">
+        <v>998.7355039816025</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1327688854795285</v>
+      </c>
+      <c r="T58">
+        <v>2.00722799581097</v>
+      </c>
+      <c r="U58">
+        <v>0.09820000000000001</v>
+      </c>
+      <c r="V58">
+        <v>0.146</v>
+      </c>
+      <c r="W58">
+        <v>0.0838628</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>1.526090181478899</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1392457023193324</v>
+      </c>
+      <c r="C59">
+        <v>1644.972318945044</v>
+      </c>
+      <c r="D59">
+        <v>7109.92188645477</v>
+      </c>
+      <c r="E59">
+        <v>-1166.539147419616</v>
+      </c>
+      <c r="F59">
+        <v>5899.949567509726</v>
+      </c>
+      <c r="G59">
+        <v>435</v>
+      </c>
+      <c r="H59">
+        <v>3284.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K59">
+        <v>743</v>
+      </c>
+      <c r="L59">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M59">
+        <v>965.2317492445911</v>
+      </c>
+      <c r="N59">
+        <v>-96.56508257792439</v>
+      </c>
+      <c r="O59">
+        <v>-14.09850205637696</v>
+      </c>
+      <c r="P59">
+        <v>-82.46658052154743</v>
+      </c>
+      <c r="Q59">
+        <v>660.5334194784525</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1354568000076187</v>
+      </c>
+      <c r="T59">
+        <v>2.069264634102713</v>
+      </c>
+      <c r="U59">
+        <v>0.1636</v>
+      </c>
+      <c r="V59">
+        <v>0.1313936610897738</v>
+      </c>
+      <c r="W59">
+        <v>0.142103997045713</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.8999565828066699</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1404237023193324</v>
+      </c>
+      <c r="C60">
+        <v>1452.950795392279</v>
+      </c>
+      <c r="D60">
+        <v>7021.408250051298</v>
+      </c>
+      <c r="E60">
+        <v>-1063.031260270323</v>
+      </c>
+      <c r="F60">
+        <v>6003.457454659018</v>
+      </c>
+      <c r="G60">
+        <v>435</v>
+      </c>
+      <c r="H60">
+        <v>3284.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K60">
+        <v>743</v>
+      </c>
+      <c r="L60">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M60">
+        <v>982.1656395822154</v>
+      </c>
+      <c r="N60">
+        <v>-113.4989729155486</v>
+      </c>
+      <c r="O60">
+        <v>-16.5708500456701</v>
+      </c>
+      <c r="P60">
+        <v>-96.92812286987852</v>
+      </c>
+      <c r="Q60">
+        <v>646.0718771301215</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1375914857220858</v>
+      </c>
+      <c r="T60">
+        <v>2.118532839676587</v>
+      </c>
+      <c r="U60">
+        <v>0.1636</v>
+      </c>
+      <c r="V60">
+        <v>0.1291282531399501</v>
+      </c>
+      <c r="W60">
+        <v>0.1424746177863042</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.8844400899996585</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1416017023193324</v>
+      </c>
+      <c r="C61">
+        <v>1263.106040334416</v>
+      </c>
+      <c r="D61">
+        <v>6935.071382142728</v>
+      </c>
+      <c r="E61">
+        <v>-959.5233731210301</v>
+      </c>
+      <c r="F61">
+        <v>6106.965341808312</v>
+      </c>
+      <c r="G61">
+        <v>435</v>
+      </c>
+      <c r="H61">
+        <v>3284.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K61">
+        <v>743</v>
+      </c>
+      <c r="L61">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M61">
+        <v>999.0995299198397</v>
+      </c>
+      <c r="N61">
+        <v>-130.432863253173</v>
+      </c>
+      <c r="O61">
+        <v>-19.04319803496325</v>
+      </c>
+      <c r="P61">
+        <v>-111.3896652182097</v>
+      </c>
+      <c r="Q61">
+        <v>631.6103347817902</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1398303024470147</v>
+      </c>
+      <c r="T61">
+        <v>2.170204372351625</v>
+      </c>
+      <c r="U61">
+        <v>0.1636</v>
+      </c>
+      <c r="V61">
+        <v>0.126939638679951</v>
+      </c>
+      <c r="W61">
+        <v>0.14283267511196</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.8694495799996644</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1427797023193324</v>
+      </c>
+      <c r="C62">
+        <v>1075.358730988673</v>
+      </c>
+      <c r="D62">
+        <v>6850.831959946278</v>
+      </c>
+      <c r="E62">
+        <v>-856.0154859717368</v>
+      </c>
+      <c r="F62">
+        <v>6210.473228957605</v>
+      </c>
+      <c r="G62">
+        <v>435</v>
+      </c>
+      <c r="H62">
+        <v>3284.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K62">
+        <v>743</v>
+      </c>
+      <c r="L62">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M62">
+        <v>1016.033420257464</v>
+      </c>
+      <c r="N62">
+        <v>-147.3667535907974</v>
+      </c>
+      <c r="O62">
+        <v>-21.51554602425642</v>
+      </c>
+      <c r="P62">
+        <v>-125.851207566541</v>
+      </c>
+      <c r="Q62">
+        <v>617.148792433459</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1421810600081901</v>
+      </c>
+      <c r="T62">
+        <v>2.224459481660416</v>
+      </c>
+      <c r="U62">
+        <v>0.1636</v>
+      </c>
+      <c r="V62">
+        <v>0.1248239780352851</v>
+      </c>
+      <c r="W62">
+        <v>0.1431787971934274</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.8549587536663366</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1439577023193324</v>
+      </c>
+      <c r="C63">
+        <v>889.6333524135716</v>
+      </c>
+      <c r="D63">
+        <v>6768.61446852047</v>
+      </c>
+      <c r="E63">
+        <v>-752.5075988224435</v>
+      </c>
+      <c r="F63">
+        <v>6313.981116106898</v>
+      </c>
+      <c r="G63">
+        <v>435</v>
+      </c>
+      <c r="H63">
+        <v>3284.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K63">
+        <v>743</v>
+      </c>
+      <c r="L63">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M63">
+        <v>1032.967310595089</v>
+      </c>
+      <c r="N63">
+        <v>-164.3006439284218</v>
+      </c>
+      <c r="O63">
+        <v>-23.98789401354958</v>
+      </c>
+      <c r="P63">
+        <v>-140.3127499148722</v>
+      </c>
+      <c r="Q63">
+        <v>602.6872500851277</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1446523692391693</v>
+      </c>
+      <c r="T63">
+        <v>2.281496904267094</v>
+      </c>
+      <c r="U63">
+        <v>0.1636</v>
+      </c>
+      <c r="V63">
+        <v>0.1227776833133952</v>
+      </c>
+      <c r="W63">
+        <v>0.1435135710099285</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.840943036393118</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1451357023193324</v>
+      </c>
+      <c r="C64">
+        <v>705.8579717272114</v>
+      </c>
+      <c r="D64">
+        <v>6688.346974983403</v>
+      </c>
+      <c r="E64">
+        <v>-648.9997116731502</v>
+      </c>
+      <c r="F64">
+        <v>6417.489003256192</v>
+      </c>
+      <c r="G64">
+        <v>435</v>
+      </c>
+      <c r="H64">
+        <v>3284.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K64">
+        <v>743</v>
+      </c>
+      <c r="L64">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M64">
+        <v>1049.901200932713</v>
+      </c>
+      <c r="N64">
+        <v>-181.2345342660462</v>
+      </c>
+      <c r="O64">
+        <v>-26.46024200284275</v>
+      </c>
+      <c r="P64">
+        <v>-154.7742922632035</v>
+      </c>
+      <c r="Q64">
+        <v>588.2257077367965</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1472537473770422</v>
+      </c>
+      <c r="T64">
+        <v>2.341536296484648</v>
+      </c>
+      <c r="U64">
+        <v>0.1636</v>
+      </c>
+      <c r="V64">
+        <v>0.120797398098663</v>
+      </c>
+      <c r="W64">
+        <v>0.1438375456710587</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.8273794390319387</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1463137023193324</v>
+      </c>
+      <c r="C65">
+        <v>523.9640282022474</v>
+      </c>
+      <c r="D65">
+        <v>6609.960918607733</v>
+      </c>
+      <c r="E65">
+        <v>-545.4918245238559</v>
+      </c>
+      <c r="F65">
+        <v>6520.996890405486</v>
+      </c>
+      <c r="G65">
+        <v>435</v>
+      </c>
+      <c r="H65">
+        <v>3284.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K65">
+        <v>743</v>
+      </c>
+      <c r="L65">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M65">
+        <v>1066.835091270337</v>
+      </c>
+      <c r="N65">
+        <v>-198.1684246036707</v>
+      </c>
+      <c r="O65">
+        <v>-28.93258999213592</v>
+      </c>
+      <c r="P65">
+        <v>-169.2358346115348</v>
+      </c>
+      <c r="Q65">
+        <v>573.7641653884652</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1499957405493947</v>
+      </c>
+      <c r="T65">
+        <v>2.404821061254504</v>
+      </c>
+      <c r="U65">
+        <v>0.1636</v>
+      </c>
+      <c r="V65">
+        <v>0.1188799790812239</v>
+      </c>
+      <c r="W65">
+        <v>0.1441512354223118</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.8142464320631777</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1474917023193325</v>
+      </c>
+      <c r="C66">
+        <v>343.8861379501568</v>
+      </c>
+      <c r="D66">
+        <v>6533.390915504936</v>
+      </c>
+      <c r="E66">
+        <v>-441.9839373745626</v>
+      </c>
+      <c r="F66">
+        <v>6624.504777554779</v>
+      </c>
+      <c r="G66">
+        <v>435</v>
+      </c>
+      <c r="H66">
+        <v>3284.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K66">
+        <v>743</v>
+      </c>
+      <c r="L66">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M66">
+        <v>1083.768981607962</v>
+      </c>
+      <c r="N66">
+        <v>-215.1023149412952</v>
+      </c>
+      <c r="O66">
+        <v>-31.40493798142909</v>
+      </c>
+      <c r="P66">
+        <v>-183.6973769598661</v>
+      </c>
+      <c r="Q66">
+        <v>559.302623040134</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1528900666757667</v>
+      </c>
+      <c r="T66">
+        <v>2.471621646289352</v>
+      </c>
+      <c r="U66">
+        <v>0.1636</v>
+      </c>
+      <c r="V66">
+        <v>0.1170224794080798</v>
+      </c>
+      <c r="W66">
+        <v>0.1444551223688381</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.8015238315621904</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1833546706004069</v>
+      </c>
+      <c r="C67">
+        <v>-1462.993871337173</v>
+      </c>
+      <c r="D67">
+        <v>4830.018793366899</v>
+      </c>
+      <c r="E67">
+        <v>-338.4760502252693</v>
+      </c>
+      <c r="F67">
+        <v>6728.012664704072</v>
+      </c>
+      <c r="G67">
+        <v>435</v>
+      </c>
+      <c r="H67">
+        <v>3284.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K67">
+        <v>743</v>
+      </c>
+      <c r="L67">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M67">
+        <v>1451.905133043139</v>
+      </c>
+      <c r="N67">
+        <v>-583.2384663764722</v>
+      </c>
+      <c r="O67">
+        <v>-85.15281609096493</v>
+      </c>
+      <c r="P67">
+        <v>-498.0856502855072</v>
+      </c>
+      <c r="Q67">
+        <v>244.9143497144928</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1581068350981444</v>
+      </c>
+      <c r="T67">
+        <v>2.592023828832255</v>
+      </c>
+      <c r="U67">
+        <v>0.2158</v>
+      </c>
+      <c r="V67">
+        <v>0.08735097799917008</v>
+      </c>
+      <c r="W67">
+        <v>0.1969496589477791</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.5982943698573293</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.185054670600407</v>
+      </c>
+      <c r="C68">
+        <v>-1625.465898887081</v>
+      </c>
+      <c r="D68">
+        <v>4771.054652966285</v>
+      </c>
+      <c r="E68">
+        <v>-234.968163075976</v>
+      </c>
+      <c r="F68">
+        <v>6831.520551853366</v>
+      </c>
+      <c r="G68">
+        <v>435</v>
+      </c>
+      <c r="H68">
+        <v>3284.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K68">
+        <v>743</v>
+      </c>
+      <c r="L68">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M68">
+        <v>1474.242135089956</v>
+      </c>
+      <c r="N68">
+        <v>-605.5754684232897</v>
+      </c>
+      <c r="O68">
+        <v>-88.4140183898003</v>
+      </c>
+      <c r="P68">
+        <v>-517.1614500334895</v>
+      </c>
+      <c r="Q68">
+        <v>225.8385499665105</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1614099773069134</v>
+      </c>
+      <c r="T68">
+        <v>2.66825982379791</v>
+      </c>
+      <c r="U68">
+        <v>0.2158</v>
+      </c>
+      <c r="V68">
+        <v>0.08602747833251599</v>
+      </c>
+      <c r="W68">
+        <v>0.1972352701758431</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.5892293036473698</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.186754670600407</v>
+      </c>
+      <c r="C69">
+        <v>-1786.515638856818</v>
+      </c>
+      <c r="D69">
+        <v>4713.512800145841</v>
+      </c>
+      <c r="E69">
+        <v>-131.4602759266827</v>
+      </c>
+      <c r="F69">
+        <v>6935.028439002659</v>
+      </c>
+      <c r="G69">
+        <v>435</v>
+      </c>
+      <c r="H69">
+        <v>3284.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K69">
+        <v>743</v>
+      </c>
+      <c r="L69">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M69">
+        <v>1496.579137136774</v>
+      </c>
+      <c r="N69">
+        <v>-627.9124704701071</v>
+      </c>
+      <c r="O69">
+        <v>-91.67522068863563</v>
+      </c>
+      <c r="P69">
+        <v>-536.2372497814715</v>
+      </c>
+      <c r="Q69">
+        <v>206.7627502185285</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1649133099525774</v>
+      </c>
+      <c r="T69">
+        <v>2.749116182094816</v>
+      </c>
+      <c r="U69">
+        <v>0.2158</v>
+      </c>
+      <c r="V69">
+        <v>0.08474348611859785</v>
+      </c>
+      <c r="W69">
+        <v>0.1975123556956066</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.5804348364287524</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.188454670600407</v>
+      </c>
+      <c r="C70">
+        <v>-1946.193938979785</v>
+      </c>
+      <c r="D70">
+        <v>4657.342387172168</v>
+      </c>
+      <c r="E70">
+        <v>-27.95238877738848</v>
+      </c>
+      <c r="F70">
+        <v>7038.536326151953</v>
+      </c>
+      <c r="G70">
+        <v>435</v>
+      </c>
+      <c r="H70">
+        <v>3284.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K70">
+        <v>743</v>
+      </c>
+      <c r="L70">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M70">
+        <v>1518.916139183592</v>
+      </c>
+      <c r="N70">
+        <v>-650.2494725169249</v>
+      </c>
+      <c r="O70">
+        <v>-94.93642298747103</v>
+      </c>
+      <c r="P70">
+        <v>-555.3130495294539</v>
+      </c>
+      <c r="Q70">
+        <v>187.6869504705461</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1686356008885955</v>
+      </c>
+      <c r="T70">
+        <v>2.83502606278528</v>
+      </c>
+      <c r="U70">
+        <v>0.2158</v>
+      </c>
+      <c r="V70">
+        <v>0.08349725838155964</v>
+      </c>
+      <c r="W70">
+        <v>0.1977812916412595</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5718990300106824</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.190154670600407</v>
+      </c>
+      <c r="C71">
+        <v>-2104.549251745872</v>
+      </c>
+      <c r="D71">
+        <v>4602.494961555374</v>
+      </c>
+      <c r="E71">
+        <v>75.55549837190483</v>
+      </c>
+      <c r="F71">
+        <v>7142.044213301247</v>
+      </c>
+      <c r="G71">
+        <v>435</v>
+      </c>
+      <c r="H71">
+        <v>3284.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K71">
+        <v>743</v>
+      </c>
+      <c r="L71">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M71">
+        <v>1541.253141230409</v>
+      </c>
+      <c r="N71">
+        <v>-672.5864745637425</v>
+      </c>
+      <c r="O71">
+        <v>-98.1976252863064</v>
+      </c>
+      <c r="P71">
+        <v>-574.3888492774361</v>
+      </c>
+      <c r="Q71">
+        <v>168.6111507225639</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1725980396269373</v>
+      </c>
+      <c r="T71">
+        <v>2.926478516423515</v>
+      </c>
+      <c r="U71">
+        <v>0.2158</v>
+      </c>
+      <c r="V71">
+        <v>0.08228715318762397</v>
+      </c>
+      <c r="W71">
+        <v>0.1980424323421108</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.5636106382713971</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.191854670600407</v>
+      </c>
+      <c r="C72">
+        <v>-2261.627773798384</v>
+      </c>
+      <c r="D72">
+        <v>4548.924326652156</v>
+      </c>
+      <c r="E72">
+        <v>179.0633855211981</v>
+      </c>
+      <c r="F72">
+        <v>7245.55210045054</v>
+      </c>
+      <c r="G72">
+        <v>435</v>
+      </c>
+      <c r="H72">
+        <v>3284.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K72">
+        <v>743</v>
+      </c>
+      <c r="L72">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M72">
+        <v>1563.590143277227</v>
+      </c>
+      <c r="N72">
+        <v>-694.9234766105599</v>
+      </c>
+      <c r="O72">
+        <v>-101.4588275851417</v>
+      </c>
+      <c r="P72">
+        <v>-593.4646490254181</v>
+      </c>
+      <c r="Q72">
+        <v>149.5353509745819</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1768246409478351</v>
+      </c>
+      <c r="T72">
+        <v>3.024027800304298</v>
+      </c>
+      <c r="U72">
+        <v>0.2158</v>
+      </c>
+      <c r="V72">
+        <v>0.08111162242780079</v>
+      </c>
+      <c r="W72">
+        <v>0.1982961118800806</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.555559057724663</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.193554670600407</v>
+      </c>
+      <c r="C73">
+        <v>-2417.473575707896</v>
+      </c>
+      <c r="D73">
+        <v>4496.586411891936</v>
+      </c>
+      <c r="E73">
+        <v>282.5712726704905</v>
+      </c>
+      <c r="F73">
+        <v>7349.059987599832</v>
+      </c>
+      <c r="G73">
+        <v>435</v>
+      </c>
+      <c r="H73">
+        <v>3284.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K73">
+        <v>743</v>
+      </c>
+      <c r="L73">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M73">
+        <v>1585.927145324044</v>
+      </c>
+      <c r="N73">
+        <v>-717.2604786573772</v>
+      </c>
+      <c r="O73">
+        <v>-104.7200298839771</v>
+      </c>
+      <c r="P73">
+        <v>-612.5404487734002</v>
+      </c>
+      <c r="Q73">
+        <v>130.4595512265998</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1813427320150019</v>
+      </c>
+      <c r="T73">
+        <v>3.128304621004446</v>
+      </c>
+      <c r="U73">
+        <v>0.2158</v>
+      </c>
+      <c r="V73">
+        <v>0.07996920521050782</v>
+      </c>
+      <c r="W73">
+        <v>0.1985426455155724</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.5477342822637523</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.195254670600407</v>
+      </c>
+      <c r="C74">
+        <v>-2572.128722889326</v>
+      </c>
+      <c r="D74">
+        <v>4445.439151859799</v>
+      </c>
+      <c r="E74">
+        <v>386.0791598197839</v>
+      </c>
+      <c r="F74">
+        <v>7452.567874749126</v>
+      </c>
+      <c r="G74">
+        <v>435</v>
+      </c>
+      <c r="H74">
+        <v>3284.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K74">
+        <v>743</v>
+      </c>
+      <c r="L74">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M74">
+        <v>1608.264147370862</v>
+      </c>
+      <c r="N74">
+        <v>-739.5974807041948</v>
+      </c>
+      <c r="O74">
+        <v>-107.9812321828124</v>
+      </c>
+      <c r="P74">
+        <v>-631.6162485213824</v>
+      </c>
+      <c r="Q74">
+        <v>111.3837514786176</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1861835438726805</v>
+      </c>
+      <c r="T74">
+        <v>3.240029786040319</v>
+      </c>
+      <c r="U74">
+        <v>0.2158</v>
+      </c>
+      <c r="V74">
+        <v>0.07885852180480633</v>
+      </c>
+      <c r="W74">
+        <v>0.1987823309945228</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.5401268616767556</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.196954670600407</v>
+      </c>
+      <c r="C75">
+        <v>-2725.633388359418</v>
+      </c>
+      <c r="D75">
+        <v>4395.442373539002</v>
+      </c>
+      <c r="E75">
+        <v>489.5870469690781</v>
+      </c>
+      <c r="F75">
+        <v>7556.07576189842</v>
+      </c>
+      <c r="G75">
+        <v>435</v>
+      </c>
+      <c r="H75">
+        <v>3284.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K75">
+        <v>743</v>
+      </c>
+      <c r="L75">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M75">
+        <v>1630.601149417679</v>
+      </c>
+      <c r="N75">
+        <v>-761.9344827510124</v>
+      </c>
+      <c r="O75">
+        <v>-111.2424344816478</v>
+      </c>
+      <c r="P75">
+        <v>-650.6920482693646</v>
+      </c>
+      <c r="Q75">
+        <v>92.30795173063541</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1913829343864835</v>
+      </c>
+      <c r="T75">
+        <v>3.360030889226997</v>
+      </c>
+      <c r="U75">
+        <v>0.2158</v>
+      </c>
+      <c r="V75">
+        <v>0.07777826808145281</v>
+      </c>
+      <c r="W75">
+        <v>0.1990154497480225</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.5327278635715946</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.198654670600407</v>
+      </c>
+      <c r="C76">
+        <v>-2878.025957969938</v>
+      </c>
+      <c r="D76">
+        <v>4346.557691077775</v>
+      </c>
+      <c r="E76">
+        <v>593.0949341183714</v>
+      </c>
+      <c r="F76">
+        <v>7659.583649047713</v>
+      </c>
+      <c r="G76">
+        <v>435</v>
+      </c>
+      <c r="H76">
+        <v>3284.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K76">
+        <v>743</v>
+      </c>
+      <c r="L76">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M76">
+        <v>1652.938151464497</v>
+      </c>
+      <c r="N76">
+        <v>-784.27148479783</v>
+      </c>
+      <c r="O76">
+        <v>-114.5036367804832</v>
+      </c>
+      <c r="P76">
+        <v>-669.7678480173469</v>
+      </c>
+      <c r="Q76">
+        <v>73.23215198265314</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1969822780167328</v>
+      </c>
+      <c r="T76">
+        <v>3.489262846504959</v>
+      </c>
+      <c r="U76">
+        <v>0.2158</v>
+      </c>
+      <c r="V76">
+        <v>0.07672721040467641</v>
+      </c>
+      <c r="W76">
+        <v>0.1992422679946708</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.5255288383881946</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.200354670600407</v>
+      </c>
+      <c r="C77">
+        <v>-3029.343128695891</v>
+      </c>
+      <c r="D77">
+        <v>4298.748407501115</v>
+      </c>
+      <c r="E77">
+        <v>696.6028212676647</v>
+      </c>
+      <c r="F77">
+        <v>7763.091536197006</v>
+      </c>
+      <c r="G77">
+        <v>435</v>
+      </c>
+      <c r="H77">
+        <v>3284.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K77">
+        <v>743</v>
+      </c>
+      <c r="L77">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M77">
+        <v>1675.275153511314</v>
+      </c>
+      <c r="N77">
+        <v>-806.6084868446474</v>
+      </c>
+      <c r="O77">
+        <v>-117.7648390793185</v>
+      </c>
+      <c r="P77">
+        <v>-688.8436477653288</v>
+      </c>
+      <c r="Q77">
+        <v>54.1563522346712</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2030295691374022</v>
+      </c>
+      <c r="T77">
+        <v>3.628833360365157</v>
+      </c>
+      <c r="U77">
+        <v>0.2158</v>
+      </c>
+      <c r="V77">
+        <v>0.07570418093261407</v>
+      </c>
+      <c r="W77">
+        <v>0.1994630377547419</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.5185217872096854</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.202054670600407</v>
+      </c>
+      <c r="C78">
+        <v>-3179.620000507669</v>
+      </c>
+      <c r="D78">
+        <v>4251.979422838631</v>
+      </c>
+      <c r="E78">
+        <v>800.110708416958</v>
+      </c>
+      <c r="F78">
+        <v>7866.5994233463</v>
+      </c>
+      <c r="G78">
+        <v>435</v>
+      </c>
+      <c r="H78">
+        <v>3284.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K78">
+        <v>743</v>
+      </c>
+      <c r="L78">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M78">
+        <v>1697.612155558132</v>
+      </c>
+      <c r="N78">
+        <v>-828.9454888914649</v>
+      </c>
+      <c r="O78">
+        <v>-121.0260413781539</v>
+      </c>
+      <c r="P78">
+        <v>-707.9194475133111</v>
+      </c>
+      <c r="Q78">
+        <v>35.08055248668893</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2095808011847939</v>
+      </c>
+      <c r="T78">
+        <v>3.780034750380373</v>
+      </c>
+      <c r="U78">
+        <v>0.2158</v>
+      </c>
+      <c r="V78">
+        <v>0.07470807328876387</v>
+      </c>
+      <c r="W78">
+        <v>0.1996779977842848</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.5116991321148212</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.203754670600407</v>
+      </c>
+      <c r="C79">
+        <v>-3328.890162310505</v>
+      </c>
+      <c r="D79">
+        <v>4206.217148185088</v>
+      </c>
+      <c r="E79">
+        <v>903.6185955662513</v>
+      </c>
+      <c r="F79">
+        <v>7970.107310495593</v>
+      </c>
+      <c r="G79">
+        <v>435</v>
+      </c>
+      <c r="H79">
+        <v>3284.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K79">
+        <v>743</v>
+      </c>
+      <c r="L79">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M79">
+        <v>1719.949157604949</v>
+      </c>
+      <c r="N79">
+        <v>-851.2824909382823</v>
+      </c>
+      <c r="O79">
+        <v>-124.2872436769892</v>
+      </c>
+      <c r="P79">
+        <v>-726.9952472612931</v>
+      </c>
+      <c r="Q79">
+        <v>16.00475273870688</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2167017055841328</v>
+      </c>
+      <c r="T79">
+        <v>3.944384087353431</v>
+      </c>
+      <c r="U79">
+        <v>0.2158</v>
+      </c>
+      <c r="V79">
+        <v>0.07373783857072799</v>
+      </c>
+      <c r="W79">
+        <v>0.1998873744364369</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.5050536888406028</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2291434597542462</v>
+      </c>
+      <c r="C80">
+        <v>-4014.860933348194</v>
+      </c>
+      <c r="D80">
+        <v>3623.754264296694</v>
+      </c>
+      <c r="E80">
+        <v>1007.126482715546</v>
+      </c>
+      <c r="F80">
+        <v>8073.615197644887</v>
+      </c>
+      <c r="G80">
+        <v>435</v>
+      </c>
+      <c r="H80">
+        <v>3284.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K80">
+        <v>743</v>
+      </c>
+      <c r="L80">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M80">
+        <v>1984.494615581114</v>
+      </c>
+      <c r="N80">
+        <v>-1115.827948914447</v>
+      </c>
+      <c r="O80">
+        <v>-162.9108805415092</v>
+      </c>
+      <c r="P80">
+        <v>-952.9170683729376</v>
+      </c>
+      <c r="Q80">
+        <v>-209.9170683729376</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2257826429008624</v>
+      </c>
+      <c r="T80">
+        <v>4.153970671220082</v>
+      </c>
+      <c r="U80">
+        <v>0.2458</v>
+      </c>
+      <c r="V80">
+        <v>0.06390812670267461</v>
+      </c>
+      <c r="W80">
+        <v>0.2300913824564826</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.4377268952237987</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2311434597542462</v>
+      </c>
+      <c r="C81">
+        <v>-4157.471945788247</v>
+      </c>
+      <c r="D81">
+        <v>3584.651139005933</v>
+      </c>
+      <c r="E81">
+        <v>1110.634369864839</v>
+      </c>
+      <c r="F81">
+        <v>8177.123084794181</v>
+      </c>
+      <c r="G81">
+        <v>435</v>
+      </c>
+      <c r="H81">
+        <v>3284.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K81">
+        <v>743</v>
+      </c>
+      <c r="L81">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M81">
+        <v>2009.93685424241</v>
+      </c>
+      <c r="N81">
+        <v>-1141.270187575743</v>
+      </c>
+      <c r="O81">
+        <v>-166.6254473860585</v>
+      </c>
+      <c r="P81">
+        <v>-974.6447401896845</v>
+      </c>
+      <c r="Q81">
+        <v>-231.6447401896845</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2343532449437607</v>
+      </c>
+      <c r="T81">
+        <v>4.351778798421039</v>
+      </c>
+      <c r="U81">
+        <v>0.2458</v>
+      </c>
+      <c r="V81">
+        <v>0.06309916307352682</v>
+      </c>
+      <c r="W81">
+        <v>0.2302902257165271</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.4321860484488139</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2331434597542462</v>
+      </c>
+      <c r="C82">
+        <v>-4299.248061182159</v>
+      </c>
+      <c r="D82">
+        <v>3546.382910761315</v>
+      </c>
+      <c r="E82">
+        <v>1214.142257014132</v>
+      </c>
+      <c r="F82">
+        <v>8280.630971943474</v>
+      </c>
+      <c r="G82">
+        <v>435</v>
+      </c>
+      <c r="H82">
+        <v>3284.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K82">
+        <v>743</v>
+      </c>
+      <c r="L82">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M82">
+        <v>2035.379092903706</v>
+      </c>
+      <c r="N82">
+        <v>-1166.712426237039</v>
+      </c>
+      <c r="O82">
+        <v>-170.3400142306077</v>
+      </c>
+      <c r="P82">
+        <v>-996.3724120064317</v>
+      </c>
+      <c r="Q82">
+        <v>-253.3724120064317</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2437809071909487</v>
+      </c>
+      <c r="T82">
+        <v>4.569367738342091</v>
+      </c>
+      <c r="U82">
+        <v>0.2458</v>
+      </c>
+      <c r="V82">
+        <v>0.06231042353510775</v>
+      </c>
+      <c r="W82">
+        <v>0.2304840978950705</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.4267837228432038</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2351434597542462</v>
+      </c>
+      <c r="C83">
+        <v>-4440.21573611989</v>
+      </c>
+      <c r="D83">
+        <v>3508.923122972878</v>
+      </c>
+      <c r="E83">
+        <v>1317.650144163425</v>
+      </c>
+      <c r="F83">
+        <v>8384.138859092767</v>
+      </c>
+      <c r="G83">
+        <v>435</v>
+      </c>
+      <c r="H83">
+        <v>3284.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K83">
+        <v>743</v>
+      </c>
+      <c r="L83">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M83">
+        <v>2060.821331565002</v>
+      </c>
+      <c r="N83">
+        <v>-1192.154664898336</v>
+      </c>
+      <c r="O83">
+        <v>-174.054581075157</v>
+      </c>
+      <c r="P83">
+        <v>-1018.100083823179</v>
+      </c>
+      <c r="Q83">
+        <v>-275.1000838231786</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2542009549378407</v>
+      </c>
+      <c r="T83">
+        <v>4.809860777202201</v>
+      </c>
+      <c r="U83">
+        <v>0.2458</v>
+      </c>
+      <c r="V83">
+        <v>0.06154115904702</v>
+      </c>
+      <c r="W83">
+        <v>0.2306731831062425</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.4215147879932877</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2371434597542462</v>
+      </c>
+      <c r="C84">
+        <v>-4580.400321051062</v>
+      </c>
+      <c r="D84">
+        <v>3472.246425190998</v>
+      </c>
+      <c r="E84">
+        <v>1421.158031312719</v>
+      </c>
+      <c r="F84">
+        <v>8487.646746242061</v>
+      </c>
+      <c r="G84">
+        <v>435</v>
+      </c>
+      <c r="H84">
+        <v>3284.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K84">
+        <v>743</v>
+      </c>
+      <c r="L84">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M84">
+        <v>2086.263570226299</v>
+      </c>
+      <c r="N84">
+        <v>-1217.596903559632</v>
+      </c>
+      <c r="O84">
+        <v>-177.7691479197063</v>
+      </c>
+      <c r="P84">
+        <v>-1039.827755639926</v>
+      </c>
+      <c r="Q84">
+        <v>-296.8277556399257</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2657787857677208</v>
+      </c>
+      <c r="T84">
+        <v>5.077075264824546</v>
+      </c>
+      <c r="U84">
+        <v>0.2458</v>
+      </c>
+      <c r="V84">
+        <v>0.06079065710742219</v>
+      </c>
+      <c r="W84">
+        <v>0.2308576564829957</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.4163743637494671</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2391434597542462</v>
+      </c>
+      <c r="C85">
+        <v>-4719.826117496119</v>
+      </c>
+      <c r="D85">
+        <v>3436.328515895235</v>
+      </c>
+      <c r="E85">
+        <v>1524.665918462012</v>
+      </c>
+      <c r="F85">
+        <v>8591.154633391354</v>
+      </c>
+      <c r="G85">
+        <v>435</v>
+      </c>
+      <c r="H85">
+        <v>3284.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K85">
+        <v>743</v>
+      </c>
+      <c r="L85">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M85">
+        <v>2111.705808887595</v>
+      </c>
+      <c r="N85">
+        <v>-1243.039142220928</v>
+      </c>
+      <c r="O85">
+        <v>-181.4837147642555</v>
+      </c>
+      <c r="P85">
+        <v>-1061.555427456673</v>
+      </c>
+      <c r="Q85">
+        <v>-318.555427456673</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2787187143422927</v>
+      </c>
+      <c r="T85">
+        <v>5.375726750990697</v>
+      </c>
+      <c r="U85">
+        <v>0.2458</v>
+      </c>
+      <c r="V85">
+        <v>0.06005823955191107</v>
+      </c>
+      <c r="W85">
+        <v>0.2310376847181403</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.4113578051500759</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2411434597542461</v>
+      </c>
+      <c r="C86">
+        <v>-4858.516431742979</v>
+      </c>
+      <c r="D86">
+        <v>3401.146088797668</v>
+      </c>
+      <c r="E86">
+        <v>1628.173805611305</v>
+      </c>
+      <c r="F86">
+        <v>8694.662520540647</v>
+      </c>
+      <c r="G86">
+        <v>435</v>
+      </c>
+      <c r="H86">
+        <v>3284.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K86">
+        <v>743</v>
+      </c>
+      <c r="L86">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M86">
+        <v>2137.148047548891</v>
+      </c>
+      <c r="N86">
+        <v>-1268.481380882224</v>
+      </c>
+      <c r="O86">
+        <v>-185.1982816088047</v>
+      </c>
+      <c r="P86">
+        <v>-1083.28309927342</v>
+      </c>
+      <c r="Q86">
+        <v>-340.2830992734196</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2932761339886858</v>
+      </c>
+      <c r="T86">
+        <v>5.711709672927612</v>
+      </c>
+      <c r="U86">
+        <v>0.2458</v>
+      </c>
+      <c r="V86">
+        <v>0.05934326050962643</v>
+      </c>
+      <c r="W86">
+        <v>0.2312134265667338</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.4064606884220988</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2431434597542461</v>
+      </c>
+      <c r="C87">
+        <v>-4996.493625278541</v>
+      </c>
+      <c r="D87">
+        <v>3366.676782411399</v>
+      </c>
+      <c r="E87">
+        <v>1731.681692760599</v>
+      </c>
+      <c r="F87">
+        <v>8798.17040768994</v>
+      </c>
+      <c r="G87">
+        <v>435</v>
+      </c>
+      <c r="H87">
+        <v>3284.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K87">
+        <v>743</v>
+      </c>
+      <c r="L87">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M87">
+        <v>2162.590286210188</v>
+      </c>
+      <c r="N87">
+        <v>-1293.923619543521</v>
+      </c>
+      <c r="O87">
+        <v>-188.912848453354</v>
+      </c>
+      <c r="P87">
+        <v>-1105.010771090167</v>
+      </c>
+      <c r="Q87">
+        <v>-362.0107710901668</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3097745429212649</v>
+      </c>
+      <c r="T87">
+        <v>6.092490317789453</v>
+      </c>
+      <c r="U87">
+        <v>0.2458</v>
+      </c>
+      <c r="V87">
+        <v>0.05864510450363082</v>
+      </c>
+      <c r="W87">
+        <v>0.2313850333130076</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.4016787979700741</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2451434597542462</v>
+      </c>
+      <c r="C88">
+        <v>-5133.77916218431</v>
+      </c>
+      <c r="D88">
+        <v>3332.899132654924</v>
+      </c>
+      <c r="E88">
+        <v>1835.189579909892</v>
+      </c>
+      <c r="F88">
+        <v>8901.678294839234</v>
+      </c>
+      <c r="G88">
+        <v>435</v>
+      </c>
+      <c r="H88">
+        <v>3284.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K88">
+        <v>743</v>
+      </c>
+      <c r="L88">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M88">
+        <v>2188.032524871484</v>
+      </c>
+      <c r="N88">
+        <v>-1319.365858204817</v>
+      </c>
+      <c r="O88">
+        <v>-192.6274152979033</v>
+      </c>
+      <c r="P88">
+        <v>-1126.738442906914</v>
+      </c>
+      <c r="Q88">
+        <v>-383.7384429069139</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.328629867415641</v>
+      </c>
+      <c r="T88">
+        <v>6.527668197631558</v>
+      </c>
+      <c r="U88">
+        <v>0.2458</v>
+      </c>
+      <c r="V88">
+        <v>0.05796318468382116</v>
+      </c>
+      <c r="W88">
+        <v>0.2315526492047168</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3970081142727477</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2471434597542462</v>
+      </c>
+      <c r="C89">
+        <v>-5270.393653707273</v>
+      </c>
+      <c r="D89">
+        <v>3299.792528281254</v>
+      </c>
+      <c r="E89">
+        <v>1938.697467059185</v>
+      </c>
+      <c r="F89">
+        <v>9005.186181988527</v>
+      </c>
+      <c r="G89">
+        <v>435</v>
+      </c>
+      <c r="H89">
+        <v>3284.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K89">
+        <v>743</v>
+      </c>
+      <c r="L89">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M89">
+        <v>2213.47476353278</v>
+      </c>
+      <c r="N89">
+        <v>-1344.808096866114</v>
+      </c>
+      <c r="O89">
+        <v>-196.3419821424526</v>
+      </c>
+      <c r="P89">
+        <v>-1148.466114723661</v>
+      </c>
+      <c r="Q89">
+        <v>-405.4661147236611</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3503860110629979</v>
+      </c>
+      <c r="T89">
+        <v>7.029796520526292</v>
+      </c>
+      <c r="U89">
+        <v>0.2458</v>
+      </c>
+      <c r="V89">
+        <v>0.05729694118170826</v>
+      </c>
+      <c r="W89">
+        <v>0.2317164118575361</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3924448026144403</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2491434597542462</v>
+      </c>
+      <c r="C90">
+        <v>-5406.3569002005</v>
+      </c>
+      <c r="D90">
+        <v>3267.337168937321</v>
+      </c>
+      <c r="E90">
+        <v>2042.205354208479</v>
+      </c>
+      <c r="F90">
+        <v>9108.69406913782</v>
+      </c>
+      <c r="G90">
+        <v>435</v>
+      </c>
+      <c r="H90">
+        <v>3284.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K90">
+        <v>743</v>
+      </c>
+      <c r="L90">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M90">
+        <v>2238.917002194076</v>
+      </c>
+      <c r="N90">
+        <v>-1370.25033552741</v>
+      </c>
+      <c r="O90">
+        <v>-200.0565489870018</v>
+      </c>
+      <c r="P90">
+        <v>-1170.193786540408</v>
+      </c>
+      <c r="Q90">
+        <v>-427.1937865404077</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3757681786515811</v>
+      </c>
+      <c r="T90">
+        <v>7.615612897236817</v>
+      </c>
+      <c r="U90">
+        <v>0.2458</v>
+      </c>
+      <c r="V90">
+        <v>0.05664583957737068</v>
+      </c>
+      <c r="W90">
+        <v>0.2318764526318823</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3879852025847308</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2511434597542462</v>
+      </c>
+      <c r="C91">
+        <v>-5541.687930612768</v>
+      </c>
+      <c r="D91">
+        <v>3235.514025674345</v>
+      </c>
+      <c r="E91">
+        <v>2145.713241357772</v>
+      </c>
+      <c r="F91">
+        <v>9212.201956287114</v>
+      </c>
+      <c r="G91">
+        <v>435</v>
+      </c>
+      <c r="H91">
+        <v>3284.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K91">
+        <v>743</v>
+      </c>
+      <c r="L91">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M91">
+        <v>2264.359240855373</v>
+      </c>
+      <c r="N91">
+        <v>-1395.692574188706</v>
+      </c>
+      <c r="O91">
+        <v>-203.7711158315511</v>
+      </c>
+      <c r="P91">
+        <v>-1191.921458357155</v>
+      </c>
+      <c r="Q91">
+        <v>-448.921458357155</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4057652858017249</v>
+      </c>
+      <c r="T91">
+        <v>8.307941342440165</v>
+      </c>
+      <c r="U91">
+        <v>0.2458</v>
+      </c>
+      <c r="V91">
+        <v>0.05600936946975978</v>
+      </c>
+      <c r="W91">
+        <v>0.2320328969843331</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3836258182860259</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2531434597542462</v>
+      </c>
+      <c r="C92">
+        <v>-5676.40503969276</v>
+      </c>
+      <c r="D92">
+        <v>3204.304803743649</v>
+      </c>
+      <c r="E92">
+        <v>2249.221128507067</v>
+      </c>
+      <c r="F92">
+        <v>9315.709843436409</v>
+      </c>
+      <c r="G92">
+        <v>435</v>
+      </c>
+      <c r="H92">
+        <v>3284.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K92">
+        <v>743</v>
+      </c>
+      <c r="L92">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M92">
+        <v>2289.80147951667</v>
+      </c>
+      <c r="N92">
+        <v>-1421.134812850003</v>
+      </c>
+      <c r="O92">
+        <v>-207.4856826761004</v>
+      </c>
+      <c r="P92">
+        <v>-1213.649130173902</v>
+      </c>
+      <c r="Q92">
+        <v>-470.6491301739024</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4417618143818974</v>
+      </c>
+      <c r="T92">
+        <v>9.138735476684182</v>
+      </c>
+      <c r="U92">
+        <v>0.2458</v>
+      </c>
+      <c r="V92">
+        <v>0.05538704314231799</v>
+      </c>
+      <c r="W92">
+        <v>0.2321858647956183</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3793633091939589</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2551434597542461</v>
+      </c>
+      <c r="C93">
+        <v>-5810.525823060595</v>
+      </c>
+      <c r="D93">
+        <v>3173.691907525107</v>
+      </c>
+      <c r="E93">
+        <v>2352.72901565636</v>
+      </c>
+      <c r="F93">
+        <v>9419.217730585702</v>
+      </c>
+      <c r="G93">
+        <v>435</v>
+      </c>
+      <c r="H93">
+        <v>3284.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K93">
+        <v>743</v>
+      </c>
+      <c r="L93">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M93">
+        <v>2315.243718177966</v>
+      </c>
+      <c r="N93">
+        <v>-1446.577051511299</v>
+      </c>
+      <c r="O93">
+        <v>-211.2002495206496</v>
+      </c>
+      <c r="P93">
+        <v>-1235.376801990649</v>
+      </c>
+      <c r="Q93">
+        <v>-492.3768019906493</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4857575715354416</v>
+      </c>
+      <c r="T93">
+        <v>10.15415052964909</v>
+      </c>
+      <c r="U93">
+        <v>0.2458</v>
+      </c>
+      <c r="V93">
+        <v>0.05477839431657824</v>
+      </c>
+      <c r="W93">
+        <v>0.2323354706769851</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3751944816203989</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2571434597542462</v>
+      </c>
+      <c r="C94">
+        <v>-5944.067210288062</v>
+      </c>
+      <c r="D94">
+        <v>3143.658407446934</v>
+      </c>
+      <c r="E94">
+        <v>2456.236902805654</v>
+      </c>
+      <c r="F94">
+        <v>9522.725617734995</v>
+      </c>
+      <c r="G94">
+        <v>435</v>
+      </c>
+      <c r="H94">
+        <v>3284.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K94">
+        <v>743</v>
+      </c>
+      <c r="L94">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M94">
+        <v>2340.685956839262</v>
+      </c>
+      <c r="N94">
+        <v>-1472.019290172595</v>
+      </c>
+      <c r="O94">
+        <v>-214.9148163651989</v>
+      </c>
+      <c r="P94">
+        <v>-1257.104473807396</v>
+      </c>
+      <c r="Q94">
+        <v>-514.1044738073963</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.540752267977372</v>
+      </c>
+      <c r="T94">
+        <v>11.42341934585523</v>
+      </c>
+      <c r="U94">
+        <v>0.2458</v>
+      </c>
+      <c r="V94">
+        <v>0.05418297698705021</v>
+      </c>
+      <c r="W94">
+        <v>0.2324818242565831</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3711162807332207</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2591434597542462</v>
+      </c>
+      <c r="C95">
+        <v>-6077.045496118131</v>
+      </c>
+      <c r="D95">
+        <v>3114.188008766158</v>
+      </c>
+      <c r="E95">
+        <v>2559.744789954947</v>
+      </c>
+      <c r="F95">
+        <v>9626.233504884289</v>
+      </c>
+      <c r="G95">
+        <v>435</v>
+      </c>
+      <c r="H95">
+        <v>3284.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K95">
+        <v>743</v>
+      </c>
+      <c r="L95">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M95">
+        <v>2366.128195500558</v>
+      </c>
+      <c r="N95">
+        <v>-1497.461528833892</v>
+      </c>
+      <c r="O95">
+        <v>-218.6293832097482</v>
+      </c>
+      <c r="P95">
+        <v>-1278.832145624144</v>
+      </c>
+      <c r="Q95">
+        <v>-535.8321456241435</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6114597348312822</v>
+      </c>
+      <c r="T95">
+        <v>13.05533639526312</v>
+      </c>
+      <c r="U95">
+        <v>0.2458</v>
+      </c>
+      <c r="V95">
+        <v>0.05360036433127548</v>
+      </c>
+      <c r="W95">
+        <v>0.2326250304473725</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3671257830909279</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2611434597542462</v>
+      </c>
+      <c r="C96">
+        <v>-6209.476369944801</v>
+      </c>
+      <c r="D96">
+        <v>3085.265022088781</v>
+      </c>
+      <c r="E96">
+        <v>2663.25267710424</v>
+      </c>
+      <c r="F96">
+        <v>9729.741392033582</v>
+      </c>
+      <c r="G96">
+        <v>435</v>
+      </c>
+      <c r="H96">
+        <v>3284.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K96">
+        <v>743</v>
+      </c>
+      <c r="L96">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M96">
+        <v>2391.570434161855</v>
+      </c>
+      <c r="N96">
+        <v>-1522.903767495188</v>
+      </c>
+      <c r="O96">
+        <v>-222.3439500542974</v>
+      </c>
+      <c r="P96">
+        <v>-1300.559817440891</v>
+      </c>
+      <c r="Q96">
+        <v>-557.5598174408906</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7057363573031629</v>
+      </c>
+      <c r="T96">
+        <v>15.23122579447365</v>
+      </c>
+      <c r="U96">
+        <v>0.2458</v>
+      </c>
+      <c r="V96">
+        <v>0.05303014768945339</v>
+      </c>
+      <c r="W96">
+        <v>0.2327651896979324</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3632201896537904</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2631434597542461</v>
+      </c>
+      <c r="C97">
+        <v>-6341.374943665269</v>
+      </c>
+      <c r="D97">
+        <v>3056.874335517607</v>
+      </c>
+      <c r="E97">
+        <v>2766.760564253534</v>
+      </c>
+      <c r="F97">
+        <v>9833.249279182875</v>
+      </c>
+      <c r="G97">
+        <v>435</v>
+      </c>
+      <c r="H97">
+        <v>3284.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K97">
+        <v>743</v>
+      </c>
+      <c r="L97">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M97">
+        <v>2417.012672823151</v>
+      </c>
+      <c r="N97">
+        <v>-1548.346006156484</v>
+      </c>
+      <c r="O97">
+        <v>-226.0585168988466</v>
+      </c>
+      <c r="P97">
+        <v>-1322.287489257637</v>
+      </c>
+      <c r="Q97">
+        <v>-579.2874892576374</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8377236287637956</v>
+      </c>
+      <c r="T97">
+        <v>18.27747095336838</v>
+      </c>
+      <c r="U97">
+        <v>0.2458</v>
+      </c>
+      <c r="V97">
+        <v>0.05247193560851179</v>
+      </c>
+      <c r="W97">
+        <v>0.2329023982274278</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3593968192363821</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2651434597542461</v>
+      </c>
+      <c r="C98">
+        <v>-6472.755778008361</v>
+      </c>
+      <c r="D98">
+        <v>3029.001388323808</v>
+      </c>
+      <c r="E98">
+        <v>2870.268451402827</v>
+      </c>
+      <c r="F98">
+        <v>9936.757166332169</v>
+      </c>
+      <c r="G98">
+        <v>435</v>
+      </c>
+      <c r="H98">
+        <v>3284.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K98">
+        <v>743</v>
+      </c>
+      <c r="L98">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M98">
+        <v>2442.454911484447</v>
+      </c>
+      <c r="N98">
+        <v>-1573.78824481778</v>
+      </c>
+      <c r="O98">
+        <v>-229.7730837433959</v>
+      </c>
+      <c r="P98">
+        <v>-1344.015161074384</v>
+      </c>
+      <c r="Q98">
+        <v>-601.0151610743844</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.035704535954743</v>
+      </c>
+      <c r="T98">
+        <v>22.84683869171043</v>
+      </c>
+      <c r="U98">
+        <v>0.2458</v>
+      </c>
+      <c r="V98">
+        <v>0.05192535294592312</v>
+      </c>
+      <c r="W98">
+        <v>0.2330367482458921</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3556531023693364</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2671434597542461</v>
+      </c>
+      <c r="C99">
+        <v>-6603.632907435577</v>
+      </c>
+      <c r="D99">
+        <v>3001.632146045885</v>
+      </c>
+      <c r="E99">
+        <v>2973.77633855212</v>
+      </c>
+      <c r="F99">
+        <v>10040.26505348146</v>
+      </c>
+      <c r="G99">
+        <v>435</v>
+      </c>
+      <c r="H99">
+        <v>3284.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K99">
+        <v>743</v>
+      </c>
+      <c r="L99">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M99">
+        <v>2467.897150145744</v>
+      </c>
+      <c r="N99">
+        <v>-1599.230483479077</v>
+      </c>
+      <c r="O99">
+        <v>-233.4876505879452</v>
+      </c>
+      <c r="P99">
+        <v>-1365.742832891132</v>
+      </c>
+      <c r="Q99">
+        <v>-622.7428328911317</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.365672714606323</v>
+      </c>
+      <c r="T99">
+        <v>30.46245158894724</v>
+      </c>
+      <c r="U99">
+        <v>0.2458</v>
+      </c>
+      <c r="V99">
+        <v>0.05139004002895484</v>
+      </c>
+      <c r="W99">
+        <v>0.2331683281608829</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3519865755407866</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2691434597542461</v>
+      </c>
+      <c r="C100">
+        <v>-6734.019863704232</v>
+      </c>
+      <c r="D100">
+        <v>2974.753076926524</v>
+      </c>
+      <c r="E100">
+        <v>3077.284225701414</v>
+      </c>
+      <c r="F100">
+        <v>10143.77294063076</v>
+      </c>
+      <c r="G100">
+        <v>435</v>
+      </c>
+      <c r="H100">
+        <v>3284.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K100">
+        <v>743</v>
+      </c>
+      <c r="L100">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M100">
+        <v>2493.33938880704</v>
+      </c>
+      <c r="N100">
+        <v>-1624.672722140373</v>
+      </c>
+      <c r="O100">
+        <v>-237.2022174324945</v>
+      </c>
+      <c r="P100">
+        <v>-1387.470504707879</v>
+      </c>
+      <c r="Q100">
+        <v>-644.4705047078787</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.025609071909485</v>
+      </c>
+      <c r="T100">
+        <v>45.69367738342086</v>
+      </c>
+      <c r="U100">
+        <v>0.2458</v>
+      </c>
+      <c r="V100">
+        <v>0.05086565186539407</v>
+      </c>
+      <c r="W100">
+        <v>0.2332972227714862</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3483948757903704</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2711434597542462</v>
+      </c>
+      <c r="C101">
+        <v>-6863.929698175811</v>
+      </c>
+      <c r="D101">
+        <v>2948.351129604238</v>
+      </c>
+      <c r="E101">
+        <v>3180.792112850707</v>
+      </c>
+      <c r="F101">
+        <v>10247.28082778005</v>
+      </c>
+      <c r="G101">
+        <v>435</v>
+      </c>
+      <c r="H101">
+        <v>3284.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1611.666666666667</v>
+      </c>
+      <c r="K101">
+        <v>743</v>
+      </c>
+      <c r="L101">
+        <v>868.6666666666667</v>
+      </c>
+      <c r="M101">
+        <v>2518.781627468336</v>
+      </c>
+      <c r="N101">
+        <v>-1650.114960801669</v>
+      </c>
+      <c r="O101">
+        <v>-240.9167842770437</v>
+      </c>
+      <c r="P101">
+        <v>-1409.198176524626</v>
+      </c>
+      <c r="Q101">
+        <v>-666.1981765246255</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.00541814381897</v>
+      </c>
+      <c r="T101">
+        <v>91.38735476684172</v>
+      </c>
+      <c r="U101">
+        <v>0.2458</v>
+      </c>
+      <c r="V101">
+        <v>0.05035185740210727</v>
+      </c>
+      <c r="W101">
+        <v>0.2334235134505621</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3448757356308717</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_oil_gas_production_and_exploration.xlsx
@@ -641,10 +641,10 @@
         <v>-0.06038577105747795</v>
       </c>
       <c r="X2">
-        <v>0.164047143098262</v>
+        <v>0.1639711206986661</v>
       </c>
       <c r="Y2">
-        <v>-0.2244329141557399</v>
+        <v>-0.224356891756144</v>
       </c>
       <c r="Z2">
         <v>0.1924429828777939</v>
@@ -653,10 +653,10 @@
         <v>0.01113545250956988</v>
       </c>
       <c r="AB2">
-        <v>0.112803408726836</v>
+        <v>0.1127792868580713</v>
       </c>
       <c r="AC2">
-        <v>-0.1016679562172662</v>
+        <v>-0.1016438343485014</v>
       </c>
       <c r="AD2">
         <v>6960</v>
@@ -769,10 +769,10 @@
         <v>-0.06038577105747795</v>
       </c>
       <c r="X3">
-        <v>0.164047143098262</v>
+        <v>0.1639711206986661</v>
       </c>
       <c r="Y3">
-        <v>-0.2244329141557399</v>
+        <v>-0.224356891756144</v>
       </c>
       <c r="Z3">
         <v>0.1924429828777939</v>
@@ -781,10 +781,10 @@
         <v>0.01113545250956988</v>
       </c>
       <c r="AB3">
-        <v>0.112803408726836</v>
+        <v>0.1127792868580713</v>
       </c>
       <c r="AC3">
-        <v>-0.1016679562172662</v>
+        <v>-0.1016438343485014</v>
       </c>
       <c r="AD3">
         <v>6960</v>
@@ -1121,49 +1121,49 @@
         <v>0.835820895522388</v>
       </c>
       <c r="F2">
-        <v>9.934037791179881</v>
+        <v>4.59875890513933</v>
       </c>
       <c r="G2">
         <v>7.30764086342228</v>
       </c>
       <c r="H2">
-        <v>1.71264342749606</v>
+        <v>3.53232706921063</v>
       </c>
       <c r="I2">
         <v>0.6827005081010949</v>
       </c>
       <c r="J2">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="K2">
         <v>3284.3</v>
       </c>
       <c r="L2">
-        <v>15148.588217668</v>
+        <v>13577.164374751</v>
       </c>
       <c r="M2">
         <v>9915.78871492934</v>
       </c>
       <c r="N2">
-        <v>16369.7144120567</v>
+        <v>16557.9246506777</v>
       </c>
       <c r="O2">
         <v>7066.48871492934</v>
       </c>
       <c r="P2">
-        <v>1656.12619438869</v>
+        <v>3415.76027592668</v>
       </c>
       <c r="Q2">
-        <v>0.112803408726836</v>
+        <v>0.112779286858071</v>
       </c>
       <c r="R2">
-        <v>0.08638663623514529</v>
+        <v>0.0859108514969656</v>
       </c>
       <c r="S2">
         <v>0.0889868</v>
       </c>
       <c r="T2">
-        <v>0.0450912</v>
+        <v>0.0472262</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1172,20 +1172,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="W2">
-        <v>0.164047143098262</v>
+        <v>0.163971120698666</v>
       </c>
       <c r="X2">
-        <v>0.0942524336132682</v>
+        <v>0.104964485816367</v>
       </c>
       <c r="Y2">
         <v>2.72912518934564</v>
       </c>
       <c r="Z2">
-        <v>1.11827443432763</v>
+        <v>1.36638535372671</v>
       </c>
       <c r="AA2">
         <v>6960.000000000001</v>
@@ -1218,7 +1218,7 @@
         <v>3284.3</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04329999999999999</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1406,13 +1406,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08747353808480632</v>
+        <v>0.08744674570503419</v>
       </c>
       <c r="C2">
-        <v>16377.77027218834</v>
+        <v>16382.2834075724</v>
       </c>
       <c r="D2">
-        <v>15942.77027218834</v>
+        <v>15947.2834075724</v>
       </c>
       <c r="E2">
         <v>-7066.488714929342</v>
@@ -1457,19 +1457,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08747353808480632</v>
+        <v>0.08744674570503419</v>
       </c>
       <c r="T2">
         <v>0.9618186075065632</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.146</v>
       </c>
       <c r="W2">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1488,13 +1488,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08739621271920249</v>
+        <v>0.08735750345630482</v>
       </c>
       <c r="C3">
-        <v>16303.89923078644</v>
+        <v>16313.0213560497</v>
       </c>
       <c r="D3">
-        <v>15972.40711793574</v>
+        <v>15981.52924319899</v>
       </c>
       <c r="E3">
         <v>-6962.980827780048</v>
@@ -1521,37 +1521,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M3">
-        <v>5.35135776561847</v>
+        <v>5.206446723609459</v>
       </c>
       <c r="N3">
-        <v>863.3153089010483</v>
+        <v>863.4602199430573</v>
       </c>
       <c r="O3">
-        <v>126.044035099553</v>
+        <v>126.0651921116864</v>
       </c>
       <c r="P3">
-        <v>737.2712738014952</v>
+        <v>737.395027831371</v>
       </c>
       <c r="Q3">
-        <v>1480.271273801495</v>
+        <v>1480.395027831371</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08783302496889141</v>
+        <v>0.08780600147101497</v>
       </c>
       <c r="T3">
         <v>0.970115507413741</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.146</v>
       </c>
       <c r="W3">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>162.3264047580031</v>
+        <v>166.8444359043491</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1570,13 +1570,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08731888735359868</v>
+        <v>0.08726826120757548</v>
       </c>
       <c r="C4">
-        <v>16230.13858154959</v>
+        <v>16243.90670281628</v>
       </c>
       <c r="D4">
-        <v>16002.15435584818</v>
+        <v>16015.92247711487</v>
       </c>
       <c r="E4">
         <v>-6859.472940630755</v>
@@ -1603,37 +1603,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M4">
-        <v>10.70271553123694</v>
+        <v>10.41289344721892</v>
       </c>
       <c r="N4">
-        <v>857.9639511354299</v>
+        <v>858.2537732194478</v>
       </c>
       <c r="O4">
-        <v>125.2627368657728</v>
+        <v>125.3050508900394</v>
       </c>
       <c r="P4">
-        <v>732.7012142696572</v>
+        <v>732.9487223294084</v>
       </c>
       <c r="Q4">
-        <v>1475.701214269657</v>
+        <v>1475.948722329408</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08819984831999865</v>
+        <v>0.08817258898732191</v>
       </c>
       <c r="T4">
         <v>0.9785817318088204</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.146</v>
       </c>
       <c r="W4">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>81.16320237900155</v>
+        <v>83.42221795217455</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1652,13 +1652,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08724156198799485</v>
+        <v>0.08717901895884612</v>
       </c>
       <c r="C5">
-        <v>16156.48894241646</v>
+        <v>16174.9404015551</v>
       </c>
       <c r="D5">
-        <v>16032.01260386434</v>
+        <v>16050.46406300298</v>
       </c>
       <c r="E5">
         <v>-6755.965053481462</v>
@@ -1685,37 +1685,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M5">
-        <v>16.05407329685541</v>
+        <v>15.61934017082838</v>
       </c>
       <c r="N5">
-        <v>852.6125933698113</v>
+        <v>853.0473264958383</v>
       </c>
       <c r="O5">
-        <v>124.4814386319924</v>
+        <v>124.5449096683924</v>
       </c>
       <c r="P5">
-        <v>728.1311547378189</v>
+        <v>728.5024168274459</v>
       </c>
       <c r="Q5">
-        <v>1471.131154737819</v>
+        <v>1471.502416827446</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08857423503916995</v>
+        <v>0.08854673500911972</v>
       </c>
       <c r="T5">
         <v>0.9872225175316334</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.146</v>
       </c>
       <c r="W5">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>54.10880158600102</v>
+        <v>55.61481196811636</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1734,13 +1734,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08716423662239103</v>
+        <v>0.08708977671011678</v>
       </c>
       <c r="C6">
-        <v>16082.95093594636</v>
+        <v>16106.12341419411</v>
       </c>
       <c r="D6">
-        <v>16061.98248454353</v>
+        <v>16085.15496279128</v>
       </c>
       <c r="E6">
         <v>-6652.457166332168</v>
@@ -1767,37 +1767,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M6">
-        <v>21.40543106247388</v>
+        <v>20.82578689443784</v>
       </c>
       <c r="N6">
-        <v>847.2612356041928</v>
+        <v>847.840879772229</v>
       </c>
       <c r="O6">
-        <v>123.7001403982121</v>
+        <v>123.7847684467454</v>
       </c>
       <c r="P6">
-        <v>723.5610952059807</v>
+        <v>724.0561113254836</v>
       </c>
       <c r="Q6">
-        <v>1466.561095205981</v>
+        <v>1467.056111325483</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08895642148165733</v>
+        <v>0.08892867573970498</v>
       </c>
       <c r="T6">
         <v>0.9960433196236718</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.146</v>
       </c>
       <c r="W6">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>40.58160118950077</v>
+        <v>41.71110897608727</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1816,13 +1816,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08708691125678722</v>
+        <v>0.08700053446138743</v>
       </c>
       <c r="C7">
-        <v>16009.5251893625</v>
+        <v>16037.45671099559</v>
       </c>
       <c r="D7">
-        <v>16092.06462510897</v>
+        <v>16119.99614674206</v>
       </c>
       <c r="E7">
         <v>-6548.949279182874</v>
@@ -1849,37 +1849,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M7">
-        <v>26.75678882809235</v>
+        <v>26.03223361804729</v>
       </c>
       <c r="N7">
-        <v>841.9098778385744</v>
+        <v>842.6344330486195</v>
       </c>
       <c r="O7">
-        <v>122.9188421644319</v>
+        <v>123.0246272250984</v>
       </c>
       <c r="P7">
-        <v>718.9910356741425</v>
+        <v>719.609805823521</v>
       </c>
       <c r="Q7">
-        <v>1461.991035674142</v>
+        <v>1462.609805823521</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08934665395451287</v>
+        <v>0.08931865732777625</v>
       </c>
       <c r="T7">
         <v>1.005049822812385</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.146</v>
       </c>
       <c r="W7">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>32.46528095160062</v>
+        <v>33.36888718086983</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1898,13 +1898,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08700958589118341</v>
+        <v>0.08691129221265807</v>
       </c>
       <c r="C8">
-        <v>15936.21233459578</v>
+        <v>15968.94127064662</v>
       </c>
       <c r="D8">
-        <v>16122.25965749154</v>
+        <v>16154.98859354238</v>
       </c>
       <c r="E8">
         <v>-6445.441392033581</v>
@@ -1931,37 +1931,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M8">
-        <v>32.10814659371082</v>
+        <v>31.23868034165675</v>
       </c>
       <c r="N8">
-        <v>836.558520072956</v>
+        <v>837.42798632501</v>
       </c>
       <c r="O8">
-        <v>122.1375439306516</v>
+        <v>122.2644860034515</v>
       </c>
       <c r="P8">
-        <v>714.4209761423044</v>
+        <v>715.1635003215586</v>
       </c>
       <c r="Q8">
-        <v>1457.420976142304</v>
+        <v>1458.163500321559</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.0897451892459398</v>
+        <v>0.08971693639644476</v>
       </c>
       <c r="T8">
         <v>1.014247953728517</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.146</v>
       </c>
       <c r="W8">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.05440079300051</v>
+        <v>27.80740598405819</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1980,13 +1980,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08693226052557959</v>
+        <v>0.08682204996392873</v>
       </c>
       <c r="C9">
-        <v>15863.01300832901</v>
+        <v>15900.57808035066</v>
       </c>
       <c r="D9">
-        <v>16152.56821837406</v>
+        <v>16190.13329039571</v>
       </c>
       <c r="E9">
         <v>-6341.933504884288</v>
@@ -2013,37 +2013,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M9">
-        <v>37.45950435932929</v>
+        <v>36.44512706526621</v>
       </c>
       <c r="N9">
-        <v>831.2071623073374</v>
+        <v>832.2215396014005</v>
       </c>
       <c r="O9">
-        <v>121.3562456968713</v>
+        <v>121.5043447818045</v>
       </c>
       <c r="P9">
-        <v>709.8509166104661</v>
+        <v>710.7171948195961</v>
       </c>
       <c r="Q9">
-        <v>1452.850916610466</v>
+        <v>1453.717194819596</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09015229518879526</v>
+        <v>0.09012378060637498</v>
       </c>
       <c r="T9">
         <v>1.023643893911663</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.146</v>
       </c>
       <c r="W9">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.18948639400044</v>
+        <v>23.83491941490701</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2062,13 +2062,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08685493515997578</v>
+        <v>0.08673280771519938</v>
       </c>
       <c r="C10">
-        <v>15789.92785204166</v>
+        <v>15832.36813592046</v>
       </c>
       <c r="D10">
-        <v>16182.990949236</v>
+        <v>16225.4312331148</v>
       </c>
       <c r="E10">
         <v>-6238.425617734994</v>
@@ -2095,37 +2095,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M10">
-        <v>42.81086212494776</v>
+        <v>41.65157378887567</v>
       </c>
       <c r="N10">
-        <v>825.855804541719</v>
+        <v>827.0150928777911</v>
       </c>
       <c r="O10">
-        <v>120.574947463091</v>
+        <v>120.7442035601575</v>
       </c>
       <c r="P10">
-        <v>705.2808570786279</v>
+        <v>706.2708893176335</v>
       </c>
       <c r="Q10">
-        <v>1448.280857078628</v>
+        <v>1449.270889317634</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09056825126084322</v>
+        <v>0.0905394692556515</v>
       </c>
       <c r="T10">
         <v>1.033244093664007</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.146</v>
       </c>
       <c r="W10">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.29080059475038</v>
+        <v>20.85555448804364</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2144,13 +2144,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08677760979437195</v>
+        <v>0.08664356546647003</v>
       </c>
       <c r="C11">
-        <v>15716.95751205513</v>
+        <v>15764.31244187206</v>
       </c>
       <c r="D11">
-        <v>16213.52849639877</v>
+        <v>16260.88342621571</v>
       </c>
       <c r="E11">
         <v>-6134.917730585701</v>
@@ -2177,37 +2177,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M11">
-        <v>48.16221989056623</v>
+        <v>46.85802051248513</v>
       </c>
       <c r="N11">
-        <v>820.5044467761005</v>
+        <v>821.8086461541816</v>
       </c>
       <c r="O11">
-        <v>119.7936492293107</v>
+        <v>119.9840623385105</v>
       </c>
       <c r="P11">
-        <v>700.7107975467899</v>
+        <v>701.8245838156711</v>
       </c>
       <c r="Q11">
-        <v>1443.71079754679</v>
+        <v>1444.824583815671</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09099334922458456</v>
+        <v>0.09096429391919783</v>
       </c>
       <c r="T11">
         <v>1.043055286817502</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.146</v>
       </c>
       <c r="W11">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.03626719533368</v>
+        <v>18.53827065603879</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2226,13 +2226,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08670028442876813</v>
+        <v>0.08655432321774069</v>
       </c>
       <c r="C12">
-        <v>15644.10263957852</v>
+        <v>15696.41201152013</v>
       </c>
       <c r="D12">
-        <v>16244.18151107145</v>
+        <v>16296.49088301306</v>
       </c>
       <c r="E12">
         <v>-6031.409843436408</v>
@@ -2259,37 +2259,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M12">
-        <v>53.5135776561847</v>
+        <v>52.06446723609459</v>
       </c>
       <c r="N12">
-        <v>815.1530890104821</v>
+        <v>816.6021994305721</v>
       </c>
       <c r="O12">
-        <v>119.0123509955304</v>
+        <v>119.2239211168635</v>
       </c>
       <c r="P12">
-        <v>696.1407380149517</v>
+        <v>697.3782783137086</v>
       </c>
       <c r="Q12">
-        <v>1439.140738014952</v>
+        <v>1440.378278313709</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09142789380974237</v>
+        <v>0.09139855913082298</v>
       </c>
       <c r="T12">
         <v>1.053084506485519</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.146</v>
       </c>
       <c r="W12">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.23264047580031</v>
+        <v>16.68444359043491</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2308,13 +2308,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08662295906316433</v>
+        <v>0.08646508096901133</v>
       </c>
       <c r="C13">
-        <v>15571.3638907549</v>
+        <v>15628.66786707445</v>
       </c>
       <c r="D13">
-        <v>16274.95064939713</v>
+        <v>16332.25462571668</v>
       </c>
       <c r="E13">
         <v>-5927.901956287114</v>
@@ -2341,37 +2341,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M13">
-        <v>58.86493542180317</v>
+        <v>57.27091395970405</v>
       </c>
       <c r="N13">
-        <v>809.8017312448636</v>
+        <v>811.3957527069626</v>
       </c>
       <c r="O13">
-        <v>118.2310527617501</v>
+        <v>118.4637798952165</v>
       </c>
       <c r="P13">
-        <v>691.5706784831135</v>
+        <v>692.9319728117462</v>
       </c>
       <c r="Q13">
-        <v>1434.570678483114</v>
+        <v>1435.931972811746</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09187220344175767</v>
+        <v>0.09184258311124868</v>
       </c>
       <c r="T13">
         <v>1.063339101876413</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.146</v>
       </c>
       <c r="W13">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.75694588709119</v>
+        <v>15.16767599130446</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2390,13 +2390,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08654563369756051</v>
+        <v>0.08637583872028197</v>
       </c>
       <c r="C14">
-        <v>15498.7419267082</v>
+        <v>15561.08103973781</v>
       </c>
       <c r="D14">
-        <v>16305.83657249972</v>
+        <v>16368.17568552933</v>
       </c>
       <c r="E14">
         <v>-5824.394069137821</v>
@@ -2423,37 +2423,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M14">
-        <v>64.21629318742164</v>
+        <v>62.47736068331351</v>
       </c>
       <c r="N14">
-        <v>804.4503734792451</v>
+        <v>806.1893059833533</v>
       </c>
       <c r="O14">
-        <v>117.4497545279698</v>
+        <v>117.7036386735696</v>
       </c>
       <c r="P14">
-        <v>687.0006189512753</v>
+        <v>688.4856673097837</v>
       </c>
       <c r="Q14">
-        <v>1430.000618951275</v>
+        <v>1431.485667309784</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09232661101995512</v>
+        <v>0.09229669854577496</v>
       </c>
       <c r="T14">
         <v>1.073826756253464</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.146</v>
       </c>
       <c r="W14">
-        <v>0.0441518</v>
+        <v>0.0429562</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>13.52720039650026</v>
+        <v>13.90370299202909</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08659043033195669</v>
+        <v>0.08645312647155264</v>
       </c>
       <c r="C15">
-        <v>15377.32673646065</v>
+        <v>15426.45477127477</v>
       </c>
       <c r="D15">
-        <v>16287.92926940147</v>
+        <v>16337.05730421558</v>
       </c>
       <c r="E15">
         <v>-5720.886181988528</v>
@@ -2505,37 +2505,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M15">
-        <v>71.047813739275</v>
+        <v>69.70221120633418</v>
       </c>
       <c r="N15">
-        <v>797.6188529273918</v>
+        <v>798.9644554603326</v>
       </c>
       <c r="O15">
-        <v>116.4523525273992</v>
+        <v>116.6488104972086</v>
       </c>
       <c r="P15">
-        <v>681.1665003999926</v>
+        <v>682.315644963124</v>
       </c>
       <c r="Q15">
-        <v>1424.166500399993</v>
+        <v>1425.315644963124</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09279146474937551</v>
+        <v>0.09276125341557774</v>
       </c>
       <c r="T15">
         <v>1.084555506133435</v>
       </c>
       <c r="U15">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.146</v>
       </c>
       <c r="W15">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.22650805068293</v>
+        <v>12.46254102463433</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2554,13 +2554,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08652249896635288</v>
+        <v>0.08637669422282329</v>
       </c>
       <c r="C16">
-        <v>15300.98961009996</v>
+        <v>15353.72016547078</v>
       </c>
       <c r="D16">
-        <v>16315.10003019007</v>
+        <v>16367.83058556089</v>
       </c>
       <c r="E16">
         <v>-5617.378294839234</v>
@@ -2587,37 +2587,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M16">
-        <v>76.5130301807577</v>
+        <v>75.06391976066759</v>
       </c>
       <c r="N16">
-        <v>792.153636485909</v>
+        <v>793.6027469059992</v>
       </c>
       <c r="O16">
-        <v>115.6544309269427</v>
+        <v>115.8660010482759</v>
       </c>
       <c r="P16">
-        <v>676.4992055589663</v>
+        <v>677.7367458577233</v>
       </c>
       <c r="Q16">
-        <v>1419.499205558966</v>
+        <v>1420.736745857723</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09326712903064288</v>
+        <v>0.09323661188700381</v>
       </c>
       <c r="T16">
         <v>1.095533761824569</v>
       </c>
       <c r="U16">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.146</v>
       </c>
       <c r="W16">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.35318604706272</v>
+        <v>11.57235952287474</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2636,13 +2636,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08645456760074906</v>
+        <v>0.08630026197409393</v>
       </c>
       <c r="C17">
-        <v>15224.7432851913</v>
+        <v>15281.10171057443</v>
       </c>
       <c r="D17">
-        <v>16342.3615924307</v>
+        <v>16398.72001781383</v>
       </c>
       <c r="E17">
         <v>-5513.87040768994</v>
@@ -2669,37 +2669,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M17">
-        <v>81.97824662224039</v>
+        <v>80.42562831500098</v>
       </c>
       <c r="N17">
-        <v>786.6884200444264</v>
+        <v>788.2410383516658</v>
       </c>
       <c r="O17">
-        <v>114.8565093264862</v>
+        <v>115.0831915993432</v>
       </c>
       <c r="P17">
-        <v>671.8319107179401</v>
+        <v>673.1578467523226</v>
       </c>
       <c r="Q17">
-        <v>1414.83191071794</v>
+        <v>1416.157846752323</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09375398541264596</v>
+        <v>0.09372315526363992</v>
       </c>
       <c r="T17">
         <v>1.106770329414317</v>
       </c>
       <c r="U17">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.146</v>
       </c>
       <c r="W17">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.59630697725854</v>
+        <v>10.80086888801642</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2718,13 +2718,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08638663623514525</v>
+        <v>0.08622382972536458</v>
       </c>
       <c r="C18">
-        <v>15148.58821766798</v>
+        <v>15208.60006543042</v>
       </c>
       <c r="D18">
-        <v>16369.71441205667</v>
+        <v>16429.72625981911</v>
       </c>
       <c r="E18">
         <v>-5410.362520540647</v>
@@ -2751,37 +2751,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M18">
-        <v>87.44346306372309</v>
+        <v>85.78733686933438</v>
       </c>
       <c r="N18">
-        <v>781.2232036029436</v>
+        <v>782.8793297973324</v>
       </c>
       <c r="O18">
-        <v>114.0585877260298</v>
+        <v>114.3003821504105</v>
       </c>
       <c r="P18">
-        <v>667.1646158769139</v>
+        <v>668.5789476469218</v>
       </c>
       <c r="Q18">
-        <v>1410.164615876914</v>
+        <v>1411.578947646922</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09425243361326816</v>
+        <v>0.09422128300638641</v>
       </c>
       <c r="T18">
         <v>1.118274434327631</v>
       </c>
       <c r="U18">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.146</v>
       </c>
       <c r="W18">
-        <v>0.0450912</v>
+        <v>0.0442372</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.934037791179875</v>
+        <v>10.1258145825154</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2800,13 +2800,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08663810086954141</v>
+        <v>0.08639420347663521</v>
       </c>
       <c r="C19">
-        <v>14944.28219930913</v>
+        <v>15036.1366660281</v>
       </c>
       <c r="D19">
-        <v>16268.91628084712</v>
+        <v>16360.77074756608</v>
       </c>
       <c r="E19">
         <v>-5306.854633391354</v>
@@ -2833,37 +2833,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M19">
-        <v>96.77987448458936</v>
+        <v>94.14042336228238</v>
       </c>
       <c r="N19">
-        <v>771.8867921820774</v>
+        <v>774.5262433043844</v>
       </c>
       <c r="O19">
-        <v>112.6954716585833</v>
+        <v>113.0808315224401</v>
       </c>
       <c r="P19">
-        <v>659.1913205234941</v>
+        <v>661.4454117819442</v>
       </c>
       <c r="Q19">
-        <v>1402.191320523494</v>
+        <v>1404.445411781944</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09476289261390532</v>
+        <v>0.09473141382727135</v>
       </c>
       <c r="T19">
         <v>1.130055746588253</v>
       </c>
       <c r="U19">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.146</v>
       </c>
       <c r="W19">
-        <v>0.04697</v>
+        <v>0.045689</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.975695321913111</v>
+        <v>9.227350330938712</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2882,13 +2882,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08658895750393761</v>
+        <v>0.08633228922790588</v>
       </c>
       <c r="C20">
-        <v>14860.37543338707</v>
+        <v>14957.62033126245</v>
       </c>
       <c r="D20">
-        <v>16288.51740207435</v>
+        <v>16385.76229994973</v>
       </c>
       <c r="E20">
         <v>-5203.34674624206</v>
@@ -2915,37 +2915,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M20">
-        <v>102.4728082778005</v>
+        <v>99.67809532476956</v>
       </c>
       <c r="N20">
-        <v>766.1938583888663</v>
+        <v>768.9885713418972</v>
       </c>
       <c r="O20">
-        <v>111.8643033247745</v>
+        <v>112.272331415917</v>
       </c>
       <c r="P20">
-        <v>654.3295550640918</v>
+        <v>656.7162399259803</v>
       </c>
       <c r="Q20">
-        <v>1397.329555064092</v>
+        <v>1399.71623992598</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09528580183407023</v>
+        <v>0.09525398686329985</v>
       </c>
       <c r="T20">
         <v>1.142124407928403</v>
       </c>
       <c r="U20">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.146</v>
       </c>
       <c r="W20">
-        <v>0.04697</v>
+        <v>0.045689</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.477045581806827</v>
+        <v>8.714719756997674</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2964,13 +2964,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.0865398141383338</v>
+        <v>0.08627037497917654</v>
       </c>
       <c r="C21">
-        <v>14776.51595609836</v>
+        <v>14879.18046394694</v>
       </c>
       <c r="D21">
-        <v>16308.16581193494</v>
+        <v>16410.83031978352</v>
       </c>
       <c r="E21">
         <v>-5099.838859092767</v>
@@ -2997,37 +2997,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M21">
-        <v>108.1657420710116</v>
+        <v>105.2157672872568</v>
       </c>
       <c r="N21">
-        <v>760.5009245956551</v>
+        <v>763.45089937941</v>
       </c>
       <c r="O21">
-        <v>111.0331349909656</v>
+        <v>111.4638313093939</v>
       </c>
       <c r="P21">
-        <v>649.4677896046894</v>
+        <v>651.9870680700161</v>
       </c>
       <c r="Q21">
-        <v>1392.467789604689</v>
+        <v>1394.987068070016</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09582162239300468</v>
+        <v>0.09578946293725499</v>
       </c>
       <c r="T21">
         <v>1.154491060906582</v>
       </c>
       <c r="U21">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.146</v>
       </c>
       <c r="W21">
-        <v>0.04697</v>
+        <v>0.045689</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.03088528802752</v>
+        <v>8.256050296103059</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3046,13 +3046,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08674687077272997</v>
+        <v>0.08620846073044719</v>
       </c>
       <c r="C22">
-        <v>14590.5423307261</v>
+        <v>14800.81741557417</v>
       </c>
       <c r="D22">
-        <v>16225.70007371196</v>
+        <v>16435.97515856004</v>
       </c>
       <c r="E22">
         <v>-4996.330971943473</v>
@@ -3079,45 +3079,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M22">
-        <v>116.9639124787016</v>
+        <v>110.753439249744</v>
       </c>
       <c r="N22">
-        <v>751.7027541879652</v>
+        <v>757.9132274169228</v>
       </c>
       <c r="O22">
-        <v>109.7486021114429</v>
+        <v>110.6553312028707</v>
       </c>
       <c r="P22">
-        <v>641.9541520765223</v>
+        <v>647.2578962140522</v>
       </c>
       <c r="Q22">
-        <v>1384.954152076522</v>
+        <v>1390.257896214052</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09637083846591246</v>
+        <v>0.09633832591305898</v>
       </c>
       <c r="T22">
         <v>1.167166880209215</v>
       </c>
       <c r="U22">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.146</v>
       </c>
       <c r="W22">
-        <v>0.048251</v>
+        <v>0.045689</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.426792146892707</v>
+        <v>7.843247781297906</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3128,13 +3128,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08671053740712616</v>
+        <v>0.08629001848171783</v>
       </c>
       <c r="C23">
-        <v>14501.44477231654</v>
+        <v>14664.20306850865</v>
       </c>
       <c r="D23">
-        <v>16240.1104024517</v>
+        <v>16402.86869864381</v>
       </c>
       <c r="E23">
         <v>-4892.82308479418</v>
@@ -3161,37 +3161,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M23">
-        <v>122.8121081026366</v>
+        <v>118.0300437163393</v>
       </c>
       <c r="N23">
-        <v>745.8545585640301</v>
+        <v>750.6366229503275</v>
       </c>
       <c r="O23">
-        <v>108.8947655503484</v>
+        <v>109.5929469507478</v>
       </c>
       <c r="P23">
-        <v>636.9597930136817</v>
+        <v>641.0436759995797</v>
       </c>
       <c r="Q23">
-        <v>1379.959793013682</v>
+        <v>1384.04367599958</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09693395874319766</v>
+        <v>0.0969010841540732</v>
       </c>
       <c r="T23">
         <v>1.180163606329635</v>
       </c>
       <c r="U23">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.146</v>
       </c>
       <c r="W23">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.073135377993054</v>
+        <v>7.359708082073805</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3210,13 +3210,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08667420404152233</v>
+        <v>0.08623493623298847</v>
       </c>
       <c r="C24">
-        <v>14412.37283279082</v>
+        <v>14583.03989060602</v>
       </c>
       <c r="D24">
-        <v>16254.54635007527</v>
+        <v>16425.21340789048</v>
       </c>
       <c r="E24">
         <v>-4789.315197644886</v>
@@ -3243,37 +3243,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M24">
-        <v>128.6603037265717</v>
+        <v>123.6505219885459</v>
       </c>
       <c r="N24">
-        <v>740.006362940095</v>
+        <v>745.0161446781208</v>
       </c>
       <c r="O24">
-        <v>108.0409289892539</v>
+        <v>108.7723571230056</v>
       </c>
       <c r="P24">
-        <v>631.9654339508411</v>
+        <v>636.2437875551152</v>
       </c>
       <c r="Q24">
-        <v>1374.965433950841</v>
+        <v>1379.243787555115</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09751151800195171</v>
+        <v>0.09747827209357497</v>
       </c>
       <c r="T24">
         <v>1.193493581837759</v>
       </c>
       <c r="U24">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.146</v>
       </c>
       <c r="W24">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.751629224447916</v>
+        <v>7.025175896524996</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3292,13 +3292,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08663787067591852</v>
+        <v>0.08617985398425912</v>
       </c>
       <c r="C25">
-        <v>14323.32658052813</v>
+        <v>14501.93767363867</v>
       </c>
       <c r="D25">
-        <v>16269.00798496188</v>
+        <v>16447.61907807241</v>
       </c>
       <c r="E25">
         <v>-4685.807310495593</v>
@@ -3325,37 +3325,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M25">
-        <v>134.5084993505068</v>
+        <v>129.2710002607526</v>
       </c>
       <c r="N25">
-        <v>734.15816731616</v>
+        <v>739.3956664059142</v>
       </c>
       <c r="O25">
-        <v>107.1870924281593</v>
+        <v>107.9517672952635</v>
       </c>
       <c r="P25">
-        <v>626.9710748880007</v>
+        <v>631.4438991106507</v>
       </c>
       <c r="Q25">
-        <v>1369.971074888001</v>
+        <v>1374.443899110651</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09810407879989418</v>
+        <v>0.09807045192760926</v>
       </c>
       <c r="T25">
         <v>1.207169790475965</v>
       </c>
       <c r="U25">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.146</v>
       </c>
       <c r="W25">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.458080127732789</v>
+        <v>6.7197334662413</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3374,13 +3374,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08660153731031471</v>
+        <v>0.08612477173552979</v>
       </c>
       <c r="C26">
-        <v>14234.30608415123</v>
+        <v>14420.89666741818</v>
       </c>
       <c r="D26">
-        <v>16283.49537573427</v>
+        <v>16470.08595900123</v>
       </c>
       <c r="E26">
         <v>-4582.2994233463</v>
@@ -3407,37 +3407,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M26">
-        <v>140.3566949744419</v>
+        <v>134.8914785329592</v>
       </c>
       <c r="N26">
-        <v>728.3099716922248</v>
+        <v>733.7751881337076</v>
       </c>
       <c r="O26">
-        <v>106.3332558670648</v>
+        <v>107.1311774675213</v>
       </c>
       <c r="P26">
-        <v>621.97671582516</v>
+        <v>626.6440106661863</v>
       </c>
       <c r="Q26">
-        <v>1364.97671582516</v>
+        <v>1369.644010666186</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09871223330304565</v>
+        <v>0.09867821544148656</v>
       </c>
       <c r="T26">
         <v>1.221205899341491</v>
       </c>
       <c r="U26">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.146</v>
       </c>
       <c r="W26">
-        <v>0.048251</v>
+        <v>0.0463722</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.188993455743923</v>
+        <v>6.43974457181458</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3456,13 +3456,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08686410394471089</v>
+        <v>0.08606968948680044</v>
       </c>
       <c r="C27">
-        <v>14026.68043559239</v>
+        <v>14339.91712312301</v>
       </c>
       <c r="D27">
-        <v>16179.37761432472</v>
+        <v>16492.61430185534</v>
       </c>
       <c r="E27">
         <v>-4478.791536197006</v>
@@ -3489,45 +3489,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M27">
-        <v>149.8276666486022</v>
+        <v>140.5119568051658</v>
       </c>
       <c r="N27">
-        <v>718.8390000180646</v>
+        <v>728.1547098615009</v>
       </c>
       <c r="O27">
-        <v>104.9504940026374</v>
+        <v>106.3105876397791</v>
       </c>
       <c r="P27">
-        <v>613.8885060154271</v>
+        <v>621.8441222217218</v>
       </c>
       <c r="Q27">
-        <v>1356.888506015427</v>
+        <v>1364.844122221722</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09933660525961452</v>
+        <v>0.09930218598240058</v>
       </c>
       <c r="T27">
         <v>1.235616304443432</v>
       </c>
       <c r="U27">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.146</v>
       </c>
       <c r="W27">
-        <v>0.0494466</v>
+        <v>0.0463722</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>5.797772107764255</v>
+        <v>6.182154788941996</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3538,13 +3538,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08683972657910706</v>
+        <v>0.08623664723807109</v>
       </c>
       <c r="C28">
-        <v>13932.78300728927</v>
+        <v>14168.31333820553</v>
       </c>
       <c r="D28">
-        <v>16188.9880731709</v>
+        <v>16424.51840408716</v>
       </c>
       <c r="E28">
         <v>-4375.283649047713</v>
@@ -3571,37 +3571,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M28">
-        <v>155.8207733145463</v>
+        <v>148.8236401432541</v>
       </c>
       <c r="N28">
-        <v>712.8458933521205</v>
+        <v>719.8430265234126</v>
       </c>
       <c r="O28">
-        <v>104.0755004294096</v>
+        <v>105.0970818724182</v>
       </c>
       <c r="P28">
-        <v>608.7703929227109</v>
+        <v>614.7459446509944</v>
       </c>
       <c r="Q28">
-        <v>1351.770392922711</v>
+        <v>1357.745944650994</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09997785213392846</v>
+        <v>0.09994302059198795</v>
       </c>
       <c r="T28">
         <v>1.250416179953532</v>
       </c>
       <c r="U28">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.146</v>
       </c>
       <c r="W28">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.574780872850246</v>
+        <v>5.83688630267684</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3620,13 +3620,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08681534921350326</v>
+        <v>0.08619010498934174</v>
       </c>
       <c r="C29">
-        <v>13838.89700288834</v>
+        <v>14083.73172077067</v>
       </c>
       <c r="D29">
-        <v>16198.60995591926</v>
+        <v>16443.4446738016</v>
       </c>
       <c r="E29">
         <v>-4271.77576189842</v>
@@ -3653,37 +3653,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M29">
-        <v>161.8138799804904</v>
+        <v>154.54762630261</v>
       </c>
       <c r="N29">
-        <v>706.8527866861764</v>
+        <v>714.1190403640567</v>
       </c>
       <c r="O29">
-        <v>103.2005068561817</v>
+        <v>104.2613798931523</v>
       </c>
       <c r="P29">
-        <v>603.6522798299947</v>
+        <v>609.8576604709044</v>
       </c>
       <c r="Q29">
-        <v>1346.652279829995</v>
+        <v>1352.857660470904</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1006366674157579</v>
+        <v>0.1006014123141668</v>
       </c>
       <c r="T29">
         <v>1.265621531505006</v>
       </c>
       <c r="U29">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.146</v>
       </c>
       <c r="W29">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.368307507189125</v>
+        <v>5.620705328503623</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3702,13 +3702,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08679097184789943</v>
+        <v>0.08614356274061238</v>
       </c>
       <c r="C30">
-        <v>13745.02244277102</v>
+        <v>13999.19377182183</v>
       </c>
       <c r="D30">
-        <v>16208.24328295123</v>
+        <v>16462.41461200205</v>
       </c>
       <c r="E30">
         <v>-4168.267874749126</v>
@@ -3735,37 +3735,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M30">
-        <v>167.8069866464345</v>
+        <v>160.2716124619659</v>
       </c>
       <c r="N30">
-        <v>700.8596800202322</v>
+        <v>708.3950542047008</v>
       </c>
       <c r="O30">
-        <v>102.3255132829539</v>
+        <v>103.4256779138863</v>
       </c>
       <c r="P30">
-        <v>598.5341667372783</v>
+        <v>604.9693762908146</v>
       </c>
       <c r="Q30">
-        <v>1341.534166737278</v>
+        <v>1347.969376290815</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1013137831220825</v>
+        <v>0.101278092695295</v>
       </c>
       <c r="T30">
         <v>1.28124925393291</v>
       </c>
       <c r="U30">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.146</v>
       </c>
       <c r="W30">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.176582239075228</v>
+        <v>5.419965852485637</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3784,13 +3784,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08676659448229561</v>
+        <v>0.08609702049188304</v>
       </c>
       <c r="C31">
-        <v>13651.15934736722</v>
+        <v>13914.69964266767</v>
       </c>
       <c r="D31">
-        <v>16217.88807469673</v>
+        <v>16481.42836999717</v>
       </c>
       <c r="E31">
         <v>-4064.759987599833</v>
@@ -3817,37 +3817,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M31">
-        <v>173.8000933123786</v>
+        <v>165.9955986213219</v>
       </c>
       <c r="N31">
-        <v>694.8665733542882</v>
+        <v>702.6710680453449</v>
       </c>
       <c r="O31">
-        <v>101.4505197097261</v>
+        <v>102.5899759346204</v>
       </c>
       <c r="P31">
-        <v>593.4160536445621</v>
+        <v>600.0810921107245</v>
       </c>
       <c r="Q31">
-        <v>1336.416053644562</v>
+        <v>1343.081092110725</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1020099725102755</v>
+        <v>0.1019738344956099</v>
       </c>
       <c r="T31">
         <v>1.297317193893994</v>
       </c>
       <c r="U31">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.146</v>
       </c>
       <c r="W31">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.998079403245049</v>
+        <v>5.233070478261993</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3866,13 +3866,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08674221711669179</v>
+        <v>0.08605047824315368</v>
       </c>
       <c r="C32">
-        <v>13557.30773715554</v>
+        <v>13830.2494853167</v>
       </c>
       <c r="D32">
-        <v>16227.54435163434</v>
+        <v>16500.48609979551</v>
       </c>
       <c r="E32">
         <v>-3961.252100450539</v>
@@ -3899,37 +3899,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M32">
-        <v>179.7931999783227</v>
+        <v>171.7195847806778</v>
       </c>
       <c r="N32">
-        <v>688.873466688344</v>
+        <v>696.947081885989</v>
       </c>
       <c r="O32">
-        <v>100.5755261364982</v>
+        <v>101.7542739553544</v>
       </c>
       <c r="P32">
-        <v>588.2979405518458</v>
+        <v>595.1928079306346</v>
       </c>
       <c r="Q32">
-        <v>1331.297940551846</v>
+        <v>1338.192807930634</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1027260530238454</v>
+        <v>0.1026894546330767</v>
       </c>
       <c r="T32">
         <v>1.313844217853966</v>
       </c>
       <c r="U32">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.146</v>
       </c>
       <c r="W32">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.831476756470213</v>
+        <v>5.05863479565326</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3948,13 +3948,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08671783975108797</v>
+        <v>0.08600393599442434</v>
       </c>
       <c r="C33">
-        <v>13463.46763266336</v>
+        <v>13745.84345248133</v>
       </c>
       <c r="D33">
-        <v>16237.21213429145</v>
+        <v>16519.58795410943</v>
       </c>
       <c r="E33">
         <v>-3857.744213301246</v>
@@ -3981,37 +3981,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M33">
-        <v>185.7863066442667</v>
+        <v>177.4435709400337</v>
       </c>
       <c r="N33">
-        <v>682.8803600224001</v>
+        <v>691.223095726633</v>
       </c>
       <c r="O33">
-        <v>99.7005325632704</v>
+        <v>100.9185719760884</v>
       </c>
       <c r="P33">
-        <v>583.1798274591297</v>
+        <v>590.3045237505446</v>
       </c>
       <c r="Q33">
-        <v>1326.17982745913</v>
+        <v>1333.304523750545</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1034628894943304</v>
+        <v>0.1034258173832237</v>
       </c>
       <c r="T33">
         <v>1.33085028598669</v>
       </c>
       <c r="U33">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.146</v>
       </c>
       <c r="W33">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.675622667551819</v>
+        <v>4.895453028051543</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4030,13 +4030,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08669346238548414</v>
+        <v>0.08595739374569498</v>
       </c>
       <c r="C34">
-        <v>13369.63905446701</v>
+        <v>13661.48169758194</v>
       </c>
       <c r="D34">
-        <v>16246.8914432444</v>
+        <v>16538.73408635933</v>
       </c>
       <c r="E34">
         <v>-3754.236326151952</v>
@@ -4063,37 +4063,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M34">
-        <v>191.7794133102109</v>
+        <v>183.1675570993897</v>
       </c>
       <c r="N34">
-        <v>676.8872533564559</v>
+        <v>685.4991095672771</v>
       </c>
       <c r="O34">
-        <v>98.82553899004255</v>
+        <v>100.0828699968224</v>
       </c>
       <c r="P34">
-        <v>578.0617143664133</v>
+        <v>585.4162395704546</v>
       </c>
       <c r="Q34">
-        <v>1321.061714366413</v>
+        <v>1328.416239570455</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.104221397625712</v>
+        <v>0.1041838378613162</v>
       </c>
       <c r="T34">
         <v>1.348356532593907</v>
       </c>
       <c r="U34">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.146</v>
       </c>
       <c r="W34">
-        <v>0.0494466</v>
+        <v>0.0472262</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.529509459190824</v>
+        <v>4.742470120924931</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4112,13 +4112,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08740181701988034</v>
+        <v>0.08591085149696563</v>
       </c>
       <c r="C35">
-        <v>12989.49515300963</v>
+        <v>13577.16437475099</v>
       </c>
       <c r="D35">
-        <v>15970.25542893631</v>
+        <v>16557.92465067768</v>
       </c>
       <c r="E35">
         <v>-3650.728439002659</v>
@@ -4145,45 +4145,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M35">
-        <v>206.6534966935643</v>
+        <v>188.8915432587456</v>
       </c>
       <c r="N35">
-        <v>662.0131699731024</v>
+        <v>679.7751234079212</v>
       </c>
       <c r="O35">
-        <v>96.65392281607295</v>
+        <v>99.24716801755649</v>
       </c>
       <c r="P35">
-        <v>565.3592471570295</v>
+        <v>580.5279553903647</v>
       </c>
       <c r="Q35">
-        <v>1308.35924715703</v>
+        <v>1323.527955390365</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1050025477908662</v>
+        <v>0.1049644858163666</v>
       </c>
       <c r="T35">
         <v>1.366385353726712</v>
       </c>
       <c r="U35">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.146</v>
       </c>
       <c r="W35">
-        <v>0.051667</v>
+        <v>0.0472262</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.203493676929005</v>
+        <v>4.598758905139328</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4194,13 +4194,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08739964365427652</v>
+        <v>0.08659020924823629</v>
       </c>
       <c r="C36">
-        <v>12886.82162886887</v>
+        <v>13197.88554492432</v>
       </c>
       <c r="D36">
-        <v>15971.08979194484</v>
+        <v>16282.1537080003</v>
       </c>
       <c r="E36">
         <v>-3547.220551853365</v>
@@ -4227,37 +4227,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M36">
-        <v>212.9157238660966</v>
+        <v>203.4136998257915</v>
       </c>
       <c r="N36">
-        <v>655.7509428005701</v>
+        <v>665.2529668408753</v>
       </c>
       <c r="O36">
-        <v>95.73963764888323</v>
+        <v>97.12693315876778</v>
       </c>
       <c r="P36">
-        <v>560.0113051516869</v>
+        <v>568.1260336821075</v>
       </c>
       <c r="Q36">
-        <v>1303.011305151687</v>
+        <v>1311.126033682107</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1058073691731463</v>
+        <v>0.105768789770055</v>
       </c>
       <c r="T36">
         <v>1.384960502772633</v>
       </c>
       <c r="U36">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.146</v>
       </c>
       <c r="W36">
-        <v>0.051667</v>
+        <v>0.0493612</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.079861509960505</v>
+        <v>4.270443275996723</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4276,13 +4276,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.0882045002886727</v>
+        <v>0.08656501699950692</v>
       </c>
       <c r="C37">
-        <v>12480.17521891949</v>
+        <v>13104.43981636721</v>
       </c>
       <c r="D37">
-        <v>15667.95126914476</v>
+        <v>16292.21586659248</v>
       </c>
       <c r="E37">
         <v>-3443.712664704072</v>
@@ -4309,45 +4309,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M37">
-        <v>228.9594463742371</v>
+        <v>209.3964557030206</v>
       </c>
       <c r="N37">
-        <v>639.7072202924296</v>
+        <v>659.2702109636462</v>
       </c>
       <c r="O37">
-        <v>93.39725416269472</v>
+        <v>96.25345080069233</v>
       </c>
       <c r="P37">
-        <v>546.3099661297349</v>
+        <v>563.0167601629538</v>
       </c>
       <c r="Q37">
-        <v>1289.309966129735</v>
+        <v>1306.016760162954</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1066369542902657</v>
+        <v>0.106597841537703</v>
       </c>
       <c r="T37">
         <v>1.40410719486612</v>
       </c>
       <c r="U37">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0.146</v>
       </c>
       <c r="W37">
-        <v>0.0539728</v>
+        <v>0.0493612</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.793976096739945</v>
+        <v>4.148430610968244</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4358,13 +4358,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.0882253849230689</v>
+        <v>0.08653982475077759</v>
       </c>
       <c r="C38">
-        <v>12368.95450996347</v>
+        <v>13011.00653206596</v>
       </c>
       <c r="D38">
-        <v>15660.23844733803</v>
+        <v>16302.29046944052</v>
       </c>
       <c r="E38">
         <v>-3340.204777554779</v>
@@ -4391,45 +4391,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M38">
-        <v>235.5011448420724</v>
+        <v>215.3792115802497</v>
       </c>
       <c r="N38">
-        <v>633.1655218245944</v>
+        <v>653.287455086417</v>
       </c>
       <c r="O38">
-        <v>92.44216618639078</v>
+        <v>95.37996844261689</v>
       </c>
       <c r="P38">
-        <v>540.7233556382037</v>
+        <v>557.9074866438001</v>
       </c>
       <c r="Q38">
-        <v>1283.723355638204</v>
+        <v>1300.9074866438</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1074924639422951</v>
+        <v>0.10745280117309</v>
       </c>
       <c r="T38">
         <v>1.423852221087529</v>
       </c>
       <c r="U38">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0.146</v>
       </c>
       <c r="W38">
-        <v>0.0539728</v>
+        <v>0.0493612</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.688587871830503</v>
+        <v>4.033196427330239</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4440,13 +4440,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08824626955746509</v>
+        <v>0.08762056250204824</v>
       </c>
       <c r="C39">
-        <v>12257.74139081288</v>
+        <v>12486.21065431059</v>
       </c>
       <c r="D39">
-        <v>15652.53321533674</v>
+        <v>15881.00247883444</v>
       </c>
       <c r="E39">
         <v>-3236.696890405485</v>
@@ -4473,37 +4473,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M39">
-        <v>242.0428433099078</v>
+        <v>234.7662388433124</v>
       </c>
       <c r="N39">
-        <v>626.623823356759</v>
+        <v>633.9004278233543</v>
       </c>
       <c r="O39">
-        <v>91.48707821008681</v>
+        <v>92.54946246220973</v>
       </c>
       <c r="P39">
-        <v>535.1367451466722</v>
+        <v>541.3509653611446</v>
       </c>
       <c r="Q39">
-        <v>1278.136745146672</v>
+        <v>1284.350965361145</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.108375132630897</v>
+        <v>0.1083349023842035</v>
       </c>
       <c r="T39">
         <v>1.444224073538188</v>
       </c>
       <c r="U39">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V39">
         <v>0.146</v>
       </c>
       <c r="W39">
-        <v>0.0539728</v>
+        <v>0.0523502</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.588896307726975</v>
+        <v>3.700134529336784</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4522,13 +4522,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08979239819186127</v>
+        <v>0.08762526025331888</v>
       </c>
       <c r="C40">
-        <v>11604.11960217715</v>
+        <v>12380.91903648939</v>
       </c>
       <c r="D40">
-        <v>15102.4193138503</v>
+        <v>15879.21874816254</v>
       </c>
       <c r="E40">
         <v>-3133.189003256192</v>
@@ -4555,45 +4555,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M40">
-        <v>267.0710504226069</v>
+        <v>241.1112723255641</v>
       </c>
       <c r="N40">
-        <v>601.5956162440598</v>
+        <v>627.5553943411027</v>
       </c>
       <c r="O40">
-        <v>87.83295997163272</v>
+        <v>91.62308757380099</v>
       </c>
       <c r="P40">
-        <v>513.7626562724271</v>
+        <v>535.9323067673017</v>
       </c>
       <c r="Q40">
-        <v>1256.762656272427</v>
+        <v>1278.932306767302</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.109286274503002</v>
+        <v>0.109245458473095</v>
       </c>
       <c r="T40">
         <v>1.465253082519515</v>
       </c>
       <c r="U40">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V40">
         <v>0.146</v>
       </c>
       <c r="W40">
-        <v>0.0579866</v>
+        <v>0.0523502</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.252567679245314</v>
+        <v>3.602762568038448</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4604,13 +4604,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08985342082625745</v>
+        <v>0.08762995800458954</v>
       </c>
       <c r="C41">
-        <v>11479.69190006227</v>
+        <v>12275.62781931516</v>
       </c>
       <c r="D41">
-        <v>15081.49949888471</v>
+        <v>15877.43541813761</v>
       </c>
       <c r="E41">
         <v>-3029.681116106898</v>
@@ -4637,45 +4637,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M41">
-        <v>274.0992359600439</v>
+        <v>247.4563058078158</v>
       </c>
       <c r="N41">
-        <v>594.5674307066229</v>
+        <v>621.2103608588509</v>
       </c>
       <c r="O41">
-        <v>86.80684488316693</v>
+        <v>90.69671268539223</v>
       </c>
       <c r="P41">
-        <v>507.7605858234559</v>
+        <v>530.5136481734587</v>
       </c>
       <c r="Q41">
-        <v>1250.760585823456</v>
+        <v>1273.513648173459</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1102272898791106</v>
+        <v>0.1101858688599829</v>
       </c>
       <c r="T41">
         <v>1.486971567205147</v>
       </c>
       <c r="U41">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V41">
         <v>0.146</v>
       </c>
       <c r="W41">
-        <v>0.0579866</v>
+        <v>0.0523502</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.169168507982614</v>
+        <v>3.510384040652846</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4686,13 +4686,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08991444346065364</v>
+        <v>0.08859113575586017</v>
       </c>
       <c r="C42">
-        <v>11355.32207387735</v>
+        <v>11815.47976822584</v>
       </c>
       <c r="D42">
-        <v>15060.63755984908</v>
+        <v>15520.79525419758</v>
       </c>
       <c r="E42">
         <v>-2926.173228957605</v>
@@ -4719,37 +4719,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M42">
-        <v>281.127421497481</v>
+        <v>265.3942226507884</v>
       </c>
       <c r="N42">
-        <v>587.5392451691857</v>
+        <v>603.2724440158784</v>
       </c>
       <c r="O42">
-        <v>85.78072979470112</v>
+        <v>88.07777682631824</v>
       </c>
       <c r="P42">
-        <v>501.7585153744846</v>
+        <v>515.1946671895602</v>
       </c>
       <c r="Q42">
-        <v>1244.758515374485</v>
+        <v>1258.19466718956</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1111996724344227</v>
+        <v>0.111157626259767</v>
       </c>
       <c r="T42">
         <v>1.5094140013803</v>
       </c>
       <c r="U42">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V42">
         <v>0.146</v>
       </c>
       <c r="W42">
-        <v>0.0579866</v>
+        <v>0.0547414</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.089939295283048</v>
+        <v>3.27311822386457</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4768,13 +4768,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08997546609504981</v>
+        <v>0.08861974550713084</v>
       </c>
       <c r="C43">
-        <v>11231.0098837783</v>
+        <v>11701.60175658172</v>
       </c>
       <c r="D43">
-        <v>15039.83325689933</v>
+        <v>15510.42512970275</v>
       </c>
       <c r="E43">
         <v>-2822.665341808311</v>
@@ -4801,37 +4801,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M43">
-        <v>288.155607034918</v>
+        <v>272.029078217058</v>
       </c>
       <c r="N43">
-        <v>580.5110596317488</v>
+        <v>596.6375884496088</v>
       </c>
       <c r="O43">
-        <v>84.75461470623532</v>
+        <v>87.10908791364287</v>
       </c>
       <c r="P43">
-        <v>495.7564449255135</v>
+        <v>509.5285005359659</v>
       </c>
       <c r="Q43">
-        <v>1238.756444925514</v>
+        <v>1252.528500535966</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1122050171102539</v>
+        <v>0.1121623245883573</v>
       </c>
       <c r="T43">
         <v>1.532617196035967</v>
       </c>
       <c r="U43">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V43">
         <v>0.146</v>
       </c>
       <c r="W43">
-        <v>0.0579866</v>
+        <v>0.0547414</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.014574922227364</v>
+        <v>3.193286072062996</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4850,13 +4850,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09337221272944599</v>
+        <v>0.08864835525840149</v>
       </c>
       <c r="C44">
-        <v>10053.62924473931</v>
+        <v>11587.73759315562</v>
       </c>
       <c r="D44">
-        <v>13965.96050500963</v>
+        <v>15500.06885342594</v>
       </c>
       <c r="E44">
         <v>-2719.157454659018</v>
@@ -4883,45 +4883,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M44">
-        <v>335.6139732928689</v>
+        <v>278.6639337833278</v>
       </c>
       <c r="N44">
-        <v>533.0526933737979</v>
+        <v>590.0027328833389</v>
       </c>
       <c r="O44">
-        <v>77.82569323257448</v>
+        <v>86.14039900096748</v>
       </c>
       <c r="P44">
-        <v>455.2270001412234</v>
+        <v>503.8623338823714</v>
       </c>
       <c r="Q44">
-        <v>1198.227000141223</v>
+        <v>1246.862333882371</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1132450288438724</v>
+        <v>0.1132016676868991</v>
       </c>
       <c r="T44">
         <v>1.556620500852174</v>
       </c>
       <c r="U44">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V44">
         <v>0.146</v>
       </c>
       <c r="W44">
-        <v>0.0659288</v>
+        <v>0.0547414</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.588291119537614</v>
+        <v>3.117255451299591</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4932,13 +4932,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.09351265736384218</v>
+        <v>0.08867696500967213</v>
       </c>
       <c r="C45">
-        <v>9909.01184230646</v>
+        <v>11473.88725022677</v>
       </c>
       <c r="D45">
-        <v>13924.85098972608</v>
+        <v>15489.72639764638</v>
       </c>
       <c r="E45">
         <v>-2615.649567509725</v>
@@ -4965,45 +4965,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M45">
-        <v>343.6047821807944</v>
+        <v>285.2987893495975</v>
       </c>
       <c r="N45">
-        <v>525.0618844858724</v>
+        <v>583.3678773170693</v>
       </c>
       <c r="O45">
-        <v>76.65903513493737</v>
+        <v>85.17171008829212</v>
       </c>
       <c r="P45">
-        <v>448.402849350935</v>
+        <v>498.1961672287772</v>
       </c>
       <c r="Q45">
-        <v>1191.402849350935</v>
+        <v>1241.196167228777</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.114321532217267</v>
+        <v>0.1142774789643371</v>
       </c>
       <c r="T45">
         <v>1.581466026890002</v>
       </c>
       <c r="U45">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.146</v>
       </c>
       <c r="W45">
-        <v>0.0659288</v>
+        <v>0.0547414</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.528098302804182</v>
+        <v>3.044761138478671</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5014,13 +5014,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.09541917399823836</v>
+        <v>0.09163650276094279</v>
       </c>
       <c r="C46">
-        <v>9270.4696548211</v>
+        <v>10370.25004977065</v>
       </c>
       <c r="D46">
-        <v>13389.81668939001</v>
+        <v>14489.59708433956</v>
       </c>
       <c r="E46">
         <v>-2512.141680360432</v>
@@ -5047,45 +5047,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M46">
-        <v>373.0010221311937</v>
+        <v>327.4575517855047</v>
       </c>
       <c r="N46">
-        <v>495.665644535473</v>
+        <v>541.2091148811621</v>
       </c>
       <c r="O46">
-        <v>72.36718410217905</v>
+        <v>79.01653077264966</v>
       </c>
       <c r="P46">
-        <v>423.2984604332939</v>
+        <v>462.1925841085124</v>
       </c>
       <c r="Q46">
-        <v>1166.298460433294</v>
+        <v>1205.192584108512</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1154364821397114</v>
+        <v>0.1153917120731121</v>
       </c>
       <c r="T46">
         <v>1.607198893143467</v>
       </c>
       <c r="U46">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V46">
         <v>0.146</v>
       </c>
       <c r="W46">
-        <v>0.06994259999999999</v>
+        <v>0.0614026</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.328858676320557</v>
+        <v>2.652761134779605</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5096,13 +5096,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.09559975663263454</v>
+        <v>0.09173172451221344</v>
       </c>
       <c r="C47">
-        <v>9118.407948630302</v>
+        <v>10236.70356023424</v>
       </c>
       <c r="D47">
-        <v>13341.26287034851</v>
+        <v>14459.55848195244</v>
       </c>
       <c r="E47">
         <v>-2408.633793211137</v>
@@ -5129,45 +5129,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M47">
-        <v>381.4783180887209</v>
+        <v>334.8997688715389</v>
       </c>
       <c r="N47">
-        <v>487.1883485779458</v>
+        <v>533.7668977951278</v>
       </c>
       <c r="O47">
-        <v>71.12949889238008</v>
+        <v>77.92996707808865</v>
       </c>
       <c r="P47">
-        <v>416.0588496855657</v>
+        <v>455.8369307170391</v>
       </c>
       <c r="Q47">
-        <v>1159.058849685566</v>
+        <v>1198.836930717039</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1165919756956992</v>
+        <v>0.116546462749479</v>
       </c>
       <c r="T47">
         <v>1.633867499987967</v>
       </c>
       <c r="U47">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V47">
         <v>0.146</v>
       </c>
       <c r="W47">
-        <v>0.06994259999999999</v>
+        <v>0.0614026</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.277106261291211</v>
+        <v>2.593810887340058</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5178,13 +5178,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09578033926703074</v>
+        <v>0.09182694626348409</v>
       </c>
       <c r="C48">
-        <v>8966.697099463723</v>
+        <v>10103.2813599917</v>
       </c>
       <c r="D48">
-        <v>13293.05990833122</v>
+        <v>14429.6441688592</v>
       </c>
       <c r="E48">
         <v>-2305.125906061844</v>
@@ -5211,45 +5211,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M48">
-        <v>389.9556140462481</v>
+        <v>342.3419859575731</v>
       </c>
       <c r="N48">
-        <v>478.7110526204187</v>
+        <v>526.3246807090936</v>
       </c>
       <c r="O48">
-        <v>69.89181368258113</v>
+        <v>76.84340338352766</v>
       </c>
       <c r="P48">
-        <v>408.8192389378376</v>
+        <v>449.481277325566</v>
       </c>
       <c r="Q48">
-        <v>1151.819238937838</v>
+        <v>1192.481277325566</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1177902653093162</v>
+        <v>0.117743981969415</v>
       </c>
       <c r="T48">
         <v>1.661523833011893</v>
       </c>
       <c r="U48">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V48">
         <v>0.146</v>
       </c>
       <c r="W48">
-        <v>0.06994259999999999</v>
+        <v>0.0614026</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.227603951263141</v>
+        <v>2.537423694137013</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5260,13 +5260,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.09596092190142691</v>
+        <v>0.09348755001475476</v>
       </c>
       <c r="C49">
-        <v>8815.333317995941</v>
+        <v>9497.29596605301</v>
       </c>
       <c r="D49">
-        <v>13245.20401401273</v>
+        <v>13927.1666620698</v>
       </c>
       <c r="E49">
         <v>-2201.618018912551</v>
@@ -5293,37 +5293,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M49">
-        <v>398.4329100037752</v>
+        <v>368.7571987580728</v>
       </c>
       <c r="N49">
-        <v>470.2337566628916</v>
+        <v>499.909467908594</v>
       </c>
       <c r="O49">
-        <v>68.65412847278216</v>
+        <v>72.98678231465472</v>
       </c>
       <c r="P49">
-        <v>401.5796281901094</v>
+        <v>426.9226855939393</v>
       </c>
       <c r="Q49">
-        <v>1144.579628190109</v>
+        <v>1169.922685593939</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1190337733989187</v>
+        <v>0.1189866905938769</v>
       </c>
       <c r="T49">
         <v>1.69022380124427</v>
       </c>
       <c r="U49">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.146</v>
       </c>
       <c r="W49">
-        <v>0.06994259999999999</v>
+        <v>0.0647332</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.180208122512862</v>
+        <v>2.355660227358884</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5342,13 +5342,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09614150453582307</v>
+        <v>0.0936160777660254</v>
       </c>
       <c r="C50">
-        <v>8664.312869273066</v>
+        <v>9356.352398348607</v>
       </c>
       <c r="D50">
-        <v>13197.69145243915</v>
+        <v>13889.73098151469</v>
       </c>
       <c r="E50">
         <v>-2098.110131763257</v>
@@ -5375,37 +5375,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M50">
-        <v>406.9102059613023</v>
+        <v>376.6030966039892</v>
       </c>
       <c r="N50">
-        <v>461.7564607053644</v>
+        <v>492.0635700626775</v>
       </c>
       <c r="O50">
-        <v>67.41644326298321</v>
+        <v>71.84128122915091</v>
       </c>
       <c r="P50">
-        <v>394.3400174423812</v>
+        <v>420.2222888335266</v>
       </c>
       <c r="Q50">
-        <v>1137.340017442381</v>
+        <v>1163.222288833527</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1203251087227367</v>
+        <v>0.120277195703895</v>
       </c>
       <c r="T50">
         <v>1.72002761440866</v>
       </c>
       <c r="U50">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.146</v>
       </c>
       <c r="W50">
-        <v>0.06994259999999999</v>
+        <v>0.0647332</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.13478711996051</v>
+        <v>2.30658397262224</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5424,13 +5424,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09632208717021926</v>
+        <v>0.09374460551729605</v>
       </c>
       <c r="C51">
-        <v>8513.632071741038</v>
+        <v>9215.609542435948</v>
       </c>
       <c r="D51">
-        <v>13150.51854205642</v>
+        <v>13852.49601275133</v>
       </c>
       <c r="E51">
         <v>-1994.602244613964</v>
@@ -5457,37 +5457,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M51">
-        <v>415.3875019188295</v>
+        <v>384.4489944499057</v>
       </c>
       <c r="N51">
-        <v>453.2791647478373</v>
+        <v>484.2176722167611</v>
       </c>
       <c r="O51">
-        <v>66.17875805318424</v>
+        <v>70.69578014364711</v>
       </c>
       <c r="P51">
-        <v>387.100406694653</v>
+        <v>413.5218920731139</v>
       </c>
       <c r="Q51">
-        <v>1130.100406694653</v>
+        <v>1156.521892073114</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1216670846474888</v>
+        <v>0.1216183088574432</v>
       </c>
       <c r="T51">
         <v>1.75100020455989</v>
       </c>
       <c r="U51">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V51">
         <v>0.146</v>
       </c>
       <c r="W51">
-        <v>0.06994259999999999</v>
+        <v>0.0647332</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.091220035879684</v>
+        <v>2.259510830323827</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5506,13 +5506,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.09650266980461546</v>
+        <v>0.09387313326856669</v>
       </c>
       <c r="C52">
-        <v>8363.2872962947</v>
+        <v>9075.065788453139</v>
       </c>
       <c r="D52">
-        <v>13103.68165375937</v>
+        <v>13815.46014591781</v>
       </c>
       <c r="E52">
         <v>-1891.094357464671</v>
@@ -5539,37 +5539,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M52">
-        <v>423.8647978763565</v>
+        <v>392.2948922958221</v>
       </c>
       <c r="N52">
-        <v>444.8018687903102</v>
+        <v>476.3717743708447</v>
       </c>
       <c r="O52">
-        <v>64.94107284338529</v>
+        <v>69.55027905814332</v>
       </c>
       <c r="P52">
-        <v>379.8607959469249</v>
+        <v>406.8214953127014</v>
       </c>
       <c r="Q52">
-        <v>1122.860795946925</v>
+        <v>1149.821495312701</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1230627396092309</v>
+        <v>0.1230130665371334</v>
       </c>
       <c r="T52">
         <v>1.783211698317168</v>
       </c>
       <c r="U52">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V52">
         <v>0.146</v>
       </c>
       <c r="W52">
-        <v>0.06994259999999999</v>
+        <v>0.0647332</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.049395635162091</v>
+        <v>2.214320613717351</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5588,13 +5588,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.09668325243901163</v>
+        <v>0.09400166101983734</v>
       </c>
       <c r="C53">
-        <v>8213.274965347109</v>
+        <v>8934.719543708798</v>
       </c>
       <c r="D53">
-        <v>13057.17720996107</v>
+        <v>13778.62178832276</v>
       </c>
       <c r="E53">
         <v>-1787.586470315377</v>
@@ -5621,37 +5621,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M53">
-        <v>432.3420938338837</v>
+        <v>400.1407901417385</v>
       </c>
       <c r="N53">
-        <v>436.3245728327831</v>
+        <v>468.5258765249282</v>
       </c>
       <c r="O53">
-        <v>63.70338763358632</v>
+        <v>68.40477797263951</v>
       </c>
       <c r="P53">
-        <v>372.6211851991968</v>
+        <v>400.1210985522887</v>
       </c>
       <c r="Q53">
-        <v>1115.621185199197</v>
+        <v>1143.121098552289</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1245153600796156</v>
+        <v>0.1244647531017088</v>
       </c>
       <c r="T53">
         <v>1.816737946921683</v>
       </c>
       <c r="U53">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V53">
         <v>0.146</v>
       </c>
       <c r="W53">
-        <v>0.06994259999999999</v>
+        <v>0.0647332</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.009211407021657</v>
+        <v>2.170902562467991</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5670,13 +5670,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1041023390734078</v>
+        <v>0.09413018877110799</v>
       </c>
       <c r="C54">
-        <v>6448.215750053092</v>
+        <v>8794.569232453754</v>
       </c>
       <c r="D54">
-        <v>11395.62588181635</v>
+        <v>13741.97936421701</v>
       </c>
       <c r="E54">
         <v>-1684.078583166084</v>
@@ -5703,45 +5703,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M54">
-        <v>528.552674939152</v>
+        <v>407.9866879876549</v>
       </c>
       <c r="N54">
-        <v>340.1139917275148</v>
+        <v>460.6799786790118</v>
       </c>
       <c r="O54">
-        <v>49.65664279221715</v>
+        <v>67.25927688713573</v>
       </c>
       <c r="P54">
-        <v>290.4573489352976</v>
+        <v>393.4207017918761</v>
       </c>
       <c r="Q54">
-        <v>1033.457348935298</v>
+        <v>1136.420701791876</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1260285064029329</v>
+        <v>0.125976926606475</v>
       </c>
       <c r="T54">
         <v>1.851661122551385</v>
       </c>
       <c r="U54">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0.146</v>
       </c>
       <c r="W54">
-        <v>0.0838628</v>
+        <v>0.0647332</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.643481733900352</v>
+        <v>2.129154436266683</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5752,13 +5752,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.104422123707804</v>
+        <v>0.09425871652237863</v>
       </c>
       <c r="C55">
-        <v>6282.544539130403</v>
+        <v>8654.613295656371</v>
       </c>
       <c r="D55">
-        <v>11333.46255804295</v>
+        <v>13705.53131456892</v>
       </c>
       <c r="E55">
         <v>-1580.57069601679</v>
@@ -5785,45 +5785,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M55">
-        <v>538.7171494572126</v>
+        <v>415.8325858335714</v>
       </c>
       <c r="N55">
-        <v>329.9495172094541</v>
+        <v>452.8340808330953</v>
       </c>
       <c r="O55">
-        <v>48.1726295125803</v>
+        <v>66.1137758016319</v>
       </c>
       <c r="P55">
-        <v>281.7768876968738</v>
+        <v>386.7203050314634</v>
       </c>
       <c r="Q55">
-        <v>1024.776887696874</v>
+        <v>1129.720305031463</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1276060419314979</v>
+        <v>0.1275534479199545</v>
       </c>
       <c r="T55">
         <v>1.888070390761075</v>
       </c>
       <c r="U55">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.146</v>
       </c>
       <c r="W55">
-        <v>0.0838628</v>
+        <v>0.0647332</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.612472644581478</v>
+        <v>2.088981711054104</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5834,13 +5834,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1047419083422002</v>
+        <v>0.09438724427364928</v>
       </c>
       <c r="C56">
-        <v>6117.547852542771</v>
+        <v>8514.850190781417</v>
       </c>
       <c r="D56">
-        <v>11271.97375860462</v>
+        <v>13669.27609684326</v>
       </c>
       <c r="E56">
         <v>-1477.062808867497</v>
@@ -5867,45 +5867,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M56">
-        <v>548.8816239752732</v>
+        <v>423.6784836794879</v>
       </c>
       <c r="N56">
-        <v>319.7850426913935</v>
+        <v>444.9881829871788</v>
       </c>
       <c r="O56">
-        <v>46.68861623294345</v>
+        <v>64.96827471612811</v>
       </c>
       <c r="P56">
-        <v>273.0964264584501</v>
+        <v>380.0199082710507</v>
       </c>
       <c r="Q56">
-        <v>1016.09642645845</v>
+        <v>1123.019908271051</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1292521659613048</v>
+        <v>0.129198513638368</v>
       </c>
       <c r="T56">
         <v>1.926062670632056</v>
       </c>
       <c r="U56">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V56">
         <v>0.146</v>
       </c>
       <c r="W56">
-        <v>0.0838628</v>
+        <v>0.0647332</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.582612040052191</v>
+        <v>2.050296864553102</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5916,13 +5916,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1050616929765964</v>
+        <v>0.09451577202491994</v>
       </c>
       <c r="C57">
-        <v>5953.214770798676</v>
+        <v>8375.278391572465</v>
       </c>
       <c r="D57">
-        <v>11211.14856400981</v>
+        <v>13633.2121847836</v>
       </c>
       <c r="E57">
         <v>-1373.554921718203</v>
@@ -5949,45 +5949,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M57">
-        <v>559.0460984933338</v>
+        <v>431.5243815254044</v>
       </c>
       <c r="N57">
-        <v>309.6205681733329</v>
+        <v>437.1422851412624</v>
       </c>
       <c r="O57">
-        <v>45.2046029533066</v>
+        <v>63.8227736306243</v>
       </c>
       <c r="P57">
-        <v>264.4159652200263</v>
+        <v>373.3195115106381</v>
       </c>
       <c r="Q57">
-        <v>1007.415965220026</v>
+        <v>1116.319511510638</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.130971451059103</v>
+        <v>0.130916693388711</v>
       </c>
       <c r="T57">
         <v>1.965743496275081</v>
       </c>
       <c r="U57">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0.146</v>
       </c>
       <c r="W57">
-        <v>0.0838628</v>
+        <v>0.0647332</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.553837275687606</v>
+        <v>2.013018739743046</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5998,13 +5998,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1053814776109926</v>
+        <v>0.1014353077761906</v>
       </c>
       <c r="C58">
-        <v>5789.5346088342</v>
+        <v>6576.165628886919</v>
       </c>
       <c r="D58">
-        <v>11150.97628919463</v>
+        <v>11937.60730924735</v>
       </c>
       <c r="E58">
         <v>-1270.04703456891</v>
@@ -6031,37 +6031,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M58">
-        <v>569.2105730113944</v>
+        <v>521.6797512324389</v>
       </c>
       <c r="N58">
-        <v>299.4560936552723</v>
+        <v>346.9869154342279</v>
       </c>
       <c r="O58">
-        <v>43.72058967366975</v>
+        <v>50.66008965339726</v>
       </c>
       <c r="P58">
-        <v>255.7355039816026</v>
+        <v>296.3268257808306</v>
       </c>
       <c r="Q58">
-        <v>998.7355039816025</v>
+        <v>1039.326825780831</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1327688854795285</v>
+        <v>0.132712972218615</v>
       </c>
       <c r="T58">
         <v>2.00722799581097</v>
       </c>
       <c r="U58">
-        <v>0.09820000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V58">
         <v>0.146</v>
       </c>
       <c r="W58">
-        <v>0.0838628</v>
+        <v>0.07686</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.526090181478899</v>
+        <v>1.665133953569198</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6080,13 +6080,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1392457023193324</v>
+        <v>0.1016851035274612</v>
       </c>
       <c r="C59">
-        <v>1644.972318945044</v>
+        <v>6419.298914465842</v>
       </c>
       <c r="D59">
-        <v>7109.92188645477</v>
+        <v>11884.24848197557</v>
       </c>
       <c r="E59">
         <v>-1166.539147419616</v>
@@ -6113,45 +6113,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M59">
-        <v>965.2317492445911</v>
+        <v>530.9954610758754</v>
       </c>
       <c r="N59">
-        <v>-96.56508257792439</v>
+        <v>337.6712055907914</v>
       </c>
       <c r="O59">
-        <v>-14.09850205637696</v>
+        <v>49.29999601625553</v>
       </c>
       <c r="P59">
-        <v>-82.46658052154743</v>
+        <v>288.3712095745358</v>
       </c>
       <c r="Q59">
-        <v>660.5334194784525</v>
+        <v>1031.371209574536</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1354568000076187</v>
+        <v>0.1345927989010726</v>
       </c>
       <c r="T59">
-        <v>2.069264634102713</v>
+        <v>2.050642006953179</v>
       </c>
       <c r="U59">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V59">
-        <v>0.1313936610897738</v>
+        <v>0.146</v>
       </c>
       <c r="W59">
-        <v>0.142103997045713</v>
+        <v>0.07686</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.8999565828066699</v>
+        <v>1.635921077190791</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6162,13 +6162,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1404237023193324</v>
+        <v>0.1019348992787319</v>
       </c>
       <c r="C60">
-        <v>1452.950795392279</v>
+        <v>6262.907084956526</v>
       </c>
       <c r="D60">
-        <v>7021.408250051298</v>
+        <v>11831.36453961554</v>
       </c>
       <c r="E60">
         <v>-1063.031260270323</v>
@@ -6195,45 +6195,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M60">
-        <v>982.1656395822154</v>
+        <v>540.3111709193116</v>
       </c>
       <c r="N60">
-        <v>-113.4989729155486</v>
+        <v>328.3554957473551</v>
       </c>
       <c r="O60">
-        <v>-16.5708500456701</v>
+        <v>47.93990237911385</v>
       </c>
       <c r="P60">
-        <v>-96.92812286987852</v>
+        <v>280.4155933682413</v>
       </c>
       <c r="Q60">
-        <v>646.0718771301215</v>
+        <v>1023.415593368241</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1375914857220858</v>
+        <v>0.1365621411398378</v>
       </c>
       <c r="T60">
-        <v>2.118532839676587</v>
+        <v>2.096123351959303</v>
       </c>
       <c r="U60">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V60">
-        <v>0.1291282531399501</v>
+        <v>0.146</v>
       </c>
       <c r="W60">
-        <v>0.1424746177863042</v>
+        <v>0.07686</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.8844400899996585</v>
+        <v>1.607715541377157</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6244,13 +6244,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1416017023193324</v>
+        <v>0.1021846950300025</v>
       </c>
       <c r="C61">
-        <v>1263.106040334416</v>
+        <v>6106.983828846603</v>
       </c>
       <c r="D61">
-        <v>6935.071382142728</v>
+        <v>11778.94917065491</v>
       </c>
       <c r="E61">
         <v>-959.5233731210301</v>
@@ -6277,45 +6277,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M61">
-        <v>999.0995299198397</v>
+        <v>549.626880762748</v>
       </c>
       <c r="N61">
-        <v>-130.432863253173</v>
+        <v>319.0397859039188</v>
       </c>
       <c r="O61">
-        <v>-19.04319803496325</v>
+        <v>46.57980874197214</v>
       </c>
       <c r="P61">
-        <v>-111.3896652182097</v>
+        <v>272.4599771619466</v>
       </c>
       <c r="Q61">
-        <v>631.6103347817902</v>
+        <v>1015.459977161947</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1398303024470147</v>
+        <v>0.1386275488536647</v>
       </c>
       <c r="T61">
-        <v>2.170204372351625</v>
+        <v>2.143823299160848</v>
       </c>
       <c r="U61">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V61">
-        <v>0.126939638679951</v>
+        <v>0.146</v>
       </c>
       <c r="W61">
-        <v>0.14283267511196</v>
+        <v>0.07686</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.8694495799996644</v>
+        <v>1.580466125421612</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6326,13 +6326,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1427797023193324</v>
+        <v>0.1024344907812732</v>
       </c>
       <c r="C62">
-        <v>1075.358730988673</v>
+        <v>5951.522945975569</v>
       </c>
       <c r="D62">
-        <v>6850.831959946278</v>
+        <v>11726.99617493317</v>
       </c>
       <c r="E62">
         <v>-856.0154859717368</v>
@@ -6359,45 +6359,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M62">
-        <v>1016.033420257464</v>
+        <v>558.9425906061845</v>
       </c>
       <c r="N62">
-        <v>-147.3667535907974</v>
+        <v>309.7240760604823</v>
       </c>
       <c r="O62">
-        <v>-21.51554602425642</v>
+        <v>45.21971510483041</v>
       </c>
       <c r="P62">
-        <v>-125.851207566541</v>
+        <v>264.5043609556519</v>
       </c>
       <c r="Q62">
-        <v>617.148792433459</v>
+        <v>1007.504360955652</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1421810600081901</v>
+        <v>0.1407962269531829</v>
       </c>
       <c r="T62">
-        <v>2.224459481660416</v>
+        <v>2.193908243722471</v>
       </c>
       <c r="U62">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V62">
-        <v>0.1248239780352851</v>
+        <v>0.146</v>
       </c>
       <c r="W62">
-        <v>0.1431787971934274</v>
+        <v>0.07686</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.8549587536663366</v>
+        <v>1.554125023331252</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6408,13 +6408,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1439577023193324</v>
+        <v>0.1026842865325438</v>
       </c>
       <c r="C63">
-        <v>889.6333524135716</v>
+        <v>5796.518345089883</v>
       </c>
       <c r="D63">
-        <v>6768.61446852047</v>
+        <v>11675.49946119678</v>
       </c>
       <c r="E63">
         <v>-752.5075988224435</v>
@@ -6441,45 +6441,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M63">
-        <v>1032.967310595089</v>
+        <v>568.2583004496208</v>
       </c>
       <c r="N63">
-        <v>-164.3006439284218</v>
+        <v>300.4083662170459</v>
       </c>
       <c r="O63">
-        <v>-23.98789401354958</v>
+        <v>43.8596214676887</v>
       </c>
       <c r="P63">
-        <v>-140.3127499148722</v>
+        <v>256.5487447493572</v>
       </c>
       <c r="Q63">
-        <v>602.6872500851277</v>
+        <v>999.5487447493572</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1446523692391693</v>
+        <v>0.143076119314215</v>
       </c>
       <c r="T63">
-        <v>2.281496904267094</v>
+        <v>2.246561646979561</v>
       </c>
       <c r="U63">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V63">
-        <v>0.1227776833133952</v>
+        <v>0.146</v>
       </c>
       <c r="W63">
-        <v>0.1435135710099285</v>
+        <v>0.07686</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.840943036393118</v>
+        <v>1.528647563932379</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6490,13 +6490,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1451357023193324</v>
+        <v>0.1029340822838145</v>
       </c>
       <c r="C64">
-        <v>705.8579717272114</v>
+        <v>5641.964041462205</v>
       </c>
       <c r="D64">
-        <v>6688.346974983403</v>
+        <v>11624.4530447184</v>
       </c>
       <c r="E64">
         <v>-648.9997116731502</v>
@@ -6523,45 +6523,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M64">
-        <v>1049.901200932713</v>
+        <v>577.5740102930572</v>
       </c>
       <c r="N64">
-        <v>-181.2345342660462</v>
+        <v>291.0926563736095</v>
       </c>
       <c r="O64">
-        <v>-26.46024200284275</v>
+        <v>42.49952783054699</v>
       </c>
       <c r="P64">
-        <v>-154.7742922632035</v>
+        <v>248.5931285430626</v>
       </c>
       <c r="Q64">
-        <v>588.2257077367965</v>
+        <v>991.5931285430626</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1472537473770422</v>
+        <v>0.1454760060100381</v>
       </c>
       <c r="T64">
-        <v>2.341536296484648</v>
+        <v>2.301986281987024</v>
       </c>
       <c r="U64">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V64">
-        <v>0.120797398098663</v>
+        <v>0.146</v>
       </c>
       <c r="W64">
-        <v>0.1438375456710587</v>
+        <v>0.07686</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.8273794390319387</v>
+        <v>1.503991958062502</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6572,13 +6572,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1463137023193324</v>
+        <v>0.1353479614586536</v>
       </c>
       <c r="C65">
-        <v>523.9640282022474</v>
+        <v>1330.726460331356</v>
       </c>
       <c r="D65">
-        <v>6609.960918607733</v>
+        <v>7416.723350736842</v>
       </c>
       <c r="E65">
         <v>-545.4918245238559</v>
@@ -6605,37 +6605,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M65">
-        <v>1066.835091270337</v>
+        <v>957.2823435115254</v>
       </c>
       <c r="N65">
-        <v>-198.1684246036707</v>
+        <v>-88.61567684485863</v>
       </c>
       <c r="O65">
-        <v>-28.93258999213592</v>
+        <v>-12.93788881934936</v>
       </c>
       <c r="P65">
-        <v>-169.2358346115348</v>
+        <v>-75.67778802550927</v>
       </c>
       <c r="Q65">
-        <v>573.7641653884652</v>
+        <v>667.3222119744908</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1499957405493947</v>
+        <v>0.1489640084935058</v>
       </c>
       <c r="T65">
-        <v>2.404821061254504</v>
+        <v>2.382540611859257</v>
       </c>
       <c r="U65">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1188799790812239</v>
+        <v>0.1324847723275765</v>
       </c>
       <c r="W65">
-        <v>0.1441512354223118</v>
+        <v>0.1273512354223118</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8142464320631777</v>
+        <v>0.9074299474491543</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6654,13 +6654,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1474917023193325</v>
+        <v>0.1363579614586536</v>
       </c>
       <c r="C66">
-        <v>343.8861379501568</v>
+        <v>1144.499279774996</v>
       </c>
       <c r="D66">
-        <v>6533.390915504936</v>
+        <v>7334.004057329775</v>
       </c>
       <c r="E66">
         <v>-441.9839373745626</v>
@@ -6687,37 +6687,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M66">
-        <v>1083.768981607962</v>
+        <v>972.4773013450417</v>
       </c>
       <c r="N66">
-        <v>-215.1023149412952</v>
+        <v>-103.810634678375</v>
       </c>
       <c r="O66">
-        <v>-31.40493798142909</v>
+        <v>-15.15635266304275</v>
       </c>
       <c r="P66">
-        <v>-183.6973769598661</v>
+        <v>-88.65428201533223</v>
       </c>
       <c r="Q66">
-        <v>559.302623040134</v>
+        <v>654.3457179846678</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1528900666757667</v>
+        <v>0.1518296753961032</v>
       </c>
       <c r="T66">
-        <v>2.471621646289352</v>
+        <v>2.448722295522014</v>
       </c>
       <c r="U66">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1170224794080798</v>
+        <v>0.1304146977599581</v>
       </c>
       <c r="W66">
-        <v>0.1444551223688381</v>
+        <v>0.1276551223688382</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8015238315621904</v>
+        <v>0.8932513545202612</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6736,13 +6736,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1833546706004069</v>
+        <v>0.1373679614586535</v>
       </c>
       <c r="C67">
-        <v>-1462.993871337173</v>
+        <v>960.0968965606398</v>
       </c>
       <c r="D67">
-        <v>4830.018793366899</v>
+        <v>7253.109561264712</v>
       </c>
       <c r="E67">
         <v>-338.4760502252693</v>
@@ -6769,45 +6769,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M67">
-        <v>1451.905133043139</v>
+        <v>987.672259178558</v>
       </c>
       <c r="N67">
-        <v>-583.2384663764722</v>
+        <v>-119.0055925118912</v>
       </c>
       <c r="O67">
-        <v>-85.15281609096493</v>
+        <v>-17.37481650673612</v>
       </c>
       <c r="P67">
-        <v>-498.0856502855072</v>
+        <v>-101.6307760051551</v>
       </c>
       <c r="Q67">
-        <v>244.9143497144928</v>
+        <v>641.3692239948449</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1581068350981444</v>
+        <v>0.1548590946931347</v>
       </c>
       <c r="T67">
-        <v>2.592023828832255</v>
+        <v>2.518685789679786</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.08735097799917008</v>
+        <v>0.1284083177944203</v>
       </c>
       <c r="W67">
-        <v>0.1969496589477791</v>
+        <v>0.1279496589477791</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.5982943698573293</v>
+        <v>0.8795090259891802</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6818,13 +6818,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.185054670600407</v>
+        <v>0.1383779614586536</v>
       </c>
       <c r="C68">
-        <v>-1625.465898887081</v>
+        <v>777.4595865826841</v>
       </c>
       <c r="D68">
-        <v>4771.054652966285</v>
+        <v>7173.98013843605</v>
       </c>
       <c r="E68">
         <v>-234.968163075976</v>
@@ -6851,45 +6851,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M68">
-        <v>1474.242135089956</v>
+        <v>1002.867217012074</v>
       </c>
       <c r="N68">
-        <v>-605.5754684232897</v>
+        <v>-134.2005503454075</v>
       </c>
       <c r="O68">
-        <v>-88.4140183898003</v>
+        <v>-19.59328035042949</v>
       </c>
       <c r="P68">
-        <v>-517.1614500334895</v>
+        <v>-114.607269994978</v>
       </c>
       <c r="Q68">
-        <v>225.8385499665105</v>
+        <v>628.392730005022</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1614099773069134</v>
+        <v>0.1580667151252857</v>
       </c>
       <c r="T68">
-        <v>2.66825982379791</v>
+        <v>2.592764783493897</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.08602747833251599</v>
+        <v>0.1264627372217776</v>
       </c>
       <c r="W68">
-        <v>0.1972352701758431</v>
+        <v>0.1282352701758431</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.5892293036473698</v>
+        <v>0.8661831316560109</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6900,13 +6900,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.186754670600407</v>
+        <v>0.1393879614586536</v>
       </c>
       <c r="C69">
-        <v>-1786.515638856818</v>
+        <v>596.5302039024564</v>
       </c>
       <c r="D69">
-        <v>4713.512800145841</v>
+        <v>7096.558642905115</v>
       </c>
       <c r="E69">
         <v>-131.4602759266827</v>
@@ -6933,45 +6933,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M69">
-        <v>1496.579137136774</v>
+        <v>1018.06217484559</v>
       </c>
       <c r="N69">
-        <v>-627.9124704701071</v>
+        <v>-149.3955081789237</v>
       </c>
       <c r="O69">
-        <v>-91.67522068863563</v>
+        <v>-21.81174419412286</v>
       </c>
       <c r="P69">
-        <v>-536.2372497814715</v>
+        <v>-127.5837639848008</v>
       </c>
       <c r="Q69">
-        <v>206.7627502185285</v>
+        <v>615.4162360151992</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1649133099525774</v>
+        <v>0.1614687367957489</v>
       </c>
       <c r="T69">
-        <v>2.749116182094816</v>
+        <v>2.671333413296743</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.08474348611859785</v>
+        <v>0.124575233681154</v>
       </c>
       <c r="W69">
-        <v>0.1975123556956066</v>
+        <v>0.1285123556956066</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.5804348364287524</v>
+        <v>0.8532550252133839</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6982,13 +6982,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.188454670600407</v>
+        <v>0.1403979614586536</v>
       </c>
       <c r="C70">
-        <v>-1946.193938979785</v>
+        <v>417.2540431158159</v>
       </c>
       <c r="D70">
-        <v>4657.342387172168</v>
+        <v>7020.790369267769</v>
       </c>
       <c r="E70">
         <v>-27.95238877738848</v>
@@ -7015,45 +7015,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M70">
-        <v>1518.916139183592</v>
+        <v>1033.257132679107</v>
       </c>
       <c r="N70">
-        <v>-650.2494725169249</v>
+        <v>-164.5904660124402</v>
       </c>
       <c r="O70">
-        <v>-94.93642298747103</v>
+        <v>-24.03020803781627</v>
       </c>
       <c r="P70">
-        <v>-555.3130495294539</v>
+        <v>-140.5602579746239</v>
       </c>
       <c r="Q70">
-        <v>187.6869504705461</v>
+        <v>602.4397420253761</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1686356008885955</v>
+        <v>0.1650833848206161</v>
       </c>
       <c r="T70">
-        <v>2.83502606278528</v>
+        <v>2.754812582462266</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.08349725838155964</v>
+        <v>0.1227432449505488</v>
       </c>
       <c r="W70">
-        <v>0.1977812916412595</v>
+        <v>0.1287812916412595</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.5718990300106824</v>
+        <v>0.8407071571955399</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7064,13 +7064,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.190154670600407</v>
+        <v>0.1414079614586536</v>
       </c>
       <c r="C71">
-        <v>-2104.549251745872</v>
+        <v>239.5787104444571</v>
       </c>
       <c r="D71">
-        <v>4602.494961555374</v>
+        <v>6946.622923745704</v>
       </c>
       <c r="E71">
         <v>75.55549837190483</v>
@@ -7097,45 +7097,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M71">
-        <v>1541.253141230409</v>
+        <v>1048.452090512623</v>
       </c>
       <c r="N71">
-        <v>-672.5864745637425</v>
+        <v>-179.7854238459563</v>
       </c>
       <c r="O71">
-        <v>-98.1976252863064</v>
+        <v>-26.24867188150962</v>
       </c>
       <c r="P71">
-        <v>-574.3888492774361</v>
+        <v>-153.5367519644467</v>
       </c>
       <c r="Q71">
-        <v>168.6111507225639</v>
+        <v>589.4632480355533</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1725980396269373</v>
+        <v>0.1689312359438618</v>
       </c>
       <c r="T71">
-        <v>2.926478516423515</v>
+        <v>2.843677504477178</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.08228715318762397</v>
+        <v>0.1209643573425699</v>
       </c>
       <c r="W71">
-        <v>0.1980424323421108</v>
+        <v>0.1290424323421108</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.5636106382713971</v>
+        <v>0.8285229954970539</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7146,13 +7146,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.191854670600407</v>
+        <v>0.1424179614586536</v>
       </c>
       <c r="C72">
-        <v>-2261.627773798384</v>
+        <v>63.45400291248916</v>
       </c>
       <c r="D72">
-        <v>4548.924326652156</v>
+        <v>6874.006103363029</v>
       </c>
       <c r="E72">
         <v>179.0633855211981</v>
@@ -7179,45 +7179,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M72">
-        <v>1563.590143277227</v>
+        <v>1063.647048346139</v>
       </c>
       <c r="N72">
-        <v>-694.9234766105599</v>
+        <v>-194.9803816794727</v>
       </c>
       <c r="O72">
-        <v>-101.4588275851417</v>
+        <v>-28.46713572520301</v>
       </c>
       <c r="P72">
-        <v>-593.4646490254181</v>
+        <v>-166.5132459542696</v>
       </c>
       <c r="Q72">
-        <v>149.5353509745819</v>
+        <v>576.4867540457303</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1768246409478351</v>
+        <v>0.1730356104753238</v>
       </c>
       <c r="T72">
-        <v>3.024027800304298</v>
+        <v>2.938466754626417</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.08111162242780079</v>
+        <v>0.1192362950948189</v>
       </c>
       <c r="W72">
-        <v>0.1982961118800806</v>
+        <v>0.1292961118800806</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.555559057724663</v>
+        <v>0.8166869527042389</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7228,13 +7228,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.193554670600407</v>
+        <v>0.1434279614586536</v>
       </c>
       <c r="C73">
-        <v>-2417.473575707896</v>
+        <v>-111.1682049771462</v>
       </c>
       <c r="D73">
-        <v>4496.586411891936</v>
+        <v>6802.891782622686</v>
       </c>
       <c r="E73">
         <v>282.5712726704905</v>
@@ -7261,45 +7261,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M73">
-        <v>1585.927145324044</v>
+        <v>1078.842006179656</v>
       </c>
       <c r="N73">
-        <v>-717.2604786573772</v>
+        <v>-210.1753395129888</v>
       </c>
       <c r="O73">
-        <v>-104.7200298839771</v>
+        <v>-30.68559956889636</v>
       </c>
       <c r="P73">
-        <v>-612.5404487734002</v>
+        <v>-179.4897399440924</v>
       </c>
       <c r="Q73">
-        <v>130.4595512265998</v>
+        <v>563.5102600559076</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1813427320150019</v>
+        <v>0.1774230453193005</v>
       </c>
       <c r="T73">
-        <v>3.128304621004446</v>
+        <v>3.039793194441121</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.07996920521050782</v>
+        <v>0.1175569106568637</v>
       </c>
       <c r="W73">
-        <v>0.1985426455155724</v>
+        <v>0.1295426455155724</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.5477342822637523</v>
+        <v>0.8051843195675594</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7310,13 +7310,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.195254670600407</v>
+        <v>0.1842527591597073</v>
       </c>
       <c r="C74">
-        <v>-2572.128722889326</v>
+        <v>-2220.607086158636</v>
       </c>
       <c r="D74">
-        <v>4445.439151859799</v>
+        <v>4796.96078859049</v>
       </c>
       <c r="E74">
         <v>386.0791598197839</v>
@@ -7343,37 +7343,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M74">
-        <v>1608.264147370862</v>
+        <v>1496.475629249624</v>
       </c>
       <c r="N74">
-        <v>-739.5974807041948</v>
+        <v>-627.8089625829577</v>
       </c>
       <c r="O74">
-        <v>-107.9812321828124</v>
+        <v>-91.66010853711182</v>
       </c>
       <c r="P74">
-        <v>-631.6162485213824</v>
+        <v>-536.148854045846</v>
       </c>
       <c r="Q74">
-        <v>111.3837514786176</v>
+        <v>206.851145954154</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1861835438726805</v>
+        <v>0.1854624315844676</v>
       </c>
       <c r="T74">
-        <v>3.240029786040319</v>
+        <v>3.225460313729044</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.07885852180480633</v>
+        <v>0.08474934763683868</v>
       </c>
       <c r="W74">
-        <v>0.1987823309945228</v>
+        <v>0.1837823309945228</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5401268616767556</v>
+        <v>0.5804749838139636</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7392,13 +7392,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.196954670600407</v>
+        <v>0.1858027591597073</v>
       </c>
       <c r="C75">
-        <v>-2725.633388359418</v>
+        <v>-2377.223135368034</v>
       </c>
       <c r="D75">
-        <v>4395.442373539002</v>
+        <v>4743.852626530385</v>
       </c>
       <c r="E75">
         <v>489.5870469690781</v>
@@ -7425,37 +7425,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M75">
-        <v>1630.601149417679</v>
+        <v>1517.260012989203</v>
       </c>
       <c r="N75">
-        <v>-761.9344827510124</v>
+        <v>-648.593346322536</v>
       </c>
       <c r="O75">
-        <v>-111.2424344816478</v>
+        <v>-94.69462856309026</v>
       </c>
       <c r="P75">
-        <v>-650.6920482693646</v>
+        <v>-553.8987177594457</v>
       </c>
       <c r="Q75">
-        <v>92.30795173063541</v>
+        <v>189.1012822405543</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1913829343864835</v>
+        <v>0.1906351142357442</v>
       </c>
       <c r="T75">
-        <v>3.360030889226997</v>
+        <v>3.34492180683012</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.07777826808145281</v>
+        <v>0.08358839766921075</v>
       </c>
       <c r="W75">
-        <v>0.1990154497480225</v>
+        <v>0.1840154497480225</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5327278635715946</v>
+        <v>0.5725232717069229</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7474,13 +7474,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.198654670600407</v>
+        <v>0.1873527591597073</v>
       </c>
       <c r="C76">
-        <v>-2878.025957969938</v>
+        <v>-2532.676117863905</v>
       </c>
       <c r="D76">
-        <v>4346.557691077775</v>
+        <v>4691.907531183808</v>
       </c>
       <c r="E76">
         <v>593.0949341183714</v>
@@ -7507,37 +7507,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M76">
-        <v>1652.938151464497</v>
+        <v>1538.044396728781</v>
       </c>
       <c r="N76">
-        <v>-784.27148479783</v>
+        <v>-669.3777300621141</v>
       </c>
       <c r="O76">
-        <v>-114.5036367804832</v>
+        <v>-97.72914858906866</v>
       </c>
       <c r="P76">
-        <v>-669.7678480173469</v>
+        <v>-571.6485814730454</v>
       </c>
       <c r="Q76">
-        <v>73.23215198265314</v>
+        <v>171.3514185269546</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1969822780167328</v>
+        <v>0.1962056955525036</v>
       </c>
       <c r="T76">
-        <v>3.489262846504959</v>
+        <v>3.473572645554356</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.07672721040467641</v>
+        <v>0.08245882472773491</v>
       </c>
       <c r="W76">
-        <v>0.1992422679946708</v>
+        <v>0.1842422679946708</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5255288383881946</v>
+        <v>0.5647864707379104</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7556,13 +7556,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.200354670600407</v>
+        <v>0.1889027591597073</v>
       </c>
       <c r="C77">
-        <v>-3029.343128695891</v>
+        <v>-2687.003826490005</v>
       </c>
       <c r="D77">
-        <v>4298.748407501115</v>
+        <v>4641.087709707002</v>
       </c>
       <c r="E77">
         <v>696.6028212676647</v>
@@ -7589,37 +7589,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M77">
-        <v>1675.275153511314</v>
+        <v>1558.828780468359</v>
       </c>
       <c r="N77">
-        <v>-806.6084868446474</v>
+        <v>-690.1621138016922</v>
       </c>
       <c r="O77">
-        <v>-117.7648390793185</v>
+        <v>-100.7636686150471</v>
       </c>
       <c r="P77">
-        <v>-688.8436477653288</v>
+        <v>-589.3984451866451</v>
       </c>
       <c r="Q77">
-        <v>54.1563522346712</v>
+        <v>153.6015548133549</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2030295691374022</v>
+        <v>0.2022219233746037</v>
       </c>
       <c r="T77">
-        <v>3.628833360365157</v>
+        <v>3.612515551376529</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.07570418093261407</v>
+        <v>0.08135937373136512</v>
       </c>
       <c r="W77">
-        <v>0.1994630377547419</v>
+        <v>0.1844630377547419</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5185217872096854</v>
+        <v>0.557255984461405</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7638,13 +7638,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.202054670600407</v>
+        <v>0.1904527591597074</v>
       </c>
       <c r="C78">
-        <v>-3179.620000507669</v>
+        <v>-2840.242434241064</v>
       </c>
       <c r="D78">
-        <v>4251.979422838631</v>
+        <v>4591.356989105236</v>
       </c>
       <c r="E78">
         <v>800.110708416958</v>
@@ -7671,37 +7671,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M78">
-        <v>1697.612155558132</v>
+        <v>1579.613164207937</v>
       </c>
       <c r="N78">
-        <v>-828.9454888914649</v>
+        <v>-710.9464975412702</v>
       </c>
       <c r="O78">
-        <v>-121.0260413781539</v>
+        <v>-103.7981886410254</v>
       </c>
       <c r="P78">
-        <v>-707.9194475133111</v>
+        <v>-607.1483089002447</v>
       </c>
       <c r="Q78">
-        <v>35.08055248668893</v>
+        <v>135.8516910997553</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2095808011847939</v>
+        <v>0.2087395035152122</v>
       </c>
       <c r="T78">
-        <v>3.780034750380373</v>
+        <v>3.763037032683886</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.07470807328876387</v>
+        <v>0.08028885565595244</v>
       </c>
       <c r="W78">
-        <v>0.1996779977842848</v>
+        <v>0.1846779977842848</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5116991321148212</v>
+        <v>0.5499236688763866</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7720,13 +7720,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.203754670600407</v>
+        <v>0.1920027591597073</v>
       </c>
       <c r="C79">
-        <v>-3328.890162310505</v>
+        <v>-2992.42658012867</v>
       </c>
       <c r="D79">
-        <v>4206.217148185088</v>
+        <v>4542.680730366923</v>
       </c>
       <c r="E79">
         <v>903.6185955662513</v>
@@ -7753,37 +7753,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M79">
-        <v>1719.949157604949</v>
+        <v>1600.397547947515</v>
       </c>
       <c r="N79">
-        <v>-851.2824909382823</v>
+        <v>-731.7308812808485</v>
       </c>
       <c r="O79">
-        <v>-124.2872436769892</v>
+        <v>-106.8327086670039</v>
       </c>
       <c r="P79">
-        <v>-726.9952472612931</v>
+        <v>-624.8981726138446</v>
       </c>
       <c r="Q79">
-        <v>16.00475273870688</v>
+        <v>118.1018273861554</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2167017055841328</v>
+        <v>0.215823829755004</v>
       </c>
       <c r="T79">
-        <v>3.944384087353431</v>
+        <v>3.926647338452749</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.07373783857072799</v>
+        <v>0.07924614324483616</v>
       </c>
       <c r="W79">
-        <v>0.1998873744364369</v>
+        <v>0.1848873744364369</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5050536888406028</v>
+        <v>0.542781803046823</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7802,13 +7802,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2291434597542462</v>
+        <v>0.1935527591597073</v>
       </c>
       <c r="C80">
-        <v>-4014.860933348194</v>
+        <v>-3143.589449642509</v>
       </c>
       <c r="D80">
-        <v>3623.754264296694</v>
+        <v>4495.025748002378</v>
       </c>
       <c r="E80">
         <v>1007.126482715546</v>
@@ -7835,45 +7835,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M80">
-        <v>1984.494615581114</v>
+        <v>1621.181931687093</v>
       </c>
       <c r="N80">
-        <v>-1115.827948914447</v>
+        <v>-752.5152650204266</v>
       </c>
       <c r="O80">
-        <v>-162.9108805415092</v>
+        <v>-109.8672286929823</v>
       </c>
       <c r="P80">
-        <v>-952.9170683729376</v>
+        <v>-642.6480363274443</v>
       </c>
       <c r="Q80">
-        <v>-209.9170683729376</v>
+        <v>100.3519636725557</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2257826429008624</v>
+        <v>0.2235521856529588</v>
       </c>
       <c r="T80">
-        <v>4.153970671220082</v>
+        <v>4.105131308382421</v>
       </c>
       <c r="U80">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.06390812670267461</v>
+        <v>0.07823016704938954</v>
       </c>
       <c r="W80">
-        <v>0.2300913824564826</v>
+        <v>0.1850913824564826</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.4377268952237987</v>
+        <v>0.5358230619821203</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7884,13 +7884,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2311434597542462</v>
+        <v>0.1951027591597074</v>
       </c>
       <c r="C81">
-        <v>-4157.471945788247</v>
+        <v>-3293.762850199702</v>
       </c>
       <c r="D81">
-        <v>3584.651139005933</v>
+        <v>4448.360234594478</v>
       </c>
       <c r="E81">
         <v>1110.634369864839</v>
@@ -7917,45 +7917,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M81">
-        <v>2009.93685424241</v>
+        <v>1641.966315426672</v>
       </c>
       <c r="N81">
-        <v>-1141.270187575743</v>
+        <v>-773.2996487600049</v>
       </c>
       <c r="O81">
-        <v>-166.6254473860585</v>
+        <v>-112.9017487189607</v>
       </c>
       <c r="P81">
-        <v>-974.6447401896845</v>
+        <v>-660.3979000410442</v>
       </c>
       <c r="Q81">
-        <v>-231.6447401896845</v>
+        <v>82.60209995895582</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2343532449437607</v>
+        <v>0.2320165754459568</v>
       </c>
       <c r="T81">
-        <v>4.351778798421039</v>
+        <v>4.300613751638727</v>
       </c>
       <c r="U81">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.06309916307352682</v>
+        <v>0.07723991177028333</v>
       </c>
       <c r="W81">
-        <v>0.2302902257165271</v>
+        <v>0.1852902257165271</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.4321860484488139</v>
+        <v>0.5290404915772832</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7966,13 +7966,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2331434597542462</v>
+        <v>0.1966527591597073</v>
       </c>
       <c r="C82">
-        <v>-4299.248061182159</v>
+        <v>-3442.977281942733</v>
       </c>
       <c r="D82">
-        <v>3546.382910761315</v>
+        <v>4402.653690000741</v>
       </c>
       <c r="E82">
         <v>1214.142257014132</v>
@@ -7999,45 +7999,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M82">
-        <v>2035.379092903706</v>
+        <v>1662.75069916625</v>
       </c>
       <c r="N82">
-        <v>-1166.712426237039</v>
+        <v>-794.0840324995829</v>
       </c>
       <c r="O82">
-        <v>-170.3400142306077</v>
+        <v>-115.9362687449391</v>
       </c>
       <c r="P82">
-        <v>-996.3724120064317</v>
+        <v>-678.1477637546438</v>
       </c>
       <c r="Q82">
-        <v>-253.3724120064317</v>
+        <v>64.85223624535615</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2437809071909487</v>
+        <v>0.2413274042182547</v>
       </c>
       <c r="T82">
-        <v>4.569367738342091</v>
+        <v>4.515644439220663</v>
       </c>
       <c r="U82">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.06231042353510775</v>
+        <v>0.0762744128731548</v>
       </c>
       <c r="W82">
-        <v>0.2304840978950705</v>
+        <v>0.1854840978950705</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.4267837228432038</v>
+        <v>0.5224274854325672</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8048,13 +8048,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2351434597542462</v>
+        <v>0.1982027591597074</v>
       </c>
       <c r="C83">
-        <v>-4440.21573611989</v>
+        <v>-3591.262004217104</v>
       </c>
       <c r="D83">
-        <v>3508.923122972878</v>
+        <v>4357.876854875663</v>
       </c>
       <c r="E83">
         <v>1317.650144163425</v>
@@ -8081,45 +8081,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M83">
-        <v>2060.821331565002</v>
+        <v>1683.535082905828</v>
       </c>
       <c r="N83">
-        <v>-1192.154664898336</v>
+        <v>-814.868416239161</v>
       </c>
       <c r="O83">
-        <v>-174.054581075157</v>
+        <v>-118.9707887709175</v>
       </c>
       <c r="P83">
-        <v>-1018.100083823179</v>
+        <v>-695.8976274682435</v>
       </c>
       <c r="Q83">
-        <v>-275.1000838231786</v>
+        <v>47.10237253175649</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2542009549378407</v>
+        <v>0.2516183202297418</v>
       </c>
       <c r="T83">
-        <v>4.809860777202201</v>
+        <v>4.753309936021751</v>
       </c>
       <c r="U83">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.06154115904702</v>
+        <v>0.0753327534549677</v>
       </c>
       <c r="W83">
-        <v>0.2306731831062425</v>
+        <v>0.1856731831062425</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.4215147879932877</v>
+        <v>0.5159777633901899</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8130,13 +8130,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2371434597542462</v>
+        <v>0.1997527591597074</v>
       </c>
       <c r="C84">
-        <v>-4580.400321051062</v>
+        <v>-3738.645098033204</v>
       </c>
       <c r="D84">
-        <v>3472.246425190998</v>
+        <v>4314.001648208857</v>
       </c>
       <c r="E84">
         <v>1421.158031312719</v>
@@ -8163,45 +8163,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M84">
-        <v>2086.263570226299</v>
+        <v>1704.319466645406</v>
       </c>
       <c r="N84">
-        <v>-1217.596903559632</v>
+        <v>-835.652799978739</v>
       </c>
       <c r="O84">
-        <v>-177.7691479197063</v>
+        <v>-122.0053087968959</v>
       </c>
       <c r="P84">
-        <v>-1039.827755639926</v>
+        <v>-713.6474911818432</v>
       </c>
       <c r="Q84">
-        <v>-296.8277556399257</v>
+        <v>29.35250881815682</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2657787857677208</v>
+        <v>0.2630526713536163</v>
       </c>
       <c r="T84">
-        <v>5.077075264824546</v>
+        <v>5.017382710245182</v>
       </c>
       <c r="U84">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.06079065710742219</v>
+        <v>0.07441406133966322</v>
       </c>
       <c r="W84">
-        <v>0.2308576564829957</v>
+        <v>0.1858576564829956</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.4163743637494671</v>
+        <v>0.5096853516415289</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8212,13 +8212,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2391434597542462</v>
+        <v>0.2013027591597074</v>
       </c>
       <c r="C85">
-        <v>-4719.826117496119</v>
+        <v>-3885.153524792578</v>
       </c>
       <c r="D85">
-        <v>3436.328515895235</v>
+        <v>4271.001108598776</v>
       </c>
       <c r="E85">
         <v>1524.665918462012</v>
@@ -8245,45 +8245,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M85">
-        <v>2111.705808887595</v>
+        <v>1725.103850384984</v>
       </c>
       <c r="N85">
-        <v>-1243.039142220928</v>
+        <v>-856.4371837183171</v>
       </c>
       <c r="O85">
-        <v>-181.4837147642555</v>
+        <v>-125.0398288228743</v>
       </c>
       <c r="P85">
-        <v>-1061.555427456673</v>
+        <v>-731.3973548954428</v>
       </c>
       <c r="Q85">
-        <v>-318.555427456673</v>
+        <v>11.60264510455715</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2787187143422927</v>
+        <v>0.2758322402567702</v>
       </c>
       <c r="T85">
-        <v>5.375726750990697</v>
+        <v>5.312522869671369</v>
       </c>
       <c r="U85">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.06005823955191107</v>
+        <v>0.07351750638376367</v>
       </c>
       <c r="W85">
-        <v>0.2310376847181403</v>
+        <v>0.1860376847181403</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.4113578051500759</v>
+        <v>0.5035445642723539</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8294,13 +8294,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2411434597542461</v>
+        <v>0.2326299613231866</v>
       </c>
       <c r="C86">
-        <v>-4858.516431742979</v>
+        <v>-4704.81268779675</v>
       </c>
       <c r="D86">
-        <v>3401.146088797668</v>
+        <v>3554.849832743897</v>
       </c>
       <c r="E86">
         <v>1628.173805611305</v>
@@ -8327,37 +8327,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M86">
-        <v>2137.148047548891</v>
+        <v>2050.201422343485</v>
       </c>
       <c r="N86">
-        <v>-1268.481380882224</v>
+        <v>-1181.534755676818</v>
       </c>
       <c r="O86">
-        <v>-185.1982816088047</v>
+        <v>-172.5040743288154</v>
       </c>
       <c r="P86">
-        <v>-1083.28309927342</v>
+        <v>-1009.030681348003</v>
       </c>
       <c r="Q86">
-        <v>-340.2830992734196</v>
+        <v>-266.0306813480026</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2932761339886858</v>
+        <v>0.2925667687945637</v>
       </c>
       <c r="T86">
-        <v>5.711709672927612</v>
+        <v>5.699001588789002</v>
       </c>
       <c r="U86">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05934326050962643</v>
+        <v>0.06185993822419921</v>
       </c>
       <c r="W86">
-        <v>0.2312134265667338</v>
+        <v>0.2212134265667338</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4064606884220988</v>
+        <v>0.4236982070150631</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8376,13 +8376,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2431434597542461</v>
+        <v>0.2345299613231866</v>
       </c>
       <c r="C87">
-        <v>-4996.493625278541</v>
+        <v>-4844.108293201584</v>
       </c>
       <c r="D87">
-        <v>3366.676782411399</v>
+        <v>3519.062114488356</v>
       </c>
       <c r="E87">
         <v>1731.681692760599</v>
@@ -8409,37 +8409,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M87">
-        <v>2162.590286210188</v>
+        <v>2074.608582133288</v>
       </c>
       <c r="N87">
-        <v>-1293.923619543521</v>
+        <v>-1205.941915466621</v>
       </c>
       <c r="O87">
-        <v>-188.912848453354</v>
+        <v>-176.0675196581267</v>
       </c>
       <c r="P87">
-        <v>-1105.010771090167</v>
+        <v>-1029.874395808495</v>
       </c>
       <c r="Q87">
-        <v>-362.0107710901668</v>
+        <v>-286.8743958084947</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3097745429212649</v>
+        <v>0.3090178867142013</v>
       </c>
       <c r="T87">
-        <v>6.092490317789453</v>
+        <v>6.078935028041602</v>
       </c>
       <c r="U87">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05864510450363082</v>
+        <v>0.06113217424509099</v>
       </c>
       <c r="W87">
-        <v>0.2313850333130076</v>
+        <v>0.2213850333130075</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4016787979700741</v>
+        <v>0.4187135222266507</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8458,13 +8458,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2451434597542462</v>
+        <v>0.2364299613231866</v>
       </c>
       <c r="C88">
-        <v>-5133.77916218431</v>
+        <v>-4982.690509544032</v>
       </c>
       <c r="D88">
-        <v>3332.899132654924</v>
+        <v>3483.987785295201</v>
       </c>
       <c r="E88">
         <v>1835.189579909892</v>
@@ -8491,37 +8491,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M88">
-        <v>2188.032524871484</v>
+        <v>2099.015741923091</v>
       </c>
       <c r="N88">
-        <v>-1319.365858204817</v>
+        <v>-1230.349075256425</v>
       </c>
       <c r="O88">
-        <v>-192.6274152979033</v>
+        <v>-179.630964987438</v>
       </c>
       <c r="P88">
-        <v>-1126.738442906914</v>
+        <v>-1050.718110268987</v>
       </c>
       <c r="Q88">
-        <v>-383.7384429069139</v>
+        <v>-307.7181102689867</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.328629867415641</v>
+        <v>0.3278191643366443</v>
       </c>
       <c r="T88">
-        <v>6.527668197631558</v>
+        <v>6.513144672901718</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05796318468382116</v>
+        <v>0.06042133500968296</v>
       </c>
       <c r="W88">
-        <v>0.2315526492047168</v>
+        <v>0.2215526492047168</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3970081142727477</v>
+        <v>0.4138447603402943</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8540,13 +8540,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2471434597542462</v>
+        <v>0.2383299613231866</v>
       </c>
       <c r="C89">
-        <v>-5270.393653707273</v>
+        <v>-5120.580457264923</v>
       </c>
       <c r="D89">
-        <v>3299.792528281254</v>
+        <v>3449.605724723604</v>
       </c>
       <c r="E89">
         <v>1938.697467059185</v>
@@ -8573,37 +8573,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M89">
-        <v>2213.47476353278</v>
+        <v>2123.422901712895</v>
       </c>
       <c r="N89">
-        <v>-1344.808096866114</v>
+        <v>-1254.756235046228</v>
       </c>
       <c r="O89">
-        <v>-196.3419821424526</v>
+        <v>-183.1944103167493</v>
       </c>
       <c r="P89">
-        <v>-1148.466114723661</v>
+        <v>-1071.561824729479</v>
       </c>
       <c r="Q89">
-        <v>-405.4661147236611</v>
+        <v>-328.5618247294785</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3503860110629979</v>
+        <v>0.3495129462086938</v>
       </c>
       <c r="T89">
-        <v>7.029796520526292</v>
+        <v>7.014155801586464</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05729694118170826</v>
+        <v>0.05972683690612339</v>
       </c>
       <c r="W89">
-        <v>0.2317164118575361</v>
+        <v>0.2217164118575361</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3924448026144403</v>
+        <v>0.4090879240145439</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2491434597542462</v>
+        <v>0.2402299613231866</v>
       </c>
       <c r="C90">
-        <v>-5406.3569002005</v>
+        <v>-5257.798431236073</v>
       </c>
       <c r="D90">
-        <v>3267.337168937321</v>
+        <v>3415.895637901747</v>
       </c>
       <c r="E90">
         <v>2042.205354208479</v>
@@ -8655,37 +8655,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M90">
-        <v>2238.917002194076</v>
+        <v>2147.830061502698</v>
       </c>
       <c r="N90">
-        <v>-1370.25033552741</v>
+        <v>-1279.163394836032</v>
       </c>
       <c r="O90">
-        <v>-200.0565489870018</v>
+        <v>-186.7578556460606</v>
       </c>
       <c r="P90">
-        <v>-1170.193786540408</v>
+        <v>-1092.405539189971</v>
       </c>
       <c r="Q90">
-        <v>-427.1937865404077</v>
+        <v>-349.405539189971</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3757681786515811</v>
+        <v>0.3748223583927517</v>
       </c>
       <c r="T90">
-        <v>7.615612897236817</v>
+        <v>7.598668785052005</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05664583957737068</v>
+        <v>0.05904812285037198</v>
       </c>
       <c r="W90">
-        <v>0.2318764526318823</v>
+        <v>0.2218764526318823</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3879852025847308</v>
+        <v>0.4044391976052876</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8704,13 +8704,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2511434597542462</v>
+        <v>0.2421299613231866</v>
       </c>
       <c r="C91">
-        <v>-5541.687930612768</v>
+        <v>-5394.363940707868</v>
       </c>
       <c r="D91">
-        <v>3235.514025674345</v>
+        <v>3382.838015579246</v>
       </c>
       <c r="E91">
         <v>2145.713241357772</v>
@@ -8737,37 +8737,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M91">
-        <v>2264.359240855373</v>
+        <v>2172.237221292502</v>
       </c>
       <c r="N91">
-        <v>-1395.692574188706</v>
+        <v>-1303.570554625835</v>
       </c>
       <c r="O91">
-        <v>-203.7711158315511</v>
+        <v>-190.3213009753719</v>
       </c>
       <c r="P91">
-        <v>-1191.921458357155</v>
+        <v>-1113.249253650463</v>
       </c>
       <c r="Q91">
-        <v>-448.921458357155</v>
+        <v>-370.2492536504628</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4057652858017249</v>
+        <v>0.4047334818830019</v>
       </c>
       <c r="T91">
-        <v>8.307941342440165</v>
+        <v>8.289456856420369</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05600936946975978</v>
+        <v>0.05838466079587343</v>
       </c>
       <c r="W91">
-        <v>0.2320328969843331</v>
+        <v>0.222032896984333</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3836258182860259</v>
+        <v>0.3998949369580371</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8786,13 +8786,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2531434597542462</v>
+        <v>0.2440299613231866</v>
       </c>
       <c r="C92">
-        <v>-5676.40503969276</v>
+        <v>-5530.295746959491</v>
       </c>
       <c r="D92">
-        <v>3204.304803743649</v>
+        <v>3350.414096476918</v>
       </c>
       <c r="E92">
         <v>2249.221128507067</v>
@@ -8819,37 +8819,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M92">
-        <v>2289.80147951667</v>
+        <v>2196.644381082305</v>
       </c>
       <c r="N92">
-        <v>-1421.134812850003</v>
+        <v>-1327.977714415639</v>
       </c>
       <c r="O92">
-        <v>-207.4856826761004</v>
+        <v>-193.8847463046832</v>
       </c>
       <c r="P92">
-        <v>-1213.649130173902</v>
+        <v>-1134.092968110955</v>
       </c>
       <c r="Q92">
-        <v>-470.6491301739024</v>
+        <v>-391.0929681109553</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4417618143818974</v>
+        <v>0.4406268300713022</v>
       </c>
       <c r="T92">
-        <v>9.138735476684182</v>
+        <v>9.118402542062407</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05538704314231799</v>
+        <v>0.05773594234258594</v>
       </c>
       <c r="W92">
-        <v>0.2321858647956183</v>
+        <v>0.2221858647956182</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3793633091939589</v>
+        <v>0.3954516598807256</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8868,13 +8868,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2551434597542461</v>
+        <v>0.2459299613231866</v>
       </c>
       <c r="C93">
-        <v>-5810.525823060595</v>
+        <v>-5665.611898804475</v>
       </c>
       <c r="D93">
-        <v>3173.691907525107</v>
+        <v>3318.605831781228</v>
       </c>
       <c r="E93">
         <v>2352.72901565636</v>
@@ -8901,37 +8901,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M93">
-        <v>2315.243718177966</v>
+        <v>2221.051540872108</v>
       </c>
       <c r="N93">
-        <v>-1446.577051511299</v>
+        <v>-1352.384874205442</v>
       </c>
       <c r="O93">
-        <v>-211.2002495206496</v>
+        <v>-197.4481916339945</v>
       </c>
       <c r="P93">
-        <v>-1235.376801990649</v>
+        <v>-1154.936682571447</v>
       </c>
       <c r="Q93">
-        <v>-492.3768019906493</v>
+        <v>-411.9366825714474</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4857575715354416</v>
+        <v>0.4844964778570025</v>
       </c>
       <c r="T93">
-        <v>10.15415052964909</v>
+        <v>10.13155838006934</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05477839431657824</v>
+        <v>0.05710148143772235</v>
       </c>
       <c r="W93">
-        <v>0.2323354706769851</v>
+        <v>0.2223354706769851</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3751944816203989</v>
+        <v>0.3911060372446736</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8950,13 +8950,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2571434597542462</v>
+        <v>0.2478299613231867</v>
       </c>
       <c r="C94">
-        <v>-5944.067210288062</v>
+        <v>-5800.329766092791</v>
       </c>
       <c r="D94">
-        <v>3143.658407446934</v>
+        <v>3287.395851642204</v>
       </c>
       <c r="E94">
         <v>2456.236902805654</v>
@@ -8983,37 +8983,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M94">
-        <v>2340.685956839262</v>
+        <v>2245.458700661912</v>
       </c>
       <c r="N94">
-        <v>-1472.019290172595</v>
+        <v>-1376.792033995245</v>
       </c>
       <c r="O94">
-        <v>-214.9148163651989</v>
+        <v>-201.0116369633058</v>
       </c>
       <c r="P94">
-        <v>-1257.104473807396</v>
+        <v>-1175.78039703194</v>
       </c>
       <c r="Q94">
-        <v>-514.1044738073963</v>
+        <v>-432.7803970319396</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.540752267977372</v>
+        <v>0.5393335375891278</v>
       </c>
       <c r="T94">
-        <v>11.42341934585523</v>
+        <v>11.39800317757801</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05418297698705021</v>
+        <v>0.05648081316122536</v>
       </c>
       <c r="W94">
-        <v>0.2324818242565831</v>
+        <v>0.2224818242565831</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3711162807332207</v>
+        <v>0.3868548846659272</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9032,13 +9032,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2591434597542462</v>
+        <v>0.2497299613231866</v>
       </c>
       <c r="C95">
-        <v>-6077.045496118131</v>
+        <v>-5934.466071340108</v>
       </c>
       <c r="D95">
-        <v>3114.188008766158</v>
+        <v>3256.767433544181</v>
       </c>
       <c r="E95">
         <v>2559.744789954947</v>
@@ -9065,37 +9065,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M95">
-        <v>2366.128195500558</v>
+        <v>2269.865860451715</v>
       </c>
       <c r="N95">
-        <v>-1497.461528833892</v>
+        <v>-1401.199193785049</v>
       </c>
       <c r="O95">
-        <v>-218.6293832097482</v>
+        <v>-204.5750822926171</v>
       </c>
       <c r="P95">
-        <v>-1278.832145624144</v>
+        <v>-1196.624111492432</v>
       </c>
       <c r="Q95">
-        <v>-535.8321456241435</v>
+        <v>-453.6241114924317</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6114597348312822</v>
+        <v>0.609838328673289</v>
       </c>
       <c r="T95">
-        <v>13.05533639526312</v>
+        <v>13.02628934580345</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05360036433127548</v>
+        <v>0.05587349258959928</v>
       </c>
       <c r="W95">
-        <v>0.2326250304473725</v>
+        <v>0.2226250304473725</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3671257830909279</v>
+        <v>0.3826951547232829</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9114,13 +9114,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2611434597542462</v>
+        <v>0.2516299613231866</v>
       </c>
       <c r="C96">
-        <v>-6209.476369944801</v>
+        <v>-6068.036919605242</v>
       </c>
       <c r="D96">
-        <v>3085.265022088781</v>
+        <v>3226.704472428341</v>
       </c>
       <c r="E96">
         <v>2663.25267710424</v>
@@ -9147,37 +9147,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M96">
-        <v>2391.570434161855</v>
+        <v>2294.273020241519</v>
       </c>
       <c r="N96">
-        <v>-1522.903767495188</v>
+        <v>-1425.606353574852</v>
       </c>
       <c r="O96">
-        <v>-222.3439500542974</v>
+        <v>-208.1385276219284</v>
       </c>
       <c r="P96">
-        <v>-1300.559817440891</v>
+        <v>-1217.467825952923</v>
       </c>
       <c r="Q96">
-        <v>-557.5598174408906</v>
+        <v>-474.4678259529235</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7057363573031629</v>
+        <v>0.7038447167855041</v>
       </c>
       <c r="T96">
-        <v>15.23122579447365</v>
+        <v>15.19733757010402</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05303014768945339</v>
+        <v>0.05527909373226313</v>
       </c>
       <c r="W96">
-        <v>0.2327651896979324</v>
+        <v>0.2227651896979324</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3632201896537904</v>
+        <v>0.3786239296730352</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9196,13 +9196,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2631434597542461</v>
+        <v>0.2535299613231866</v>
       </c>
       <c r="C97">
-        <v>-6341.374943665269</v>
+        <v>-6201.057826727978</v>
       </c>
       <c r="D97">
-        <v>3056.874335517607</v>
+        <v>3197.191452454897</v>
       </c>
       <c r="E97">
         <v>2766.760564253534</v>
@@ -9229,37 +9229,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M97">
-        <v>2417.012672823151</v>
+        <v>2318.680180031322</v>
       </c>
       <c r="N97">
-        <v>-1548.346006156484</v>
+        <v>-1450.013513364655</v>
       </c>
       <c r="O97">
-        <v>-226.0585168988466</v>
+        <v>-211.7019729512396</v>
       </c>
       <c r="P97">
-        <v>-1322.287489257637</v>
+        <v>-1238.311540413416</v>
       </c>
       <c r="Q97">
-        <v>-579.2874892576374</v>
+        <v>-495.3115404134155</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8377236287637956</v>
+        <v>0.8354536601426051</v>
       </c>
       <c r="T97">
-        <v>18.27747095336838</v>
+        <v>18.23680508412484</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05247193560851179</v>
+        <v>0.05469720853508141</v>
       </c>
       <c r="W97">
-        <v>0.2329023982274278</v>
+        <v>0.2229023982274278</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3593968192363821</v>
+        <v>0.3746384146238454</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9278,13 +9278,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2651434597542461</v>
+        <v>0.2554299613231866</v>
       </c>
       <c r="C98">
-        <v>-6472.755778008361</v>
+        <v>-6333.543746031268</v>
       </c>
       <c r="D98">
-        <v>3029.001388323808</v>
+        <v>3168.213420300901</v>
       </c>
       <c r="E98">
         <v>2870.268451402827</v>
@@ -9311,37 +9311,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M98">
-        <v>2442.454911484447</v>
+        <v>2343.087339821126</v>
       </c>
       <c r="N98">
-        <v>-1573.78824481778</v>
+        <v>-1474.420673154459</v>
       </c>
       <c r="O98">
-        <v>-229.7730837433959</v>
+        <v>-215.265418280551</v>
       </c>
       <c r="P98">
-        <v>-1344.015161074384</v>
+        <v>-1259.155254873908</v>
       </c>
       <c r="Q98">
-        <v>-601.0151610743844</v>
+        <v>-516.1552548739078</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.035704535954743</v>
+        <v>1.032867075178254</v>
       </c>
       <c r="T98">
-        <v>22.84683869171043</v>
+        <v>22.79600635515599</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05192535294592312</v>
+        <v>0.05412744594617431</v>
       </c>
       <c r="W98">
-        <v>0.2330367482458921</v>
+        <v>0.2230367482458921</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3556531023693364</v>
+        <v>0.3707359311381803</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9360,13 +9360,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2671434597542461</v>
+        <v>0.2573299613231866</v>
       </c>
       <c r="C99">
-        <v>-6603.632907435577</v>
+        <v>-6465.50909358436</v>
       </c>
       <c r="D99">
-        <v>3001.632146045885</v>
+        <v>3139.755959897102</v>
       </c>
       <c r="E99">
         <v>2973.77633855212</v>
@@ -9393,37 +9393,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M99">
-        <v>2467.897150145744</v>
+        <v>2367.494499610929</v>
       </c>
       <c r="N99">
-        <v>-1599.230483479077</v>
+        <v>-1498.827832944262</v>
       </c>
       <c r="O99">
-        <v>-233.4876505879452</v>
+        <v>-218.8288636098623</v>
       </c>
       <c r="P99">
-        <v>-1365.742832891132</v>
+        <v>-1279.9989693344</v>
       </c>
       <c r="Q99">
-        <v>-622.7428328911317</v>
+        <v>-536.9989693343998</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.365672714606323</v>
+        <v>1.361889433571006</v>
       </c>
       <c r="T99">
-        <v>30.46245158894724</v>
+        <v>30.39467514020799</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05139004002895484</v>
+        <v>0.05356943103951272</v>
       </c>
       <c r="W99">
-        <v>0.2331683281608829</v>
+        <v>0.2231683281608829</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3519865755407866</v>
+        <v>0.3669139112295392</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9442,13 +9442,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2691434597542461</v>
+        <v>0.2592299613231867</v>
       </c>
       <c r="C100">
-        <v>-6734.019863704232</v>
+        <v>-6596.967772116553</v>
       </c>
       <c r="D100">
-        <v>2974.753076926524</v>
+        <v>3111.805168514203</v>
       </c>
       <c r="E100">
         <v>3077.284225701414</v>
@@ -9475,37 +9475,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M100">
-        <v>2493.33938880704</v>
+        <v>2391.901659400732</v>
       </c>
       <c r="N100">
-        <v>-1624.672722140373</v>
+        <v>-1523.234992734065</v>
       </c>
       <c r="O100">
-        <v>-237.2022174324945</v>
+        <v>-222.3923089391735</v>
       </c>
       <c r="P100">
-        <v>-1387.470504707879</v>
+        <v>-1300.842683794892</v>
       </c>
       <c r="Q100">
-        <v>-644.4705047078787</v>
+        <v>-557.8426837948919</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.025609071909485</v>
+        <v>2.019934150356508</v>
       </c>
       <c r="T100">
-        <v>45.69367738342086</v>
+        <v>45.59201271031198</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05086565186539407</v>
+        <v>0.05302280419217076</v>
       </c>
       <c r="W100">
-        <v>0.2332972227714862</v>
+        <v>0.2232972227714861</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3483948757903704</v>
+        <v>0.363169891727197</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9524,13 +9524,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2711434597542462</v>
+        <v>0.2611299613231866</v>
       </c>
       <c r="C101">
-        <v>-6863.929698175811</v>
+        <v>-6727.933193664892</v>
       </c>
       <c r="D101">
-        <v>2948.351129604238</v>
+        <v>3084.347634115156</v>
       </c>
       <c r="E101">
         <v>3180.792112850707</v>
@@ -9557,37 +9557,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M101">
-        <v>2518.781627468336</v>
+        <v>2416.308819190535</v>
       </c>
       <c r="N101">
-        <v>-1650.114960801669</v>
+        <v>-1547.642152523869</v>
       </c>
       <c r="O101">
-        <v>-240.9167842770437</v>
+        <v>-225.9557542684848</v>
       </c>
       <c r="P101">
-        <v>-1409.198176524626</v>
+        <v>-1321.686398255384</v>
       </c>
       <c r="Q101">
-        <v>-666.1981765246255</v>
+        <v>-578.6863982553839</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.00541814381897</v>
+        <v>3.994068300713018</v>
       </c>
       <c r="T101">
-        <v>91.38735476684172</v>
+        <v>91.18402542062398</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.05035185740210727</v>
+        <v>0.05248722031144176</v>
       </c>
       <c r="W101">
-        <v>0.2334235134505621</v>
+        <v>0.2234235134505621</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3448757356308717</v>
+        <v>0.3595015089824779</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/switzerland/switzerland_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_oil_gas_production_and_exploration.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08744674570503419</v>
+        <v>0.08735750345630482</v>
       </c>
       <c r="C2">
-        <v>16382.2834075724</v>
+        <v>16313.0213560497</v>
       </c>
       <c r="D2">
-        <v>15947.2834075724</v>
+        <v>15981.52924319899</v>
       </c>
       <c r="E2">
-        <v>-7066.488714929342</v>
+        <v>-6962.980827780048</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>103.5078871492934</v>
       </c>
       <c r="G2">
         <v>435</v>
@@ -1439,28 +1439,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.206446723609459</v>
       </c>
       <c r="N2">
-        <v>868.6666666666667</v>
+        <v>863.4602199430573</v>
       </c>
       <c r="O2">
-        <v>126.8253333333333</v>
+        <v>126.0651921116864</v>
       </c>
       <c r="P2">
-        <v>741.8413333333334</v>
+        <v>737.395027831371</v>
       </c>
       <c r="Q2">
-        <v>1484.841333333333</v>
+        <v>1480.395027831371</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08744674570503419</v>
+        <v>0.08780600147101497</v>
       </c>
       <c r="T2">
-        <v>0.9618186075065632</v>
+        <v>0.970115507413741</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>166.8444359043491</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08735750345630482</v>
+        <v>0.08726826120757548</v>
       </c>
       <c r="C3">
-        <v>16313.0213560497</v>
+        <v>16243.90670281628</v>
       </c>
       <c r="D3">
-        <v>15981.52924319899</v>
+        <v>16015.92247711487</v>
       </c>
       <c r="E3">
-        <v>-6962.980827780048</v>
+        <v>-6859.472940630755</v>
       </c>
       <c r="F3">
-        <v>103.5078871492934</v>
+        <v>207.0157742985868</v>
       </c>
       <c r="G3">
         <v>435</v>
@@ -1521,28 +1521,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M3">
-        <v>5.206446723609459</v>
+        <v>10.41289344721892</v>
       </c>
       <c r="N3">
-        <v>863.4602199430573</v>
+        <v>858.2537732194478</v>
       </c>
       <c r="O3">
-        <v>126.0651921116864</v>
+        <v>125.3050508900394</v>
       </c>
       <c r="P3">
-        <v>737.395027831371</v>
+        <v>732.9487223294084</v>
       </c>
       <c r="Q3">
-        <v>1480.395027831371</v>
+        <v>1475.948722329408</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08780600147101497</v>
+        <v>0.08817258898732191</v>
       </c>
       <c r="T3">
-        <v>0.970115507413741</v>
+        <v>0.9785817318088204</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>166.8444359043491</v>
+        <v>83.42221795217455</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08726826120757548</v>
+        <v>0.08717901895884612</v>
       </c>
       <c r="C4">
-        <v>16243.90670281628</v>
+        <v>16174.9404015551</v>
       </c>
       <c r="D4">
-        <v>16015.92247711487</v>
+        <v>16050.46406300298</v>
       </c>
       <c r="E4">
-        <v>-6859.472940630755</v>
+        <v>-6755.965053481462</v>
       </c>
       <c r="F4">
-        <v>207.0157742985868</v>
+        <v>310.5236614478803</v>
       </c>
       <c r="G4">
         <v>435</v>
@@ -1603,28 +1603,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M4">
-        <v>10.41289344721892</v>
+        <v>15.61934017082838</v>
       </c>
       <c r="N4">
-        <v>858.2537732194478</v>
+        <v>853.0473264958383</v>
       </c>
       <c r="O4">
-        <v>125.3050508900394</v>
+        <v>124.5449096683924</v>
       </c>
       <c r="P4">
-        <v>732.9487223294084</v>
+        <v>728.5024168274459</v>
       </c>
       <c r="Q4">
-        <v>1475.948722329408</v>
+        <v>1471.502416827446</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08817258898732191</v>
+        <v>0.08854673500911972</v>
       </c>
       <c r="T4">
-        <v>0.9785817318088204</v>
+        <v>0.9872225175316334</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>83.42221795217455</v>
+        <v>55.61481196811636</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08717901895884612</v>
+        <v>0.08708977671011678</v>
       </c>
       <c r="C5">
-        <v>16174.9404015551</v>
+        <v>16106.12341419411</v>
       </c>
       <c r="D5">
-        <v>16050.46406300298</v>
+        <v>16085.15496279128</v>
       </c>
       <c r="E5">
-        <v>-6755.965053481462</v>
+        <v>-6652.457166332168</v>
       </c>
       <c r="F5">
-        <v>310.5236614478803</v>
+        <v>414.0315485971737</v>
       </c>
       <c r="G5">
         <v>435</v>
@@ -1685,28 +1685,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M5">
-        <v>15.61934017082838</v>
+        <v>20.82578689443784</v>
       </c>
       <c r="N5">
-        <v>853.0473264958383</v>
+        <v>847.840879772229</v>
       </c>
       <c r="O5">
-        <v>124.5449096683924</v>
+        <v>123.7847684467454</v>
       </c>
       <c r="P5">
-        <v>728.5024168274459</v>
+        <v>724.0561113254836</v>
       </c>
       <c r="Q5">
-        <v>1471.502416827446</v>
+        <v>1467.056111325483</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08854673500911972</v>
+        <v>0.08892867573970498</v>
       </c>
       <c r="T5">
-        <v>0.9872225175316334</v>
+        <v>0.9960433196236718</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>55.61481196811636</v>
+        <v>41.71110897608727</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08708977671011678</v>
+        <v>0.08700053446138743</v>
       </c>
       <c r="C6">
-        <v>16106.12341419411</v>
+        <v>16037.45671099559</v>
       </c>
       <c r="D6">
-        <v>16085.15496279128</v>
+        <v>16119.99614674206</v>
       </c>
       <c r="E6">
-        <v>-6652.457166332168</v>
+        <v>-6548.949279182874</v>
       </c>
       <c r="F6">
-        <v>414.0315485971737</v>
+        <v>517.5394357464671</v>
       </c>
       <c r="G6">
         <v>435</v>
@@ -1767,28 +1767,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M6">
-        <v>20.82578689443784</v>
+        <v>26.03223361804729</v>
       </c>
       <c r="N6">
-        <v>847.840879772229</v>
+        <v>842.6344330486195</v>
       </c>
       <c r="O6">
-        <v>123.7847684467454</v>
+        <v>123.0246272250984</v>
       </c>
       <c r="P6">
-        <v>724.0561113254836</v>
+        <v>719.609805823521</v>
       </c>
       <c r="Q6">
-        <v>1467.056111325483</v>
+        <v>1462.609805823521</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08892867573970498</v>
+        <v>0.08931865732777625</v>
       </c>
       <c r="T6">
-        <v>0.9960433196236718</v>
+        <v>1.005049822812385</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>41.71110897608727</v>
+        <v>33.36888718086983</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08700053446138743</v>
+        <v>0.08691129221265807</v>
       </c>
       <c r="C7">
-        <v>16037.45671099559</v>
+        <v>15968.94127064662</v>
       </c>
       <c r="D7">
-        <v>16119.99614674206</v>
+        <v>16154.98859354238</v>
       </c>
       <c r="E7">
-        <v>-6548.949279182874</v>
+        <v>-6445.441392033581</v>
       </c>
       <c r="F7">
-        <v>517.5394357464671</v>
+        <v>621.0473228957605</v>
       </c>
       <c r="G7">
         <v>435</v>
@@ -1849,28 +1849,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M7">
-        <v>26.03223361804729</v>
+        <v>31.23868034165675</v>
       </c>
       <c r="N7">
-        <v>842.6344330486195</v>
+        <v>837.42798632501</v>
       </c>
       <c r="O7">
-        <v>123.0246272250984</v>
+        <v>122.2644860034515</v>
       </c>
       <c r="P7">
-        <v>719.609805823521</v>
+        <v>715.1635003215586</v>
       </c>
       <c r="Q7">
-        <v>1462.609805823521</v>
+        <v>1458.163500321559</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08931865732777625</v>
+        <v>0.08971693639644476</v>
       </c>
       <c r="T7">
-        <v>1.005049822812385</v>
+        <v>1.014247953728517</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.36888718086983</v>
+        <v>27.80740598405819</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08691129221265807</v>
+        <v>0.08682204996392874</v>
       </c>
       <c r="C8">
-        <v>15968.94127064662</v>
+        <v>15900.57808035066</v>
       </c>
       <c r="D8">
-        <v>16154.98859354238</v>
+        <v>16190.13329039571</v>
       </c>
       <c r="E8">
-        <v>-6445.441392033581</v>
+        <v>-6341.933504884288</v>
       </c>
       <c r="F8">
-        <v>621.0473228957605</v>
+        <v>724.5552100450539</v>
       </c>
       <c r="G8">
         <v>435</v>
@@ -1931,28 +1931,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M8">
-        <v>31.23868034165675</v>
+        <v>36.44512706526621</v>
       </c>
       <c r="N8">
-        <v>837.42798632501</v>
+        <v>832.2215396014005</v>
       </c>
       <c r="O8">
-        <v>122.2644860034515</v>
+        <v>121.5043447818045</v>
       </c>
       <c r="P8">
-        <v>715.1635003215586</v>
+        <v>710.7171948195961</v>
       </c>
       <c r="Q8">
-        <v>1458.163500321559</v>
+        <v>1453.717194819596</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08971693639644476</v>
+        <v>0.09012378060637498</v>
       </c>
       <c r="T8">
-        <v>1.014247953728517</v>
+        <v>1.023643893911663</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.80740598405819</v>
+        <v>23.83491941490702</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08682204996392873</v>
+        <v>0.08673280771519938</v>
       </c>
       <c r="C9">
-        <v>15900.57808035066</v>
+        <v>15832.36813592046</v>
       </c>
       <c r="D9">
-        <v>16190.13329039571</v>
+        <v>16225.4312331148</v>
       </c>
       <c r="E9">
-        <v>-6341.933504884288</v>
+        <v>-6238.425617734994</v>
       </c>
       <c r="F9">
-        <v>724.555210045054</v>
+        <v>828.0630971943474</v>
       </c>
       <c r="G9">
         <v>435</v>
@@ -2013,28 +2013,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M9">
-        <v>36.44512706526621</v>
+        <v>41.65157378887567</v>
       </c>
       <c r="N9">
-        <v>832.2215396014005</v>
+        <v>827.0150928777911</v>
       </c>
       <c r="O9">
-        <v>121.5043447818045</v>
+        <v>120.7442035601575</v>
       </c>
       <c r="P9">
-        <v>710.7171948195961</v>
+        <v>706.2708893176335</v>
       </c>
       <c r="Q9">
-        <v>1453.717194819596</v>
+        <v>1449.270889317634</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09012378060637498</v>
+        <v>0.0905394692556515</v>
       </c>
       <c r="T9">
-        <v>1.023643893911663</v>
+        <v>1.033244093664007</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.83491941490701</v>
+        <v>20.85555448804364</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08673280771519938</v>
+        <v>0.08664356546647003</v>
       </c>
       <c r="C10">
-        <v>15832.36813592046</v>
+        <v>15764.31244187206</v>
       </c>
       <c r="D10">
-        <v>16225.4312331148</v>
+        <v>16260.88342621571</v>
       </c>
       <c r="E10">
-        <v>-6238.425617734994</v>
+        <v>-6134.917730585701</v>
       </c>
       <c r="F10">
-        <v>828.0630971943474</v>
+        <v>931.5709843436407</v>
       </c>
       <c r="G10">
         <v>435</v>
@@ -2095,28 +2095,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M10">
-        <v>41.65157378887567</v>
+        <v>46.85802051248513</v>
       </c>
       <c r="N10">
-        <v>827.0150928777911</v>
+        <v>821.8086461541816</v>
       </c>
       <c r="O10">
-        <v>120.7442035601575</v>
+        <v>119.9840623385105</v>
       </c>
       <c r="P10">
-        <v>706.2708893176335</v>
+        <v>701.8245838156711</v>
       </c>
       <c r="Q10">
-        <v>1449.270889317634</v>
+        <v>1444.824583815671</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0905394692556515</v>
+        <v>0.09096429391919783</v>
       </c>
       <c r="T10">
-        <v>1.033244093664007</v>
+        <v>1.043055286817502</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.85555448804364</v>
+        <v>18.53827065603879</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08664356546647003</v>
+        <v>0.08655432321774069</v>
       </c>
       <c r="C11">
-        <v>15764.31244187206</v>
+        <v>15696.41201152013</v>
       </c>
       <c r="D11">
-        <v>16260.88342621571</v>
+        <v>16296.49088301306</v>
       </c>
       <c r="E11">
-        <v>-6134.917730585701</v>
+        <v>-6031.409843436408</v>
       </c>
       <c r="F11">
-        <v>931.5709843436407</v>
+        <v>1035.078871492934</v>
       </c>
       <c r="G11">
         <v>435</v>
@@ -2177,28 +2177,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M11">
-        <v>46.85802051248513</v>
+        <v>52.06446723609458</v>
       </c>
       <c r="N11">
-        <v>821.8086461541816</v>
+        <v>816.6021994305721</v>
       </c>
       <c r="O11">
-        <v>119.9840623385105</v>
+        <v>119.2239211168635</v>
       </c>
       <c r="P11">
-        <v>701.8245838156711</v>
+        <v>697.3782783137086</v>
       </c>
       <c r="Q11">
-        <v>1444.824583815671</v>
+        <v>1440.378278313709</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09096429391919783</v>
+        <v>0.09139855913082298</v>
       </c>
       <c r="T11">
-        <v>1.043055286817502</v>
+        <v>1.053084506485519</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.53827065603879</v>
+        <v>16.68444359043491</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08655432321774069</v>
+        <v>0.08646508096901133</v>
       </c>
       <c r="C12">
-        <v>15696.41201152013</v>
+        <v>15628.66786707445</v>
       </c>
       <c r="D12">
-        <v>16296.49088301306</v>
+        <v>16332.25462571668</v>
       </c>
       <c r="E12">
-        <v>-6031.409843436408</v>
+        <v>-5927.901956287114</v>
       </c>
       <c r="F12">
-        <v>1035.078871492934</v>
+        <v>1138.586758642228</v>
       </c>
       <c r="G12">
         <v>435</v>
@@ -2259,28 +2259,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M12">
-        <v>52.06446723609459</v>
+        <v>57.27091395970405</v>
       </c>
       <c r="N12">
-        <v>816.6021994305721</v>
+        <v>811.3957527069626</v>
       </c>
       <c r="O12">
-        <v>119.2239211168635</v>
+        <v>118.4637798952165</v>
       </c>
       <c r="P12">
-        <v>697.3782783137086</v>
+        <v>692.9319728117462</v>
       </c>
       <c r="Q12">
-        <v>1440.378278313709</v>
+        <v>1435.931972811746</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09139855913082298</v>
+        <v>0.09184258311124868</v>
       </c>
       <c r="T12">
-        <v>1.053084506485519</v>
+        <v>1.063339101876413</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.68444359043491</v>
+        <v>15.16767599130446</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08646508096901133</v>
+        <v>0.08637583872028197</v>
       </c>
       <c r="C13">
-        <v>15628.66786707445</v>
+        <v>15561.08103973781</v>
       </c>
       <c r="D13">
-        <v>16332.25462571668</v>
+        <v>16368.17568552933</v>
       </c>
       <c r="E13">
-        <v>-5927.901956287114</v>
+        <v>-5824.394069137821</v>
       </c>
       <c r="F13">
-        <v>1138.586758642228</v>
+        <v>1242.094645791521</v>
       </c>
       <c r="G13">
         <v>435</v>
@@ -2341,28 +2341,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M13">
-        <v>57.27091395970405</v>
+        <v>62.47736068331351</v>
       </c>
       <c r="N13">
-        <v>811.3957527069626</v>
+        <v>806.1893059833533</v>
       </c>
       <c r="O13">
-        <v>118.4637798952165</v>
+        <v>117.7036386735696</v>
       </c>
       <c r="P13">
-        <v>692.9319728117462</v>
+        <v>688.4856673097837</v>
       </c>
       <c r="Q13">
-        <v>1435.931972811746</v>
+        <v>1431.485667309784</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09184258311124868</v>
+        <v>0.09229669854577496</v>
       </c>
       <c r="T13">
-        <v>1.063339101876413</v>
+        <v>1.073826756253464</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.16767599130446</v>
+        <v>13.90370299202909</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08637583872028197</v>
+        <v>0.08645312647155264</v>
       </c>
       <c r="C14">
-        <v>15561.08103973781</v>
+        <v>15426.45477127477</v>
       </c>
       <c r="D14">
-        <v>16368.17568552933</v>
+        <v>16337.05730421558</v>
       </c>
       <c r="E14">
-        <v>-5824.394069137821</v>
+        <v>-5720.886181988528</v>
       </c>
       <c r="F14">
-        <v>1242.094645791521</v>
+        <v>1345.602532940814</v>
       </c>
       <c r="G14">
         <v>435</v>
@@ -2423,45 +2423,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M14">
-        <v>62.47736068331351</v>
+        <v>69.70221120633418</v>
       </c>
       <c r="N14">
-        <v>806.1893059833533</v>
+        <v>798.9644554603326</v>
       </c>
       <c r="O14">
-        <v>117.7036386735696</v>
+        <v>116.6488104972086</v>
       </c>
       <c r="P14">
-        <v>688.4856673097837</v>
+        <v>682.315644963124</v>
       </c>
       <c r="Q14">
-        <v>1431.485667309784</v>
+        <v>1425.315644963124</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09229669854577496</v>
+        <v>0.09276125341557774</v>
       </c>
       <c r="T14">
-        <v>1.073826756253464</v>
+        <v>1.084555506133435</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.146</v>
       </c>
       <c r="W14">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.90370299202909</v>
+        <v>12.46254102463433</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08645312647155264</v>
+        <v>0.08637669422282329</v>
       </c>
       <c r="C15">
-        <v>15426.45477127477</v>
+        <v>15353.72016547078</v>
       </c>
       <c r="D15">
-        <v>16337.05730421558</v>
+        <v>16367.83058556089</v>
       </c>
       <c r="E15">
-        <v>-5720.886181988528</v>
+        <v>-5617.378294839234</v>
       </c>
       <c r="F15">
-        <v>1345.602532940814</v>
+        <v>1449.110420090108</v>
       </c>
       <c r="G15">
         <v>435</v>
@@ -2505,28 +2505,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M15">
-        <v>69.70221120633418</v>
+        <v>75.06391976066759</v>
       </c>
       <c r="N15">
-        <v>798.9644554603326</v>
+        <v>793.6027469059992</v>
       </c>
       <c r="O15">
-        <v>116.6488104972086</v>
+        <v>115.8660010482759</v>
       </c>
       <c r="P15">
-        <v>682.315644963124</v>
+        <v>677.7367458577233</v>
       </c>
       <c r="Q15">
-        <v>1425.315644963124</v>
+        <v>1420.736745857723</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09276125341557774</v>
+        <v>0.09323661188700381</v>
       </c>
       <c r="T15">
-        <v>1.084555506133435</v>
+        <v>1.095533761824569</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.46254102463433</v>
+        <v>11.57235952287474</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08637669422282329</v>
+        <v>0.08630026197409393</v>
       </c>
       <c r="C16">
-        <v>15353.72016547078</v>
+        <v>15281.10171057443</v>
       </c>
       <c r="D16">
-        <v>16367.83058556089</v>
+        <v>16398.72001781383</v>
       </c>
       <c r="E16">
-        <v>-5617.378294839234</v>
+        <v>-5513.87040768994</v>
       </c>
       <c r="F16">
-        <v>1449.110420090108</v>
+        <v>1552.618307239401</v>
       </c>
       <c r="G16">
         <v>435</v>
@@ -2587,28 +2587,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M16">
-        <v>75.06391976066759</v>
+        <v>80.42562831500099</v>
       </c>
       <c r="N16">
-        <v>793.6027469059992</v>
+        <v>788.2410383516658</v>
       </c>
       <c r="O16">
-        <v>115.8660010482759</v>
+        <v>115.0831915993432</v>
       </c>
       <c r="P16">
-        <v>677.7367458577233</v>
+        <v>673.1578467523226</v>
       </c>
       <c r="Q16">
-        <v>1420.736745857723</v>
+        <v>1416.157846752323</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09323661188700381</v>
+        <v>0.09372315526363992</v>
       </c>
       <c r="T16">
-        <v>1.095533761824569</v>
+        <v>1.106770329414317</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.57235952287474</v>
+        <v>10.80086888801642</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08630026197409393</v>
+        <v>0.08622382972536458</v>
       </c>
       <c r="C17">
-        <v>15281.10171057443</v>
+        <v>15208.60006543042</v>
       </c>
       <c r="D17">
-        <v>16398.72001781383</v>
+        <v>16429.72625981911</v>
       </c>
       <c r="E17">
-        <v>-5513.87040768994</v>
+        <v>-5410.362520540647</v>
       </c>
       <c r="F17">
-        <v>1552.618307239401</v>
+        <v>1656.126194388695</v>
       </c>
       <c r="G17">
         <v>435</v>
@@ -2669,28 +2669,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M17">
-        <v>80.42562831500098</v>
+        <v>85.78733686933438</v>
       </c>
       <c r="N17">
-        <v>788.2410383516658</v>
+        <v>782.8793297973324</v>
       </c>
       <c r="O17">
-        <v>115.0831915993432</v>
+        <v>114.3003821504105</v>
       </c>
       <c r="P17">
-        <v>673.1578467523226</v>
+        <v>668.5789476469218</v>
       </c>
       <c r="Q17">
-        <v>1416.157846752323</v>
+        <v>1411.578947646922</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09372315526363992</v>
+        <v>0.09422128300638641</v>
       </c>
       <c r="T17">
-        <v>1.106770329414317</v>
+        <v>1.118274434327631</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.80086888801642</v>
+        <v>10.1258145825154</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08622382972536458</v>
+        <v>0.08639420347663521</v>
       </c>
       <c r="C18">
-        <v>15208.60006543042</v>
+        <v>15036.1366660281</v>
       </c>
       <c r="D18">
-        <v>16429.72625981911</v>
+        <v>16360.77074756608</v>
       </c>
       <c r="E18">
-        <v>-5410.362520540647</v>
+        <v>-5306.854633391354</v>
       </c>
       <c r="F18">
-        <v>1656.126194388695</v>
+        <v>1759.634081537988</v>
       </c>
       <c r="G18">
         <v>435</v>
@@ -2751,45 +2751,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M18">
-        <v>85.78733686933438</v>
+        <v>94.14042336228238</v>
       </c>
       <c r="N18">
-        <v>782.8793297973324</v>
+        <v>774.5262433043844</v>
       </c>
       <c r="O18">
-        <v>114.3003821504105</v>
+        <v>113.0808315224401</v>
       </c>
       <c r="P18">
-        <v>668.5789476469218</v>
+        <v>661.4454117819442</v>
       </c>
       <c r="Q18">
-        <v>1411.578947646922</v>
+        <v>1404.445411781944</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09422128300638641</v>
+        <v>0.09473141382727135</v>
       </c>
       <c r="T18">
-        <v>1.118274434327631</v>
+        <v>1.130055746588253</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.146</v>
       </c>
       <c r="W18">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.1258145825154</v>
+        <v>9.227350330938712</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08639420347663521</v>
+        <v>0.08633228922790587</v>
       </c>
       <c r="C19">
-        <v>15036.1366660281</v>
+        <v>14957.62033126245</v>
       </c>
       <c r="D19">
-        <v>16360.77074756608</v>
+        <v>16385.76229994974</v>
       </c>
       <c r="E19">
-        <v>-5306.854633391354</v>
+        <v>-5203.346746242059</v>
       </c>
       <c r="F19">
-        <v>1759.634081537988</v>
+        <v>1863.141968687282</v>
       </c>
       <c r="G19">
         <v>435</v>
@@ -2833,28 +2833,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M19">
-        <v>94.14042336228238</v>
+        <v>99.67809532476957</v>
       </c>
       <c r="N19">
-        <v>774.5262433043844</v>
+        <v>768.9885713418971</v>
       </c>
       <c r="O19">
-        <v>113.0808315224401</v>
+        <v>112.272331415917</v>
       </c>
       <c r="P19">
-        <v>661.4454117819442</v>
+        <v>656.7162399259802</v>
       </c>
       <c r="Q19">
-        <v>1404.445411781944</v>
+        <v>1399.71623992598</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09473141382727135</v>
+        <v>0.09525398686329985</v>
       </c>
       <c r="T19">
-        <v>1.130055746588253</v>
+        <v>1.142124407928403</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.227350330938712</v>
+        <v>8.714719756997672</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08633228922790588</v>
+        <v>0.08627037497917654</v>
       </c>
       <c r="C20">
-        <v>14957.62033126245</v>
+        <v>14879.18046394694</v>
       </c>
       <c r="D20">
-        <v>16385.76229994973</v>
+        <v>16410.83031978352</v>
       </c>
       <c r="E20">
-        <v>-5203.34674624206</v>
+        <v>-5099.838859092767</v>
       </c>
       <c r="F20">
-        <v>1863.141968687281</v>
+        <v>1966.649855836575</v>
       </c>
       <c r="G20">
         <v>435</v>
@@ -2915,28 +2915,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M20">
-        <v>99.67809532476956</v>
+        <v>105.2157672872568</v>
       </c>
       <c r="N20">
-        <v>768.9885713418972</v>
+        <v>763.45089937941</v>
       </c>
       <c r="O20">
-        <v>112.272331415917</v>
+        <v>111.4638313093939</v>
       </c>
       <c r="P20">
-        <v>656.7162399259803</v>
+        <v>651.9870680700161</v>
       </c>
       <c r="Q20">
-        <v>1399.71623992598</v>
+        <v>1394.987068070016</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09525398686329985</v>
+        <v>0.09578946293725499</v>
       </c>
       <c r="T20">
-        <v>1.142124407928403</v>
+        <v>1.154491060906582</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.714719756997674</v>
+        <v>8.256050296103059</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08627037497917654</v>
+        <v>0.08620846073044719</v>
       </c>
       <c r="C21">
-        <v>14879.18046394694</v>
+        <v>14800.81741557417</v>
       </c>
       <c r="D21">
-        <v>16410.83031978352</v>
+        <v>16435.97515856004</v>
       </c>
       <c r="E21">
-        <v>-5099.838859092767</v>
+        <v>-4996.330971943473</v>
       </c>
       <c r="F21">
-        <v>1966.649855836575</v>
+        <v>2070.157742985868</v>
       </c>
       <c r="G21">
         <v>435</v>
@@ -2997,28 +2997,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M21">
-        <v>105.2157672872568</v>
+        <v>110.753439249744</v>
       </c>
       <c r="N21">
-        <v>763.45089937941</v>
+        <v>757.9132274169228</v>
       </c>
       <c r="O21">
-        <v>111.4638313093939</v>
+        <v>110.6553312028707</v>
       </c>
       <c r="P21">
-        <v>651.9870680700161</v>
+        <v>647.2578962140522</v>
       </c>
       <c r="Q21">
-        <v>1394.987068070016</v>
+        <v>1390.257896214052</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09578946293725499</v>
+        <v>0.09633832591305898</v>
       </c>
       <c r="T21">
-        <v>1.154491060906582</v>
+        <v>1.167166880209215</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.256050296103059</v>
+        <v>7.843247781297906</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08620846073044719</v>
+        <v>0.08629001848171783</v>
       </c>
       <c r="C22">
-        <v>14800.81741557417</v>
+        <v>14664.20306850865</v>
       </c>
       <c r="D22">
-        <v>16435.97515856004</v>
+        <v>16402.86869864381</v>
       </c>
       <c r="E22">
-        <v>-4996.330971943473</v>
+        <v>-4892.82308479418</v>
       </c>
       <c r="F22">
-        <v>2070.157742985868</v>
+        <v>2173.665630135162</v>
       </c>
       <c r="G22">
         <v>435</v>
@@ -3079,45 +3079,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M22">
-        <v>110.753439249744</v>
+        <v>118.0300437163393</v>
       </c>
       <c r="N22">
-        <v>757.9132274169228</v>
+        <v>750.6366229503275</v>
       </c>
       <c r="O22">
-        <v>110.6553312028707</v>
+        <v>109.5929469507478</v>
       </c>
       <c r="P22">
-        <v>647.2578962140522</v>
+        <v>641.0436759995797</v>
       </c>
       <c r="Q22">
-        <v>1390.257896214052</v>
+        <v>1384.04367599958</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09633832591305898</v>
+        <v>0.0969010841540732</v>
       </c>
       <c r="T22">
-        <v>1.167166880209215</v>
+        <v>1.180163606329635</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.146</v>
       </c>
       <c r="W22">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.843247781297906</v>
+        <v>7.359708082073805</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08629001848171783</v>
+        <v>0.08623493623298847</v>
       </c>
       <c r="C23">
-        <v>14664.20306850865</v>
+        <v>14583.03989060602</v>
       </c>
       <c r="D23">
-        <v>16402.86869864381</v>
+        <v>16425.21340789048</v>
       </c>
       <c r="E23">
-        <v>-4892.82308479418</v>
+        <v>-4789.315197644886</v>
       </c>
       <c r="F23">
-        <v>2173.665630135162</v>
+        <v>2277.173517284455</v>
       </c>
       <c r="G23">
         <v>435</v>
@@ -3161,28 +3161,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M23">
-        <v>118.0300437163393</v>
+        <v>123.6505219885459</v>
       </c>
       <c r="N23">
-        <v>750.6366229503275</v>
+        <v>745.0161446781208</v>
       </c>
       <c r="O23">
-        <v>109.5929469507478</v>
+        <v>108.7723571230056</v>
       </c>
       <c r="P23">
-        <v>641.0436759995797</v>
+        <v>636.2437875551152</v>
       </c>
       <c r="Q23">
-        <v>1384.04367599958</v>
+        <v>1379.243787555115</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0969010841540732</v>
+        <v>0.09747827209357497</v>
       </c>
       <c r="T23">
-        <v>1.180163606329635</v>
+        <v>1.193493581837759</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.359708082073805</v>
+        <v>7.025175896524996</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08623493623298847</v>
+        <v>0.08617985398425912</v>
       </c>
       <c r="C24">
-        <v>14583.03989060602</v>
+        <v>14501.93767363867</v>
       </c>
       <c r="D24">
-        <v>16425.21340789048</v>
+        <v>16447.61907807241</v>
       </c>
       <c r="E24">
-        <v>-4789.315197644886</v>
+        <v>-4685.807310495593</v>
       </c>
       <c r="F24">
-        <v>2277.173517284455</v>
+        <v>2380.681404433749</v>
       </c>
       <c r="G24">
         <v>435</v>
@@ -3243,28 +3243,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M24">
-        <v>123.6505219885459</v>
+        <v>129.2710002607526</v>
       </c>
       <c r="N24">
-        <v>745.0161446781208</v>
+        <v>739.3956664059142</v>
       </c>
       <c r="O24">
-        <v>108.7723571230056</v>
+        <v>107.9517672952635</v>
       </c>
       <c r="P24">
-        <v>636.2437875551152</v>
+        <v>631.4438991106507</v>
       </c>
       <c r="Q24">
-        <v>1379.243787555115</v>
+        <v>1374.443899110651</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09747827209357497</v>
+        <v>0.09807045192760926</v>
       </c>
       <c r="T24">
-        <v>1.193493581837759</v>
+        <v>1.207169790475965</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.025175896524996</v>
+        <v>6.7197334662413</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08617985398425912</v>
+        <v>0.08612477173552979</v>
       </c>
       <c r="C25">
-        <v>14501.93767363867</v>
+        <v>14420.89666741818</v>
       </c>
       <c r="D25">
-        <v>16447.61907807241</v>
+        <v>16470.08595900123</v>
       </c>
       <c r="E25">
-        <v>-4685.807310495593</v>
+        <v>-4582.2994233463</v>
       </c>
       <c r="F25">
-        <v>2380.681404433749</v>
+        <v>2484.189291583042</v>
       </c>
       <c r="G25">
         <v>435</v>
@@ -3325,28 +3325,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M25">
-        <v>129.2710002607526</v>
+        <v>134.8914785329592</v>
       </c>
       <c r="N25">
-        <v>739.3956664059142</v>
+        <v>733.7751881337076</v>
       </c>
       <c r="O25">
-        <v>107.9517672952635</v>
+        <v>107.1311774675213</v>
       </c>
       <c r="P25">
-        <v>631.4438991106507</v>
+        <v>626.6440106661863</v>
       </c>
       <c r="Q25">
-        <v>1374.443899110651</v>
+        <v>1369.644010666186</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09807045192760926</v>
+        <v>0.09867821544148656</v>
       </c>
       <c r="T25">
-        <v>1.207169790475965</v>
+        <v>1.221205899341491</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.7197334662413</v>
+        <v>6.43974457181458</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08612477173552979</v>
+        <v>0.08606968948680044</v>
       </c>
       <c r="C26">
-        <v>14420.89666741818</v>
+        <v>14339.91712312301</v>
       </c>
       <c r="D26">
-        <v>16470.08595900123</v>
+        <v>16492.61430185534</v>
       </c>
       <c r="E26">
-        <v>-4582.2994233463</v>
+        <v>-4478.791536197006</v>
       </c>
       <c r="F26">
-        <v>2484.189291583042</v>
+        <v>2587.697178732335</v>
       </c>
       <c r="G26">
         <v>435</v>
@@ -3407,28 +3407,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M26">
-        <v>134.8914785329592</v>
+        <v>140.5119568051658</v>
       </c>
       <c r="N26">
-        <v>733.7751881337076</v>
+        <v>728.1547098615009</v>
       </c>
       <c r="O26">
-        <v>107.1311774675213</v>
+        <v>106.3105876397791</v>
       </c>
       <c r="P26">
-        <v>626.6440106661863</v>
+        <v>621.8441222217218</v>
       </c>
       <c r="Q26">
-        <v>1369.644010666186</v>
+        <v>1364.844122221722</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09867821544148656</v>
+        <v>0.09930218598240058</v>
       </c>
       <c r="T26">
-        <v>1.221205899341491</v>
+        <v>1.235616304443432</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.43974457181458</v>
+        <v>6.182154788941996</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08606968948680044</v>
+        <v>0.08623664723807109</v>
       </c>
       <c r="C27">
-        <v>14339.91712312301</v>
+        <v>14168.31333820553</v>
       </c>
       <c r="D27">
-        <v>16492.61430185534</v>
+        <v>16424.51840408716</v>
       </c>
       <c r="E27">
-        <v>-4478.791536197006</v>
+        <v>-4375.283649047713</v>
       </c>
       <c r="F27">
-        <v>2587.697178732335</v>
+        <v>2691.205065881629</v>
       </c>
       <c r="G27">
         <v>435</v>
@@ -3489,45 +3489,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M27">
-        <v>140.5119568051658</v>
+        <v>148.8236401432541</v>
       </c>
       <c r="N27">
-        <v>728.1547098615009</v>
+        <v>719.8430265234126</v>
       </c>
       <c r="O27">
-        <v>106.3105876397791</v>
+        <v>105.0970818724182</v>
       </c>
       <c r="P27">
-        <v>621.8441222217218</v>
+        <v>614.7459446509944</v>
       </c>
       <c r="Q27">
-        <v>1364.844122221722</v>
+        <v>1357.745944650994</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09930218598240058</v>
+        <v>0.09994302059198795</v>
       </c>
       <c r="T27">
-        <v>1.235616304443432</v>
+        <v>1.250416179953532</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.146</v>
       </c>
       <c r="W27">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.182154788941996</v>
+        <v>5.83688630267684</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08623664723807109</v>
+        <v>0.08619010498934174</v>
       </c>
       <c r="C28">
-        <v>14168.31333820553</v>
+        <v>14083.73172077067</v>
       </c>
       <c r="D28">
-        <v>16424.51840408716</v>
+        <v>16443.4446738016</v>
       </c>
       <c r="E28">
-        <v>-4375.283649047713</v>
+        <v>-4271.77576189842</v>
       </c>
       <c r="F28">
-        <v>2691.205065881629</v>
+        <v>2794.712953030923</v>
       </c>
       <c r="G28">
         <v>435</v>
@@ -3571,28 +3571,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M28">
-        <v>148.8236401432541</v>
+        <v>154.54762630261</v>
       </c>
       <c r="N28">
-        <v>719.8430265234126</v>
+        <v>714.1190403640567</v>
       </c>
       <c r="O28">
-        <v>105.0970818724182</v>
+        <v>104.2613798931523</v>
       </c>
       <c r="P28">
-        <v>614.7459446509944</v>
+        <v>609.8576604709044</v>
       </c>
       <c r="Q28">
-        <v>1357.745944650994</v>
+        <v>1352.857660470904</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09994302059198795</v>
+        <v>0.1006014123141668</v>
       </c>
       <c r="T28">
-        <v>1.250416179953532</v>
+        <v>1.265621531505006</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.83688630267684</v>
+        <v>5.620705328503623</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08619010498934174</v>
+        <v>0.08614356274061238</v>
       </c>
       <c r="C29">
-        <v>14083.73172077067</v>
+        <v>13999.19377182183</v>
       </c>
       <c r="D29">
-        <v>16443.4446738016</v>
+        <v>16462.41461200205</v>
       </c>
       <c r="E29">
-        <v>-4271.77576189842</v>
+        <v>-4168.267874749126</v>
       </c>
       <c r="F29">
-        <v>2794.712953030923</v>
+        <v>2898.220840180216</v>
       </c>
       <c r="G29">
         <v>435</v>
@@ -3653,28 +3653,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M29">
-        <v>154.54762630261</v>
+        <v>160.2716124619659</v>
       </c>
       <c r="N29">
-        <v>714.1190403640567</v>
+        <v>708.3950542047008</v>
       </c>
       <c r="O29">
-        <v>104.2613798931523</v>
+        <v>103.4256779138863</v>
       </c>
       <c r="P29">
-        <v>609.8576604709044</v>
+        <v>604.9693762908146</v>
       </c>
       <c r="Q29">
-        <v>1352.857660470904</v>
+        <v>1347.969376290815</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1006014123141668</v>
+        <v>0.101278092695295</v>
       </c>
       <c r="T29">
-        <v>1.265621531505006</v>
+        <v>1.28124925393291</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.620705328503623</v>
+        <v>5.419965852485637</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08614356274061238</v>
+        <v>0.08609702049188304</v>
       </c>
       <c r="C30">
-        <v>13999.19377182183</v>
+        <v>13914.69964266767</v>
       </c>
       <c r="D30">
-        <v>16462.41461200205</v>
+        <v>16481.42836999717</v>
       </c>
       <c r="E30">
-        <v>-4168.267874749126</v>
+        <v>-4064.759987599832</v>
       </c>
       <c r="F30">
-        <v>2898.220840180216</v>
+        <v>3001.72872732951</v>
       </c>
       <c r="G30">
         <v>435</v>
@@ -3735,28 +3735,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M30">
-        <v>160.2716124619659</v>
+        <v>165.9955986213219</v>
       </c>
       <c r="N30">
-        <v>708.3950542047008</v>
+        <v>702.6710680453449</v>
       </c>
       <c r="O30">
-        <v>103.4256779138863</v>
+        <v>102.5899759346204</v>
       </c>
       <c r="P30">
-        <v>604.9693762908146</v>
+        <v>600.0810921107245</v>
       </c>
       <c r="Q30">
-        <v>1347.969376290815</v>
+        <v>1343.081092110725</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.101278092695295</v>
+        <v>0.1019738344956099</v>
       </c>
       <c r="T30">
-        <v>1.28124925393291</v>
+        <v>1.297317193893994</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.419965852485637</v>
+        <v>5.233070478261993</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08609702049188304</v>
+        <v>0.08605047824315368</v>
       </c>
       <c r="C31">
-        <v>13914.69964266767</v>
+        <v>13830.2494853167</v>
       </c>
       <c r="D31">
-        <v>16481.42836999717</v>
+        <v>16500.48609979551</v>
       </c>
       <c r="E31">
-        <v>-4064.759987599833</v>
+        <v>-3961.252100450539</v>
       </c>
       <c r="F31">
-        <v>3001.728727329509</v>
+        <v>3105.236614478802</v>
       </c>
       <c r="G31">
         <v>435</v>
@@ -3817,28 +3817,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M31">
-        <v>165.9955986213219</v>
+        <v>171.7195847806778</v>
       </c>
       <c r="N31">
-        <v>702.6710680453449</v>
+        <v>696.947081885989</v>
       </c>
       <c r="O31">
-        <v>102.5899759346204</v>
+        <v>101.7542739553544</v>
       </c>
       <c r="P31">
-        <v>600.0810921107245</v>
+        <v>595.1928079306346</v>
       </c>
       <c r="Q31">
-        <v>1343.081092110725</v>
+        <v>1338.192807930634</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1019738344956099</v>
+        <v>0.1026894546330767</v>
       </c>
       <c r="T31">
-        <v>1.297317193893994</v>
+        <v>1.313844217853966</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.233070478261993</v>
+        <v>5.05863479565326</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08605047824315368</v>
+        <v>0.08600393599442434</v>
       </c>
       <c r="C32">
-        <v>13830.2494853167</v>
+        <v>13745.84345248133</v>
       </c>
       <c r="D32">
-        <v>16500.48609979551</v>
+        <v>16519.58795410943</v>
       </c>
       <c r="E32">
-        <v>-3961.252100450539</v>
+        <v>-3857.744213301246</v>
       </c>
       <c r="F32">
-        <v>3105.236614478802</v>
+        <v>3208.744501628096</v>
       </c>
       <c r="G32">
         <v>435</v>
@@ -3899,28 +3899,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M32">
-        <v>171.7195847806778</v>
+        <v>177.4435709400337</v>
       </c>
       <c r="N32">
-        <v>696.947081885989</v>
+        <v>691.223095726633</v>
       </c>
       <c r="O32">
-        <v>101.7542739553544</v>
+        <v>100.9185719760884</v>
       </c>
       <c r="P32">
-        <v>595.1928079306346</v>
+        <v>590.3045237505446</v>
       </c>
       <c r="Q32">
-        <v>1338.192807930634</v>
+        <v>1333.304523750545</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1026894546330767</v>
+        <v>0.1034258173832237</v>
       </c>
       <c r="T32">
-        <v>1.313844217853966</v>
+        <v>1.33085028598669</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.05863479565326</v>
+        <v>4.895453028051543</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08600393599442434</v>
+        <v>0.08595739374569498</v>
       </c>
       <c r="C33">
-        <v>13745.84345248133</v>
+        <v>13661.48169758194</v>
       </c>
       <c r="D33">
-        <v>16519.58795410943</v>
+        <v>16538.73408635933</v>
       </c>
       <c r="E33">
-        <v>-3857.744213301246</v>
+        <v>-3754.236326151952</v>
       </c>
       <c r="F33">
-        <v>3208.744501628096</v>
+        <v>3312.25238877739</v>
       </c>
       <c r="G33">
         <v>435</v>
@@ -3981,28 +3981,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M33">
-        <v>177.4435709400337</v>
+        <v>183.1675570993897</v>
       </c>
       <c r="N33">
-        <v>691.223095726633</v>
+        <v>685.4991095672771</v>
       </c>
       <c r="O33">
-        <v>100.9185719760884</v>
+        <v>100.0828699968224</v>
       </c>
       <c r="P33">
-        <v>590.3045237505446</v>
+        <v>585.4162395704546</v>
       </c>
       <c r="Q33">
-        <v>1333.304523750545</v>
+        <v>1328.416239570455</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1034258173832237</v>
+        <v>0.1041838378613162</v>
       </c>
       <c r="T33">
-        <v>1.33085028598669</v>
+        <v>1.348356532593907</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.895453028051543</v>
+        <v>4.742470120924931</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08595739374569498</v>
+        <v>0.08591085149696563</v>
       </c>
       <c r="C34">
-        <v>13661.48169758194</v>
+        <v>13577.16437475099</v>
       </c>
       <c r="D34">
-        <v>16538.73408635933</v>
+        <v>16557.92465067768</v>
       </c>
       <c r="E34">
-        <v>-3754.236326151952</v>
+        <v>-3650.728439002659</v>
       </c>
       <c r="F34">
-        <v>3312.25238877739</v>
+        <v>3415.760275926683</v>
       </c>
       <c r="G34">
         <v>435</v>
@@ -4063,28 +4063,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M34">
-        <v>183.1675570993897</v>
+        <v>188.8915432587456</v>
       </c>
       <c r="N34">
-        <v>685.4991095672771</v>
+        <v>679.7751234079212</v>
       </c>
       <c r="O34">
-        <v>100.0828699968224</v>
+        <v>99.24716801755649</v>
       </c>
       <c r="P34">
-        <v>585.4162395704546</v>
+        <v>580.5279553903647</v>
       </c>
       <c r="Q34">
-        <v>1328.416239570455</v>
+        <v>1323.527955390365</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1041838378613162</v>
+        <v>0.1049644858163666</v>
       </c>
       <c r="T34">
-        <v>1.348356532593907</v>
+        <v>1.366385353726712</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.742470120924931</v>
+        <v>4.598758905139328</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08591085149696563</v>
+        <v>0.08659020924823629</v>
       </c>
       <c r="C35">
-        <v>13577.16437475099</v>
+        <v>13197.88554492432</v>
       </c>
       <c r="D35">
-        <v>16557.92465067768</v>
+        <v>16282.1537080003</v>
       </c>
       <c r="E35">
-        <v>-3650.728439002659</v>
+        <v>-3547.220551853365</v>
       </c>
       <c r="F35">
-        <v>3415.760275926683</v>
+        <v>3519.268163075977</v>
       </c>
       <c r="G35">
         <v>435</v>
@@ -4145,45 +4145,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M35">
-        <v>188.8915432587456</v>
+        <v>203.4136998257915</v>
       </c>
       <c r="N35">
-        <v>679.7751234079212</v>
+        <v>665.2529668408753</v>
       </c>
       <c r="O35">
-        <v>99.24716801755649</v>
+        <v>97.12693315876778</v>
       </c>
       <c r="P35">
-        <v>580.5279553903647</v>
+        <v>568.1260336821075</v>
       </c>
       <c r="Q35">
-        <v>1323.527955390365</v>
+        <v>1311.126033682107</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1049644858163666</v>
+        <v>0.105768789770055</v>
       </c>
       <c r="T35">
-        <v>1.366385353726712</v>
+        <v>1.384960502772633</v>
       </c>
       <c r="U35">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.146</v>
       </c>
       <c r="W35">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.598758905139328</v>
+        <v>4.270443275996723</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08659020924823629</v>
+        <v>0.08656501699950692</v>
       </c>
       <c r="C36">
-        <v>13197.88554492432</v>
+        <v>13104.43981636721</v>
       </c>
       <c r="D36">
-        <v>16282.1537080003</v>
+        <v>16292.21586659248</v>
       </c>
       <c r="E36">
-        <v>-3547.220551853365</v>
+        <v>-3443.712664704072</v>
       </c>
       <c r="F36">
-        <v>3519.268163075977</v>
+        <v>3622.77605022527</v>
       </c>
       <c r="G36">
         <v>435</v>
@@ -4227,28 +4227,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M36">
-        <v>203.4136998257915</v>
+        <v>209.3964557030206</v>
       </c>
       <c r="N36">
-        <v>665.2529668408753</v>
+        <v>659.2702109636462</v>
       </c>
       <c r="O36">
-        <v>97.12693315876778</v>
+        <v>96.25345080069233</v>
       </c>
       <c r="P36">
-        <v>568.1260336821075</v>
+        <v>563.0167601629538</v>
       </c>
       <c r="Q36">
-        <v>1311.126033682107</v>
+        <v>1306.016760162954</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.105768789770055</v>
+        <v>0.106597841537703</v>
       </c>
       <c r="T36">
-        <v>1.384960502772633</v>
+        <v>1.40410719486612</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.270443275996723</v>
+        <v>4.148430610968244</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08656501699950692</v>
+        <v>0.08653982475077758</v>
       </c>
       <c r="C37">
-        <v>13104.43981636721</v>
+        <v>13011.00653206597</v>
       </c>
       <c r="D37">
-        <v>16292.21586659248</v>
+        <v>16302.29046944053</v>
       </c>
       <c r="E37">
-        <v>-3443.712664704072</v>
+        <v>-3340.204777554778</v>
       </c>
       <c r="F37">
-        <v>3622.77605022527</v>
+        <v>3726.283937374564</v>
       </c>
       <c r="G37">
         <v>435</v>
@@ -4309,28 +4309,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M37">
-        <v>209.3964557030206</v>
+        <v>215.3792115802498</v>
       </c>
       <c r="N37">
-        <v>659.2702109636462</v>
+        <v>653.2874550864169</v>
       </c>
       <c r="O37">
-        <v>96.25345080069233</v>
+        <v>95.37996844261686</v>
       </c>
       <c r="P37">
-        <v>563.0167601629538</v>
+        <v>557.9074866438001</v>
       </c>
       <c r="Q37">
-        <v>1306.016760162954</v>
+        <v>1300.9074866438</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.106597841537703</v>
+        <v>0.10745280117309</v>
       </c>
       <c r="T37">
-        <v>1.40410719486612</v>
+        <v>1.423852221087529</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.148430610968244</v>
+        <v>4.033196427330237</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08653982475077759</v>
+        <v>0.08762056250204824</v>
       </c>
       <c r="C38">
-        <v>13011.00653206596</v>
+        <v>12486.21065431059</v>
       </c>
       <c r="D38">
-        <v>16302.29046944052</v>
+        <v>15881.00247883444</v>
       </c>
       <c r="E38">
-        <v>-3340.204777554779</v>
+        <v>-3236.696890405485</v>
       </c>
       <c r="F38">
-        <v>3726.283937374563</v>
+        <v>3829.791824523857</v>
       </c>
       <c r="G38">
         <v>435</v>
@@ -4391,45 +4391,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M38">
-        <v>215.3792115802497</v>
+        <v>234.7662388433124</v>
       </c>
       <c r="N38">
-        <v>653.287455086417</v>
+        <v>633.9004278233543</v>
       </c>
       <c r="O38">
-        <v>95.37996844261689</v>
+        <v>92.54946246220973</v>
       </c>
       <c r="P38">
-        <v>557.9074866438001</v>
+        <v>541.3509653611446</v>
       </c>
       <c r="Q38">
-        <v>1300.9074866438</v>
+        <v>1284.350965361145</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.10745280117309</v>
+        <v>0.1083349023842035</v>
       </c>
       <c r="T38">
-        <v>1.423852221087529</v>
+        <v>1.444224073538188</v>
       </c>
       <c r="U38">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V38">
         <v>0.146</v>
       </c>
       <c r="W38">
-        <v>0.0493612</v>
+        <v>0.0523502</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.033196427330239</v>
+        <v>3.700134529336784</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08762056250204824</v>
+        <v>0.08762526025331888</v>
       </c>
       <c r="C39">
-        <v>12486.21065431059</v>
+        <v>12380.91903648939</v>
       </c>
       <c r="D39">
-        <v>15881.00247883444</v>
+        <v>15879.21874816254</v>
       </c>
       <c r="E39">
-        <v>-3236.696890405485</v>
+        <v>-3133.189003256192</v>
       </c>
       <c r="F39">
-        <v>3829.791824523857</v>
+        <v>3933.29971167315</v>
       </c>
       <c r="G39">
         <v>435</v>
@@ -4473,28 +4473,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M39">
-        <v>234.7662388433124</v>
+        <v>241.1112723255641</v>
       </c>
       <c r="N39">
-        <v>633.9004278233543</v>
+        <v>627.5553943411027</v>
       </c>
       <c r="O39">
-        <v>92.54946246220973</v>
+        <v>91.62308757380099</v>
       </c>
       <c r="P39">
-        <v>541.3509653611446</v>
+        <v>535.9323067673017</v>
       </c>
       <c r="Q39">
-        <v>1284.350965361145</v>
+        <v>1278.932306767302</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1083349023842035</v>
+        <v>0.109245458473095</v>
       </c>
       <c r="T39">
-        <v>1.444224073538188</v>
+        <v>1.465253082519515</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.700134529336784</v>
+        <v>3.602762568038448</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08762526025331888</v>
+        <v>0.08762995800458954</v>
       </c>
       <c r="C40">
-        <v>12380.91903648939</v>
+        <v>12275.62781931516</v>
       </c>
       <c r="D40">
-        <v>15879.21874816254</v>
+        <v>15877.43541813761</v>
       </c>
       <c r="E40">
-        <v>-3133.189003256192</v>
+        <v>-3029.681116106898</v>
       </c>
       <c r="F40">
-        <v>3933.29971167315</v>
+        <v>4036.807598822444</v>
       </c>
       <c r="G40">
         <v>435</v>
@@ -4555,28 +4555,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M40">
-        <v>241.1112723255641</v>
+        <v>247.4563058078158</v>
       </c>
       <c r="N40">
-        <v>627.5553943411027</v>
+        <v>621.2103608588509</v>
       </c>
       <c r="O40">
-        <v>91.62308757380099</v>
+        <v>90.69671268539223</v>
       </c>
       <c r="P40">
-        <v>535.9323067673017</v>
+        <v>530.5136481734587</v>
       </c>
       <c r="Q40">
-        <v>1278.932306767302</v>
+        <v>1273.513648173459</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.109245458473095</v>
+        <v>0.1101858688599829</v>
       </c>
       <c r="T40">
-        <v>1.465253082519515</v>
+        <v>1.486971567205147</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.602762568038448</v>
+        <v>3.510384040652846</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08762995800458954</v>
+        <v>0.08859113575586017</v>
       </c>
       <c r="C41">
-        <v>12275.62781931516</v>
+        <v>11815.47976822584</v>
       </c>
       <c r="D41">
-        <v>15877.43541813761</v>
+        <v>15520.79525419758</v>
       </c>
       <c r="E41">
-        <v>-3029.681116106898</v>
+        <v>-2926.173228957605</v>
       </c>
       <c r="F41">
-        <v>4036.807598822444</v>
+        <v>4140.315485971737</v>
       </c>
       <c r="G41">
         <v>435</v>
@@ -4637,45 +4637,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M41">
-        <v>247.4563058078158</v>
+        <v>265.3942226507884</v>
       </c>
       <c r="N41">
-        <v>621.2103608588509</v>
+        <v>603.2724440158784</v>
       </c>
       <c r="O41">
-        <v>90.69671268539223</v>
+        <v>88.07777682631824</v>
       </c>
       <c r="P41">
-        <v>530.5136481734587</v>
+        <v>515.1946671895602</v>
       </c>
       <c r="Q41">
-        <v>1273.513648173459</v>
+        <v>1258.19466718956</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1101858688599829</v>
+        <v>0.111157626259767</v>
       </c>
       <c r="T41">
-        <v>1.486971567205147</v>
+        <v>1.5094140013803</v>
       </c>
       <c r="U41">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0.146</v>
       </c>
       <c r="W41">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.510384040652846</v>
+        <v>3.27311822386457</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08859113575586017</v>
+        <v>0.08861974550713084</v>
       </c>
       <c r="C42">
-        <v>11815.47976822584</v>
+        <v>11701.60175658172</v>
       </c>
       <c r="D42">
-        <v>15520.79525419758</v>
+        <v>15510.42512970275</v>
       </c>
       <c r="E42">
-        <v>-2926.173228957605</v>
+        <v>-2822.665341808311</v>
       </c>
       <c r="F42">
-        <v>4140.315485971737</v>
+        <v>4243.82337312103</v>
       </c>
       <c r="G42">
         <v>435</v>
@@ -4719,28 +4719,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M42">
-        <v>265.3942226507884</v>
+        <v>272.029078217058</v>
       </c>
       <c r="N42">
-        <v>603.2724440158784</v>
+        <v>596.6375884496088</v>
       </c>
       <c r="O42">
-        <v>88.07777682631824</v>
+        <v>87.10908791364287</v>
       </c>
       <c r="P42">
-        <v>515.1946671895602</v>
+        <v>509.5285005359659</v>
       </c>
       <c r="Q42">
-        <v>1258.19466718956</v>
+        <v>1252.528500535966</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.111157626259767</v>
+        <v>0.1121623245883573</v>
       </c>
       <c r="T42">
-        <v>1.5094140013803</v>
+        <v>1.532617196035967</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.27311822386457</v>
+        <v>3.193286072062996</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08861974550713084</v>
+        <v>0.08864835525840149</v>
       </c>
       <c r="C43">
-        <v>11701.60175658172</v>
+        <v>11587.73759315562</v>
       </c>
       <c r="D43">
-        <v>15510.42512970275</v>
+        <v>15500.06885342594</v>
       </c>
       <c r="E43">
-        <v>-2822.665341808311</v>
+        <v>-2719.157454659018</v>
       </c>
       <c r="F43">
-        <v>4243.82337312103</v>
+        <v>4347.331260270324</v>
       </c>
       <c r="G43">
         <v>435</v>
@@ -4801,28 +4801,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M43">
-        <v>272.029078217058</v>
+        <v>278.6639337833278</v>
       </c>
       <c r="N43">
-        <v>596.6375884496088</v>
+        <v>590.0027328833389</v>
       </c>
       <c r="O43">
-        <v>87.10908791364287</v>
+        <v>86.14039900096748</v>
       </c>
       <c r="P43">
-        <v>509.5285005359659</v>
+        <v>503.8623338823714</v>
       </c>
       <c r="Q43">
-        <v>1252.528500535966</v>
+        <v>1246.862333882371</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1121623245883573</v>
+        <v>0.1132016676868991</v>
       </c>
       <c r="T43">
-        <v>1.532617196035967</v>
+        <v>1.556620500852174</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.193286072062996</v>
+        <v>3.117255451299591</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08864835525840149</v>
+        <v>0.08867696500967213</v>
       </c>
       <c r="C44">
-        <v>11587.73759315562</v>
+        <v>11473.88725022677</v>
       </c>
       <c r="D44">
-        <v>15500.06885342594</v>
+        <v>15489.72639764638</v>
       </c>
       <c r="E44">
-        <v>-2719.157454659018</v>
+        <v>-2615.649567509725</v>
       </c>
       <c r="F44">
-        <v>4347.331260270324</v>
+        <v>4450.839147419617</v>
       </c>
       <c r="G44">
         <v>435</v>
@@ -4883,28 +4883,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M44">
-        <v>278.6639337833278</v>
+        <v>285.2987893495975</v>
       </c>
       <c r="N44">
-        <v>590.0027328833389</v>
+        <v>583.3678773170693</v>
       </c>
       <c r="O44">
-        <v>86.14039900096748</v>
+        <v>85.17171008829212</v>
       </c>
       <c r="P44">
-        <v>503.8623338823714</v>
+        <v>498.1961672287772</v>
       </c>
       <c r="Q44">
-        <v>1246.862333882371</v>
+        <v>1241.196167228777</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1132016676868991</v>
+        <v>0.1142774789643371</v>
       </c>
       <c r="T44">
-        <v>1.556620500852174</v>
+        <v>1.581466026890002</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.117255451299591</v>
+        <v>3.044761138478671</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08867696500967213</v>
+        <v>0.09163650276094279</v>
       </c>
       <c r="C45">
-        <v>11473.88725022677</v>
+        <v>10370.25004977065</v>
       </c>
       <c r="D45">
-        <v>15489.72639764638</v>
+        <v>14489.59708433956</v>
       </c>
       <c r="E45">
-        <v>-2615.649567509725</v>
+        <v>-2512.141680360432</v>
       </c>
       <c r="F45">
-        <v>4450.839147419617</v>
+        <v>4554.34703456891</v>
       </c>
       <c r="G45">
         <v>435</v>
@@ -4965,45 +4965,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M45">
-        <v>285.2987893495975</v>
+        <v>327.4575517855047</v>
       </c>
       <c r="N45">
-        <v>583.3678773170693</v>
+        <v>541.2091148811621</v>
       </c>
       <c r="O45">
-        <v>85.17171008829212</v>
+        <v>79.01653077264966</v>
       </c>
       <c r="P45">
-        <v>498.1961672287772</v>
+        <v>462.1925841085124</v>
       </c>
       <c r="Q45">
-        <v>1241.196167228777</v>
+        <v>1205.192584108512</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1142774789643371</v>
+        <v>0.1153917120731121</v>
       </c>
       <c r="T45">
-        <v>1.581466026890002</v>
+        <v>1.607198893143467</v>
       </c>
       <c r="U45">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V45">
         <v>0.146</v>
       </c>
       <c r="W45">
-        <v>0.0547414</v>
+        <v>0.0614026</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.044761138478671</v>
+        <v>2.652761134779605</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09163650276094279</v>
+        <v>0.09173172451221344</v>
       </c>
       <c r="C46">
-        <v>10370.25004977065</v>
+        <v>10236.70356023424</v>
       </c>
       <c r="D46">
-        <v>14489.59708433956</v>
+        <v>14459.55848195244</v>
       </c>
       <c r="E46">
-        <v>-2512.141680360432</v>
+        <v>-2408.633793211137</v>
       </c>
       <c r="F46">
-        <v>4554.34703456891</v>
+        <v>4657.854921718204</v>
       </c>
       <c r="G46">
         <v>435</v>
@@ -5047,28 +5047,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M46">
-        <v>327.4575517855047</v>
+        <v>334.8997688715389</v>
       </c>
       <c r="N46">
-        <v>541.2091148811621</v>
+        <v>533.7668977951278</v>
       </c>
       <c r="O46">
-        <v>79.01653077264966</v>
+        <v>77.92996707808865</v>
       </c>
       <c r="P46">
-        <v>462.1925841085124</v>
+        <v>455.8369307170391</v>
       </c>
       <c r="Q46">
-        <v>1205.192584108512</v>
+        <v>1198.836930717039</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1153917120731121</v>
+        <v>0.116546462749479</v>
       </c>
       <c r="T46">
-        <v>1.607198893143467</v>
+        <v>1.633867499987967</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.652761134779605</v>
+        <v>2.593810887340058</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09173172451221344</v>
+        <v>0.09182694626348409</v>
       </c>
       <c r="C47">
-        <v>10236.70356023424</v>
+        <v>10103.2813599917</v>
       </c>
       <c r="D47">
-        <v>14459.55848195244</v>
+        <v>14429.6441688592</v>
       </c>
       <c r="E47">
-        <v>-2408.633793211137</v>
+        <v>-2305.125906061844</v>
       </c>
       <c r="F47">
-        <v>4657.854921718204</v>
+        <v>4761.362808867498</v>
       </c>
       <c r="G47">
         <v>435</v>
@@ -5129,28 +5129,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M47">
-        <v>334.8997688715389</v>
+        <v>342.3419859575731</v>
       </c>
       <c r="N47">
-        <v>533.7668977951278</v>
+        <v>526.3246807090936</v>
       </c>
       <c r="O47">
-        <v>77.92996707808865</v>
+        <v>76.84340338352766</v>
       </c>
       <c r="P47">
-        <v>455.8369307170391</v>
+        <v>449.481277325566</v>
       </c>
       <c r="Q47">
-        <v>1198.836930717039</v>
+        <v>1192.481277325566</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.116546462749479</v>
+        <v>0.117743981969415</v>
       </c>
       <c r="T47">
-        <v>1.633867499987967</v>
+        <v>1.661523833011893</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.593810887340058</v>
+        <v>2.537423694137013</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09182694626348409</v>
+        <v>0.09348755001475476</v>
       </c>
       <c r="C48">
-        <v>10103.2813599917</v>
+        <v>9497.29596605301</v>
       </c>
       <c r="D48">
-        <v>14429.6441688592</v>
+        <v>13927.1666620698</v>
       </c>
       <c r="E48">
-        <v>-2305.125906061844</v>
+        <v>-2201.618018912551</v>
       </c>
       <c r="F48">
-        <v>4761.362808867498</v>
+        <v>4864.870696016791</v>
       </c>
       <c r="G48">
         <v>435</v>
@@ -5211,45 +5211,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M48">
-        <v>342.3419859575731</v>
+        <v>368.7571987580728</v>
       </c>
       <c r="N48">
-        <v>526.3246807090936</v>
+        <v>499.909467908594</v>
       </c>
       <c r="O48">
-        <v>76.84340338352766</v>
+        <v>72.98678231465472</v>
       </c>
       <c r="P48">
-        <v>449.481277325566</v>
+        <v>426.9226855939393</v>
       </c>
       <c r="Q48">
-        <v>1192.481277325566</v>
+        <v>1169.922685593939</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.117743981969415</v>
+        <v>0.1189866905938769</v>
       </c>
       <c r="T48">
-        <v>1.661523833011893</v>
+        <v>1.69022380124427</v>
       </c>
       <c r="U48">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V48">
         <v>0.146</v>
       </c>
       <c r="W48">
-        <v>0.0614026</v>
+        <v>0.0647332</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.537423694137013</v>
+        <v>2.355660227358884</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09348755001475476</v>
+        <v>0.0936160777660254</v>
       </c>
       <c r="C49">
-        <v>9497.29596605301</v>
+        <v>9356.352398348607</v>
       </c>
       <c r="D49">
-        <v>13927.1666620698</v>
+        <v>13889.73098151469</v>
       </c>
       <c r="E49">
-        <v>-2201.618018912551</v>
+        <v>-2098.110131763257</v>
       </c>
       <c r="F49">
-        <v>4864.870696016791</v>
+        <v>4968.378583166084</v>
       </c>
       <c r="G49">
         <v>435</v>
@@ -5293,28 +5293,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M49">
-        <v>368.7571987580728</v>
+        <v>376.6030966039892</v>
       </c>
       <c r="N49">
-        <v>499.909467908594</v>
+        <v>492.0635700626775</v>
       </c>
       <c r="O49">
-        <v>72.98678231465472</v>
+        <v>71.84128122915091</v>
       </c>
       <c r="P49">
-        <v>426.9226855939393</v>
+        <v>420.2222888335266</v>
       </c>
       <c r="Q49">
-        <v>1169.922685593939</v>
+        <v>1163.222288833527</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1189866905938769</v>
+        <v>0.120277195703895</v>
       </c>
       <c r="T49">
-        <v>1.69022380124427</v>
+        <v>1.72002761440866</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.355660227358884</v>
+        <v>2.30658397262224</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0936160777660254</v>
+        <v>0.09374460551729605</v>
       </c>
       <c r="C50">
-        <v>9356.352398348607</v>
+        <v>9215.609542435948</v>
       </c>
       <c r="D50">
-        <v>13889.73098151469</v>
+        <v>13852.49601275133</v>
       </c>
       <c r="E50">
-        <v>-2098.110131763257</v>
+        <v>-1994.602244613964</v>
       </c>
       <c r="F50">
-        <v>4968.378583166084</v>
+        <v>5071.886470315378</v>
       </c>
       <c r="G50">
         <v>435</v>
@@ -5375,28 +5375,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M50">
-        <v>376.6030966039892</v>
+        <v>384.4489944499057</v>
       </c>
       <c r="N50">
-        <v>492.0635700626775</v>
+        <v>484.2176722167611</v>
       </c>
       <c r="O50">
-        <v>71.84128122915091</v>
+        <v>70.69578014364711</v>
       </c>
       <c r="P50">
-        <v>420.2222888335266</v>
+        <v>413.5218920731139</v>
       </c>
       <c r="Q50">
-        <v>1163.222288833527</v>
+        <v>1156.521892073114</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.120277195703895</v>
+        <v>0.1216183088574432</v>
       </c>
       <c r="T50">
-        <v>1.72002761440866</v>
+        <v>1.75100020455989</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.30658397262224</v>
+        <v>2.259510830323827</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09374460551729605</v>
+        <v>0.09387313326856669</v>
       </c>
       <c r="C51">
-        <v>9215.609542435948</v>
+        <v>9075.065788453139</v>
       </c>
       <c r="D51">
-        <v>13852.49601275133</v>
+        <v>13815.46014591781</v>
       </c>
       <c r="E51">
-        <v>-1994.602244613964</v>
+        <v>-1891.094357464671</v>
       </c>
       <c r="F51">
-        <v>5071.886470315378</v>
+        <v>5175.394357464671</v>
       </c>
       <c r="G51">
         <v>435</v>
@@ -5457,28 +5457,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M51">
-        <v>384.4489944499057</v>
+        <v>392.2948922958221</v>
       </c>
       <c r="N51">
-        <v>484.2176722167611</v>
+        <v>476.3717743708447</v>
       </c>
       <c r="O51">
-        <v>70.69578014364711</v>
+        <v>69.55027905814332</v>
       </c>
       <c r="P51">
-        <v>413.5218920731139</v>
+        <v>406.8214953127014</v>
       </c>
       <c r="Q51">
-        <v>1156.521892073114</v>
+        <v>1149.821495312701</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1216183088574432</v>
+        <v>0.1230130665371334</v>
       </c>
       <c r="T51">
-        <v>1.75100020455989</v>
+        <v>1.783211698317168</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.259510830323827</v>
+        <v>2.214320613717351</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09387313326856669</v>
+        <v>0.09400166101983734</v>
       </c>
       <c r="C52">
-        <v>9075.065788453139</v>
+        <v>8934.719543708798</v>
       </c>
       <c r="D52">
-        <v>13815.46014591781</v>
+        <v>13778.62178832276</v>
       </c>
       <c r="E52">
-        <v>-1891.094357464671</v>
+        <v>-1787.586470315377</v>
       </c>
       <c r="F52">
-        <v>5175.394357464671</v>
+        <v>5278.902244613964</v>
       </c>
       <c r="G52">
         <v>435</v>
@@ -5539,28 +5539,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M52">
-        <v>392.2948922958221</v>
+        <v>400.1407901417385</v>
       </c>
       <c r="N52">
-        <v>476.3717743708447</v>
+        <v>468.5258765249282</v>
       </c>
       <c r="O52">
-        <v>69.55027905814332</v>
+        <v>68.40477797263951</v>
       </c>
       <c r="P52">
-        <v>406.8214953127014</v>
+        <v>400.1210985522887</v>
       </c>
       <c r="Q52">
-        <v>1149.821495312701</v>
+        <v>1143.121098552289</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1230130665371334</v>
+        <v>0.1244647531017088</v>
       </c>
       <c r="T52">
-        <v>1.783211698317168</v>
+        <v>1.816737946921683</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.214320613717351</v>
+        <v>2.170902562467991</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09400166101983734</v>
+        <v>0.09413018877110799</v>
       </c>
       <c r="C53">
-        <v>8934.719543708798</v>
+        <v>8794.569232453754</v>
       </c>
       <c r="D53">
-        <v>13778.62178832276</v>
+        <v>13741.97936421701</v>
       </c>
       <c r="E53">
-        <v>-1787.586470315377</v>
+        <v>-1684.078583166084</v>
       </c>
       <c r="F53">
-        <v>5278.902244613964</v>
+        <v>5382.410131763258</v>
       </c>
       <c r="G53">
         <v>435</v>
@@ -5621,28 +5621,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M53">
-        <v>400.1407901417385</v>
+        <v>407.9866879876549</v>
       </c>
       <c r="N53">
-        <v>468.5258765249282</v>
+        <v>460.6799786790118</v>
       </c>
       <c r="O53">
-        <v>68.40477797263951</v>
+        <v>67.25927688713573</v>
       </c>
       <c r="P53">
-        <v>400.1210985522887</v>
+        <v>393.4207017918761</v>
       </c>
       <c r="Q53">
-        <v>1143.121098552289</v>
+        <v>1136.420701791876</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1244647531017088</v>
+        <v>0.125976926606475</v>
       </c>
       <c r="T53">
-        <v>1.816737946921683</v>
+        <v>1.851661122551385</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.170902562467991</v>
+        <v>2.129154436266683</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09413018877110799</v>
+        <v>0.09425871652237863</v>
       </c>
       <c r="C54">
-        <v>8794.569232453754</v>
+        <v>8654.613295656371</v>
       </c>
       <c r="D54">
-        <v>13741.97936421701</v>
+        <v>13705.53131456892</v>
       </c>
       <c r="E54">
-        <v>-1684.078583166084</v>
+        <v>-1580.57069601679</v>
       </c>
       <c r="F54">
-        <v>5382.410131763258</v>
+        <v>5485.918018912552</v>
       </c>
       <c r="G54">
         <v>435</v>
@@ -5703,28 +5703,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M54">
-        <v>407.9866879876549</v>
+        <v>415.8325858335714</v>
       </c>
       <c r="N54">
-        <v>460.6799786790118</v>
+        <v>452.8340808330953</v>
       </c>
       <c r="O54">
-        <v>67.25927688713573</v>
+        <v>66.1137758016319</v>
       </c>
       <c r="P54">
-        <v>393.4207017918761</v>
+        <v>386.7203050314634</v>
       </c>
       <c r="Q54">
-        <v>1136.420701791876</v>
+        <v>1129.720305031463</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.125976926606475</v>
+        <v>0.1275534479199545</v>
       </c>
       <c r="T54">
-        <v>1.851661122551385</v>
+        <v>1.888070390761075</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.129154436266683</v>
+        <v>2.088981711054104</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09425871652237863</v>
+        <v>0.09438724427364928</v>
       </c>
       <c r="C55">
-        <v>8654.613295656371</v>
+        <v>8514.850190781417</v>
       </c>
       <c r="D55">
-        <v>13705.53131456892</v>
+        <v>13669.27609684326</v>
       </c>
       <c r="E55">
-        <v>-1580.57069601679</v>
+        <v>-1477.062808867497</v>
       </c>
       <c r="F55">
-        <v>5485.918018912552</v>
+        <v>5589.425906061845</v>
       </c>
       <c r="G55">
         <v>435</v>
@@ -5785,28 +5785,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M55">
-        <v>415.8325858335714</v>
+        <v>423.6784836794879</v>
       </c>
       <c r="N55">
-        <v>452.8340808330953</v>
+        <v>444.9881829871788</v>
       </c>
       <c r="O55">
-        <v>66.1137758016319</v>
+        <v>64.96827471612811</v>
       </c>
       <c r="P55">
-        <v>386.7203050314634</v>
+        <v>380.0199082710507</v>
       </c>
       <c r="Q55">
-        <v>1129.720305031463</v>
+        <v>1123.019908271051</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1275534479199545</v>
+        <v>0.129198513638368</v>
       </c>
       <c r="T55">
-        <v>1.888070390761075</v>
+        <v>1.926062670632056</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.088981711054104</v>
+        <v>2.050296864553102</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09438724427364928</v>
+        <v>0.09451577202491994</v>
       </c>
       <c r="C56">
-        <v>8514.850190781417</v>
+        <v>8375.278391572465</v>
       </c>
       <c r="D56">
-        <v>13669.27609684326</v>
+        <v>13633.2121847836</v>
       </c>
       <c r="E56">
-        <v>-1477.062808867497</v>
+        <v>-1373.554921718203</v>
       </c>
       <c r="F56">
-        <v>5589.425906061845</v>
+        <v>5692.933793211138</v>
       </c>
       <c r="G56">
         <v>435</v>
@@ -5867,28 +5867,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M56">
-        <v>423.6784836794879</v>
+        <v>431.5243815254044</v>
       </c>
       <c r="N56">
-        <v>444.9881829871788</v>
+        <v>437.1422851412624</v>
       </c>
       <c r="O56">
-        <v>64.96827471612811</v>
+        <v>63.8227736306243</v>
       </c>
       <c r="P56">
-        <v>380.0199082710507</v>
+        <v>373.3195115106381</v>
       </c>
       <c r="Q56">
-        <v>1123.019908271051</v>
+        <v>1116.319511510638</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.129198513638368</v>
+        <v>0.130916693388711</v>
       </c>
       <c r="T56">
-        <v>1.926062670632056</v>
+        <v>1.965743496275081</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.050296864553102</v>
+        <v>2.013018739743046</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09451577202491994</v>
+        <v>0.1014353077761906</v>
       </c>
       <c r="C57">
-        <v>8375.278391572465</v>
+        <v>6576.165628886919</v>
       </c>
       <c r="D57">
-        <v>13633.2121847836</v>
+        <v>11937.60730924735</v>
       </c>
       <c r="E57">
-        <v>-1373.554921718203</v>
+        <v>-1270.04703456891</v>
       </c>
       <c r="F57">
-        <v>5692.933793211138</v>
+        <v>5796.441680360432</v>
       </c>
       <c r="G57">
         <v>435</v>
@@ -5949,45 +5949,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M57">
-        <v>431.5243815254044</v>
+        <v>521.6797512324389</v>
       </c>
       <c r="N57">
-        <v>437.1422851412624</v>
+        <v>346.9869154342279</v>
       </c>
       <c r="O57">
-        <v>63.8227736306243</v>
+        <v>50.66008965339726</v>
       </c>
       <c r="P57">
-        <v>373.3195115106381</v>
+        <v>296.3268257808306</v>
       </c>
       <c r="Q57">
-        <v>1116.319511510638</v>
+        <v>1039.326825780831</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.130916693388711</v>
+        <v>0.132712972218615</v>
       </c>
       <c r="T57">
-        <v>1.965743496275081</v>
+        <v>2.00722799581097</v>
       </c>
       <c r="U57">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V57">
         <v>0.146</v>
       </c>
       <c r="W57">
-        <v>0.0647332</v>
+        <v>0.07686</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.013018739743046</v>
+        <v>1.665133953569198</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1014353077761906</v>
+        <v>0.1016851035274612</v>
       </c>
       <c r="C58">
-        <v>6576.165628886919</v>
+        <v>6419.298914465842</v>
       </c>
       <c r="D58">
-        <v>11937.60730924735</v>
+        <v>11884.24848197557</v>
       </c>
       <c r="E58">
-        <v>-1270.04703456891</v>
+        <v>-1166.539147419616</v>
       </c>
       <c r="F58">
-        <v>5796.441680360432</v>
+        <v>5899.949567509726</v>
       </c>
       <c r="G58">
         <v>435</v>
@@ -6031,28 +6031,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M58">
-        <v>521.6797512324389</v>
+        <v>530.9954610758754</v>
       </c>
       <c r="N58">
-        <v>346.9869154342279</v>
+        <v>337.6712055907914</v>
       </c>
       <c r="O58">
-        <v>50.66008965339726</v>
+        <v>49.29999601625553</v>
       </c>
       <c r="P58">
-        <v>296.3268257808306</v>
+        <v>288.3712095745358</v>
       </c>
       <c r="Q58">
-        <v>1039.326825780831</v>
+        <v>1031.371209574536</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.132712972218615</v>
+        <v>0.1345927989010726</v>
       </c>
       <c r="T58">
-        <v>2.00722799581097</v>
+        <v>2.050642006953179</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.665133953569198</v>
+        <v>1.635921077190791</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1016851035274612</v>
+        <v>0.1019348992787319</v>
       </c>
       <c r="C59">
-        <v>6419.298914465842</v>
+        <v>6262.907084956527</v>
       </c>
       <c r="D59">
-        <v>11884.24848197557</v>
+        <v>11831.36453961555</v>
       </c>
       <c r="E59">
-        <v>-1166.539147419616</v>
+        <v>-1063.031260270322</v>
       </c>
       <c r="F59">
-        <v>5899.949567509726</v>
+        <v>6003.457454659019</v>
       </c>
       <c r="G59">
         <v>435</v>
@@ -6113,28 +6113,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M59">
-        <v>530.9954610758754</v>
+        <v>540.3111709193117</v>
       </c>
       <c r="N59">
-        <v>337.6712055907914</v>
+        <v>328.355495747355</v>
       </c>
       <c r="O59">
-        <v>49.29999601625553</v>
+        <v>47.93990237911382</v>
       </c>
       <c r="P59">
-        <v>288.3712095745358</v>
+        <v>280.4155933682412</v>
       </c>
       <c r="Q59">
-        <v>1031.371209574536</v>
+        <v>1023.415593368241</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1345927989010726</v>
+        <v>0.1365621411398378</v>
       </c>
       <c r="T59">
-        <v>2.050642006953179</v>
+        <v>2.096123351959304</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.635921077190791</v>
+        <v>1.607715541377157</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1019348992787319</v>
+        <v>0.1021846950300025</v>
       </c>
       <c r="C60">
-        <v>6262.907084956526</v>
+        <v>6106.983828846603</v>
       </c>
       <c r="D60">
-        <v>11831.36453961554</v>
+        <v>11778.94917065491</v>
       </c>
       <c r="E60">
-        <v>-1063.031260270323</v>
+        <v>-959.5233731210301</v>
       </c>
       <c r="F60">
-        <v>6003.457454659018</v>
+        <v>6106.965341808312</v>
       </c>
       <c r="G60">
         <v>435</v>
@@ -6195,28 +6195,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M60">
-        <v>540.3111709193116</v>
+        <v>549.626880762748</v>
       </c>
       <c r="N60">
-        <v>328.3554957473551</v>
+        <v>319.0397859039188</v>
       </c>
       <c r="O60">
-        <v>47.93990237911385</v>
+        <v>46.57980874197214</v>
       </c>
       <c r="P60">
-        <v>280.4155933682413</v>
+        <v>272.4599771619466</v>
       </c>
       <c r="Q60">
-        <v>1023.415593368241</v>
+        <v>1015.459977161947</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1365621411398378</v>
+        <v>0.1386275488536647</v>
       </c>
       <c r="T60">
-        <v>2.096123351959303</v>
+        <v>2.143823299160848</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.607715541377157</v>
+        <v>1.580466125421612</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1021846950300025</v>
+        <v>0.1024344907812732</v>
       </c>
       <c r="C61">
-        <v>6106.983828846603</v>
+        <v>5951.522945975569</v>
       </c>
       <c r="D61">
-        <v>11778.94917065491</v>
+        <v>11726.99617493317</v>
       </c>
       <c r="E61">
-        <v>-959.5233731210301</v>
+        <v>-856.0154859717368</v>
       </c>
       <c r="F61">
-        <v>6106.965341808312</v>
+        <v>6210.473228957605</v>
       </c>
       <c r="G61">
         <v>435</v>
@@ -6277,28 +6277,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M61">
-        <v>549.626880762748</v>
+        <v>558.9425906061845</v>
       </c>
       <c r="N61">
-        <v>319.0397859039188</v>
+        <v>309.7240760604823</v>
       </c>
       <c r="O61">
-        <v>46.57980874197214</v>
+        <v>45.21971510483041</v>
       </c>
       <c r="P61">
-        <v>272.4599771619466</v>
+        <v>264.5043609556519</v>
       </c>
       <c r="Q61">
-        <v>1015.459977161947</v>
+        <v>1007.504360955652</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1386275488536647</v>
+        <v>0.1407962269531829</v>
       </c>
       <c r="T61">
-        <v>2.143823299160848</v>
+        <v>2.193908243722471</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.580466125421612</v>
+        <v>1.554125023331252</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1024344907812732</v>
+        <v>0.1026842865325438</v>
       </c>
       <c r="C62">
-        <v>5951.522945975569</v>
+        <v>5796.518345089883</v>
       </c>
       <c r="D62">
-        <v>11726.99617493317</v>
+        <v>11675.49946119678</v>
       </c>
       <c r="E62">
-        <v>-856.0154859717368</v>
+        <v>-752.5075988224435</v>
       </c>
       <c r="F62">
-        <v>6210.473228957605</v>
+        <v>6313.981116106898</v>
       </c>
       <c r="G62">
         <v>435</v>
@@ -6359,28 +6359,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M62">
-        <v>558.9425906061845</v>
+        <v>568.2583004496208</v>
       </c>
       <c r="N62">
-        <v>309.7240760604823</v>
+        <v>300.4083662170459</v>
       </c>
       <c r="O62">
-        <v>45.21971510483041</v>
+        <v>43.8596214676887</v>
       </c>
       <c r="P62">
-        <v>264.5043609556519</v>
+        <v>256.5487447493572</v>
       </c>
       <c r="Q62">
-        <v>1007.504360955652</v>
+        <v>999.5487447493572</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1407962269531829</v>
+        <v>0.143076119314215</v>
       </c>
       <c r="T62">
-        <v>2.193908243722471</v>
+        <v>2.246561646979561</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.554125023331252</v>
+        <v>1.528647563932379</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1026842865325438</v>
+        <v>0.1029340822838145</v>
       </c>
       <c r="C63">
-        <v>5796.518345089883</v>
+        <v>5641.964041462205</v>
       </c>
       <c r="D63">
-        <v>11675.49946119678</v>
+        <v>11624.4530447184</v>
       </c>
       <c r="E63">
-        <v>-752.5075988224435</v>
+        <v>-648.9997116731502</v>
       </c>
       <c r="F63">
-        <v>6313.981116106898</v>
+        <v>6417.489003256192</v>
       </c>
       <c r="G63">
         <v>435</v>
@@ -6441,28 +6441,28 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M63">
-        <v>568.2583004496208</v>
+        <v>577.5740102930572</v>
       </c>
       <c r="N63">
-        <v>300.4083662170459</v>
+        <v>291.0926563736095</v>
       </c>
       <c r="O63">
-        <v>43.8596214676887</v>
+        <v>42.49952783054699</v>
       </c>
       <c r="P63">
-        <v>256.5487447493572</v>
+        <v>248.5931285430626</v>
       </c>
       <c r="Q63">
-        <v>999.5487447493572</v>
+        <v>991.5931285430626</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.143076119314215</v>
+        <v>0.1454760060100381</v>
       </c>
       <c r="T63">
-        <v>2.246561646979561</v>
+        <v>2.301986281987024</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.528647563932379</v>
+        <v>1.503991958062502</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1029340822838145</v>
+        <v>0.1353479614586536</v>
       </c>
       <c r="C64">
-        <v>5641.964041462205</v>
+        <v>1330.726460331356</v>
       </c>
       <c r="D64">
-        <v>11624.4530447184</v>
+        <v>7416.723350736842</v>
       </c>
       <c r="E64">
-        <v>-648.9997116731502</v>
+        <v>-545.4918245238559</v>
       </c>
       <c r="F64">
-        <v>6417.489003256192</v>
+        <v>6520.996890405486</v>
       </c>
       <c r="G64">
         <v>435</v>
@@ -6523,45 +6523,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M64">
-        <v>577.5740102930572</v>
+        <v>957.2823435115254</v>
       </c>
       <c r="N64">
-        <v>291.0926563736095</v>
+        <v>-88.61567684485863</v>
       </c>
       <c r="O64">
-        <v>42.49952783054699</v>
+        <v>-12.93788881934936</v>
       </c>
       <c r="P64">
-        <v>248.5931285430626</v>
+        <v>-75.67778802550927</v>
       </c>
       <c r="Q64">
-        <v>991.5931285430626</v>
+        <v>667.3222119744908</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1454760060100381</v>
+        <v>0.1489640084935058</v>
       </c>
       <c r="T64">
-        <v>2.301986281987024</v>
+        <v>2.382540611859257</v>
       </c>
       <c r="U64">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.146</v>
+        <v>0.1324847723275765</v>
       </c>
       <c r="W64">
-        <v>0.07686</v>
+        <v>0.1273512354223118</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.503991958062502</v>
+        <v>0.9074299474491543</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1353479614586536</v>
+        <v>0.1363579614586536</v>
       </c>
       <c r="C65">
-        <v>1330.726460331356</v>
+        <v>1144.499279774996</v>
       </c>
       <c r="D65">
-        <v>7416.723350736842</v>
+        <v>7334.004057329775</v>
       </c>
       <c r="E65">
-        <v>-545.4918245238559</v>
+        <v>-441.9839373745626</v>
       </c>
       <c r="F65">
-        <v>6520.996890405486</v>
+        <v>6624.504777554779</v>
       </c>
       <c r="G65">
         <v>435</v>
@@ -6605,37 +6605,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M65">
-        <v>957.2823435115254</v>
+        <v>972.4773013450417</v>
       </c>
       <c r="N65">
-        <v>-88.61567684485863</v>
+        <v>-103.810634678375</v>
       </c>
       <c r="O65">
-        <v>-12.93788881934936</v>
+        <v>-15.15635266304275</v>
       </c>
       <c r="P65">
-        <v>-75.67778802550927</v>
+        <v>-88.65428201533223</v>
       </c>
       <c r="Q65">
-        <v>667.3222119744908</v>
+        <v>654.3457179846678</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1489640084935058</v>
+        <v>0.1518296753961032</v>
       </c>
       <c r="T65">
-        <v>2.382540611859257</v>
+        <v>2.448722295522014</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1324847723275765</v>
+        <v>0.1304146977599581</v>
       </c>
       <c r="W65">
-        <v>0.1273512354223118</v>
+        <v>0.1276551223688382</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.9074299474491543</v>
+        <v>0.8932513545202612</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1363579614586536</v>
+        <v>0.1373679614586535</v>
       </c>
       <c r="C66">
-        <v>1144.499279774996</v>
+        <v>960.0968965606398</v>
       </c>
       <c r="D66">
-        <v>7334.004057329775</v>
+        <v>7253.109561264712</v>
       </c>
       <c r="E66">
-        <v>-441.9839373745626</v>
+        <v>-338.4760502252693</v>
       </c>
       <c r="F66">
-        <v>6624.504777554779</v>
+        <v>6728.012664704072</v>
       </c>
       <c r="G66">
         <v>435</v>
@@ -6687,37 +6687,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M66">
-        <v>972.4773013450417</v>
+        <v>987.672259178558</v>
       </c>
       <c r="N66">
-        <v>-103.810634678375</v>
+        <v>-119.0055925118912</v>
       </c>
       <c r="O66">
-        <v>-15.15635266304275</v>
+        <v>-17.37481650673612</v>
       </c>
       <c r="P66">
-        <v>-88.65428201533223</v>
+        <v>-101.6307760051551</v>
       </c>
       <c r="Q66">
-        <v>654.3457179846678</v>
+        <v>641.3692239948449</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1518296753961032</v>
+        <v>0.1548590946931347</v>
       </c>
       <c r="T66">
-        <v>2.448722295522014</v>
+        <v>2.518685789679786</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1304146977599581</v>
+        <v>0.1284083177944203</v>
       </c>
       <c r="W66">
-        <v>0.1276551223688382</v>
+        <v>0.1279496589477791</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8932513545202612</v>
+        <v>0.8795090259891802</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1373679614586535</v>
+        <v>0.1383779614586536</v>
       </c>
       <c r="C67">
-        <v>960.0968965606398</v>
+        <v>777.4595865826841</v>
       </c>
       <c r="D67">
-        <v>7253.109561264712</v>
+        <v>7173.98013843605</v>
       </c>
       <c r="E67">
-        <v>-338.4760502252693</v>
+        <v>-234.968163075976</v>
       </c>
       <c r="F67">
-        <v>6728.012664704072</v>
+        <v>6831.520551853366</v>
       </c>
       <c r="G67">
         <v>435</v>
@@ -6769,37 +6769,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M67">
-        <v>987.672259178558</v>
+        <v>1002.867217012074</v>
       </c>
       <c r="N67">
-        <v>-119.0055925118912</v>
+        <v>-134.2005503454075</v>
       </c>
       <c r="O67">
-        <v>-17.37481650673612</v>
+        <v>-19.59328035042949</v>
       </c>
       <c r="P67">
-        <v>-101.6307760051551</v>
+        <v>-114.607269994978</v>
       </c>
       <c r="Q67">
-        <v>641.3692239948449</v>
+        <v>628.392730005022</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1548590946931347</v>
+        <v>0.1580667151252857</v>
       </c>
       <c r="T67">
-        <v>2.518685789679786</v>
+        <v>2.592764783493897</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1284083177944203</v>
+        <v>0.1264627372217776</v>
       </c>
       <c r="W67">
-        <v>0.1279496589477791</v>
+        <v>0.1282352701758431</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8795090259891802</v>
+        <v>0.8661831316560109</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1383779614586536</v>
+        <v>0.1393879614586536</v>
       </c>
       <c r="C68">
-        <v>777.4595865826841</v>
+        <v>596.5302039024564</v>
       </c>
       <c r="D68">
-        <v>7173.98013843605</v>
+        <v>7096.558642905115</v>
       </c>
       <c r="E68">
-        <v>-234.968163075976</v>
+        <v>-131.4602759266827</v>
       </c>
       <c r="F68">
-        <v>6831.520551853366</v>
+        <v>6935.028439002659</v>
       </c>
       <c r="G68">
         <v>435</v>
@@ -6851,37 +6851,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M68">
-        <v>1002.867217012074</v>
+        <v>1018.06217484559</v>
       </c>
       <c r="N68">
-        <v>-134.2005503454075</v>
+        <v>-149.3955081789237</v>
       </c>
       <c r="O68">
-        <v>-19.59328035042949</v>
+        <v>-21.81174419412286</v>
       </c>
       <c r="P68">
-        <v>-114.607269994978</v>
+        <v>-127.5837639848008</v>
       </c>
       <c r="Q68">
-        <v>628.392730005022</v>
+        <v>615.4162360151992</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1580667151252857</v>
+        <v>0.1614687367957489</v>
       </c>
       <c r="T68">
-        <v>2.592764783493897</v>
+        <v>2.671333413296743</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1264627372217776</v>
+        <v>0.124575233681154</v>
       </c>
       <c r="W68">
-        <v>0.1282352701758431</v>
+        <v>0.1285123556956066</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8661831316560109</v>
+        <v>0.8532550252133839</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1393879614586536</v>
+        <v>0.1403979614586536</v>
       </c>
       <c r="C69">
-        <v>596.5302039024564</v>
+        <v>417.2540431158159</v>
       </c>
       <c r="D69">
-        <v>7096.558642905115</v>
+        <v>7020.790369267769</v>
       </c>
       <c r="E69">
-        <v>-131.4602759266827</v>
+        <v>-27.95238877738848</v>
       </c>
       <c r="F69">
-        <v>6935.028439002659</v>
+        <v>7038.536326151953</v>
       </c>
       <c r="G69">
         <v>435</v>
@@ -6933,37 +6933,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M69">
-        <v>1018.06217484559</v>
+        <v>1033.257132679107</v>
       </c>
       <c r="N69">
-        <v>-149.3955081789237</v>
+        <v>-164.5904660124402</v>
       </c>
       <c r="O69">
-        <v>-21.81174419412286</v>
+        <v>-24.03020803781627</v>
       </c>
       <c r="P69">
-        <v>-127.5837639848008</v>
+        <v>-140.5602579746239</v>
       </c>
       <c r="Q69">
-        <v>615.4162360151992</v>
+        <v>602.4397420253761</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1614687367957489</v>
+        <v>0.1650833848206161</v>
       </c>
       <c r="T69">
-        <v>2.671333413296743</v>
+        <v>2.754812582462266</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.124575233681154</v>
+        <v>0.1227432449505488</v>
       </c>
       <c r="W69">
-        <v>0.1285123556956066</v>
+        <v>0.1287812916412595</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8532550252133839</v>
+        <v>0.8407071571955399</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1403979614586536</v>
+        <v>0.1414079614586536</v>
       </c>
       <c r="C70">
-        <v>417.2540431158159</v>
+        <v>239.5787104444571</v>
       </c>
       <c r="D70">
-        <v>7020.790369267769</v>
+        <v>6946.622923745704</v>
       </c>
       <c r="E70">
-        <v>-27.95238877738848</v>
+        <v>75.55549837190483</v>
       </c>
       <c r="F70">
-        <v>7038.536326151953</v>
+        <v>7142.044213301247</v>
       </c>
       <c r="G70">
         <v>435</v>
@@ -7015,37 +7015,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M70">
-        <v>1033.257132679107</v>
+        <v>1048.452090512623</v>
       </c>
       <c r="N70">
-        <v>-164.5904660124402</v>
+        <v>-179.7854238459563</v>
       </c>
       <c r="O70">
-        <v>-24.03020803781627</v>
+        <v>-26.24867188150962</v>
       </c>
       <c r="P70">
-        <v>-140.5602579746239</v>
+        <v>-153.5367519644467</v>
       </c>
       <c r="Q70">
-        <v>602.4397420253761</v>
+        <v>589.4632480355533</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1650833848206161</v>
+        <v>0.1689312359438618</v>
       </c>
       <c r="T70">
-        <v>2.754812582462266</v>
+        <v>2.843677504477178</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.1227432449505488</v>
+        <v>0.1209643573425699</v>
       </c>
       <c r="W70">
-        <v>0.1287812916412595</v>
+        <v>0.1290424323421108</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8407071571955399</v>
+        <v>0.8285229954970539</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1414079614586536</v>
+        <v>0.1424179614586536</v>
       </c>
       <c r="C71">
-        <v>239.5787104444571</v>
+        <v>63.45400291248916</v>
       </c>
       <c r="D71">
-        <v>6946.622923745704</v>
+        <v>6874.006103363029</v>
       </c>
       <c r="E71">
-        <v>75.55549837190483</v>
+        <v>179.0633855211981</v>
       </c>
       <c r="F71">
-        <v>7142.044213301247</v>
+        <v>7245.55210045054</v>
       </c>
       <c r="G71">
         <v>435</v>
@@ -7097,37 +7097,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M71">
-        <v>1048.452090512623</v>
+        <v>1063.647048346139</v>
       </c>
       <c r="N71">
-        <v>-179.7854238459563</v>
+        <v>-194.9803816794727</v>
       </c>
       <c r="O71">
-        <v>-26.24867188150962</v>
+        <v>-28.46713572520301</v>
       </c>
       <c r="P71">
-        <v>-153.5367519644467</v>
+        <v>-166.5132459542696</v>
       </c>
       <c r="Q71">
-        <v>589.4632480355533</v>
+        <v>576.4867540457303</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1689312359438618</v>
+        <v>0.1730356104753238</v>
       </c>
       <c r="T71">
-        <v>2.843677504477178</v>
+        <v>2.938466754626417</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1209643573425699</v>
+        <v>0.1192362950948189</v>
       </c>
       <c r="W71">
-        <v>0.1290424323421108</v>
+        <v>0.1292961118800806</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8285229954970539</v>
+        <v>0.8166869527042389</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1424179614586536</v>
+        <v>0.1434279614586536</v>
       </c>
       <c r="C72">
-        <v>63.45400291248916</v>
+        <v>-111.1682049771471</v>
       </c>
       <c r="D72">
-        <v>6874.006103363029</v>
+        <v>6802.891782622686</v>
       </c>
       <c r="E72">
-        <v>179.0633855211981</v>
+        <v>282.5712726704915</v>
       </c>
       <c r="F72">
-        <v>7245.55210045054</v>
+        <v>7349.059987599833</v>
       </c>
       <c r="G72">
         <v>435</v>
@@ -7179,37 +7179,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M72">
-        <v>1063.647048346139</v>
+        <v>1078.842006179656</v>
       </c>
       <c r="N72">
-        <v>-194.9803816794727</v>
+        <v>-210.1753395129888</v>
       </c>
       <c r="O72">
-        <v>-28.46713572520301</v>
+        <v>-30.68559956889636</v>
       </c>
       <c r="P72">
-        <v>-166.5132459542696</v>
+        <v>-179.4897399440924</v>
       </c>
       <c r="Q72">
-        <v>576.4867540457303</v>
+        <v>563.5102600559076</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1730356104753238</v>
+        <v>0.1774230453193005</v>
       </c>
       <c r="T72">
-        <v>2.938466754626417</v>
+        <v>3.039793194441121</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1192362950948189</v>
+        <v>0.1175569106568637</v>
       </c>
       <c r="W72">
-        <v>0.1292961118800806</v>
+        <v>0.1295426455155724</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8166869527042389</v>
+        <v>0.8051843195675594</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1434279614586536</v>
+        <v>0.1842527591597073</v>
       </c>
       <c r="C73">
-        <v>-111.1682049771462</v>
+        <v>-2220.607086158636</v>
       </c>
       <c r="D73">
-        <v>6802.891782622686</v>
+        <v>4796.96078859049</v>
       </c>
       <c r="E73">
-        <v>282.5712726704905</v>
+        <v>386.0791598197839</v>
       </c>
       <c r="F73">
-        <v>7349.059987599832</v>
+        <v>7452.567874749126</v>
       </c>
       <c r="G73">
         <v>435</v>
@@ -7261,45 +7261,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M73">
-        <v>1078.842006179656</v>
+        <v>1496.475629249624</v>
       </c>
       <c r="N73">
-        <v>-210.1753395129888</v>
+        <v>-627.8089625829577</v>
       </c>
       <c r="O73">
-        <v>-30.68559956889636</v>
+        <v>-91.66010853711182</v>
       </c>
       <c r="P73">
-        <v>-179.4897399440924</v>
+        <v>-536.148854045846</v>
       </c>
       <c r="Q73">
-        <v>563.5102600559076</v>
+        <v>206.851145954154</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1774230453193005</v>
+        <v>0.1854624315844676</v>
       </c>
       <c r="T73">
-        <v>3.039793194441121</v>
+        <v>3.225460313729044</v>
       </c>
       <c r="U73">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1175569106568637</v>
+        <v>0.08474934763683868</v>
       </c>
       <c r="W73">
-        <v>0.1295426455155724</v>
+        <v>0.1837823309945228</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.8051843195675594</v>
+        <v>0.5804749838139636</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1842527591597073</v>
+        <v>0.1858027591597073</v>
       </c>
       <c r="C74">
-        <v>-2220.607086158636</v>
+        <v>-2377.223135368034</v>
       </c>
       <c r="D74">
-        <v>4796.96078859049</v>
+        <v>4743.852626530385</v>
       </c>
       <c r="E74">
-        <v>386.0791598197839</v>
+        <v>489.5870469690781</v>
       </c>
       <c r="F74">
-        <v>7452.567874749126</v>
+        <v>7556.07576189842</v>
       </c>
       <c r="G74">
         <v>435</v>
@@ -7343,37 +7343,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M74">
-        <v>1496.475629249624</v>
+        <v>1517.260012989203</v>
       </c>
       <c r="N74">
-        <v>-627.8089625829577</v>
+        <v>-648.593346322536</v>
       </c>
       <c r="O74">
-        <v>-91.66010853711182</v>
+        <v>-94.69462856309026</v>
       </c>
       <c r="P74">
-        <v>-536.148854045846</v>
+        <v>-553.8987177594457</v>
       </c>
       <c r="Q74">
-        <v>206.851145954154</v>
+        <v>189.1012822405543</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1854624315844676</v>
+        <v>0.1906351142357442</v>
       </c>
       <c r="T74">
-        <v>3.225460313729044</v>
+        <v>3.34492180683012</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.08474934763683868</v>
+        <v>0.08358839766921075</v>
       </c>
       <c r="W74">
-        <v>0.1837823309945228</v>
+        <v>0.1840154497480225</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5804749838139636</v>
+        <v>0.5725232717069229</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1858027591597073</v>
+        <v>0.1873527591597073</v>
       </c>
       <c r="C75">
-        <v>-2377.223135368034</v>
+        <v>-2532.676117863905</v>
       </c>
       <c r="D75">
-        <v>4743.852626530385</v>
+        <v>4691.907531183808</v>
       </c>
       <c r="E75">
-        <v>489.5870469690781</v>
+        <v>593.0949341183714</v>
       </c>
       <c r="F75">
-        <v>7556.07576189842</v>
+        <v>7659.583649047713</v>
       </c>
       <c r="G75">
         <v>435</v>
@@ -7425,37 +7425,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M75">
-        <v>1517.260012989203</v>
+        <v>1538.044396728781</v>
       </c>
       <c r="N75">
-        <v>-648.593346322536</v>
+        <v>-669.3777300621141</v>
       </c>
       <c r="O75">
-        <v>-94.69462856309026</v>
+        <v>-97.72914858906866</v>
       </c>
       <c r="P75">
-        <v>-553.8987177594457</v>
+        <v>-571.6485814730454</v>
       </c>
       <c r="Q75">
-        <v>189.1012822405543</v>
+        <v>171.3514185269546</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1906351142357442</v>
+        <v>0.1962056955525036</v>
       </c>
       <c r="T75">
-        <v>3.34492180683012</v>
+        <v>3.473572645554356</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.08358839766921075</v>
+        <v>0.08245882472773491</v>
       </c>
       <c r="W75">
-        <v>0.1840154497480225</v>
+        <v>0.1842422679946708</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5725232717069229</v>
+        <v>0.5647864707379104</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1873527591597073</v>
+        <v>0.1889027591597073</v>
       </c>
       <c r="C76">
-        <v>-2532.676117863905</v>
+        <v>-2687.003826490005</v>
       </c>
       <c r="D76">
-        <v>4691.907531183808</v>
+        <v>4641.087709707002</v>
       </c>
       <c r="E76">
-        <v>593.0949341183714</v>
+        <v>696.6028212676647</v>
       </c>
       <c r="F76">
-        <v>7659.583649047713</v>
+        <v>7763.091536197006</v>
       </c>
       <c r="G76">
         <v>435</v>
@@ -7507,37 +7507,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M76">
-        <v>1538.044396728781</v>
+        <v>1558.828780468359</v>
       </c>
       <c r="N76">
-        <v>-669.3777300621141</v>
+        <v>-690.1621138016922</v>
       </c>
       <c r="O76">
-        <v>-97.72914858906866</v>
+        <v>-100.7636686150471</v>
       </c>
       <c r="P76">
-        <v>-571.6485814730454</v>
+        <v>-589.3984451866451</v>
       </c>
       <c r="Q76">
-        <v>171.3514185269546</v>
+        <v>153.6015548133549</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1962056955525036</v>
+        <v>0.2022219233746037</v>
       </c>
       <c r="T76">
-        <v>3.473572645554356</v>
+        <v>3.612515551376529</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.08245882472773491</v>
+        <v>0.08135937373136512</v>
       </c>
       <c r="W76">
-        <v>0.1842422679946708</v>
+        <v>0.1844630377547419</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5647864707379104</v>
+        <v>0.557255984461405</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1889027591597073</v>
+        <v>0.1904527591597074</v>
       </c>
       <c r="C77">
-        <v>-2687.003826490005</v>
+        <v>-2840.242434241064</v>
       </c>
       <c r="D77">
-        <v>4641.087709707002</v>
+        <v>4591.356989105236</v>
       </c>
       <c r="E77">
-        <v>696.6028212676647</v>
+        <v>800.110708416958</v>
       </c>
       <c r="F77">
-        <v>7763.091536197006</v>
+        <v>7866.5994233463</v>
       </c>
       <c r="G77">
         <v>435</v>
@@ -7589,37 +7589,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M77">
-        <v>1558.828780468359</v>
+        <v>1579.613164207937</v>
       </c>
       <c r="N77">
-        <v>-690.1621138016922</v>
+        <v>-710.9464975412702</v>
       </c>
       <c r="O77">
-        <v>-100.7636686150471</v>
+        <v>-103.7981886410254</v>
       </c>
       <c r="P77">
-        <v>-589.3984451866451</v>
+        <v>-607.1483089002447</v>
       </c>
       <c r="Q77">
-        <v>153.6015548133549</v>
+        <v>135.8516910997553</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2022219233746037</v>
+        <v>0.2087395035152122</v>
       </c>
       <c r="T77">
-        <v>3.612515551376529</v>
+        <v>3.763037032683886</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.08135937373136512</v>
+        <v>0.08028885565595244</v>
       </c>
       <c r="W77">
-        <v>0.1844630377547419</v>
+        <v>0.1846779977842848</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.557255984461405</v>
+        <v>0.5499236688763866</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1904527591597074</v>
+        <v>0.1920027591597073</v>
       </c>
       <c r="C78">
-        <v>-2840.242434241064</v>
+        <v>-2992.42658012867</v>
       </c>
       <c r="D78">
-        <v>4591.356989105236</v>
+        <v>4542.680730366923</v>
       </c>
       <c r="E78">
-        <v>800.110708416958</v>
+        <v>903.6185955662513</v>
       </c>
       <c r="F78">
-        <v>7866.5994233463</v>
+        <v>7970.107310495593</v>
       </c>
       <c r="G78">
         <v>435</v>
@@ -7671,37 +7671,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M78">
-        <v>1579.613164207937</v>
+        <v>1600.397547947515</v>
       </c>
       <c r="N78">
-        <v>-710.9464975412702</v>
+        <v>-731.7308812808485</v>
       </c>
       <c r="O78">
-        <v>-103.7981886410254</v>
+        <v>-106.8327086670039</v>
       </c>
       <c r="P78">
-        <v>-607.1483089002447</v>
+        <v>-624.8981726138446</v>
       </c>
       <c r="Q78">
-        <v>135.8516910997553</v>
+        <v>118.1018273861554</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2087395035152122</v>
+        <v>0.215823829755004</v>
       </c>
       <c r="T78">
-        <v>3.763037032683886</v>
+        <v>3.926647338452749</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.08028885565595244</v>
+        <v>0.07924614324483616</v>
       </c>
       <c r="W78">
-        <v>0.1846779977842848</v>
+        <v>0.1848873744364369</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5499236688763866</v>
+        <v>0.542781803046823</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1920027591597073</v>
+        <v>0.1935527591597073</v>
       </c>
       <c r="C79">
-        <v>-2992.42658012867</v>
+        <v>-3143.589449642509</v>
       </c>
       <c r="D79">
-        <v>4542.680730366923</v>
+        <v>4495.025748002378</v>
       </c>
       <c r="E79">
-        <v>903.6185955662513</v>
+        <v>1007.126482715546</v>
       </c>
       <c r="F79">
-        <v>7970.107310495593</v>
+        <v>8073.615197644887</v>
       </c>
       <c r="G79">
         <v>435</v>
@@ -7753,37 +7753,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M79">
-        <v>1600.397547947515</v>
+        <v>1621.181931687093</v>
       </c>
       <c r="N79">
-        <v>-731.7308812808485</v>
+        <v>-752.5152650204266</v>
       </c>
       <c r="O79">
-        <v>-106.8327086670039</v>
+        <v>-109.8672286929823</v>
       </c>
       <c r="P79">
-        <v>-624.8981726138446</v>
+        <v>-642.6480363274443</v>
       </c>
       <c r="Q79">
-        <v>118.1018273861554</v>
+        <v>100.3519636725557</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.215823829755004</v>
+        <v>0.2235521856529588</v>
       </c>
       <c r="T79">
-        <v>3.926647338452749</v>
+        <v>4.105131308382421</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.07924614324483616</v>
+        <v>0.07823016704938954</v>
       </c>
       <c r="W79">
-        <v>0.1848873744364369</v>
+        <v>0.1850913824564826</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.542781803046823</v>
+        <v>0.5358230619821203</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1935527591597073</v>
+        <v>0.1951027591597074</v>
       </c>
       <c r="C80">
-        <v>-3143.589449642509</v>
+        <v>-3293.762850199702</v>
       </c>
       <c r="D80">
-        <v>4495.025748002378</v>
+        <v>4448.360234594478</v>
       </c>
       <c r="E80">
-        <v>1007.126482715546</v>
+        <v>1110.634369864839</v>
       </c>
       <c r="F80">
-        <v>8073.615197644887</v>
+        <v>8177.123084794181</v>
       </c>
       <c r="G80">
         <v>435</v>
@@ -7835,37 +7835,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M80">
-        <v>1621.181931687093</v>
+        <v>1641.966315426672</v>
       </c>
       <c r="N80">
-        <v>-752.5152650204266</v>
+        <v>-773.2996487600049</v>
       </c>
       <c r="O80">
-        <v>-109.8672286929823</v>
+        <v>-112.9017487189607</v>
       </c>
       <c r="P80">
-        <v>-642.6480363274443</v>
+        <v>-660.3979000410442</v>
       </c>
       <c r="Q80">
-        <v>100.3519636725557</v>
+        <v>82.60209995895582</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2235521856529588</v>
+        <v>0.2320165754459568</v>
       </c>
       <c r="T80">
-        <v>4.105131308382421</v>
+        <v>4.300613751638727</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.07823016704938954</v>
+        <v>0.07723991177028333</v>
       </c>
       <c r="W80">
-        <v>0.1850913824564826</v>
+        <v>0.1852902257165271</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5358230619821203</v>
+        <v>0.5290404915772832</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1951027591597074</v>
+        <v>0.1966527591597073</v>
       </c>
       <c r="C81">
-        <v>-3293.762850199702</v>
+        <v>-3442.977281942733</v>
       </c>
       <c r="D81">
-        <v>4448.360234594478</v>
+        <v>4402.653690000741</v>
       </c>
       <c r="E81">
-        <v>1110.634369864839</v>
+        <v>1214.142257014132</v>
       </c>
       <c r="F81">
-        <v>8177.123084794181</v>
+        <v>8280.630971943474</v>
       </c>
       <c r="G81">
         <v>435</v>
@@ -7917,37 +7917,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M81">
-        <v>1641.966315426672</v>
+        <v>1662.75069916625</v>
       </c>
       <c r="N81">
-        <v>-773.2996487600049</v>
+        <v>-794.0840324995829</v>
       </c>
       <c r="O81">
-        <v>-112.9017487189607</v>
+        <v>-115.9362687449391</v>
       </c>
       <c r="P81">
-        <v>-660.3979000410442</v>
+        <v>-678.1477637546438</v>
       </c>
       <c r="Q81">
-        <v>82.60209995895582</v>
+        <v>64.85223624535615</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2320165754459568</v>
+        <v>0.2413274042182547</v>
       </c>
       <c r="T81">
-        <v>4.300613751638727</v>
+        <v>4.515644439220663</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.07723991177028333</v>
+        <v>0.0762744128731548</v>
       </c>
       <c r="W81">
-        <v>0.1852902257165271</v>
+        <v>0.1854840978950705</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5290404915772832</v>
+        <v>0.5224274854325672</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1966527591597073</v>
+        <v>0.1982027591597074</v>
       </c>
       <c r="C82">
-        <v>-3442.977281942733</v>
+        <v>-3591.262004217104</v>
       </c>
       <c r="D82">
-        <v>4402.653690000741</v>
+        <v>4357.876854875663</v>
       </c>
       <c r="E82">
-        <v>1214.142257014132</v>
+        <v>1317.650144163425</v>
       </c>
       <c r="F82">
-        <v>8280.630971943474</v>
+        <v>8384.138859092767</v>
       </c>
       <c r="G82">
         <v>435</v>
@@ -7999,37 +7999,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M82">
-        <v>1662.75069916625</v>
+        <v>1683.535082905828</v>
       </c>
       <c r="N82">
-        <v>-794.0840324995829</v>
+        <v>-814.868416239161</v>
       </c>
       <c r="O82">
-        <v>-115.9362687449391</v>
+        <v>-118.9707887709175</v>
       </c>
       <c r="P82">
-        <v>-678.1477637546438</v>
+        <v>-695.8976274682435</v>
       </c>
       <c r="Q82">
-        <v>64.85223624535615</v>
+        <v>47.10237253175649</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2413274042182547</v>
+        <v>0.2516183202297418</v>
       </c>
       <c r="T82">
-        <v>4.515644439220663</v>
+        <v>4.753309936021751</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.0762744128731548</v>
+        <v>0.0753327534549677</v>
       </c>
       <c r="W82">
-        <v>0.1854840978950705</v>
+        <v>0.1856731831062425</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5224274854325672</v>
+        <v>0.5159777633901899</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1982027591597074</v>
+        <v>0.1997527591597074</v>
       </c>
       <c r="C83">
-        <v>-3591.262004217104</v>
+        <v>-3738.645098033204</v>
       </c>
       <c r="D83">
-        <v>4357.876854875663</v>
+        <v>4314.001648208857</v>
       </c>
       <c r="E83">
-        <v>1317.650144163425</v>
+        <v>1421.158031312719</v>
       </c>
       <c r="F83">
-        <v>8384.138859092767</v>
+        <v>8487.646746242061</v>
       </c>
       <c r="G83">
         <v>435</v>
@@ -8081,37 +8081,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M83">
-        <v>1683.535082905828</v>
+        <v>1704.319466645406</v>
       </c>
       <c r="N83">
-        <v>-814.868416239161</v>
+        <v>-835.652799978739</v>
       </c>
       <c r="O83">
-        <v>-118.9707887709175</v>
+        <v>-122.0053087968959</v>
       </c>
       <c r="P83">
-        <v>-695.8976274682435</v>
+        <v>-713.6474911818432</v>
       </c>
       <c r="Q83">
-        <v>47.10237253175649</v>
+        <v>29.35250881815682</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2516183202297418</v>
+        <v>0.2630526713536163</v>
       </c>
       <c r="T83">
-        <v>4.753309936021751</v>
+        <v>5.017382710245182</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.0753327534549677</v>
+        <v>0.07441406133966322</v>
       </c>
       <c r="W83">
-        <v>0.1856731831062425</v>
+        <v>0.1858576564829956</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5159777633901899</v>
+        <v>0.5096853516415289</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1997527591597074</v>
+        <v>0.2013027591597074</v>
       </c>
       <c r="C84">
-        <v>-3738.645098033204</v>
+        <v>-3885.153524792578</v>
       </c>
       <c r="D84">
-        <v>4314.001648208857</v>
+        <v>4271.001108598776</v>
       </c>
       <c r="E84">
-        <v>1421.158031312719</v>
+        <v>1524.665918462012</v>
       </c>
       <c r="F84">
-        <v>8487.646746242061</v>
+        <v>8591.154633391354</v>
       </c>
       <c r="G84">
         <v>435</v>
@@ -8163,37 +8163,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M84">
-        <v>1704.319466645406</v>
+        <v>1725.103850384984</v>
       </c>
       <c r="N84">
-        <v>-835.652799978739</v>
+        <v>-856.4371837183171</v>
       </c>
       <c r="O84">
-        <v>-122.0053087968959</v>
+        <v>-125.0398288228743</v>
       </c>
       <c r="P84">
-        <v>-713.6474911818432</v>
+        <v>-731.3973548954428</v>
       </c>
       <c r="Q84">
-        <v>29.35250881815682</v>
+        <v>11.60264510455715</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2630526713536163</v>
+        <v>0.2758322402567702</v>
       </c>
       <c r="T84">
-        <v>5.017382710245182</v>
+        <v>5.312522869671369</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.07441406133966322</v>
+        <v>0.07351750638376367</v>
       </c>
       <c r="W84">
-        <v>0.1858576564829956</v>
+        <v>0.1860376847181403</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5096853516415289</v>
+        <v>0.5035445642723539</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2013027591597074</v>
+        <v>0.2326299613231866</v>
       </c>
       <c r="C85">
-        <v>-3885.153524792578</v>
+        <v>-4704.81268779675</v>
       </c>
       <c r="D85">
-        <v>4271.001108598776</v>
+        <v>3554.849832743897</v>
       </c>
       <c r="E85">
-        <v>1524.665918462012</v>
+        <v>1628.173805611305</v>
       </c>
       <c r="F85">
-        <v>8591.154633391354</v>
+        <v>8694.662520540647</v>
       </c>
       <c r="G85">
         <v>435</v>
@@ -8245,45 +8245,45 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M85">
-        <v>1725.103850384984</v>
+        <v>2050.201422343485</v>
       </c>
       <c r="N85">
-        <v>-856.4371837183171</v>
+        <v>-1181.534755676818</v>
       </c>
       <c r="O85">
-        <v>-125.0398288228743</v>
+        <v>-172.5040743288154</v>
       </c>
       <c r="P85">
-        <v>-731.3973548954428</v>
+        <v>-1009.030681348003</v>
       </c>
       <c r="Q85">
-        <v>11.60264510455715</v>
+        <v>-266.0306813480026</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2758322402567702</v>
+        <v>0.2925667687945639</v>
       </c>
       <c r="T85">
-        <v>5.312522869671369</v>
+        <v>5.699001588789007</v>
       </c>
       <c r="U85">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07351750638376367</v>
+        <v>0.06185993822419921</v>
       </c>
       <c r="W85">
-        <v>0.1860376847181403</v>
+        <v>0.2212134265667338</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.5035445642723539</v>
+        <v>0.4236982070150631</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2326299613231866</v>
+        <v>0.2345299613231866</v>
       </c>
       <c r="C86">
-        <v>-4704.81268779675</v>
+        <v>-4844.108293201584</v>
       </c>
       <c r="D86">
-        <v>3554.849832743897</v>
+        <v>3519.062114488356</v>
       </c>
       <c r="E86">
-        <v>1628.173805611305</v>
+        <v>1731.681692760599</v>
       </c>
       <c r="F86">
-        <v>8694.662520540647</v>
+        <v>8798.17040768994</v>
       </c>
       <c r="G86">
         <v>435</v>
@@ -8327,37 +8327,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M86">
-        <v>2050.201422343485</v>
+        <v>2074.608582133288</v>
       </c>
       <c r="N86">
-        <v>-1181.534755676818</v>
+        <v>-1205.941915466621</v>
       </c>
       <c r="O86">
-        <v>-172.5040743288154</v>
+        <v>-176.0675196581267</v>
       </c>
       <c r="P86">
-        <v>-1009.030681348003</v>
+        <v>-1029.874395808495</v>
       </c>
       <c r="Q86">
-        <v>-266.0306813480026</v>
+        <v>-286.8743958084947</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2925667687945637</v>
+        <v>0.3090178867142013</v>
       </c>
       <c r="T86">
-        <v>5.699001588789002</v>
+        <v>6.078935028041602</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06185993822419921</v>
+        <v>0.06113217424509099</v>
       </c>
       <c r="W86">
-        <v>0.2212134265667338</v>
+        <v>0.2213850333130075</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4236982070150631</v>
+        <v>0.4187135222266507</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2345299613231866</v>
+        <v>0.2364299613231866</v>
       </c>
       <c r="C87">
-        <v>-4844.108293201584</v>
+        <v>-4982.690509544032</v>
       </c>
       <c r="D87">
-        <v>3519.062114488356</v>
+        <v>3483.987785295201</v>
       </c>
       <c r="E87">
-        <v>1731.681692760599</v>
+        <v>1835.189579909892</v>
       </c>
       <c r="F87">
-        <v>8798.17040768994</v>
+        <v>8901.678294839234</v>
       </c>
       <c r="G87">
         <v>435</v>
@@ -8409,37 +8409,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M87">
-        <v>2074.608582133288</v>
+        <v>2099.015741923091</v>
       </c>
       <c r="N87">
-        <v>-1205.941915466621</v>
+        <v>-1230.349075256425</v>
       </c>
       <c r="O87">
-        <v>-176.0675196581267</v>
+        <v>-179.630964987438</v>
       </c>
       <c r="P87">
-        <v>-1029.874395808495</v>
+        <v>-1050.718110268987</v>
       </c>
       <c r="Q87">
-        <v>-286.8743958084947</v>
+        <v>-307.7181102689867</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3090178867142013</v>
+        <v>0.3278191643366443</v>
       </c>
       <c r="T87">
-        <v>6.078935028041602</v>
+        <v>6.513144672901718</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06113217424509099</v>
+        <v>0.06042133500968296</v>
       </c>
       <c r="W87">
-        <v>0.2213850333130075</v>
+        <v>0.2215526492047168</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4187135222266507</v>
+        <v>0.4138447603402943</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2364299613231866</v>
+        <v>0.2383299613231866</v>
       </c>
       <c r="C88">
-        <v>-4982.690509544032</v>
+        <v>-5120.580457264923</v>
       </c>
       <c r="D88">
-        <v>3483.987785295201</v>
+        <v>3449.605724723604</v>
       </c>
       <c r="E88">
-        <v>1835.189579909892</v>
+        <v>1938.697467059185</v>
       </c>
       <c r="F88">
-        <v>8901.678294839234</v>
+        <v>9005.186181988527</v>
       </c>
       <c r="G88">
         <v>435</v>
@@ -8491,37 +8491,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M88">
-        <v>2099.015741923091</v>
+        <v>2123.422901712895</v>
       </c>
       <c r="N88">
-        <v>-1230.349075256425</v>
+        <v>-1254.756235046228</v>
       </c>
       <c r="O88">
-        <v>-179.630964987438</v>
+        <v>-183.1944103167493</v>
       </c>
       <c r="P88">
-        <v>-1050.718110268987</v>
+        <v>-1071.561824729479</v>
       </c>
       <c r="Q88">
-        <v>-307.7181102689867</v>
+        <v>-328.5618247294785</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3278191643366443</v>
+        <v>0.3495129462086938</v>
       </c>
       <c r="T88">
-        <v>6.513144672901718</v>
+        <v>7.014155801586464</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06042133500968296</v>
+        <v>0.05972683690612339</v>
       </c>
       <c r="W88">
-        <v>0.2215526492047168</v>
+        <v>0.2217164118575361</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4138447603402943</v>
+        <v>0.4090879240145439</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2383299613231866</v>
+        <v>0.2402299613231866</v>
       </c>
       <c r="C89">
-        <v>-5120.580457264923</v>
+        <v>-5257.798431236073</v>
       </c>
       <c r="D89">
-        <v>3449.605724723604</v>
+        <v>3415.895637901747</v>
       </c>
       <c r="E89">
-        <v>1938.697467059185</v>
+        <v>2042.205354208479</v>
       </c>
       <c r="F89">
-        <v>9005.186181988527</v>
+        <v>9108.69406913782</v>
       </c>
       <c r="G89">
         <v>435</v>
@@ -8573,37 +8573,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M89">
-        <v>2123.422901712895</v>
+        <v>2147.830061502698</v>
       </c>
       <c r="N89">
-        <v>-1254.756235046228</v>
+        <v>-1279.163394836032</v>
       </c>
       <c r="O89">
-        <v>-183.1944103167493</v>
+        <v>-186.7578556460606</v>
       </c>
       <c r="P89">
-        <v>-1071.561824729479</v>
+        <v>-1092.405539189971</v>
       </c>
       <c r="Q89">
-        <v>-328.5618247294785</v>
+        <v>-349.405539189971</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3495129462086938</v>
+        <v>0.3748223583927517</v>
       </c>
       <c r="T89">
-        <v>7.014155801586464</v>
+        <v>7.598668785052005</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05972683690612339</v>
+        <v>0.05904812285037198</v>
       </c>
       <c r="W89">
-        <v>0.2217164118575361</v>
+        <v>0.2218764526318823</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4090879240145439</v>
+        <v>0.4044391976052876</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2402299613231866</v>
+        <v>0.2421299613231866</v>
       </c>
       <c r="C90">
-        <v>-5257.798431236073</v>
+        <v>-5394.363940707868</v>
       </c>
       <c r="D90">
-        <v>3415.895637901747</v>
+        <v>3382.838015579246</v>
       </c>
       <c r="E90">
-        <v>2042.205354208479</v>
+        <v>2145.713241357772</v>
       </c>
       <c r="F90">
-        <v>9108.69406913782</v>
+        <v>9212.201956287114</v>
       </c>
       <c r="G90">
         <v>435</v>
@@ -8655,37 +8655,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M90">
-        <v>2147.830061502698</v>
+        <v>2172.237221292502</v>
       </c>
       <c r="N90">
-        <v>-1279.163394836032</v>
+        <v>-1303.570554625835</v>
       </c>
       <c r="O90">
-        <v>-186.7578556460606</v>
+        <v>-190.3213009753719</v>
       </c>
       <c r="P90">
-        <v>-1092.405539189971</v>
+        <v>-1113.249253650463</v>
       </c>
       <c r="Q90">
-        <v>-349.405539189971</v>
+        <v>-370.2492536504628</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3748223583927517</v>
+        <v>0.4047334818830019</v>
       </c>
       <c r="T90">
-        <v>7.598668785052005</v>
+        <v>8.289456856420369</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05904812285037198</v>
+        <v>0.05838466079587343</v>
       </c>
       <c r="W90">
-        <v>0.2218764526318823</v>
+        <v>0.222032896984333</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4044391976052876</v>
+        <v>0.3998949369580371</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2421299613231866</v>
+        <v>0.2440299613231866</v>
       </c>
       <c r="C91">
-        <v>-5394.363940707868</v>
+        <v>-5530.295746959491</v>
       </c>
       <c r="D91">
-        <v>3382.838015579246</v>
+        <v>3350.414096476918</v>
       </c>
       <c r="E91">
-        <v>2145.713241357772</v>
+        <v>2249.221128507067</v>
       </c>
       <c r="F91">
-        <v>9212.201956287114</v>
+        <v>9315.709843436409</v>
       </c>
       <c r="G91">
         <v>435</v>
@@ -8737,37 +8737,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M91">
-        <v>2172.237221292502</v>
+        <v>2196.644381082305</v>
       </c>
       <c r="N91">
-        <v>-1303.570554625835</v>
+        <v>-1327.977714415639</v>
       </c>
       <c r="O91">
-        <v>-190.3213009753719</v>
+        <v>-193.8847463046832</v>
       </c>
       <c r="P91">
-        <v>-1113.249253650463</v>
+        <v>-1134.092968110955</v>
       </c>
       <c r="Q91">
-        <v>-370.2492536504628</v>
+        <v>-391.0929681109553</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4047334818830019</v>
+        <v>0.4406268300713022</v>
       </c>
       <c r="T91">
-        <v>8.289456856420369</v>
+        <v>9.118402542062407</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05838466079587343</v>
+        <v>0.05773594234258594</v>
       </c>
       <c r="W91">
-        <v>0.222032896984333</v>
+        <v>0.2221858647956182</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3998949369580371</v>
+        <v>0.3954516598807256</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2440299613231866</v>
+        <v>0.2459299613231866</v>
       </c>
       <c r="C92">
-        <v>-5530.295746959491</v>
+        <v>-5665.611898804475</v>
       </c>
       <c r="D92">
-        <v>3350.414096476918</v>
+        <v>3318.605831781228</v>
       </c>
       <c r="E92">
-        <v>2249.221128507067</v>
+        <v>2352.72901565636</v>
       </c>
       <c r="F92">
-        <v>9315.709843436409</v>
+        <v>9419.217730585702</v>
       </c>
       <c r="G92">
         <v>435</v>
@@ -8819,37 +8819,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M92">
-        <v>2196.644381082305</v>
+        <v>2221.051540872108</v>
       </c>
       <c r="N92">
-        <v>-1327.977714415639</v>
+        <v>-1352.384874205442</v>
       </c>
       <c r="O92">
-        <v>-193.8847463046832</v>
+        <v>-197.4481916339945</v>
       </c>
       <c r="P92">
-        <v>-1134.092968110955</v>
+        <v>-1154.936682571447</v>
       </c>
       <c r="Q92">
-        <v>-391.0929681109553</v>
+        <v>-411.9366825714474</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4406268300713022</v>
+        <v>0.4844964778570025</v>
       </c>
       <c r="T92">
-        <v>9.118402542062407</v>
+        <v>10.13155838006934</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05773594234258594</v>
+        <v>0.05710148143772235</v>
       </c>
       <c r="W92">
-        <v>0.2221858647956182</v>
+        <v>0.2223354706769851</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3954516598807256</v>
+        <v>0.3911060372446736</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2459299613231866</v>
+        <v>0.2478299613231867</v>
       </c>
       <c r="C93">
-        <v>-5665.611898804475</v>
+        <v>-5800.329766092791</v>
       </c>
       <c r="D93">
-        <v>3318.605831781228</v>
+        <v>3287.395851642204</v>
       </c>
       <c r="E93">
-        <v>2352.72901565636</v>
+        <v>2456.236902805654</v>
       </c>
       <c r="F93">
-        <v>9419.217730585702</v>
+        <v>9522.725617734995</v>
       </c>
       <c r="G93">
         <v>435</v>
@@ -8901,37 +8901,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M93">
-        <v>2221.051540872108</v>
+        <v>2245.458700661912</v>
       </c>
       <c r="N93">
-        <v>-1352.384874205442</v>
+        <v>-1376.792033995245</v>
       </c>
       <c r="O93">
-        <v>-197.4481916339945</v>
+        <v>-201.0116369633058</v>
       </c>
       <c r="P93">
-        <v>-1154.936682571447</v>
+        <v>-1175.78039703194</v>
       </c>
       <c r="Q93">
-        <v>-411.9366825714474</v>
+        <v>-432.7803970319396</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4844964778570025</v>
+        <v>0.5393335375891278</v>
       </c>
       <c r="T93">
-        <v>10.13155838006934</v>
+        <v>11.39800317757801</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05710148143772235</v>
+        <v>0.05648081316122536</v>
       </c>
       <c r="W93">
-        <v>0.2223354706769851</v>
+        <v>0.2224818242565831</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3911060372446736</v>
+        <v>0.3868548846659272</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2478299613231867</v>
+        <v>0.2497299613231866</v>
       </c>
       <c r="C94">
-        <v>-5800.329766092791</v>
+        <v>-5934.466071340108</v>
       </c>
       <c r="D94">
-        <v>3287.395851642204</v>
+        <v>3256.767433544181</v>
       </c>
       <c r="E94">
-        <v>2456.236902805654</v>
+        <v>2559.744789954947</v>
       </c>
       <c r="F94">
-        <v>9522.725617734995</v>
+        <v>9626.233504884289</v>
       </c>
       <c r="G94">
         <v>435</v>
@@ -8983,37 +8983,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M94">
-        <v>2245.458700661912</v>
+        <v>2269.865860451715</v>
       </c>
       <c r="N94">
-        <v>-1376.792033995245</v>
+        <v>-1401.199193785049</v>
       </c>
       <c r="O94">
-        <v>-201.0116369633058</v>
+        <v>-204.5750822926171</v>
       </c>
       <c r="P94">
-        <v>-1175.78039703194</v>
+        <v>-1196.624111492432</v>
       </c>
       <c r="Q94">
-        <v>-432.7803970319396</v>
+        <v>-453.6241114924317</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5393335375891278</v>
+        <v>0.609838328673289</v>
       </c>
       <c r="T94">
-        <v>11.39800317757801</v>
+        <v>13.02628934580345</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05648081316122536</v>
+        <v>0.05587349258959928</v>
       </c>
       <c r="W94">
-        <v>0.2224818242565831</v>
+        <v>0.2226250304473725</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3868548846659272</v>
+        <v>0.3826951547232829</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2497299613231866</v>
+        <v>0.2516299613231866</v>
       </c>
       <c r="C95">
-        <v>-5934.466071340108</v>
+        <v>-6068.036919605242</v>
       </c>
       <c r="D95">
-        <v>3256.767433544181</v>
+        <v>3226.704472428341</v>
       </c>
       <c r="E95">
-        <v>2559.744789954947</v>
+        <v>2663.25267710424</v>
       </c>
       <c r="F95">
-        <v>9626.233504884289</v>
+        <v>9729.741392033582</v>
       </c>
       <c r="G95">
         <v>435</v>
@@ -9065,37 +9065,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M95">
-        <v>2269.865860451715</v>
+        <v>2294.273020241519</v>
       </c>
       <c r="N95">
-        <v>-1401.199193785049</v>
+        <v>-1425.606353574852</v>
       </c>
       <c r="O95">
-        <v>-204.5750822926171</v>
+        <v>-208.1385276219284</v>
       </c>
       <c r="P95">
-        <v>-1196.624111492432</v>
+        <v>-1217.467825952923</v>
       </c>
       <c r="Q95">
-        <v>-453.6241114924317</v>
+        <v>-474.4678259529235</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.609838328673289</v>
+        <v>0.7038447167855041</v>
       </c>
       <c r="T95">
-        <v>13.02628934580345</v>
+        <v>15.19733757010402</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05587349258959928</v>
+        <v>0.05527909373226313</v>
       </c>
       <c r="W95">
-        <v>0.2226250304473725</v>
+        <v>0.2227651896979324</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3826951547232829</v>
+        <v>0.3786239296730352</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2516299613231866</v>
+        <v>0.2535299613231866</v>
       </c>
       <c r="C96">
-        <v>-6068.036919605242</v>
+        <v>-6201.057826727978</v>
       </c>
       <c r="D96">
-        <v>3226.704472428341</v>
+        <v>3197.191452454897</v>
       </c>
       <c r="E96">
-        <v>2663.25267710424</v>
+        <v>2766.760564253534</v>
       </c>
       <c r="F96">
-        <v>9729.741392033582</v>
+        <v>9833.249279182875</v>
       </c>
       <c r="G96">
         <v>435</v>
@@ -9147,37 +9147,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M96">
-        <v>2294.273020241519</v>
+        <v>2318.680180031322</v>
       </c>
       <c r="N96">
-        <v>-1425.606353574852</v>
+        <v>-1450.013513364655</v>
       </c>
       <c r="O96">
-        <v>-208.1385276219284</v>
+        <v>-211.7019729512396</v>
       </c>
       <c r="P96">
-        <v>-1217.467825952923</v>
+        <v>-1238.311540413416</v>
       </c>
       <c r="Q96">
-        <v>-474.4678259529235</v>
+        <v>-495.3115404134155</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7038447167855041</v>
+        <v>0.8354536601426051</v>
       </c>
       <c r="T96">
-        <v>15.19733757010402</v>
+        <v>18.23680508412484</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05527909373226313</v>
+        <v>0.05469720853508141</v>
       </c>
       <c r="W96">
-        <v>0.2227651896979324</v>
+        <v>0.2229023982274278</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3786239296730352</v>
+        <v>0.3746384146238454</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2535299613231866</v>
+        <v>0.2554299613231866</v>
       </c>
       <c r="C97">
-        <v>-6201.057826727978</v>
+        <v>-6333.543746031268</v>
       </c>
       <c r="D97">
-        <v>3197.191452454897</v>
+        <v>3168.213420300901</v>
       </c>
       <c r="E97">
-        <v>2766.760564253534</v>
+        <v>2870.268451402827</v>
       </c>
       <c r="F97">
-        <v>9833.249279182875</v>
+        <v>9936.757166332169</v>
       </c>
       <c r="G97">
         <v>435</v>
@@ -9229,37 +9229,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M97">
-        <v>2318.680180031322</v>
+        <v>2343.087339821126</v>
       </c>
       <c r="N97">
-        <v>-1450.013513364655</v>
+        <v>-1474.420673154459</v>
       </c>
       <c r="O97">
-        <v>-211.7019729512396</v>
+        <v>-215.265418280551</v>
       </c>
       <c r="P97">
-        <v>-1238.311540413416</v>
+        <v>-1259.155254873908</v>
       </c>
       <c r="Q97">
-        <v>-495.3115404134155</v>
+        <v>-516.1552548739078</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8354536601426051</v>
+        <v>1.032867075178257</v>
       </c>
       <c r="T97">
-        <v>18.23680508412484</v>
+        <v>22.79600635515605</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05469720853508141</v>
+        <v>0.05412744594617431</v>
       </c>
       <c r="W97">
-        <v>0.2229023982274278</v>
+        <v>0.2230367482458921</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3746384146238454</v>
+        <v>0.3707359311381803</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2554299613231866</v>
+        <v>0.2573299613231866</v>
       </c>
       <c r="C98">
-        <v>-6333.543746031268</v>
+        <v>-6465.50909358436</v>
       </c>
       <c r="D98">
-        <v>3168.213420300901</v>
+        <v>3139.755959897102</v>
       </c>
       <c r="E98">
-        <v>2870.268451402827</v>
+        <v>2973.77633855212</v>
       </c>
       <c r="F98">
-        <v>9936.757166332169</v>
+        <v>10040.26505348146</v>
       </c>
       <c r="G98">
         <v>435</v>
@@ -9311,37 +9311,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M98">
-        <v>2343.087339821126</v>
+        <v>2367.494499610929</v>
       </c>
       <c r="N98">
-        <v>-1474.420673154459</v>
+        <v>-1498.827832944262</v>
       </c>
       <c r="O98">
-        <v>-215.265418280551</v>
+        <v>-218.8288636098623</v>
       </c>
       <c r="P98">
-        <v>-1259.155254873908</v>
+        <v>-1279.9989693344</v>
       </c>
       <c r="Q98">
-        <v>-516.1552548739078</v>
+        <v>-536.9989693343998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.032867075178254</v>
+        <v>1.361889433571006</v>
       </c>
       <c r="T98">
-        <v>22.79600635515599</v>
+        <v>30.39467514020799</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05412744594617431</v>
+        <v>0.05356943103951272</v>
       </c>
       <c r="W98">
-        <v>0.2230367482458921</v>
+        <v>0.2231683281608829</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3707359311381803</v>
+        <v>0.3669139112295392</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2573299613231866</v>
+        <v>0.2592299613231867</v>
       </c>
       <c r="C99">
-        <v>-6465.50909358436</v>
+        <v>-6596.967772116553</v>
       </c>
       <c r="D99">
-        <v>3139.755959897102</v>
+        <v>3111.805168514203</v>
       </c>
       <c r="E99">
-        <v>2973.77633855212</v>
+        <v>3077.284225701414</v>
       </c>
       <c r="F99">
-        <v>10040.26505348146</v>
+        <v>10143.77294063076</v>
       </c>
       <c r="G99">
         <v>435</v>
@@ -9393,37 +9393,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M99">
-        <v>2367.494499610929</v>
+        <v>2391.901659400732</v>
       </c>
       <c r="N99">
-        <v>-1498.827832944262</v>
+        <v>-1523.234992734065</v>
       </c>
       <c r="O99">
-        <v>-218.8288636098623</v>
+        <v>-222.3923089391735</v>
       </c>
       <c r="P99">
-        <v>-1279.9989693344</v>
+        <v>-1300.842683794892</v>
       </c>
       <c r="Q99">
-        <v>-536.9989693343998</v>
+        <v>-557.8426837948919</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.361889433571006</v>
+        <v>2.019934150356508</v>
       </c>
       <c r="T99">
-        <v>30.39467514020799</v>
+        <v>45.59201271031198</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05356943103951272</v>
+        <v>0.05302280419217076</v>
       </c>
       <c r="W99">
-        <v>0.2231683281608829</v>
+        <v>0.2232972227714861</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3669139112295392</v>
+        <v>0.363169891727197</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2592299613231867</v>
+        <v>0.2611299613231866</v>
       </c>
       <c r="C100">
-        <v>-6596.967772116553</v>
+        <v>-6727.933193664892</v>
       </c>
       <c r="D100">
-        <v>3111.805168514203</v>
+        <v>3084.347634115156</v>
       </c>
       <c r="E100">
-        <v>3077.284225701414</v>
+        <v>3180.792112850707</v>
       </c>
       <c r="F100">
-        <v>10143.77294063076</v>
+        <v>10247.28082778005</v>
       </c>
       <c r="G100">
         <v>435</v>
@@ -9475,37 +9475,37 @@
         <v>868.6666666666667</v>
       </c>
       <c r="M100">
-        <v>2391.901659400732</v>
+        <v>2416.308819190535</v>
       </c>
       <c r="N100">
-        <v>-1523.234992734065</v>
+        <v>-1547.642152523869</v>
       </c>
       <c r="O100">
-        <v>-222.3923089391735</v>
+        <v>-225.9557542684848</v>
       </c>
       <c r="P100">
-        <v>-1300.842683794892</v>
+        <v>-1321.686398255384</v>
       </c>
       <c r="Q100">
-        <v>-557.8426837948919</v>
+        <v>-578.6863982553839</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.019934150356508</v>
+        <v>3.994068300713018</v>
       </c>
       <c r="T100">
-        <v>45.59201271031198</v>
+        <v>91.18402542062398</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05302280419217076</v>
+        <v>0.05248722031144176</v>
       </c>
       <c r="W100">
-        <v>0.2232972227714861</v>
+        <v>0.2234235134505621</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.363169891727197</v>
+        <v>0.3595015089824779</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2611299613231866</v>
-      </c>
-      <c r="C101">
-        <v>-6727.933193664892</v>
-      </c>
-      <c r="D101">
-        <v>3084.347634115156</v>
-      </c>
-      <c r="E101">
-        <v>3180.792112850707</v>
-      </c>
-      <c r="F101">
-        <v>10247.28082778005</v>
-      </c>
-      <c r="G101">
-        <v>435</v>
-      </c>
-      <c r="H101">
-        <v>3284.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1611.666666666667</v>
-      </c>
-      <c r="K101">
-        <v>743</v>
-      </c>
-      <c r="L101">
-        <v>868.6666666666667</v>
-      </c>
-      <c r="M101">
-        <v>2416.308819190535</v>
-      </c>
-      <c r="N101">
-        <v>-1547.642152523869</v>
-      </c>
-      <c r="O101">
-        <v>-225.9557542684848</v>
-      </c>
-      <c r="P101">
-        <v>-1321.686398255384</v>
-      </c>
-      <c r="Q101">
-        <v>-578.6863982553839</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.994068300713018</v>
-      </c>
-      <c r="T101">
-        <v>91.18402542062398</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05248722031144176</v>
-      </c>
-      <c r="W101">
-        <v>0.2234235134505621</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3595015089824779</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
